--- a/社区代码仓列表.xlsx
+++ b/社区代码仓列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27516" windowHeight="14220"/>
+    <workbookView windowWidth="21240" windowHeight="14220"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -839,14 +839,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1319,133 +1312,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1465,10 +1458,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2247,7 +2240,7 @@
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:6">
       <c r="A33" s="1" t="s">
         <v>87</v>
       </c>
@@ -2261,7 +2254,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:6">
       <c r="A34" s="1"/>
       <c r="B34" s="4" t="s">
         <v>90</v>
@@ -2273,7 +2266,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:6">
       <c r="A35" s="1"/>
       <c r="B35" s="4" t="s">
         <v>92</v>
@@ -2285,7 +2278,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:6">
       <c r="A36" s="1"/>
       <c r="B36" s="4" t="s">
         <v>94</v>
@@ -2297,7 +2290,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:6">
       <c r="A37" s="1"/>
       <c r="B37" s="4"/>
       <c r="C37" s="3" t="s">
@@ -2307,7 +2300,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:6">
       <c r="A38" s="1"/>
       <c r="B38" s="4"/>
       <c r="C38" s="3" t="s">
@@ -2317,7 +2310,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:6">
       <c r="A39" s="1"/>
       <c r="B39" s="4"/>
       <c r="C39" s="3" t="s">
@@ -2327,7 +2320,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:6">
       <c r="A40" s="1"/>
       <c r="B40" s="4" t="s">
         <v>103</v>
@@ -2339,7 +2332,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:6">
       <c r="A41" s="1"/>
       <c r="B41" s="4"/>
       <c r="C41" s="3" t="s">
@@ -2349,7 +2342,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:6">
       <c r="A42" s="1"/>
       <c r="B42" s="4"/>
       <c r="C42" s="3" t="s">
@@ -2359,7 +2352,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:6">
       <c r="A43" s="1"/>
       <c r="B43" s="4"/>
       <c r="C43" s="3" t="s">
@@ -2369,7 +2362,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:6">
       <c r="A44" s="1"/>
       <c r="B44" s="4"/>
       <c r="C44" s="3" t="s">
@@ -2379,7 +2372,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:6">
       <c r="A45" s="1"/>
       <c r="B45" s="4" t="s">
         <v>114</v>
@@ -2390,8 +2383,11 @@
       <c r="D45" s="3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="46" spans="1:4">
+      <c r="F45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46" s="1"/>
       <c r="B46" s="4"/>
       <c r="C46" s="3" t="s">
@@ -2400,8 +2396,11 @@
       <c r="D46" s="3" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="47" spans="1:4">
+      <c r="F46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47" s="1"/>
       <c r="B47" s="4"/>
       <c r="C47" s="3" t="s">
@@ -2410,8 +2409,11 @@
       <c r="D47" s="3" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="48" spans="1:4">
+      <c r="F47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48" s="1"/>
       <c r="B48" s="4"/>
       <c r="C48" s="3" t="s">
@@ -2420,8 +2422,11 @@
       <c r="D48" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="49" spans="1:4">
+      <c r="F48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49" s="1"/>
       <c r="B49" s="4"/>
       <c r="C49" s="3" t="s">
@@ -2430,8 +2435,11 @@
       <c r="D49" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="50" spans="1:4">
+      <c r="F49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50" s="1"/>
       <c r="B50" s="4"/>
       <c r="C50" s="3" t="s">
@@ -2440,8 +2448,11 @@
       <c r="D50" s="3" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="51" spans="1:4">
+      <c r="F50">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51" s="1"/>
       <c r="B51" s="4"/>
       <c r="C51" s="3" t="s">
@@ -2450,8 +2461,11 @@
       <c r="D51" s="3" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="52" spans="1:4">
+      <c r="F51">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52" s="1"/>
       <c r="B52" s="4"/>
       <c r="C52" s="3" t="s">
@@ -2460,8 +2474,11 @@
       <c r="D52" s="3" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="53" spans="1:4">
+      <c r="F52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
       <c r="A53" s="1"/>
       <c r="B53" s="4" t="s">
         <v>131</v>
@@ -2473,7 +2490,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:6">
       <c r="A54" s="1"/>
       <c r="B54" s="4"/>
       <c r="C54" s="3" t="s">
@@ -2483,7 +2500,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:6">
       <c r="A55" s="1"/>
       <c r="B55" s="4"/>
       <c r="C55" s="3" t="s">
@@ -2493,7 +2510,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:6">
       <c r="A56" s="1"/>
       <c r="B56" s="4"/>
       <c r="C56" s="3" t="s">
@@ -2503,7 +2520,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:6">
       <c r="A57" s="1"/>
       <c r="B57" s="4"/>
       <c r="C57" s="3" t="s">
@@ -2513,7 +2530,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:6">
       <c r="A58" s="1"/>
       <c r="B58" s="4"/>
       <c r="C58" s="3" t="s">
@@ -2523,7 +2540,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:6">
       <c r="A59" s="1"/>
       <c r="B59" s="4"/>
       <c r="C59" s="3" t="s">
@@ -2533,7 +2550,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:6">
       <c r="A60" s="1"/>
       <c r="B60" s="4"/>
       <c r="C60" s="3" t="s">
@@ -2543,7 +2560,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:6">
       <c r="A61" s="1"/>
       <c r="B61" s="4"/>
       <c r="C61" s="3" t="s">
@@ -2553,7 +2570,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:6">
       <c r="A62" s="1"/>
       <c r="B62" s="4"/>
       <c r="C62" s="3" t="s">
@@ -2563,7 +2580,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:6">
       <c r="A63" s="1"/>
       <c r="B63" s="4"/>
       <c r="C63" s="3" t="s">
@@ -2573,7 +2590,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:6">
       <c r="A64" s="1"/>
       <c r="B64" s="4"/>
       <c r="C64" s="3" t="s">

--- a/社区代码仓列表.xlsx
+++ b/社区代码仓列表.xlsx
@@ -1442,7 +1442,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1457,6 +1457,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1773,12 +1776,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G132"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="15.2222222222222" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="26.5555555555556" customWidth="1"/>
+    <col min="3" max="3" width="37.5555555555556" customWidth="1"/>
     <col min="4" max="4" width="57.4444444444444" customWidth="1"/>
     <col min="5" max="5" width="12.5555555555556" customWidth="1"/>
     <col min="6" max="6" width="12.4444444444444" customWidth="1"/>
@@ -2331,6 +2334,9 @@
       <c r="D40" s="3" t="s">
         <v>105</v>
       </c>
+      <c r="F40">
+        <v>11</v>
+      </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="1"/>
@@ -2341,6 +2347,9 @@
       <c r="D41" s="3" t="s">
         <v>107</v>
       </c>
+      <c r="F41">
+        <v>25</v>
+      </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="1"/>
@@ -2351,6 +2360,9 @@
       <c r="D42" s="3" t="s">
         <v>109</v>
       </c>
+      <c r="F42">
+        <v>22</v>
+      </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="1"/>
@@ -2361,6 +2373,9 @@
       <c r="D43" s="3" t="s">
         <v>111</v>
       </c>
+      <c r="F43">
+        <v>6</v>
+      </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="1"/>
@@ -2371,6 +2386,9 @@
       <c r="D44" s="3" t="s">
         <v>113</v>
       </c>
+      <c r="F44">
+        <v>4</v>
+      </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="1"/>
@@ -2458,7 +2476,7 @@
       <c r="C51" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D51" t="s">
         <v>128</v>
       </c>
       <c r="F51">
@@ -2471,7 +2489,7 @@
       <c r="C52" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D52" t="s">
         <v>130</v>
       </c>
       <c r="F52">
@@ -2486,7 +2504,7 @@
       <c r="C53" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="D53" t="s">
         <v>133</v>
       </c>
     </row>
@@ -2496,7 +2514,7 @@
       <c r="C54" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="D54" t="s">
         <v>135</v>
       </c>
     </row>
@@ -2506,231 +2524,267 @@
       <c r="C55" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="D55" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="1"/>
       <c r="B56" s="4"/>
-      <c r="C56" s="3" t="s">
+      <c r="C56" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="D56" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="1"/>
       <c r="B57" s="4"/>
-      <c r="C57" s="3" t="s">
+      <c r="C57" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="D57" t="s">
         <v>141</v>
+      </c>
+      <c r="F57">
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="1"/>
       <c r="B58" s="4"/>
-      <c r="C58" s="3" t="s">
+      <c r="C58" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="D58" t="s">
         <v>143</v>
+      </c>
+      <c r="F58">
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="1"/>
       <c r="B59" s="4"/>
-      <c r="C59" s="3" t="s">
+      <c r="C59" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="D59" t="s">
         <v>145</v>
+      </c>
+      <c r="F59">
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="1"/>
       <c r="B60" s="4"/>
-      <c r="C60" s="3" t="s">
+      <c r="C60" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="D60" s="3" t="s">
+      <c r="D60" t="s">
         <v>147</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="1"/>
       <c r="B61" s="4"/>
-      <c r="C61" s="3" t="s">
+      <c r="C61" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="D61" t="s">
         <v>149</v>
+      </c>
+      <c r="F61">
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="1"/>
       <c r="B62" s="4"/>
-      <c r="C62" s="3" t="s">
+      <c r="C62" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="D62" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="1"/>
       <c r="B63" s="4"/>
-      <c r="C63" s="3" t="s">
+      <c r="C63" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="D63" t="s">
         <v>153</v>
+      </c>
+      <c r="F63">
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="1"/>
       <c r="B64" s="4"/>
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="D64" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
+    <row r="65" spans="1:6">
       <c r="A65" s="1"/>
       <c r="B65" s="4"/>
-      <c r="C65" s="3" t="s">
+      <c r="C65" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="D65" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="66" spans="1:4">
+      <c r="F65">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
       <c r="A66" s="1"/>
       <c r="B66" s="4"/>
-      <c r="C66" s="3" t="s">
+      <c r="C66" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="D66" s="3" t="s">
+      <c r="D66" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
+    <row r="67" spans="1:6">
       <c r="A67" s="1"/>
       <c r="B67" s="4"/>
-      <c r="C67" s="3" t="s">
+      <c r="C67" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="D67" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
+    <row r="68" spans="1:6">
       <c r="A68" s="1"/>
       <c r="B68" s="4"/>
-      <c r="C68" s="3" t="s">
+      <c r="C68" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="D68" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="69" spans="1:4">
+      <c r="F68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
       <c r="A69" s="1"/>
       <c r="B69" s="4"/>
-      <c r="C69" s="3" t="s">
+      <c r="C69" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="D69" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="70" spans="1:4">
+      <c r="F69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
       <c r="A70" s="1"/>
       <c r="B70" s="4"/>
-      <c r="C70" s="3" t="s">
+      <c r="C70" s="5" t="s">
         <v>166</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="71" spans="1:4">
+      <c r="F70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
       <c r="A71" s="1"/>
       <c r="B71" s="4"/>
-      <c r="C71" s="3" t="s">
+      <c r="C71" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="72" spans="1:4">
+      <c r="F71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
       <c r="A72" s="1"/>
       <c r="B72" s="4"/>
-      <c r="C72" s="3" t="s">
+      <c r="C72" s="5" t="s">
         <v>170</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="73" spans="1:4">
+      <c r="F72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
       <c r="A73" s="1"/>
       <c r="B73" s="4"/>
-      <c r="C73" s="3" t="s">
+      <c r="C73" s="5" t="s">
         <v>172</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
+    <row r="74" spans="1:6">
       <c r="A74" s="1"/>
       <c r="B74" s="4"/>
-      <c r="C74" s="3" t="s">
+      <c r="C74" s="5" t="s">
         <v>174</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
+    <row r="75" spans="1:6">
       <c r="A75" s="1"/>
       <c r="B75" s="4"/>
-      <c r="C75" s="3" t="s">
+      <c r="C75" s="5" t="s">
         <v>176</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
+    <row r="76" spans="1:6">
       <c r="A76" s="1"/>
       <c r="B76" s="4"/>
-      <c r="C76" s="3" t="s">
+      <c r="C76" s="5" t="s">
         <v>178</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="77" spans="1:4">
+    <row r="77" spans="1:6">
       <c r="A77" s="1"/>
       <c r="B77" s="4"/>
-      <c r="C77" s="3" t="s">
+      <c r="C77" s="5" t="s">
         <v>180</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="78" spans="1:4">
+    <row r="78" spans="1:6">
       <c r="A78" s="1"/>
       <c r="B78" s="4" t="s">
         <v>182</v>
@@ -2742,7 +2796,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
+    <row r="79" spans="1:6">
       <c r="A79" s="1"/>
       <c r="B79" s="4"/>
       <c r="C79" s="3" t="s">
@@ -2752,7 +2806,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="80" spans="1:4">
+    <row r="80" spans="1:6">
       <c r="A80" s="1"/>
       <c r="B80" s="4"/>
       <c r="C80" s="3" t="s">
@@ -2762,7 +2816,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:5">
       <c r="A81" s="1"/>
       <c r="B81" s="4"/>
       <c r="C81" s="3" t="s">
@@ -2772,7 +2826,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:5">
       <c r="A82" s="1"/>
       <c r="B82" s="4"/>
       <c r="C82" s="3" t="s">
@@ -2782,7 +2836,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:5">
       <c r="A83" s="1"/>
       <c r="B83" s="4"/>
       <c r="C83" s="3" t="s">
@@ -2792,346 +2846,346 @@
         <v>193</v>
       </c>
     </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="1"/>
+      <c r="B86" s="6"/>
+      <c r="C86" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="1"/>
+      <c r="B87" s="6"/>
+      <c r="C87" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="1"/>
+      <c r="B88" s="6"/>
+      <c r="C88" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="1"/>
+      <c r="B89" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="1"/>
+      <c r="B90" s="6"/>
+      <c r="C90" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="E90" s="7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="1"/>
+      <c r="B91" s="6"/>
+      <c r="C91" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="1"/>
+      <c r="B92" s="6"/>
+      <c r="C92" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="1"/>
+      <c r="B93" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="1"/>
+      <c r="B94" s="6"/>
+      <c r="C94" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="1"/>
+      <c r="B95" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="1"/>
+      <c r="B96" s="6"/>
+      <c r="C96" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="1"/>
+      <c r="B97" s="6"/>
+      <c r="C97" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" s="1"/>
+      <c r="B98" s="6"/>
+      <c r="C98" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="1"/>
+      <c r="B99" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="1"/>
+      <c r="B100" s="6"/>
+      <c r="C100" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" s="1"/>
+      <c r="B101" s="6"/>
+      <c r="C101" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" s="1"/>
+      <c r="B102" s="6"/>
+      <c r="C102" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="E102" s="7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" s="1"/>
+      <c r="B103" s="6"/>
+      <c r="C103" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="E103" s="7" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" s="1"/>
+      <c r="B104" s="6"/>
+      <c r="C104" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="E104" s="7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" s="1"/>
+      <c r="B105" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="E105" s="7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" s="1"/>
+      <c r="B106" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="E106" s="7" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" s="1"/>
+      <c r="B107" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="E107" s="7" t="s">
+        <v>260</v>
+      </c>
+    </row>
     <row r="108" spans="1:5">
-      <c r="A108" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="B108" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="D108" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="E108" s="6" t="s">
+      <c r="A108" s="1"/>
+      <c r="B108" s="6"/>
+      <c r="C108" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="E108" s="7" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="1"/>
-      <c r="B109" s="5"/>
-      <c r="C109" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="D109" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="E109" s="6" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
-      <c r="A110" s="1"/>
-      <c r="B110" s="5"/>
-      <c r="C110" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D110" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="E110" s="6" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
-      <c r="A111" s="1"/>
-      <c r="B111" s="5"/>
-      <c r="C111" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="D111" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="E111" s="6" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5">
-      <c r="A112" s="1"/>
-      <c r="B112" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="C112" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="D112" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="E112" s="6" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5">
-      <c r="A113" s="1"/>
-      <c r="B113" s="5"/>
-      <c r="C113" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="D113" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="E113" s="6" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5">
-      <c r="A114" s="1"/>
-      <c r="B114" s="5"/>
-      <c r="C114" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="D114" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="E114" s="6" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5">
-      <c r="A115" s="1"/>
-      <c r="B115" s="5"/>
-      <c r="C115" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="D115" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="E115" s="6" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5">
-      <c r="A116" s="1"/>
-      <c r="B116" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="C116" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="D116" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="E116" s="6" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5">
-      <c r="A117" s="1"/>
-      <c r="B117" s="5"/>
-      <c r="C117" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="D117" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="E117" s="6" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5">
-      <c r="A118" s="1"/>
-      <c r="B118" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="C118" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="D118" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="E118" s="6" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5">
-      <c r="A119" s="1"/>
-      <c r="B119" s="5"/>
-      <c r="C119" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="D119" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="E119" s="6" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5">
-      <c r="A120" s="1"/>
-      <c r="B120" s="5"/>
-      <c r="C120" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="D120" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="E120" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5">
-      <c r="A121" s="1"/>
-      <c r="B121" s="5"/>
-      <c r="C121" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="D121" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="E121" s="6" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5">
-      <c r="A122" s="1"/>
-      <c r="B122" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="C122" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="D122" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="E122" s="6" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5">
-      <c r="A123" s="1"/>
-      <c r="B123" s="5"/>
-      <c r="C123" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="D123" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="E123" s="6" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5">
-      <c r="A124" s="1"/>
-      <c r="B124" s="5"/>
-      <c r="C124" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="D124" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="E124" s="6" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5">
-      <c r="A125" s="1"/>
-      <c r="B125" s="5"/>
-      <c r="C125" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="D125" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="E125" s="6" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5">
-      <c r="A126" s="1"/>
-      <c r="B126" s="5"/>
-      <c r="C126" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D126" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="E126" s="6" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5">
-      <c r="A127" s="1"/>
-      <c r="B127" s="5"/>
-      <c r="C127" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="D127" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="E127" s="6" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5">
-      <c r="A128" s="1"/>
-      <c r="B128" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="C128" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="D128" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="E128" s="6" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5">
-      <c r="A129" s="1"/>
-      <c r="B129" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="C129" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="D129" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="E129" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5">
-      <c r="A130" s="1"/>
-      <c r="B130" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="C130" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="D130" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="E130" s="6" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5">
-      <c r="A131" s="1"/>
-      <c r="B131" s="5"/>
-      <c r="C131" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="D131" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="E131" s="6" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5">
-      <c r="A132" s="1"/>
-      <c r="B132" s="5"/>
-      <c r="C132" s="6" t="s">
+      <c r="B109" s="6"/>
+      <c r="C109" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="D132" s="6" t="s">
+      <c r="D109" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="E132" s="6" t="s">
+      <c r="E109" s="7" t="s">
         <v>265</v>
       </c>
     </row>
@@ -3139,7 +3193,7 @@
   <mergeCells count="22">
     <mergeCell ref="A2:A31"/>
     <mergeCell ref="A33:A83"/>
-    <mergeCell ref="A108:A132"/>
+    <mergeCell ref="A85:A109"/>
     <mergeCell ref="B2:B6"/>
     <mergeCell ref="B7:B12"/>
     <mergeCell ref="B13:B15"/>
@@ -3153,37 +3207,21 @@
     <mergeCell ref="B45:B52"/>
     <mergeCell ref="B53:B77"/>
     <mergeCell ref="B78:B83"/>
-    <mergeCell ref="B108:B111"/>
-    <mergeCell ref="B112:B115"/>
-    <mergeCell ref="B116:B117"/>
-    <mergeCell ref="B118:B121"/>
-    <mergeCell ref="B122:B127"/>
-    <mergeCell ref="B130:B132"/>
+    <mergeCell ref="B85:B88"/>
+    <mergeCell ref="B89:B92"/>
+    <mergeCell ref="B93:B94"/>
+    <mergeCell ref="B95:B98"/>
+    <mergeCell ref="B99:B104"/>
+    <mergeCell ref="B107:B109"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D15" r:id="rId1" display="https://gitcode.com/boostkit/hadoop/tree/hdfs-ec-24.0.0/"/>
-    <hyperlink ref="C56" r:id="rId2" display="MindStudio-Debugger" tooltip="https://gitcode.com/Ascend/msdebug"/>
-    <hyperlink ref="C57" r:id="rId3" display="MindStudio-Monitor" tooltip="https://gitcode.com/Ascend/msmonitor"/>
-    <hyperlink ref="C58" r:id="rId4" display="MindStudio-Probe" tooltip="https://gitcode.com/Ascend/msprobe"/>
-    <hyperlink ref="C59" r:id="rId5" display="MindStudio-Insight" tooltip="https://gitcode.com/Ascend/msinsight"/>
-    <hyperlink ref="C60" r:id="rId6" display="MindStudio-Profiler" tooltip="https://gitcode.com/Ascend/msprof"/>
-    <hyperlink ref="C61" r:id="rId7" display="MindStudio-Service-Profiler" tooltip="https://gitcode.com/Ascend/msserviceprofiler"/>
-    <hyperlink ref="C62" r:id="rId8" display="MindStudio-ModelSlim" tooltip="https://gitcode.com/Ascend/msmodelslim"/>
-    <hyperlink ref="C63" r:id="rId9" display="MindStudio-Modeling" tooltip="https://gitcode.com/Ascend/msmodeling"/>
-    <hyperlink ref="C64" r:id="rId10" display="MindStudio-Sanitizer" tooltip="https://gitcode.com/Ascend/mssanitizer"/>
-    <hyperlink ref="C65" r:id="rId11" display="MindStudio-Ops-Common" tooltip="https://gitcode.com/Ascend/msopcom"/>
-    <hyperlink ref="C66" r:id="rId12" display="MindStudio-Profiler-Tools-Interface" tooltip="https://gitcode.com/Ascend/mspti"/>
-    <hyperlink ref="C67" r:id="rId13" display="MindStudio-Agent" tooltip="https://gitcode.com/Ascend/msagent"/>
-    <hyperlink ref="C68" r:id="rId14" display="MindStudio-Ops-Profiler" tooltip="https://gitcode.com/Ascend/msopprof"/>
-    <hyperlink ref="C69" r:id="rId15" display="MindStudio-MemScope" tooltip="https://gitcode.com/Ascend/msmemscope"/>
-    <hyperlink ref="C70" r:id="rId16" display="MindStudio-Profiler-Analyze" tooltip="https://gitcode.com/Ascend/msprof-analyze"/>
-    <hyperlink ref="C71" r:id="rId17" display="MindStudio-Tools-Extension-Library" tooltip="https://gitcode.com/Ascend/mstx"/>
-    <hyperlink ref="C72" r:id="rId18" display="MindStudio-CommReport" tooltip="https://gitcode.com/Ascend/mscommreport"/>
-    <hyperlink ref="C73" r:id="rId19" display="MindStudio-Kernel-Launcher" tooltip="https://gitcode.com/Ascend/mskl"/>
-    <hyperlink ref="C74" r:id="rId20" display="MindStudio-Ops-Tuner" tooltip="https://gitcode.com/Ascend/msoptuner"/>
-    <hyperlink ref="C75" r:id="rId21" display="MindStudio-Ops-Generator" tooltip="https://gitcode.com/Ascend/msopgen"/>
-    <hyperlink ref="C76" r:id="rId22" display="MindStudio-Kernel-Performance-Prediction" tooltip="https://gitcode.com/Ascend/mskpp"/>
-    <hyperlink ref="C77" r:id="rId23" display="mockcpp" tooltip="https://gitcode.com/Ascend/mockcpp"/>
+    <hyperlink ref="D63" r:id="rId1" display="https://gitcode.com/Ascend/msmodeling"/>
+    <hyperlink ref="D62" r:id="rId2" display="https://gitcode.com/Ascend/msmodelslim"/>
+    <hyperlink ref="D64" r:id="rId3" display="https://gitcode.com/Ascend/mssanitizer"/>
+    <hyperlink ref="D66" r:id="rId4" display="https://gitcode.com/Ascend/mspti"/>
+    <hyperlink ref="D53" r:id="rId5" display="https://gitcode.com/Ascend/mstt"/>
+    <hyperlink ref="D54" r:id="rId6" display="https://gitcode.com/Ascend/msit"/>
+    <hyperlink ref="D55" r:id="rId7" display="https://gitcode.com/Ascend/msot"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/社区代码仓列表.xlsx
+++ b/社区代码仓列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21240" windowHeight="14220"/>
+    <workbookView windowWidth="23388" windowHeight="14220"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="821">
   <si>
     <t>社区名</t>
   </si>
@@ -49,6 +49,9 @@
     <t>报告数量1</t>
   </si>
   <si>
+    <t>筛选</t>
+  </si>
+  <si>
     <t>报告数量2</t>
   </si>
   <si>
@@ -827,6 +830,1668 @@
   </si>
   <si>
     <t>Python (95.19%)</t>
+  </si>
+  <si>
+    <t>openubmc社区</t>
+  </si>
+  <si>
+    <t>component_drivers</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/component_drivers</t>
+  </si>
+  <si>
+    <t>C++ 94.6%; Meson 2.97%; Shell 1.2%; C 0.97%; Lua 0.15%</t>
+  </si>
+  <si>
+    <t>general_hardware</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/general_hardware</t>
+  </si>
+  <si>
+    <t>Lua 99.91%; Python 0.04%; CMake 0.03%; Makefile 0.02%</t>
+  </si>
+  <si>
+    <t>profile_schema</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/profile_schema</t>
+  </si>
+  <si>
+    <t>Lua 48.15%; Python 41.59%; CMake 10.26%</t>
+  </si>
+  <si>
+    <t>libroute_mapper</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/libroute_mapper</t>
+  </si>
+  <si>
+    <t>Lua 2.29%; CMake 0.4%; Python 0.21%; C 0.06%</t>
+  </si>
+  <si>
+    <t>docs</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/docs</t>
+  </si>
+  <si>
+    <t>Vue 47.99%; TypeScript 20.61%; CSS 15.87%; SCSS 8.07%; JavaScript 4.4%</t>
+  </si>
+  <si>
+    <t>vpd</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/vpd</t>
+  </si>
+  <si>
+    <t>manifest</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/manifest</t>
+  </si>
+  <si>
+    <t>Python 82.21%; Lua 16.92%; Shell 0.87%</t>
+  </si>
+  <si>
+    <t>bingo</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/bingo</t>
+  </si>
+  <si>
+    <t>Python 84.56%; Mako 9.98%; C 2.77%; Makefile 1.57%; Shell 1.01%</t>
+  </si>
+  <si>
+    <t>community</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/community</t>
+  </si>
+  <si>
+    <t>account</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/account</t>
+  </si>
+  <si>
+    <t>Lua 92.68%; C 6.9%; CMake 0.18%; Python 0.18%; Shell 0.04%</t>
+  </si>
+  <si>
+    <t>sensor</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/sensor</t>
+  </si>
+  <si>
+    <t>Lua 99.81%; CMake 0.07%; Makefile 0.06%; Python 0.05%</t>
+  </si>
+  <si>
+    <t>skills-marketplace</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/skills-marketplace</t>
+  </si>
+  <si>
+    <t>TypeScript 44.54%; JavaScript 23.38%; Shell 18.44%; Python 8.72%; HTML 4.8%</t>
+  </si>
+  <si>
+    <t>rackmount</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/rackmount</t>
+  </si>
+  <si>
+    <t>Lua 81.42%; Python 18.56%; CMake 0.03%</t>
+  </si>
+  <si>
+    <t>storage</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/storage</t>
+  </si>
+  <si>
+    <t>Lua 60.19%; C 37.07%; C++ 2.58%; CMake 0.13%; Makefile 0.01%</t>
+  </si>
+  <si>
+    <t>bios</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/bios</t>
+  </si>
+  <si>
+    <t>Lua 99.73%; C 0.13%; CMake 0.09%; Makefile 0.03%; Python 0.03%</t>
+  </si>
+  <si>
+    <t>network_adapter</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/network_adapter</t>
+  </si>
+  <si>
+    <t>Lua 99.84%; C 0.07%; CMake 0.05%; Makefile 0.02%; Python 0.02%</t>
+  </si>
+  <si>
+    <t>infrastructure</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/infrastructure</t>
+  </si>
+  <si>
+    <t>Python 79.27%; Shell 20.73%</t>
+  </si>
+  <si>
+    <t>libmcpp</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/libmcpp</t>
+  </si>
+  <si>
+    <t>C++ 93.19%; Lua 4.36%; Shell 0.98%; Meson 0.71%; C 0.58%</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/QA</t>
+  </si>
+  <si>
+    <t>Python 52.3%; RobotFramework 46.7%; Shell 0.76%; CSS 0.2%; PowerShell 0.05%</t>
+  </si>
+  <si>
+    <t>bcal</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/bcal</t>
+  </si>
+  <si>
+    <t>C++ 96.26%; Python 1.78%; Meson 1.45%; Makefile 0.51%</t>
+  </si>
+  <si>
+    <t>webui</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/webui</t>
+  </si>
+  <si>
+    <t>Vue 62.1%; TypeScript 36.16%; SCSS 0.87%; JavaScript 0.58%; CSS 0.2%</t>
+  </si>
+  <si>
+    <t>thermal_mgmt</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/thermal_mgmt</t>
+  </si>
+  <si>
+    <t>Lua 99.84%; CMake 0.08%; Makefile 0.04%; Python 0.04%</t>
+  </si>
+  <si>
+    <t>observability</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/observability</t>
+  </si>
+  <si>
+    <t>Lua 77.77%; C++ 21.07%; CMake 0.66%; Shell 0.31%; Makefile 0.16%</t>
+  </si>
+  <si>
+    <t>pcie_device</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/pcie_device</t>
+  </si>
+  <si>
+    <t>Lua 99.76%; Python 0.12%; CMake 0.08%; Makefile 0.04%</t>
+  </si>
+  <si>
+    <t>qemu</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/qemu</t>
+  </si>
+  <si>
+    <t>C 79.99%; POV-Ray SDL 8.42%; Python 4.18%; C++ 2.04%; Shell 1.57%</t>
+  </si>
+  <si>
+    <t>mdb_interface</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/mdb_interface</t>
+  </si>
+  <si>
+    <t>Python 95.78%; CMake 2.4%; Makefile 1.82%</t>
+  </si>
+  <si>
+    <t>libipmi</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/libipmi</t>
+  </si>
+  <si>
+    <t>C++ 92.18%; Meson 3.75%; Python 2.99%; C 0.55%; Lua 0.53%</t>
+  </si>
+  <si>
+    <t>frudata</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/frudata</t>
+  </si>
+  <si>
+    <t>Lua 97.11%; C 2.39%; CMake 0.29%; Makefile 0.1%; Shell 0.1%</t>
+  </si>
+  <si>
+    <t>iam_lite</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/iam_lite</t>
+  </si>
+  <si>
+    <t>Lua 99.46%; Python 0.29%; CMake 0.16%; Makefile 0.09%</t>
+  </si>
+  <si>
+    <t>spdm</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/spdm</t>
+  </si>
+  <si>
+    <t>Lua 68.48%; C++ 28.53%; C 1.76%; CMake 0.65%; Makefile 0.22%</t>
+  </si>
+  <si>
+    <t>libirc</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/libirc</t>
+  </si>
+  <si>
+    <t>C++ 95.66%; CMake 2.87%; Batchfile 1.47%</t>
+  </si>
+  <si>
+    <t>release_management</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/release_management</t>
+  </si>
+  <si>
+    <t>power_mgmt</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/power_mgmt</t>
+  </si>
+  <si>
+    <t>Lua 99.86%; CMake 0.07%; Makefile 0.03%; Python 0.03%</t>
+  </si>
+  <si>
+    <t>devmon</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/devmon</t>
+  </si>
+  <si>
+    <t>C++ 95.48%; Shell 2.78%; Meson 0.61%; C 0.51%; Python 0.35%</t>
+  </si>
+  <si>
+    <t>manufacture</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/manufacture</t>
+  </si>
+  <si>
+    <t>Lua 99.32%; CMake 0.29%; Python 0.2%; Makefile 0.19%</t>
+  </si>
+  <si>
+    <t>compute_mgmt</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/compute_mgmt</t>
+  </si>
+  <si>
+    <t>Lua 99.45%; CMake 0.33%; Makefile 0.18%; Python 0.04%</t>
+  </si>
+  <si>
+    <t>chassis</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/chassis</t>
+  </si>
+  <si>
+    <t>Lua 99.71%; CMake 0.13%; Makefile 0.08%; Python 0.08%</t>
+  </si>
+  <si>
+    <t>rack_mgmt</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/rack_mgmt</t>
+  </si>
+  <si>
+    <t>Lua 95.2%; CMake 1.77%; Makefile 1.53%; Python 1.5%</t>
+  </si>
+  <si>
+    <t>fructrl</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/fructrl</t>
+  </si>
+  <si>
+    <t>Lua 99.55%; Python 0.22%; CMake 0.13%; Makefile 0.1%</t>
+  </si>
+  <si>
+    <t>conan_index</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/conan_index</t>
+  </si>
+  <si>
+    <t>Python 98.79%; Makefile 1.21%</t>
+  </si>
+  <si>
+    <t>web_online_help</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/web_online_help</t>
+  </si>
+  <si>
+    <t>HTML 99.96%; Python 0.04%</t>
+  </si>
+  <si>
+    <t>bus_tools</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/bus_tools</t>
+  </si>
+  <si>
+    <t>C 78.53%; Python 14.98%; Makefile 6.49%</t>
+  </si>
+  <si>
+    <t>lcd_console</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/lcd_console</t>
+  </si>
+  <si>
+    <t>Lua 99.58%; CMake 0.19%; Python 0.13%; Makefile 0.1%</t>
+  </si>
+  <si>
+    <t>dcmid</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/dcmid</t>
+  </si>
+  <si>
+    <t>Lua 96.59%; CMake 2.04%; Makefile 1.14%; Python 0.24%</t>
+  </si>
+  <si>
+    <t>bmc_datasync</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/bmc_datasync</t>
+  </si>
+  <si>
+    <t>Lua 96.12%; C 2.21%; CMake 0.91%; Python 0.4%; Makefile 0.36%</t>
+  </si>
+  <si>
+    <t>openubmc-ci</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/openubmc-ci</t>
+  </si>
+  <si>
+    <t>Python 76.74%; Shell 23.26%</t>
+  </si>
+  <si>
+    <t>rootfs_user</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/rootfs_user</t>
+  </si>
+  <si>
+    <t>Python 51.68%; Lua 35.93%; Makefile 8.04%; CMake 4.34%</t>
+  </si>
+  <si>
+    <t>lsw</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/lsw</t>
+  </si>
+  <si>
+    <t>Lua 91.19%; C 7.62%; CMake 0.73%; Makefile 0.23%; Python 0.23%</t>
+  </si>
+  <si>
+    <t>nagios_plugin</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/nagios_plugin</t>
+  </si>
+  <si>
+    <t>Python 99.62%; Shell 0.38%</t>
+  </si>
+  <si>
+    <t>zabbix_plugin</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/zabbix_plugin</t>
+  </si>
+  <si>
+    <t>software-center-config</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/software-center-config</t>
+  </si>
+  <si>
+    <t>hica</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/hica</t>
+  </si>
+  <si>
+    <t>Lua 92.36%; Python 2.94%; Makefile 2.89%; CMake 1.81%</t>
+  </si>
+  <si>
+    <t>active_standby_mgmt</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/active_standby_mgmt</t>
+  </si>
+  <si>
+    <t>Lua 98.87%; CMake 0.64%; Makefile 0.32%; Python 0.16%</t>
+  </si>
+  <si>
+    <t>ansible_plugin</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/ansible_plugin</t>
+  </si>
+  <si>
+    <t>qemu_mockup</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/qemu_mockup</t>
+  </si>
+  <si>
+    <t>C 83.72%; Shell 6.12%; Python 5.41%; Lua 2.03%; Makefile 1.88%</t>
+  </si>
+  <si>
+    <t>irc_client</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/irc_client</t>
+  </si>
+  <si>
+    <t>ccf_openubmc</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/ccf_openubmc</t>
+  </si>
+  <si>
+    <t>vnc_proxy</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/vnc_proxy</t>
+  </si>
+  <si>
+    <t>CMake 2.98%; Makefile 1.67%; Python 0.34%</t>
+  </si>
+  <si>
+    <t>cmdlets_plugin</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/cmdlets_plugin</t>
+  </si>
+  <si>
+    <t>PowerShell 99.9%; Shell 0.1%</t>
+  </si>
+  <si>
+    <t>.gitcode</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openUBMC/.gitcode</t>
+  </si>
+  <si>
+    <t>mindspore社区</t>
+  </si>
+  <si>
+    <t>mindspore</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore/mindspore</t>
+  </si>
+  <si>
+    <t>vllm-mindspore</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore/vllm-mindspore</t>
+  </si>
+  <si>
+    <t>akg</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore/akg</t>
+  </si>
+  <si>
+    <t>Python (56.3%)</t>
+  </si>
+  <si>
+    <t>hyper-parallel</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore/hyper-parallel</t>
+  </si>
+  <si>
+    <t>mindspore-lite</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore/mindspore-lite</t>
+  </si>
+  <si>
+    <t>C++ (66.29%)</t>
+  </si>
+  <si>
+    <t>mindformers</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore/mindformers</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore/docs</t>
+  </si>
+  <si>
+    <t>mindquantum</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore/mindquantum</t>
+  </si>
+  <si>
+    <t>dvm</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore/dvm</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore/community</t>
+  </si>
+  <si>
+    <t>Python (94.08%)</t>
+  </si>
+  <si>
+    <t>ms_custom_ops</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore/ms_custom_ops</t>
+  </si>
+  <si>
+    <t>mindspore-agreements</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore/mindspore-agreements</t>
+  </si>
+  <si>
+    <t>mindspore_op_plugin</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore/mindspore_op_plugin</t>
+  </si>
+  <si>
+    <t>golden-stick</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore/golden-stick</t>
+  </si>
+  <si>
+    <t>Python (95.1%)</t>
+  </si>
+  <si>
+    <t>mindrlhf</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore/mindrlhf</t>
+  </si>
+  <si>
+    <t>Python (97.33%)</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore/.gitcode</t>
+  </si>
+  <si>
+    <t>mindspore-lab</t>
+  </si>
+  <si>
+    <t>mindscience</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore-lab/mindscience</t>
+  </si>
+  <si>
+    <t>Python 77.46%; Jupyter Notebook 16.8%; TeX 2.29%; C++ 1.97%; Shell 0.69%</t>
+  </si>
+  <si>
+    <t>mindspore-cli</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore-lab/mindspore-cli</t>
+  </si>
+  <si>
+    <t>mindcv</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore-lab/mindcv</t>
+  </si>
+  <si>
+    <t>mindone</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore-lab/mindone</t>
+  </si>
+  <si>
+    <t>Python 99.86%; C 0.12%; Shell 0.01%</t>
+  </si>
+  <si>
+    <t>mindhf</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore-lab/mindhf</t>
+  </si>
+  <si>
+    <t>Python 86.35%; Jupyter Notebook 9.51%; Cuda 2.64%; C++ 1.17%; JavaScript 0.13%</t>
+  </si>
+  <si>
+    <t>tutorials</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore-lab/tutorials</t>
+  </si>
+  <si>
+    <t>hub</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore-lab/hub</t>
+  </si>
+  <si>
+    <t>mindspore-skills</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore-lab/mindspore-skills</t>
+  </si>
+  <si>
+    <t>mindyolo</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore-lab/mindyolo</t>
+  </si>
+  <si>
+    <t>mindocr</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore-lab/mindocr</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore-lab/mindrlhf</t>
+  </si>
+  <si>
+    <t>mindediting</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore-lab/mindediting</t>
+  </si>
+  <si>
+    <t>mindarmour</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore-lab/mindarmour</t>
+  </si>
+  <si>
+    <t>Python 99.88%; Shell 0.12%</t>
+  </si>
+  <si>
+    <t>mindrl</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore-lab/mindrl</t>
+  </si>
+  <si>
+    <t>models</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore-lab/models</t>
+  </si>
+  <si>
+    <t>Python 57.3%; C 38.71%; Shell 1.48%; TeX 1.34%; Makefile 0.36%</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore-lab/infrastructure</t>
+  </si>
+  <si>
+    <t>mindface</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore-lab/mindface</t>
+  </si>
+  <si>
+    <t>mindaudio</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/mindspore-lab/mindaudio</t>
+  </si>
+  <si>
+    <t>opengauss社区</t>
+  </si>
+  <si>
+    <t>openGauss-server</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-server</t>
+  </si>
+  <si>
+    <t>C++ 77.5%; C 7.77%; SQL 5.28%; PLpgSQL 3.01%; Yacc 2.56%</t>
+  </si>
+  <si>
+    <t>oGRAC</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/oGRAC</t>
+  </si>
+  <si>
+    <t>openGauss-third_party</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-third_party</t>
+  </si>
+  <si>
+    <t>C 46.69%; Shell 36.98%; Python 15.92%; Makefile 0.25%; CMake 0.16%</t>
+  </si>
+  <si>
+    <t>openGauss-DBMind</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-DBMind</t>
+  </si>
+  <si>
+    <t>Python 77.94%; JavaScript 20.87%; CSS 0.75%; Shell 0.25%; Makefile 0.12%</t>
+  </si>
+  <si>
+    <t>DataStudio</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/DataStudio</t>
+  </si>
+  <si>
+    <t>oG-Memory</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/oG-Memory</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/docs</t>
+  </si>
+  <si>
+    <t>Python 52.3%; CSS 41.39%; Dockerfile 3.36%; Batchfile 1.32%; Makefile 1.09%</t>
+  </si>
+  <si>
+    <t>openGauss-workbench</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-workbench</t>
+  </si>
+  <si>
+    <t>Java 57.93%; Vue 26.2%; HTML 4.79%; SQL 3.41%</t>
+  </si>
+  <si>
+    <t>openGauss-container</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-container</t>
+  </si>
+  <si>
+    <t>Shell 87.94%; Python 12.06%</t>
+  </si>
+  <si>
+    <t>openGauss-connector-python-psycopg2</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-connector-python-psycopg2</t>
+  </si>
+  <si>
+    <t>website</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/website</t>
+  </si>
+  <si>
+    <t>debezium</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/debezium</t>
+  </si>
+  <si>
+    <t>Java 94.88%; ANTLR 2.89%; Groovy 1.02%; SQL 0.54%; Shell 0.25%</t>
+  </si>
+  <si>
+    <t>Yat</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/Yat</t>
+  </si>
+  <si>
+    <t>Python 85.36%; SQL 8.04%; PLpgSQL 3.87%; PLSQL 1.55%; Java 0.61%</t>
+  </si>
+  <si>
+    <t>CM</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/CM</t>
+  </si>
+  <si>
+    <t>spq_plugin_v2</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/spq_plugin_v2</t>
+  </si>
+  <si>
+    <t>mcp-opengauss</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/mcp-opengauss</t>
+  </si>
+  <si>
+    <t>Python 73.54%; Java 26.46%</t>
+  </si>
+  <si>
+    <t>Plugin</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/Plugin</t>
+  </si>
+  <si>
+    <t>C++ 73.85%; SQL 5.96%; Yacc 5.06%; PLpgSQL 4.84%; C 4.16%</t>
+  </si>
+  <si>
+    <t>openGauss-connector-odbc</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-connector-odbc</t>
+  </si>
+  <si>
+    <t>C 76.74%; Shell 13.02%; Makefile 3.43%; PowerShell 2.07%; C++ 1.72%</t>
+  </si>
+  <si>
+    <t>openGauss-embedded</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-embedded</t>
+  </si>
+  <si>
+    <t>C 66.8%; C++ 27.4%; Yacc 0.82%; Less 0.66%; Rust 0.65%</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/QA</t>
+  </si>
+  <si>
+    <t>openGauss-connector-jdbc</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-connector-jdbc</t>
+  </si>
+  <si>
+    <t>Java 99.36%; Shell 0.38%; Smarty 0.13%; Perl 0.06%; Scala 0.06%</t>
+  </si>
+  <si>
+    <t>docs-website</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/docs-website</t>
+  </si>
+  <si>
+    <t>Vue 38.76%; CSS 12.32%; HTML 6.88%</t>
+  </si>
+  <si>
+    <t>tc</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/tc</t>
+  </si>
+  <si>
+    <t>openGauss-tools-chameleon</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-tools-chameleon</t>
+  </si>
+  <si>
+    <t>Python 98.74%; Shell 1.07%; PLpgSQL 0.19%</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/community</t>
+  </si>
+  <si>
+    <t>openGauss-connector-python-pyog</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-connector-python-pyog</t>
+  </si>
+  <si>
+    <t>DSS</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/DSS</t>
+  </si>
+  <si>
+    <t>C 96.73%; Shell 1.23%; C++ 1.12%; CMake 0.92%</t>
+  </si>
+  <si>
+    <t>openGauss-wasm</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-wasm</t>
+  </si>
+  <si>
+    <t>openGauss-connector-adonet</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-connector-adonet</t>
+  </si>
+  <si>
+    <t>ogx</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/ogx</t>
+  </si>
+  <si>
+    <t>openGauss-GaussMaster</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-GaussMaster</t>
+  </si>
+  <si>
+    <t>opengauss-prometheus-exporter</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/opengauss-prometheus-exporter</t>
+  </si>
+  <si>
+    <t>yukon</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/yukon</t>
+  </si>
+  <si>
+    <t>C 63.6%; C++ 19.14%; PLpgSQL 14.88%; Shell 1.27%; Perl 0.43%</t>
+  </si>
+  <si>
+    <t>openGauss-operator</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-operator</t>
+  </si>
+  <si>
+    <t>easyVisualization</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/easyVisualization</t>
+  </si>
+  <si>
+    <t>Vue 43.27%; Java 36.26%; JavaScript 18.41%; CSS 1.86%; HTML 0.2%</t>
+  </si>
+  <si>
+    <t>openGauss-webclient</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-webclient</t>
+  </si>
+  <si>
+    <t>Go 44.72%; JavaScript 20.26%; PLpgSQL 18.11%; HTML 5.83%; CSS 5.47%</t>
+  </si>
+  <si>
+    <t>compatibility-assessment</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/compatibility-assessment</t>
+  </si>
+  <si>
+    <t>Java 98.76%; Shell 1.24%</t>
+  </si>
+  <si>
+    <t>openGauss-connector-nodejs</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-connector-nodejs</t>
+  </si>
+  <si>
+    <t>openGauss-tools-onlineMigration</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-tools-onlineMigration</t>
+  </si>
+  <si>
+    <t>ham4db</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/ham4db</t>
+  </si>
+  <si>
+    <t>Go 70.67%; JavaScript 16.99%; Python 7.55%; Shell 3.91%; CSS 0.67%</t>
+  </si>
+  <si>
+    <t>openGauss-tools-monitor</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-tools-monitor</t>
+  </si>
+  <si>
+    <t>Java 69.88%; Vue 25.41%; CSS 2.85%; JavaScript 1.52%; HTML 0.33%</t>
+  </si>
+  <si>
+    <t>oGRecorder</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/oGRecorder</t>
+  </si>
+  <si>
+    <t>hcom4db</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/hcom4db</t>
+  </si>
+  <si>
+    <t>C++ 54.63%; C 40.31%; CMake 2.87%; Shell 2.2%</t>
+  </si>
+  <si>
+    <t>openGauss-tools-ogtop</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-tools-ogtop</t>
+  </si>
+  <si>
+    <t>openGauss-webclient-portal</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-webclient-portal</t>
+  </si>
+  <si>
+    <t>JavaScript 66.67%; Vue 21.33%; SCSS 8.41%; Dockerfile 2.14%; HTML 1.45%</t>
+  </si>
+  <si>
+    <t>openGauss-tools-datachecker</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-tools-datachecker</t>
+  </si>
+  <si>
+    <t>Java 95.51%; Shell 4.05%; Batchfile 0.44%</t>
+  </si>
+  <si>
+    <t>openGauss-batman</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-batman</t>
+  </si>
+  <si>
+    <t>open-gauss-server-multi-master</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/open-gauss-server-multi-master</t>
+  </si>
+  <si>
+    <t>C++ 83.43%; C 8.3%; PLpgSQL 2.16%; Shell 1.25%</t>
+  </si>
+  <si>
+    <t>openGauss-sqlalchemy</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-sqlalchemy</t>
+  </si>
+  <si>
+    <t>security</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/security</t>
+  </si>
+  <si>
+    <t>openGauss-migration-portal</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-migration-portal</t>
+  </si>
+  <si>
+    <t>openGauss-connector-go-pq</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-connector-go-pq</t>
+  </si>
+  <si>
+    <t>ora-migration-tool</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/ora-migration-tool</t>
+  </si>
+  <si>
+    <t>Java 97.29%; Python 2.12%; ANTLR 0.59%</t>
+  </si>
+  <si>
+    <t>neon</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/neon</t>
+  </si>
+  <si>
+    <t>openGauss-tools-loader</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-tools-loader</t>
+  </si>
+  <si>
+    <t>Common Lisp 97.29%; Makefile 1.81%; Shell 0.7%; Dockerfile 0.13%; Batchfile 0.08%</t>
+  </si>
+  <si>
+    <t>openGauss-tools-ora2og</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-tools-ora2og</t>
+  </si>
+  <si>
+    <t>CM-RestAPI</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/CM-RestAPI</t>
+  </si>
+  <si>
+    <t>Java 99.99%; Shell 0.01%</t>
+  </si>
+  <si>
+    <t>DCF</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/DCF</t>
+  </si>
+  <si>
+    <t>C 97.53%; CMake 1.22%; Shell 0.75%; Makefile 0.45%; HTML 0.05%</t>
+  </si>
+  <si>
+    <t>DCC</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/DCC</t>
+  </si>
+  <si>
+    <t>C 99.6%; CMake 0.22%; Makefile 0.11%; Shell 0.04%; C++ 0.03%</t>
+  </si>
+  <si>
+    <t>DMS</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/DMS</t>
+  </si>
+  <si>
+    <t>C 97.23%; Shell 2.09%; CMake 0.68%</t>
+  </si>
+  <si>
+    <t>openGauss-tools-sqlines</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-tools-sqlines</t>
+  </si>
+  <si>
+    <t>C++ 86.16%; Java 10.31%; C 2.5%; CSS 0.45%; Makefile 0.19%</t>
+  </si>
+  <si>
+    <t>compatible-certification</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/compatible-certification</t>
+  </si>
+  <si>
+    <t>openGauss-tools-datachecker-performance</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-tools-datachecker-performance</t>
+  </si>
+  <si>
+    <t>openGauss-OM</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-OM</t>
+  </si>
+  <si>
+    <t>Python 94.49%; SQL 3.8%; Shell 1.15%; PLpgSQL 0.57%</t>
+  </si>
+  <si>
+    <t>CBB</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/CBB</t>
+  </si>
+  <si>
+    <t>C 98.97%; CMake 0.59%; Shell 0.3%; Makefile 0.14%</t>
+  </si>
+  <si>
+    <t>og-agreements</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/og-agreements</t>
+  </si>
+  <si>
+    <t>org-issue</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/org-issue</t>
+  </si>
+  <si>
+    <t>migration-website</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/migration-website</t>
+  </si>
+  <si>
+    <t>ops</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/ops</t>
+  </si>
+  <si>
+    <t>tryme</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/tryme</t>
+  </si>
+  <si>
+    <t>Java 59.02%; Vue 28.82%; CSS 7.97%; JavaScript 3.62%; HTML 0.56%</t>
+  </si>
+  <si>
+    <t>playground-course</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/playground-course</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/.gitcode</t>
+  </si>
+  <si>
+    <t>blog</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/blog</t>
+  </si>
+  <si>
+    <t>HTML 20.36%; Vue 8.81%; SCSS 8.33%; Shell 2.56%</t>
+  </si>
+  <si>
+    <t>oGRAC_DOC</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/oGRAC_DOC</t>
+  </si>
+  <si>
+    <t>oGRAC-docs</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/oGRAC-docs</t>
+  </si>
+  <si>
+    <t>openGauss-tools-onlineMigration-mysql</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-tools-onlineMigration-mysql</t>
+  </si>
+  <si>
+    <t>examples</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/examples</t>
+  </si>
+  <si>
+    <t>C++ 54.37%; SQL 13.28%; Java 7.2%; C 6.44%; Python 5.03%</t>
+  </si>
+  <si>
+    <t>Blockchain</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/Blockchain</t>
+  </si>
+  <si>
+    <t>opensource-intership</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/opensource-intership</t>
+  </si>
+  <si>
+    <t>practice-course</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/practice-course</t>
+  </si>
+  <si>
+    <t>Java 84.55%; C 13.47%; Tcl 1.98%</t>
+  </si>
+  <si>
+    <t>openGauss-distributed-solutions</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-distributed-solutions</t>
+  </si>
+  <si>
+    <t>Python 93.41%; Shell 6.59%</t>
+  </si>
+  <si>
+    <t>openGauss-tools-sql-translator</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-tools-sql-translator</t>
+  </si>
+  <si>
+    <t>Java 97.78%; PLpgSQL 2.22%</t>
+  </si>
+  <si>
+    <t>release-management</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/release-management</t>
+  </si>
+  <si>
+    <t>MDCE</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/MDCE</t>
+  </si>
+  <si>
+    <t>distribution-certification</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/distribution-certification</t>
+  </si>
+  <si>
+    <t>openGauss-CI</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-CI</t>
+  </si>
+  <si>
+    <t>Shell 84.83%; Groovy 11.75%; Python 3.42%</t>
+  </si>
+  <si>
+    <t>open-gauss-compile-opt-tools</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/open-gauss-compile-opt-tools</t>
+  </si>
+  <si>
+    <t>Presentations</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/Presentations</t>
+  </si>
+  <si>
+    <t>riscv</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/riscv</t>
+  </si>
+  <si>
+    <t>TeX 89.65%; Shell 7.69%; Dockerfile 1.53%; BibTeX 0.14%</t>
+  </si>
+  <si>
+    <t>openGauss-jdbc-skywalking</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-jdbc-skywalking</t>
+  </si>
+  <si>
+    <t>Java 91.29%; Vue 3.98%; Shell 1.31%; HTML 0.73%</t>
+  </si>
+  <si>
+    <t>practice-platform</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/practice-platform</t>
+  </si>
+  <si>
+    <t>Java 56.19%; Vue 35.28%; JavaScript 4.26%; PLpgSQL 4.2%; HTML 0.06%</t>
+  </si>
+  <si>
+    <t>shardingsphere</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/shardingsphere</t>
+  </si>
+  <si>
+    <t>Java 95.35%; ANTLR 3.92%; Fluent 0.44%; Shell 0.13%; FreeMarker 0.12%</t>
+  </si>
+  <si>
+    <t>service-partner-certification</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/service-partner-certification</t>
+  </si>
+  <si>
+    <t>openGauss-graph</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-graph</t>
+  </si>
+  <si>
+    <t>C++ 82.78%; C 8.09%; Yacc 1.92%; PLpgSQL 1.82%; Python 1.58%</t>
+  </si>
+  <si>
+    <t>open-gauss-cm-operator</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/open-gauss-cm-operator</t>
+  </si>
+  <si>
+    <t>openGauss-sandbox</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-sandbox</t>
+  </si>
+  <si>
+    <t>openGauss-DBMind-3rd</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-DBMind-3rd</t>
+  </si>
+  <si>
+    <t>distribution-evaluation</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/distribution-evaluation</t>
+  </si>
+  <si>
+    <t>openGauss-tools-migrationAssessmentReport</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-tools-migrationAssessmentReport</t>
+  </si>
+  <si>
+    <t>Java 63.99%; JavaScript 34.27%; Shell 0.91%; HTML 0.54%; CSS 0.29%</t>
+  </si>
+  <si>
+    <t>openGauss-housekeeper</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-housekeeper</t>
+  </si>
+  <si>
+    <t>Python 96.79%; Shell 3.21%</t>
+  </si>
+  <si>
+    <t>training-partner-certification</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/training-partner-certification</t>
+  </si>
+  <si>
+    <t>uc</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/uc</t>
+  </si>
+  <si>
+    <t>dbms-fuzzing-scu</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/dbms-fuzzing-scu</t>
+  </si>
+  <si>
+    <t>C++ 53.95%; C 32.66%; Yacc 12.05%; Lex 0.94%; Makefile 0.36%</t>
+  </si>
+  <si>
+    <t>openGauss-test-toolset</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-test-toolset</t>
+  </si>
+  <si>
+    <t>Java 71.28%; Python 24.04%; Shell 3.16%; Batchfile 1.52%</t>
+  </si>
+  <si>
+    <t>openGauss-tools-pg2og</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-tools-pg2og</t>
+  </si>
+  <si>
+    <t>board</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/board</t>
+  </si>
+  <si>
+    <t>knowledgeGraph</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/knowledgeGraph</t>
+  </si>
+  <si>
+    <t>openGauss-AI</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-AI</t>
+  </si>
+  <si>
+    <t>Python 94.6%; Java 2.95%; Shell 1.78%; ANTLR 0.67%</t>
+  </si>
+  <si>
+    <t>landscope</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/landscope</t>
+  </si>
+  <si>
+    <t>openGauss-User-Group</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-User-Group</t>
+  </si>
+  <si>
+    <t>quick-issue-website</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/quick-issue-website</t>
+  </si>
+  <si>
+    <t>Vue 56.1%; SCSS 13.95%; JavaScript 6.21%; TSX 5.01%</t>
+  </si>
+  <si>
+    <t>openGauss-connector-rust</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-connector-rust</t>
+  </si>
+  <si>
+    <t>Rust 99.27%; Shell 0.72%; Dockerfile 0.01%</t>
+  </si>
+  <si>
+    <t>ngxdb-for-opengauss</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/ngxdb-for-opengauss</t>
+  </si>
+  <si>
+    <t>PLpgSQL 90.79%; C 7.63%; Python 1.57%</t>
+  </si>
+  <si>
+    <t>openGauss-tools-backup</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/openGauss-tools-backup</t>
+  </si>
+  <si>
+    <t>bc</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/bc</t>
+  </si>
+  <si>
+    <t>open-gauss-finance</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/open-gauss-finance</t>
+  </si>
+  <si>
+    <t>ansible-for-opengauss</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/opengauss/ansible-for-opengauss</t>
+  </si>
+  <si>
+    <t>Jinja 53.35%; Ruby 28.17%; HCL 10.95%; Dockerfile 6.67%; Shell 0.86%</t>
+  </si>
+  <si>
+    <t>openlibing社区</t>
+  </si>
+  <si>
+    <t>openlibing-web</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openlibing/openlibing-web</t>
+  </si>
+  <si>
+    <t>vue</t>
+  </si>
+  <si>
+    <t>openlibing-pytest-executor</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openlibing/openlibing-pytest-executor</t>
+  </si>
+  <si>
+    <t>python</t>
+  </si>
+  <si>
+    <t>openlibing-platform-release</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openlibing/openlibing-platform-release</t>
+  </si>
+  <si>
+    <t>java</t>
+  </si>
+  <si>
+    <t>社区</t>
+  </si>
+  <si>
+    <t>组件</t>
+  </si>
+  <si>
+    <t>问题描述</t>
+  </si>
+  <si>
+    <t>问题级别</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>原始报告</t>
+  </si>
+  <si>
+    <t>MindIE-Motor</t>
+  </si>
+  <si>
+    <t>HttpServer.cpp ResourceNotFound() 函数存在反射型XSS漏洞</t>
+  </si>
+  <si>
+    <t>严重</t>
+  </si>
+  <si>
+    <t>https://github.com/TTY-flag/community_reports/blob/main/Ascend/MindIE/MindIE-Motor/scan-results/details/VULN-DF-CPP-001.md</t>
   </si>
 </sst>
 </file>
@@ -850,7 +2515,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -858,7 +2523,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1312,10 +2977,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
@@ -1442,7 +3107,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1461,10 +3126,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1776,8 +3450,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G109"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <dimension ref="A1:I330"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.2222222222222" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -1785,11 +3459,11 @@
     <col min="4" max="4" width="57.4444444444444" customWidth="1"/>
     <col min="5" max="5" width="12.5555555555556" customWidth="1"/>
     <col min="6" max="6" width="12.4444444444444" customWidth="1"/>
-    <col min="7" max="7" width="13.5555555555556" customWidth="1"/>
-    <col min="9" max="9" width="11.2222222222222" customWidth="1"/>
+    <col min="7" max="9" width="13.5555555555556" customWidth="1"/>
+    <col min="11" max="11" width="11.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1811,430 +3485,433 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1"/>
       <c r="B3" s="2"/>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9">
       <c r="A4" s="1"/>
       <c r="B4" s="2"/>
       <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
         <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
       </c>
       <c r="F4">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:9">
       <c r="A5" s="1"/>
       <c r="B5" s="2"/>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:9">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1"/>
       <c r="B8" s="2"/>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1"/>
       <c r="B9" s="2"/>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1"/>
       <c r="B10" s="2"/>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1"/>
       <c r="B11" s="2"/>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1"/>
       <c r="B12" s="2"/>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1"/>
       <c r="B14" s="2"/>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1"/>
       <c r="B15" s="2"/>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1"/>
       <c r="B16" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1"/>
       <c r="B17" s="2"/>
       <c r="C17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1"/>
       <c r="B19" s="2"/>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="1"/>
       <c r="B21" s="2"/>
       <c r="C21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="1"/>
       <c r="B22" s="2"/>
       <c r="C22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D22" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="1"/>
       <c r="B24" s="2"/>
       <c r="C24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="1"/>
       <c r="B25" s="2"/>
       <c r="C25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D26" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1"/>
       <c r="B27" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D28" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="1"/>
       <c r="B29" s="2"/>
       <c r="C29" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C30" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D30" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E30" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C31" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D31" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E31" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2243,202 +3920,223 @@
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:7">
       <c r="A33" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" s="1"/>
       <c r="B34" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" s="1"/>
       <c r="B35" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" s="1"/>
       <c r="B36" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+        <v>97</v>
+      </c>
+      <c r="F36">
+        <v>2</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" s="1"/>
       <c r="B37" s="4"/>
       <c r="C37" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+        <v>99</v>
+      </c>
+      <c r="F37">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" s="1"/>
       <c r="B38" s="4"/>
       <c r="C38" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+        <v>101</v>
+      </c>
+      <c r="F38">
+        <v>3</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" s="1"/>
       <c r="B39" s="4"/>
       <c r="C39" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+        <v>103</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" s="1"/>
       <c r="B40" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F40">
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:7">
       <c r="A41" s="1"/>
       <c r="B41" s="4"/>
       <c r="C41" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F41">
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:7">
       <c r="A42" s="1"/>
       <c r="B42" s="4"/>
       <c r="C42" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F42">
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:7">
       <c r="A43" s="1"/>
       <c r="B43" s="4"/>
       <c r="C43" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F43">
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:7">
       <c r="A44" s="1"/>
       <c r="B44" s="4"/>
       <c r="C44" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F44">
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:7">
       <c r="A45" s="1"/>
       <c r="B45" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F45">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:7">
       <c r="A46" s="1"/>
       <c r="B46" s="4"/>
       <c r="C46" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F46">
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:7">
       <c r="A47" s="1"/>
       <c r="B47" s="4"/>
       <c r="C47" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F47">
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:7">
       <c r="A48" s="1"/>
       <c r="B48" s="4"/>
       <c r="C48" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -2448,10 +4146,10 @@
       <c r="A49" s="1"/>
       <c r="B49" s="4"/>
       <c r="C49" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -2461,10 +4159,10 @@
       <c r="A50" s="1"/>
       <c r="B50" s="4"/>
       <c r="C50" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F50">
         <v>6</v>
@@ -2474,10 +4172,10 @@
       <c r="A51" s="1"/>
       <c r="B51" s="4"/>
       <c r="C51" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D51" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F51">
         <v>8</v>
@@ -2487,10 +4185,10 @@
       <c r="A52" s="1"/>
       <c r="B52" s="4"/>
       <c r="C52" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D52" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -2499,53 +4197,62 @@
     <row r="53" spans="1:6">
       <c r="A53" s="1"/>
       <c r="B53" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D53" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="1"/>
       <c r="B54" s="4"/>
       <c r="C54" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D54" t="s">
-        <v>135</v>
+        <v>136</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="1"/>
       <c r="B55" s="4"/>
       <c r="C55" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D55" t="s">
-        <v>137</v>
+        <v>138</v>
+      </c>
+      <c r="F55">
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="1"/>
       <c r="B56" s="4"/>
       <c r="C56" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D56" t="s">
-        <v>139</v>
+        <v>140</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="1"/>
       <c r="B57" s="4"/>
       <c r="C57" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D57" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F57">
         <v>2</v>
@@ -2555,10 +4262,10 @@
       <c r="A58" s="1"/>
       <c r="B58" s="4"/>
       <c r="C58" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D58" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F58">
         <v>7</v>
@@ -2568,10 +4275,10 @@
       <c r="A59" s="1"/>
       <c r="B59" s="4"/>
       <c r="C59" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D59" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F59">
         <v>9</v>
@@ -2581,10 +4288,10 @@
       <c r="A60" s="1"/>
       <c r="B60" s="4"/>
       <c r="C60" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D60" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -2594,10 +4301,10 @@
       <c r="A61" s="1"/>
       <c r="B61" s="4"/>
       <c r="C61" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D61" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F61">
         <v>3</v>
@@ -2607,20 +4314,23 @@
       <c r="A62" s="1"/>
       <c r="B62" s="4"/>
       <c r="C62" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D62" t="s">
-        <v>151</v>
+        <v>152</v>
+      </c>
+      <c r="F62">
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="1"/>
       <c r="B63" s="4"/>
       <c r="C63" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D63" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F63">
         <v>8</v>
@@ -2630,20 +4340,23 @@
       <c r="A64" s="1"/>
       <c r="B64" s="4"/>
       <c r="C64" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D64" t="s">
-        <v>155</v>
+        <v>156</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="1"/>
       <c r="B65" s="4"/>
       <c r="C65" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D65" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F65">
         <v>7</v>
@@ -2653,30 +4366,33 @@
       <c r="A66" s="1"/>
       <c r="B66" s="4"/>
       <c r="C66" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D66" t="s">
-        <v>159</v>
+        <v>160</v>
+      </c>
+      <c r="F66">
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="1"/>
       <c r="B67" s="4"/>
       <c r="C67" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D67" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="1"/>
       <c r="B68" s="4"/>
       <c r="C68" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D68" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -2686,10 +4402,10 @@
       <c r="A69" s="1"/>
       <c r="B69" s="4"/>
       <c r="C69" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D69" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F69">
         <v>1</v>
@@ -2699,10 +4415,10 @@
       <c r="A70" s="1"/>
       <c r="B70" s="4"/>
       <c r="C70" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -2712,10 +4428,10 @@
       <c r="A71" s="1"/>
       <c r="B71" s="4"/>
       <c r="C71" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -2725,10 +4441,10 @@
       <c r="A72" s="1"/>
       <c r="B72" s="4"/>
       <c r="C72" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -2738,462 +4454,3289 @@
       <c r="A73" s="1"/>
       <c r="B73" s="4"/>
       <c r="C73" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D73" s="3" t="s">
         <v>173</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="F73">
+        <v>9</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="1"/>
       <c r="B74" s="4"/>
       <c r="C74" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D74" s="3" t="s">
         <v>175</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="1"/>
       <c r="B75" s="4"/>
       <c r="C75" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D75" s="3" t="s">
         <v>177</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="1"/>
       <c r="B76" s="4"/>
       <c r="C76" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="D76" s="3" t="s">
         <v>179</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="1"/>
       <c r="B77" s="4"/>
       <c r="C77" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="1"/>
       <c r="B78" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="1"/>
       <c r="B79" s="4"/>
       <c r="C79" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="1"/>
       <c r="B80" s="4"/>
       <c r="C80" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="1"/>
       <c r="B81" s="4"/>
       <c r="C81" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="1"/>
       <c r="B82" s="4"/>
       <c r="C82" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="1"/>
       <c r="B83" s="4"/>
       <c r="C83" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="B85" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="C85" s="7" t="s">
+      <c r="B85" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="D85" s="7" t="s">
+      <c r="C85" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="E85" s="7" t="s">
+      <c r="D85" s="9" t="s">
         <v>198</v>
+      </c>
+      <c r="E85" s="9" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="1"/>
-      <c r="B86" s="6"/>
-      <c r="C86" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="D86" s="7" t="s">
+      <c r="B86" s="8"/>
+      <c r="C86" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="E86" s="7" t="s">
-        <v>198</v>
+      <c r="D86" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="E86" s="9" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="1"/>
-      <c r="B87" s="6"/>
-      <c r="C87" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="D87" s="7" t="s">
+      <c r="B87" s="8"/>
+      <c r="C87" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="E87" s="7" t="s">
-        <v>198</v>
+      <c r="D87" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="E87" s="9" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="1"/>
-      <c r="B88" s="6"/>
-      <c r="C88" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="D88" s="7" t="s">
+      <c r="B88" s="8"/>
+      <c r="C88" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="E88" s="7" t="s">
-        <v>198</v>
+      <c r="D88" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="E88" s="9" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="1"/>
-      <c r="B89" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="C89" s="7" t="s">
+      <c r="B89" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="D89" s="7" t="s">
+      <c r="C89" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="E89" s="7" t="s">
+      <c r="D89" s="9" t="s">
         <v>208</v>
+      </c>
+      <c r="E89" s="9" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="1"/>
-      <c r="B90" s="6"/>
-      <c r="C90" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="D90" s="7" t="s">
+      <c r="B90" s="8"/>
+      <c r="C90" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="E90" s="7" t="s">
-        <v>198</v>
+      <c r="D90" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="E90" s="9" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="1"/>
-      <c r="B91" s="6"/>
-      <c r="C91" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="D91" s="7" t="s">
+      <c r="B91" s="8"/>
+      <c r="C91" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="E91" s="7" t="s">
+      <c r="D91" s="9" t="s">
         <v>213</v>
+      </c>
+      <c r="E91" s="9" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="1"/>
-      <c r="B92" s="6"/>
-      <c r="C92" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="D92" s="7" t="s">
+      <c r="B92" s="8"/>
+      <c r="C92" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="E92" s="7" t="s">
+      <c r="D92" s="9" t="s">
         <v>216</v>
+      </c>
+      <c r="E92" s="9" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="1"/>
-      <c r="B93" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="C93" s="7" t="s">
+      <c r="B93" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="D93" s="7" t="s">
+      <c r="C93" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="E93" s="7" t="s">
-        <v>198</v>
+      <c r="D93" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="E93" s="9" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="1"/>
-      <c r="B94" s="6"/>
-      <c r="C94" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="D94" s="7" t="s">
+      <c r="B94" s="8"/>
+      <c r="C94" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="E94" s="7" t="s">
-        <v>198</v>
+      <c r="D94" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="E94" s="9" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="1"/>
-      <c r="B95" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="C95" s="7" t="s">
+      <c r="B95" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="D95" s="7" t="s">
+      <c r="C95" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="E95" s="7" t="s">
+      <c r="D95" s="9" t="s">
         <v>225</v>
+      </c>
+      <c r="E95" s="9" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="1"/>
-      <c r="B96" s="6"/>
-      <c r="C96" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="D96" s="7" t="s">
+      <c r="B96" s="8"/>
+      <c r="C96" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="E96" s="7" t="s">
+      <c r="D96" s="9" t="s">
         <v>228</v>
+      </c>
+      <c r="E96" s="9" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="1"/>
-      <c r="B97" s="6"/>
-      <c r="C97" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="D97" s="7" t="s">
+      <c r="B97" s="8"/>
+      <c r="C97" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="E97" s="7" t="s">
+      <c r="D97" s="9" t="s">
         <v>231</v>
+      </c>
+      <c r="E97" s="9" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="1"/>
-      <c r="B98" s="6"/>
-      <c r="C98" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="D98" s="7" t="s">
+      <c r="B98" s="8"/>
+      <c r="C98" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="E98" s="7" t="s">
+      <c r="D98" s="9" t="s">
         <v>234</v>
+      </c>
+      <c r="E98" s="9" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="1"/>
-      <c r="B99" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="C99" s="7" t="s">
+      <c r="B99" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="D99" s="7" t="s">
+      <c r="C99" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="E99" s="7" t="s">
-        <v>198</v>
+      <c r="D99" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="E99" s="9" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="1"/>
-      <c r="B100" s="6"/>
-      <c r="C100" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="D100" s="7" t="s">
+      <c r="B100" s="8"/>
+      <c r="C100" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="E100" s="7" t="s">
-        <v>198</v>
+      <c r="D100" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="E100" s="9" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="1"/>
-      <c r="B101" s="6"/>
-      <c r="C101" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="D101" s="7" t="s">
+      <c r="B101" s="8"/>
+      <c r="C101" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="E101" s="7" t="s">
+      <c r="D101" s="9" t="s">
         <v>242</v>
+      </c>
+      <c r="E101" s="9" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="1"/>
-      <c r="B102" s="6"/>
-      <c r="C102" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="D102" s="7" t="s">
+      <c r="B102" s="8"/>
+      <c r="C102" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="E102" s="7" t="s">
-        <v>198</v>
+      <c r="D102" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="E102" s="9" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="1"/>
-      <c r="B103" s="6"/>
-      <c r="C103" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="D103" s="7" t="s">
+      <c r="B103" s="8"/>
+      <c r="C103" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="E103" s="7" t="s">
+      <c r="D103" s="9" t="s">
         <v>247</v>
+      </c>
+      <c r="E103" s="9" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="1"/>
-      <c r="B104" s="6"/>
-      <c r="C104" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="D104" s="7" t="s">
+      <c r="B104" s="8"/>
+      <c r="C104" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="E104" s="7" t="s">
-        <v>198</v>
+      <c r="D104" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="E104" s="9" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="1"/>
-      <c r="B105" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="C105" s="7" t="s">
+      <c r="B105" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="D105" s="7" t="s">
+      <c r="C105" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="E105" s="7" t="s">
-        <v>198</v>
+      <c r="D105" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="E105" s="9" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="1"/>
-      <c r="B106" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="C106" s="7" t="s">
+      <c r="B106" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="D106" s="7" t="s">
+      <c r="C106" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="E106" s="7" t="s">
+      <c r="D106" s="9" t="s">
         <v>256</v>
+      </c>
+      <c r="E106" s="9" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="1"/>
-      <c r="B107" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="C107" s="7" t="s">
+      <c r="B107" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="D107" s="7" t="s">
+      <c r="C107" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="E107" s="7" t="s">
+      <c r="D107" s="9" t="s">
         <v>260</v>
+      </c>
+      <c r="E107" s="9" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="1"/>
-      <c r="B108" s="6"/>
-      <c r="C108" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="D108" s="7" t="s">
+      <c r="B108" s="8"/>
+      <c r="C108" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="E108" s="7" t="s">
-        <v>198</v>
+      <c r="D108" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="E108" s="9" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="1"/>
-      <c r="B109" s="6"/>
-      <c r="C109" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="D109" s="7" t="s">
+      <c r="B109" s="8"/>
+      <c r="C109" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="E109" s="7" t="s">
+      <c r="D109" s="9" t="s">
         <v>265</v>
       </c>
+      <c r="E109" s="9" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B111" s="9"/>
+      <c r="C111" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="D111" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="E111" s="10" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" s="1"/>
+      <c r="B112" s="9"/>
+      <c r="C112" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="D112" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="E112" s="10" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" s="1"/>
+      <c r="B113" s="9"/>
+      <c r="C113" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="D113" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E113" s="10" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" s="1"/>
+      <c r="B114" s="9"/>
+      <c r="C114" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="D114" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="E114" s="10" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" s="1"/>
+      <c r="B115" s="9"/>
+      <c r="C115" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="D115" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="E115" s="10" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" s="1"/>
+      <c r="B116" s="9"/>
+      <c r="C116" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="D116" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="E116" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" s="1"/>
+      <c r="B117" s="9"/>
+      <c r="C117" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="D117" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="E117" s="10" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" s="1"/>
+      <c r="B118" s="9"/>
+      <c r="C118" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="D118" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="E118" s="10" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" s="1"/>
+      <c r="B119" s="9"/>
+      <c r="C119" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="D119" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="E119" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" s="1"/>
+      <c r="B120" s="9"/>
+      <c r="C120" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="D120" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="E120" s="10" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" s="1"/>
+      <c r="B121" s="9"/>
+      <c r="C121" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="D121" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="E121" s="10" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" s="1"/>
+      <c r="B122" s="9"/>
+      <c r="C122" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="D122" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="E122" s="10" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" s="1"/>
+      <c r="B123" s="9"/>
+      <c r="C123" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="D123" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="E123" s="10" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" s="1"/>
+      <c r="B124" s="9"/>
+      <c r="C124" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="D124" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="E124" s="10" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" s="1"/>
+      <c r="B125" s="9"/>
+      <c r="C125" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="D125" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="E125" s="10" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" s="1"/>
+      <c r="B126" s="9"/>
+      <c r="C126" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="D126" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="E126" s="10" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" s="1"/>
+      <c r="B127" s="9"/>
+      <c r="C127" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="D127" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="E127" s="10" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128" s="1"/>
+      <c r="B128" s="9"/>
+      <c r="C128" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="D128" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="E128" s="10" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129" s="1"/>
+      <c r="B129" s="9"/>
+      <c r="C129" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="D129" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="E129" s="10" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" s="1"/>
+      <c r="B130" s="9"/>
+      <c r="C130" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="D130" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="E130" s="10" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" s="1"/>
+      <c r="B131" s="9"/>
+      <c r="C131" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="D131" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="E131" s="10" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132" s="1"/>
+      <c r="B132" s="9"/>
+      <c r="C132" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="D132" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="E132" s="10" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" s="1"/>
+      <c r="B133" s="9"/>
+      <c r="C133" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="D133" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="E133" s="10" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" s="1"/>
+      <c r="B134" s="9"/>
+      <c r="C134" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="D134" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="E134" s="10" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" s="1"/>
+      <c r="B135" s="9"/>
+      <c r="C135" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="D135" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="E135" s="10" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" s="1"/>
+      <c r="B136" s="9"/>
+      <c r="C136" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="D136" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="E136" s="10" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" s="1"/>
+      <c r="B137" s="9"/>
+      <c r="C137" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="D137" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="E137" s="10" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" s="1"/>
+      <c r="B138" s="9"/>
+      <c r="C138" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="D138" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="E138" s="10" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" s="1"/>
+      <c r="B139" s="9"/>
+      <c r="C139" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="D139" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="E139" s="10" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" s="1"/>
+      <c r="B140" s="9"/>
+      <c r="C140" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="D140" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="E140" s="10" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" s="1"/>
+      <c r="B141" s="9"/>
+      <c r="C141" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="D141" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="E141" s="10" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" s="1"/>
+      <c r="B142" s="9"/>
+      <c r="C142" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="D142" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="E142" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="1"/>
+      <c r="B143" s="9"/>
+      <c r="C143" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="D143" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="E143" s="10" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" s="1"/>
+      <c r="B144" s="9"/>
+      <c r="C144" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="D144" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="E144" s="10" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" s="1"/>
+      <c r="B145" s="9"/>
+      <c r="C145" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="D145" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="E145" s="10" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" s="1"/>
+      <c r="B146" s="9"/>
+      <c r="C146" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="D146" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="E146" s="10" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" s="1"/>
+      <c r="B147" s="9"/>
+      <c r="C147" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="D147" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="E147" s="10" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" s="1"/>
+      <c r="B148" s="9"/>
+      <c r="C148" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="D148" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="E148" s="10" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" s="1"/>
+      <c r="B149" s="9"/>
+      <c r="C149" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="D149" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="E149" s="10" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" s="1"/>
+      <c r="B150" s="9"/>
+      <c r="C150" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="D150" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="E150" s="10" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" s="1"/>
+      <c r="B151" s="9"/>
+      <c r="C151" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="D151" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="E151" s="10" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" s="1"/>
+      <c r="B152" s="9"/>
+      <c r="C152" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="D152" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="E152" s="10" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" s="1"/>
+      <c r="B153" s="9"/>
+      <c r="C153" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="D153" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="E153" s="10" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" s="1"/>
+      <c r="B154" s="9"/>
+      <c r="C154" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="D154" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="E154" s="10" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" s="1"/>
+      <c r="B155" s="9"/>
+      <c r="C155" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="D155" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="E155" s="10" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" s="1"/>
+      <c r="B156" s="9"/>
+      <c r="C156" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="D156" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="E156" s="10" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" s="1"/>
+      <c r="B157" s="9"/>
+      <c r="C157" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="D157" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="E157" s="10" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" s="1"/>
+      <c r="B158" s="9"/>
+      <c r="C158" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="D158" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="E158" s="10" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" s="1"/>
+      <c r="B159" s="9"/>
+      <c r="C159" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="D159" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="E159" s="10" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160" s="1"/>
+      <c r="B160" s="9"/>
+      <c r="C160" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="D160" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="E160" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161" s="1"/>
+      <c r="B161" s="9"/>
+      <c r="C161" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="D161" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="E161" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162" s="1"/>
+      <c r="B162" s="9"/>
+      <c r="C162" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="D162" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="E162" s="10" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" s="1"/>
+      <c r="B163" s="9"/>
+      <c r="C163" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="D163" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="E163" s="10" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164" s="1"/>
+      <c r="B164" s="9"/>
+      <c r="C164" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="D164" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="E164" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165" s="1"/>
+      <c r="B165" s="9"/>
+      <c r="C165" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="D165" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="E165" s="10" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" s="1"/>
+      <c r="B166" s="9"/>
+      <c r="C166" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="D166" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="E166" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167" s="1"/>
+      <c r="B167" s="9"/>
+      <c r="C167" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="D167" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="E167" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168" s="1"/>
+      <c r="B168" s="9"/>
+      <c r="C168" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="D168" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="E168" s="10" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" s="1"/>
+      <c r="B169" s="9"/>
+      <c r="C169" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="D169" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="E169" s="10" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170" s="1"/>
+      <c r="B170" s="9"/>
+      <c r="C170" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="D170" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="E170" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="B171" s="9"/>
+      <c r="C171" s="9"/>
+      <c r="D171" s="9"/>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C172" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="D172" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="E172" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" s="1"/>
+      <c r="B173" s="1"/>
+      <c r="C173" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="D173" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="E173" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" s="1"/>
+      <c r="B174" s="1"/>
+      <c r="C174" s="10" t="s">
+        <v>444</v>
+      </c>
+      <c r="D174" s="10" t="s">
+        <v>445</v>
+      </c>
+      <c r="E174" s="10" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" s="1"/>
+      <c r="B175" s="1"/>
+      <c r="C175" s="10" t="s">
+        <v>447</v>
+      </c>
+      <c r="D175" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="E175" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" s="1"/>
+      <c r="B176" s="1"/>
+      <c r="C176" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="D176" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="E176" s="10" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" s="1"/>
+      <c r="B177" s="1"/>
+      <c r="C177" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="D177" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="E177" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" s="1"/>
+      <c r="B178" s="1"/>
+      <c r="C178" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="D178" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="E178" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" s="1"/>
+      <c r="B179" s="1"/>
+      <c r="C179" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="D179" s="10" t="s">
+        <v>456</v>
+      </c>
+      <c r="E179" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" s="1"/>
+      <c r="B180" s="1"/>
+      <c r="C180" s="10" t="s">
+        <v>457</v>
+      </c>
+      <c r="D180" s="10" t="s">
+        <v>458</v>
+      </c>
+      <c r="E180" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" s="1"/>
+      <c r="B181" s="1"/>
+      <c r="C181" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="D181" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="E181" s="10" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182" s="1"/>
+      <c r="B182" s="1"/>
+      <c r="C182" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="D182" s="10" t="s">
+        <v>462</v>
+      </c>
+      <c r="E182" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" s="1"/>
+      <c r="B183" s="1"/>
+      <c r="C183" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="D183" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="E183" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184" s="1"/>
+      <c r="B184" s="1"/>
+      <c r="C184" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="D184" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="E184" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" s="1"/>
+      <c r="B185" s="1"/>
+      <c r="C185" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="D185" s="10" t="s">
+        <v>468</v>
+      </c>
+      <c r="E185" s="10" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186" s="1"/>
+      <c r="B186" s="1"/>
+      <c r="C186" s="10" t="s">
+        <v>470</v>
+      </c>
+      <c r="D186" s="10" t="s">
+        <v>471</v>
+      </c>
+      <c r="E186" s="10" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187" s="1"/>
+      <c r="B187" s="1"/>
+      <c r="C187" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="D187" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="E187" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188" s="1"/>
+      <c r="B188" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C188" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="D188" s="10" t="s">
+        <v>476</v>
+      </c>
+      <c r="E188" s="10" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189" s="1"/>
+      <c r="B189" s="1"/>
+      <c r="C189" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="D189" s="10" t="s">
+        <v>479</v>
+      </c>
+      <c r="E189" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" s="1"/>
+      <c r="B190" s="1"/>
+      <c r="C190" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="D190" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="E190" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" s="1"/>
+      <c r="B191" s="1"/>
+      <c r="C191" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="D191" s="10" t="s">
+        <v>483</v>
+      </c>
+      <c r="E191" s="10" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" s="1"/>
+      <c r="B192" s="1"/>
+      <c r="C192" s="10" t="s">
+        <v>485</v>
+      </c>
+      <c r="D192" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="E192" s="10" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193" s="1"/>
+      <c r="B193" s="1"/>
+      <c r="C193" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="D193" s="10" t="s">
+        <v>489</v>
+      </c>
+      <c r="E193" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" s="1"/>
+      <c r="B194" s="1"/>
+      <c r="C194" s="10" t="s">
+        <v>490</v>
+      </c>
+      <c r="D194" s="10" t="s">
+        <v>491</v>
+      </c>
+      <c r="E194" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" s="1"/>
+      <c r="B195" s="1"/>
+      <c r="C195" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="D195" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="E195" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" s="1"/>
+      <c r="B196" s="1"/>
+      <c r="C196" s="10" t="s">
+        <v>494</v>
+      </c>
+      <c r="D196" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="E196" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" s="1"/>
+      <c r="B197" s="1"/>
+      <c r="C197" s="10" t="s">
+        <v>496</v>
+      </c>
+      <c r="D197" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="E197" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" s="1"/>
+      <c r="B198" s="1"/>
+      <c r="C198" s="10" t="s">
+        <v>470</v>
+      </c>
+      <c r="D198" s="10" t="s">
+        <v>498</v>
+      </c>
+      <c r="E198" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" s="1"/>
+      <c r="B199" s="1"/>
+      <c r="C199" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="D199" s="10" t="s">
+        <v>500</v>
+      </c>
+      <c r="E199" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" s="1"/>
+      <c r="B200" s="1"/>
+      <c r="C200" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="D200" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="E200" s="10" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" s="1"/>
+      <c r="B201" s="1"/>
+      <c r="C201" s="10" t="s">
+        <v>504</v>
+      </c>
+      <c r="D201" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="E201" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" s="1"/>
+      <c r="B202" s="1"/>
+      <c r="C202" s="10" t="s">
+        <v>506</v>
+      </c>
+      <c r="D202" s="10" t="s">
+        <v>507</v>
+      </c>
+      <c r="E202" s="10" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" s="1"/>
+      <c r="B203" s="1"/>
+      <c r="C203" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="D203" s="10" t="s">
+        <v>509</v>
+      </c>
+      <c r="E203" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" s="1"/>
+      <c r="B204" s="1"/>
+      <c r="C204" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="D204" s="10" t="s">
+        <v>511</v>
+      </c>
+      <c r="E204" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" s="1"/>
+      <c r="B205" s="1"/>
+      <c r="C205" s="10" t="s">
+        <v>512</v>
+      </c>
+      <c r="D205" s="10" t="s">
+        <v>513</v>
+      </c>
+      <c r="E205" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="B206" s="10"/>
+      <c r="C206" s="10"/>
+      <c r="D206" s="10"/>
+      <c r="E206" s="10"/>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="B207" s="10"/>
+      <c r="C207" s="10" t="s">
+        <v>515</v>
+      </c>
+      <c r="D207" s="10" t="s">
+        <v>516</v>
+      </c>
+      <c r="E207" s="10" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" s="1"/>
+      <c r="B208" s="10"/>
+      <c r="C208" s="10" t="s">
+        <v>518</v>
+      </c>
+      <c r="D208" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="E208" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" s="1"/>
+      <c r="B209" s="10"/>
+      <c r="C209" s="10" t="s">
+        <v>520</v>
+      </c>
+      <c r="D209" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="E209" s="10" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" s="1"/>
+      <c r="B210" s="10"/>
+      <c r="C210" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="D210" s="10" t="s">
+        <v>524</v>
+      </c>
+      <c r="E210" s="10" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" s="1"/>
+      <c r="B211" s="10"/>
+      <c r="C211" s="10" t="s">
+        <v>526</v>
+      </c>
+      <c r="D211" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="E211" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" s="1"/>
+      <c r="B212" s="10"/>
+      <c r="C212" s="10" t="s">
+        <v>528</v>
+      </c>
+      <c r="D212" s="10" t="s">
+        <v>529</v>
+      </c>
+      <c r="E212" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" s="1"/>
+      <c r="B213" s="10"/>
+      <c r="C213" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="D213" s="10" t="s">
+        <v>530</v>
+      </c>
+      <c r="E213" s="10" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" s="1"/>
+      <c r="B214" s="10"/>
+      <c r="C214" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="D214" s="10" t="s">
+        <v>533</v>
+      </c>
+      <c r="E214" s="10" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" s="1"/>
+      <c r="B215" s="10"/>
+      <c r="C215" s="10" t="s">
+        <v>535</v>
+      </c>
+      <c r="D215" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="E215" s="10" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" s="1"/>
+      <c r="B216" s="10"/>
+      <c r="C216" s="10" t="s">
+        <v>538</v>
+      </c>
+      <c r="D216" s="10" t="s">
+        <v>539</v>
+      </c>
+      <c r="E216" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" s="1"/>
+      <c r="B217" s="10"/>
+      <c r="C217" s="10" t="s">
+        <v>540</v>
+      </c>
+      <c r="D217" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="E217" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" s="1"/>
+      <c r="B218" s="10"/>
+      <c r="C218" s="10" t="s">
+        <v>542</v>
+      </c>
+      <c r="D218" s="10" t="s">
+        <v>543</v>
+      </c>
+      <c r="E218" s="10" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" s="1"/>
+      <c r="B219" s="10"/>
+      <c r="C219" s="10" t="s">
+        <v>545</v>
+      </c>
+      <c r="D219" s="10" t="s">
+        <v>546</v>
+      </c>
+      <c r="E219" s="10" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" s="1"/>
+      <c r="B220" s="10"/>
+      <c r="C220" s="10" t="s">
+        <v>548</v>
+      </c>
+      <c r="D220" s="10" t="s">
+        <v>549</v>
+      </c>
+      <c r="E220" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" s="1"/>
+      <c r="B221" s="10"/>
+      <c r="C221" s="10" t="s">
+        <v>550</v>
+      </c>
+      <c r="D221" s="10" t="s">
+        <v>551</v>
+      </c>
+      <c r="E221" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" s="1"/>
+      <c r="B222" s="10"/>
+      <c r="C222" s="10" t="s">
+        <v>552</v>
+      </c>
+      <c r="D222" s="10" t="s">
+        <v>553</v>
+      </c>
+      <c r="E222" s="10" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" s="1"/>
+      <c r="B223" s="10"/>
+      <c r="C223" s="10" t="s">
+        <v>555</v>
+      </c>
+      <c r="D223" s="10" t="s">
+        <v>556</v>
+      </c>
+      <c r="E223" s="10" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" s="1"/>
+      <c r="B224" s="10"/>
+      <c r="C224" s="10" t="s">
+        <v>558</v>
+      </c>
+      <c r="D224" s="10" t="s">
+        <v>559</v>
+      </c>
+      <c r="E224" s="10" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" s="1"/>
+      <c r="B225" s="10"/>
+      <c r="C225" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="D225" s="10" t="s">
+        <v>562</v>
+      </c>
+      <c r="E225" s="10" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" s="1"/>
+      <c r="B226" s="10"/>
+      <c r="C226" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="D226" s="10" t="s">
+        <v>564</v>
+      </c>
+      <c r="E226" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" s="1"/>
+      <c r="B227" s="10"/>
+      <c r="C227" s="10" t="s">
+        <v>565</v>
+      </c>
+      <c r="D227" s="10" t="s">
+        <v>566</v>
+      </c>
+      <c r="E227" s="10" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" s="1"/>
+      <c r="B228" s="10"/>
+      <c r="C228" s="10" t="s">
+        <v>568</v>
+      </c>
+      <c r="D228" s="10" t="s">
+        <v>569</v>
+      </c>
+      <c r="E228" s="10" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" s="1"/>
+      <c r="B229" s="10"/>
+      <c r="C229" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D229" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="E229" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" s="1"/>
+      <c r="B230" s="10"/>
+      <c r="C230" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D230" s="10" t="s">
+        <v>574</v>
+      </c>
+      <c r="E230" s="10" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" s="1"/>
+      <c r="B231" s="10"/>
+      <c r="C231" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="D231" s="10" t="s">
+        <v>576</v>
+      </c>
+      <c r="E231" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" s="1"/>
+      <c r="B232" s="10"/>
+      <c r="C232" s="10" t="s">
+        <v>577</v>
+      </c>
+      <c r="D232" s="10" t="s">
+        <v>578</v>
+      </c>
+      <c r="E232" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" s="1"/>
+      <c r="B233" s="10"/>
+      <c r="C233" s="10" t="s">
+        <v>579</v>
+      </c>
+      <c r="D233" s="10" t="s">
+        <v>580</v>
+      </c>
+      <c r="E233" s="10" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" s="1"/>
+      <c r="B234" s="10"/>
+      <c r="C234" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="D234" s="10" t="s">
+        <v>583</v>
+      </c>
+      <c r="E234" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" s="1"/>
+      <c r="B235" s="10"/>
+      <c r="C235" s="10" t="s">
+        <v>584</v>
+      </c>
+      <c r="D235" s="10" t="s">
+        <v>585</v>
+      </c>
+      <c r="E235" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" s="1"/>
+      <c r="B236" s="10"/>
+      <c r="C236" s="10" t="s">
+        <v>586</v>
+      </c>
+      <c r="D236" s="10" t="s">
+        <v>587</v>
+      </c>
+      <c r="E236" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" s="1"/>
+      <c r="B237" s="10"/>
+      <c r="C237" s="10" t="s">
+        <v>588</v>
+      </c>
+      <c r="D237" s="10" t="s">
+        <v>589</v>
+      </c>
+      <c r="E237" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" s="1"/>
+      <c r="B238" s="10"/>
+      <c r="C238" s="10" t="s">
+        <v>590</v>
+      </c>
+      <c r="D238" s="10" t="s">
+        <v>591</v>
+      </c>
+      <c r="E238" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" s="1"/>
+      <c r="B239" s="10"/>
+      <c r="C239" s="10" t="s">
+        <v>592</v>
+      </c>
+      <c r="D239" s="10" t="s">
+        <v>593</v>
+      </c>
+      <c r="E239" s="10" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" s="1"/>
+      <c r="B240" s="10"/>
+      <c r="C240" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="D240" s="10" t="s">
+        <v>596</v>
+      </c>
+      <c r="E240" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" s="1"/>
+      <c r="B241" s="10"/>
+      <c r="C241" s="10" t="s">
+        <v>597</v>
+      </c>
+      <c r="D241" s="10" t="s">
+        <v>598</v>
+      </c>
+      <c r="E241" s="10" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" s="1"/>
+      <c r="B242" s="10"/>
+      <c r="C242" s="10" t="s">
+        <v>600</v>
+      </c>
+      <c r="D242" s="10" t="s">
+        <v>601</v>
+      </c>
+      <c r="E242" s="10" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" s="1"/>
+      <c r="B243" s="10"/>
+      <c r="C243" s="10" t="s">
+        <v>603</v>
+      </c>
+      <c r="D243" s="10" t="s">
+        <v>604</v>
+      </c>
+      <c r="E243" s="10" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" s="1"/>
+      <c r="B244" s="10"/>
+      <c r="C244" s="10" t="s">
+        <v>606</v>
+      </c>
+      <c r="D244" s="10" t="s">
+        <v>607</v>
+      </c>
+      <c r="E244" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" s="1"/>
+      <c r="B245" s="10"/>
+      <c r="C245" s="10" t="s">
+        <v>608</v>
+      </c>
+      <c r="D245" s="10" t="s">
+        <v>609</v>
+      </c>
+      <c r="E245" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" s="1"/>
+      <c r="B246" s="10"/>
+      <c r="C246" s="10" t="s">
+        <v>610</v>
+      </c>
+      <c r="D246" s="10" t="s">
+        <v>611</v>
+      </c>
+      <c r="E246" s="10" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" s="1"/>
+      <c r="B247" s="10"/>
+      <c r="C247" s="10" t="s">
+        <v>613</v>
+      </c>
+      <c r="D247" s="10" t="s">
+        <v>614</v>
+      </c>
+      <c r="E247" s="10" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" s="1"/>
+      <c r="B248" s="10"/>
+      <c r="C248" s="10" t="s">
+        <v>616</v>
+      </c>
+      <c r="D248" s="10" t="s">
+        <v>617</v>
+      </c>
+      <c r="E248" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" s="1"/>
+      <c r="B249" s="10"/>
+      <c r="C249" s="10" t="s">
+        <v>618</v>
+      </c>
+      <c r="D249" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="E249" s="10" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" s="1"/>
+      <c r="B250" s="10"/>
+      <c r="C250" s="10" t="s">
+        <v>621</v>
+      </c>
+      <c r="D250" s="10" t="s">
+        <v>622</v>
+      </c>
+      <c r="E250" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" s="1"/>
+      <c r="B251" s="10"/>
+      <c r="C251" s="10" t="s">
+        <v>623</v>
+      </c>
+      <c r="D251" s="10" t="s">
+        <v>624</v>
+      </c>
+      <c r="E251" s="10" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" s="1"/>
+      <c r="B252" s="10"/>
+      <c r="C252" s="10" t="s">
+        <v>626</v>
+      </c>
+      <c r="D252" s="10" t="s">
+        <v>627</v>
+      </c>
+      <c r="E252" s="10" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" s="1"/>
+      <c r="B253" s="10"/>
+      <c r="C253" s="10" t="s">
+        <v>629</v>
+      </c>
+      <c r="D253" s="10" t="s">
+        <v>630</v>
+      </c>
+      <c r="E253" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" s="1"/>
+      <c r="B254" s="10"/>
+      <c r="C254" s="10" t="s">
+        <v>631</v>
+      </c>
+      <c r="D254" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="E254" s="10" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" s="1"/>
+      <c r="B255" s="10"/>
+      <c r="C255" s="10" t="s">
+        <v>634</v>
+      </c>
+      <c r="D255" s="10" t="s">
+        <v>635</v>
+      </c>
+      <c r="E255" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" s="1"/>
+      <c r="B256" s="10"/>
+      <c r="C256" s="10" t="s">
+        <v>636</v>
+      </c>
+      <c r="D256" s="10" t="s">
+        <v>637</v>
+      </c>
+      <c r="E256" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" s="1"/>
+      <c r="B257" s="10"/>
+      <c r="C257" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="D257" s="10" t="s">
+        <v>639</v>
+      </c>
+      <c r="E257" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" s="1"/>
+      <c r="B258" s="10"/>
+      <c r="C258" s="10" t="s">
+        <v>640</v>
+      </c>
+      <c r="D258" s="10" t="s">
+        <v>641</v>
+      </c>
+      <c r="E258" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" s="1"/>
+      <c r="B259" s="10"/>
+      <c r="C259" s="10" t="s">
+        <v>642</v>
+      </c>
+      <c r="D259" s="10" t="s">
+        <v>643</v>
+      </c>
+      <c r="E259" s="10" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" s="1"/>
+      <c r="B260" s="10"/>
+      <c r="C260" s="10" t="s">
+        <v>645</v>
+      </c>
+      <c r="D260" s="10" t="s">
+        <v>646</v>
+      </c>
+      <c r="E260" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" s="1"/>
+      <c r="B261" s="10"/>
+      <c r="C261" s="10" t="s">
+        <v>647</v>
+      </c>
+      <c r="D261" s="10" t="s">
+        <v>648</v>
+      </c>
+      <c r="E261" s="10" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" s="1"/>
+      <c r="B262" s="10"/>
+      <c r="C262" s="10" t="s">
+        <v>650</v>
+      </c>
+      <c r="D262" s="10" t="s">
+        <v>651</v>
+      </c>
+      <c r="E262" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" s="1"/>
+      <c r="B263" s="10"/>
+      <c r="C263" s="10" t="s">
+        <v>652</v>
+      </c>
+      <c r="D263" s="10" t="s">
+        <v>653</v>
+      </c>
+      <c r="E263" s="10" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" s="1"/>
+      <c r="B264" s="10"/>
+      <c r="C264" s="10" t="s">
+        <v>655</v>
+      </c>
+      <c r="D264" s="10" t="s">
+        <v>656</v>
+      </c>
+      <c r="E264" s="10" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" s="1"/>
+      <c r="B265" s="10"/>
+      <c r="C265" s="10" t="s">
+        <v>658</v>
+      </c>
+      <c r="D265" s="10" t="s">
+        <v>659</v>
+      </c>
+      <c r="E265" s="10" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" s="1"/>
+      <c r="B266" s="10"/>
+      <c r="C266" s="10" t="s">
+        <v>661</v>
+      </c>
+      <c r="D266" s="10" t="s">
+        <v>662</v>
+      </c>
+      <c r="E266" s="10" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" s="1"/>
+      <c r="B267" s="10"/>
+      <c r="C267" s="10" t="s">
+        <v>664</v>
+      </c>
+      <c r="D267" s="10" t="s">
+        <v>665</v>
+      </c>
+      <c r="E267" s="10" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" s="1"/>
+      <c r="B268" s="10"/>
+      <c r="C268" s="10" t="s">
+        <v>667</v>
+      </c>
+      <c r="D268" s="10" t="s">
+        <v>668</v>
+      </c>
+      <c r="E268" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" s="1"/>
+      <c r="B269" s="10"/>
+      <c r="C269" s="10" t="s">
+        <v>669</v>
+      </c>
+      <c r="D269" s="10" t="s">
+        <v>670</v>
+      </c>
+      <c r="E269" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" s="1"/>
+      <c r="B270" s="10"/>
+      <c r="C270" s="10" t="s">
+        <v>671</v>
+      </c>
+      <c r="D270" s="10" t="s">
+        <v>672</v>
+      </c>
+      <c r="E270" s="10" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" s="1"/>
+      <c r="B271" s="10"/>
+      <c r="C271" s="10" t="s">
+        <v>674</v>
+      </c>
+      <c r="D271" s="10" t="s">
+        <v>675</v>
+      </c>
+      <c r="E271" s="10" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" s="1"/>
+      <c r="B272" s="10"/>
+      <c r="C272" s="10" t="s">
+        <v>677</v>
+      </c>
+      <c r="D272" s="10" t="s">
+        <v>678</v>
+      </c>
+      <c r="E272" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273" s="1"/>
+      <c r="B273" s="10"/>
+      <c r="C273" s="10" t="s">
+        <v>679</v>
+      </c>
+      <c r="D273" s="10" t="s">
+        <v>680</v>
+      </c>
+      <c r="E273" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274" s="1"/>
+      <c r="B274" s="10"/>
+      <c r="C274" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="D274" s="10" t="s">
+        <v>682</v>
+      </c>
+      <c r="E274" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275" s="1"/>
+      <c r="B275" s="10"/>
+      <c r="C275" s="10" t="s">
+        <v>683</v>
+      </c>
+      <c r="D275" s="10" t="s">
+        <v>684</v>
+      </c>
+      <c r="E275" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276" s="1"/>
+      <c r="B276" s="10"/>
+      <c r="C276" s="10" t="s">
+        <v>685</v>
+      </c>
+      <c r="D276" s="10" t="s">
+        <v>686</v>
+      </c>
+      <c r="E276" s="10" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277" s="1"/>
+      <c r="B277" s="10"/>
+      <c r="C277" s="10" t="s">
+        <v>688</v>
+      </c>
+      <c r="D277" s="10" t="s">
+        <v>689</v>
+      </c>
+      <c r="E277" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278" s="1"/>
+      <c r="B278" s="10"/>
+      <c r="C278" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="D278" s="10" t="s">
+        <v>690</v>
+      </c>
+      <c r="E278" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279" s="1"/>
+      <c r="B279" s="10"/>
+      <c r="C279" s="10" t="s">
+        <v>691</v>
+      </c>
+      <c r="D279" s="10" t="s">
+        <v>692</v>
+      </c>
+      <c r="E279" s="10" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280" s="1"/>
+      <c r="B280" s="10"/>
+      <c r="C280" s="10" t="s">
+        <v>694</v>
+      </c>
+      <c r="D280" s="10" t="s">
+        <v>695</v>
+      </c>
+      <c r="E280" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281" s="1"/>
+      <c r="B281" s="10"/>
+      <c r="C281" s="10" t="s">
+        <v>696</v>
+      </c>
+      <c r="D281" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="E281" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282" s="1"/>
+      <c r="B282" s="10"/>
+      <c r="C282" s="10" t="s">
+        <v>698</v>
+      </c>
+      <c r="D282" s="10" t="s">
+        <v>699</v>
+      </c>
+      <c r="E282" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" s="1"/>
+      <c r="B283" s="10"/>
+      <c r="C283" s="10" t="s">
+        <v>700</v>
+      </c>
+      <c r="D283" s="10" t="s">
+        <v>701</v>
+      </c>
+      <c r="E283" s="10" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" s="1"/>
+      <c r="B284" s="10"/>
+      <c r="C284" s="10" t="s">
+        <v>703</v>
+      </c>
+      <c r="D284" s="10" t="s">
+        <v>704</v>
+      </c>
+      <c r="E284" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" s="1"/>
+      <c r="B285" s="10"/>
+      <c r="C285" s="10" t="s">
+        <v>705</v>
+      </c>
+      <c r="D285" s="10" t="s">
+        <v>706</v>
+      </c>
+      <c r="E285" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" s="1"/>
+      <c r="B286" s="10"/>
+      <c r="C286" s="10" t="s">
+        <v>707</v>
+      </c>
+      <c r="D286" s="10" t="s">
+        <v>708</v>
+      </c>
+      <c r="E286" s="10" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" s="1"/>
+      <c r="B287" s="10"/>
+      <c r="C287" s="10" t="s">
+        <v>710</v>
+      </c>
+      <c r="D287" s="10" t="s">
+        <v>711</v>
+      </c>
+      <c r="E287" s="10" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288" s="1"/>
+      <c r="B288" s="10"/>
+      <c r="C288" s="10" t="s">
+        <v>713</v>
+      </c>
+      <c r="D288" s="10" t="s">
+        <v>714</v>
+      </c>
+      <c r="E288" s="10" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" s="1"/>
+      <c r="B289" s="10"/>
+      <c r="C289" s="10" t="s">
+        <v>716</v>
+      </c>
+      <c r="D289" s="10" t="s">
+        <v>717</v>
+      </c>
+      <c r="E289" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" s="1"/>
+      <c r="B290" s="10"/>
+      <c r="C290" s="10" t="s">
+        <v>718</v>
+      </c>
+      <c r="D290" s="10" t="s">
+        <v>719</v>
+      </c>
+      <c r="E290" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" s="1"/>
+      <c r="B291" s="10"/>
+      <c r="C291" s="10" t="s">
+        <v>720</v>
+      </c>
+      <c r="D291" s="10" t="s">
+        <v>721</v>
+      </c>
+      <c r="E291" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" s="1"/>
+      <c r="B292" s="10"/>
+      <c r="C292" s="10" t="s">
+        <v>722</v>
+      </c>
+      <c r="D292" s="10" t="s">
+        <v>723</v>
+      </c>
+      <c r="E292" s="10" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="1"/>
+      <c r="B293" s="10"/>
+      <c r="C293" s="10" t="s">
+        <v>725</v>
+      </c>
+      <c r="D293" s="10" t="s">
+        <v>726</v>
+      </c>
+      <c r="E293" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="1"/>
+      <c r="B294" s="10"/>
+      <c r="C294" s="10" t="s">
+        <v>727</v>
+      </c>
+      <c r="D294" s="10" t="s">
+        <v>728</v>
+      </c>
+      <c r="E294" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="1"/>
+      <c r="B295" s="10"/>
+      <c r="C295" s="10" t="s">
+        <v>729</v>
+      </c>
+      <c r="D295" s="10" t="s">
+        <v>730</v>
+      </c>
+      <c r="E295" s="10" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="1"/>
+      <c r="B296" s="10"/>
+      <c r="C296" s="10" t="s">
+        <v>732</v>
+      </c>
+      <c r="D296" s="10" t="s">
+        <v>733</v>
+      </c>
+      <c r="E296" s="10" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="1"/>
+      <c r="B297" s="10"/>
+      <c r="C297" s="10" t="s">
+        <v>735</v>
+      </c>
+      <c r="D297" s="10" t="s">
+        <v>736</v>
+      </c>
+      <c r="E297" s="10" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" s="1"/>
+      <c r="B298" s="10"/>
+      <c r="C298" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="D298" s="10" t="s">
+        <v>739</v>
+      </c>
+      <c r="E298" s="10" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" s="1"/>
+      <c r="B299" s="10"/>
+      <c r="C299" s="10" t="s">
+        <v>741</v>
+      </c>
+      <c r="D299" s="10" t="s">
+        <v>742</v>
+      </c>
+      <c r="E299" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="1"/>
+      <c r="B300" s="10"/>
+      <c r="C300" s="10" t="s">
+        <v>743</v>
+      </c>
+      <c r="D300" s="10" t="s">
+        <v>744</v>
+      </c>
+      <c r="E300" s="10" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" s="1"/>
+      <c r="B301" s="10"/>
+      <c r="C301" s="10" t="s">
+        <v>746</v>
+      </c>
+      <c r="D301" s="10" t="s">
+        <v>747</v>
+      </c>
+      <c r="E301" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" s="1"/>
+      <c r="B302" s="10"/>
+      <c r="C302" s="10" t="s">
+        <v>748</v>
+      </c>
+      <c r="D302" s="10" t="s">
+        <v>749</v>
+      </c>
+      <c r="E302" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="1"/>
+      <c r="B303" s="10"/>
+      <c r="C303" s="10" t="s">
+        <v>750</v>
+      </c>
+      <c r="D303" s="10" t="s">
+        <v>751</v>
+      </c>
+      <c r="E303" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="1"/>
+      <c r="B304" s="10"/>
+      <c r="C304" s="10" t="s">
+        <v>752</v>
+      </c>
+      <c r="D304" s="10" t="s">
+        <v>753</v>
+      </c>
+      <c r="E304" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" s="1"/>
+      <c r="B305" s="10"/>
+      <c r="C305" s="10" t="s">
+        <v>754</v>
+      </c>
+      <c r="D305" s="10" t="s">
+        <v>755</v>
+      </c>
+      <c r="E305" s="10" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="1"/>
+      <c r="B306" s="10"/>
+      <c r="C306" s="10" t="s">
+        <v>757</v>
+      </c>
+      <c r="D306" s="10" t="s">
+        <v>758</v>
+      </c>
+      <c r="E306" s="10" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="1"/>
+      <c r="B307" s="10"/>
+      <c r="C307" s="10" t="s">
+        <v>760</v>
+      </c>
+      <c r="D307" s="10" t="s">
+        <v>761</v>
+      </c>
+      <c r="E307" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" s="1"/>
+      <c r="B308" s="10"/>
+      <c r="C308" s="10" t="s">
+        <v>762</v>
+      </c>
+      <c r="D308" s="10" t="s">
+        <v>763</v>
+      </c>
+      <c r="E308" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="1"/>
+      <c r="B309" s="10"/>
+      <c r="C309" s="10" t="s">
+        <v>764</v>
+      </c>
+      <c r="D309" s="10" t="s">
+        <v>765</v>
+      </c>
+      <c r="E309" s="10" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" s="1"/>
+      <c r="B310" s="10"/>
+      <c r="C310" s="10" t="s">
+        <v>767</v>
+      </c>
+      <c r="D310" s="10" t="s">
+        <v>768</v>
+      </c>
+      <c r="E310" s="10" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="1"/>
+      <c r="B311" s="10"/>
+      <c r="C311" s="10" t="s">
+        <v>770</v>
+      </c>
+      <c r="D311" s="10" t="s">
+        <v>771</v>
+      </c>
+      <c r="E311" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="1"/>
+      <c r="B312" s="10"/>
+      <c r="C312" s="10" t="s">
+        <v>772</v>
+      </c>
+      <c r="D312" s="10" t="s">
+        <v>773</v>
+      </c>
+      <c r="E312" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" s="1"/>
+      <c r="B313" s="10"/>
+      <c r="C313" s="10" t="s">
+        <v>774</v>
+      </c>
+      <c r="D313" s="10" t="s">
+        <v>775</v>
+      </c>
+      <c r="E313" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="1"/>
+      <c r="B314" s="10"/>
+      <c r="C314" s="10" t="s">
+        <v>776</v>
+      </c>
+      <c r="D314" s="10" t="s">
+        <v>777</v>
+      </c>
+      <c r="E314" s="10" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="1"/>
+      <c r="B315" s="10"/>
+      <c r="C315" s="10" t="s">
+        <v>779</v>
+      </c>
+      <c r="D315" s="10" t="s">
+        <v>780</v>
+      </c>
+      <c r="E315" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="1"/>
+      <c r="B316" s="10"/>
+      <c r="C316" s="10" t="s">
+        <v>781</v>
+      </c>
+      <c r="D316" s="10" t="s">
+        <v>782</v>
+      </c>
+      <c r="E316" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" s="1"/>
+      <c r="B317" s="10"/>
+      <c r="C317" s="10" t="s">
+        <v>783</v>
+      </c>
+      <c r="D317" s="10" t="s">
+        <v>784</v>
+      </c>
+      <c r="E317" s="10" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="1"/>
+      <c r="B318" s="10"/>
+      <c r="C318" s="10" t="s">
+        <v>786</v>
+      </c>
+      <c r="D318" s="10" t="s">
+        <v>787</v>
+      </c>
+      <c r="E318" s="10" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="1"/>
+      <c r="B319" s="10"/>
+      <c r="C319" s="10" t="s">
+        <v>789</v>
+      </c>
+      <c r="D319" s="10" t="s">
+        <v>790</v>
+      </c>
+      <c r="E319" s="10" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="1"/>
+      <c r="B320" s="10"/>
+      <c r="C320" s="10" t="s">
+        <v>792</v>
+      </c>
+      <c r="D320" s="10" t="s">
+        <v>793</v>
+      </c>
+      <c r="E320" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" s="1"/>
+      <c r="B321" s="10"/>
+      <c r="C321" s="10" t="s">
+        <v>794</v>
+      </c>
+      <c r="D321" s="10" t="s">
+        <v>795</v>
+      </c>
+      <c r="E321" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" s="1"/>
+      <c r="B322" s="10"/>
+      <c r="C322" s="10" t="s">
+        <v>796</v>
+      </c>
+      <c r="D322" s="10" t="s">
+        <v>797</v>
+      </c>
+      <c r="E322" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" s="1"/>
+      <c r="B323" s="10"/>
+      <c r="C323" s="10" t="s">
+        <v>798</v>
+      </c>
+      <c r="D323" s="10" t="s">
+        <v>799</v>
+      </c>
+      <c r="E323" s="10" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="B324" s="10"/>
+      <c r="C324" s="10"/>
+      <c r="D324" s="10"/>
+      <c r="E324" s="10"/>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="C325" s="10" t="s">
+        <v>802</v>
+      </c>
+      <c r="D325" s="10" t="s">
+        <v>803</v>
+      </c>
+      <c r="E325" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326" s="1"/>
+      <c r="C326" s="10" t="s">
+        <v>805</v>
+      </c>
+      <c r="D326" s="10" t="s">
+        <v>806</v>
+      </c>
+      <c r="E326" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" s="1"/>
+      <c r="C327" s="10" t="s">
+        <v>808</v>
+      </c>
+      <c r="D327" s="10" t="s">
+        <v>809</v>
+      </c>
+      <c r="E327" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="C328" s="10"/>
+      <c r="D328" s="10"/>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="C329" s="10"/>
+      <c r="D329" s="10"/>
+    </row>
+    <row r="330" spans="1:5">
+      <c r="C330" s="10"/>
+      <c r="D330" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="28">
     <mergeCell ref="A2:A31"/>
     <mergeCell ref="A33:A83"/>
     <mergeCell ref="A85:A109"/>
+    <mergeCell ref="A111:A170"/>
+    <mergeCell ref="A172:A205"/>
+    <mergeCell ref="A207:A323"/>
+    <mergeCell ref="A325:A327"/>
     <mergeCell ref="B2:B6"/>
     <mergeCell ref="B7:B12"/>
     <mergeCell ref="B13:B15"/>
@@ -3213,6 +7756,8 @@
     <mergeCell ref="B95:B98"/>
     <mergeCell ref="B99:B104"/>
     <mergeCell ref="B107:B109"/>
+    <mergeCell ref="B172:B187"/>
+    <mergeCell ref="B188:B205"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D63" r:id="rId1" display="https://gitcode.com/Ascend/msmodeling"/>
@@ -3222,6 +7767,13 @@
     <hyperlink ref="D53" r:id="rId5" display="https://gitcode.com/Ascend/mstt"/>
     <hyperlink ref="D54" r:id="rId6" display="https://gitcode.com/Ascend/msit"/>
     <hyperlink ref="D55" r:id="rId7" display="https://gitcode.com/Ascend/msot"/>
+    <hyperlink ref="D73" r:id="rId8" display="https://gitcode.com/Ascend/mskl"/>
+    <hyperlink ref="D74" r:id="rId9" display="https://gitcode.com/Ascend/msoptuner" tooltip="https://gitcode.com/Ascend/msoptuner"/>
+    <hyperlink ref="D75" r:id="rId10" display="https://gitcode.com/Ascend/msopgen" tooltip="https://gitcode.com/Ascend/msopgen"/>
+    <hyperlink ref="D76" r:id="rId11" display="https://gitcode.com/Ascend/mskpp"/>
+    <hyperlink ref="C325" r:id="rId12" display="openlibing-web" tooltip="https://gitcode.com/openlibing/openlibing-web"/>
+    <hyperlink ref="C326" r:id="rId13" display="openlibing-pytest-executor" tooltip="https://gitcode.com/openlibing/openlibing-pytest-executor"/>
+    <hyperlink ref="C327" r:id="rId14" display="openlibing-platform-release" tooltip="https://gitcode.com/openlibing/openlibing-platform-release"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3232,9 +7784,54 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="10.6666666666667" customWidth="1"/>
+    <col min="2" max="2" width="17.7777777777778" customWidth="1"/>
+    <col min="3" max="3" width="56.5555555555556" customWidth="1"/>
+    <col min="4" max="4" width="11.3333333333333" customWidth="1"/>
+    <col min="5" max="5" width="14.8888888888889" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>811</v>
+      </c>
+      <c r="B1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C1" t="s">
+        <v>813</v>
+      </c>
+      <c r="D1" t="s">
+        <v>814</v>
+      </c>
+      <c r="E1" t="s">
+        <v>815</v>
+      </c>
+      <c r="F1" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" t="s">
+        <v>817</v>
+      </c>
+      <c r="C2" t="s">
+        <v>818</v>
+      </c>
+      <c r="D2" t="s">
+        <v>819</v>
+      </c>
+      <c r="F2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/社区代码仓列表.xlsx
+++ b/社区代码仓列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25860" windowHeight="12851"/>
+    <workbookView windowWidth="26111" windowHeight="12851" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="850">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="878">
   <si>
     <t>社区名</t>
   </si>
@@ -2579,6 +2579,90 @@
   </si>
   <si>
     <t>https://github.com/TTY-flag/community_reports/blob/main/Ascend/MindIE/MindIE-LLM/scan-results/details/VULN-RH-008.md</t>
+  </si>
+  <si>
+    <t>开发者误用了 &amp;&amp; 运算符进行条件判断，导致当 ZooKeeper 读取成功时，数据验证逻辑被完全跳过。这使得从 ZooKeeper 获取的任何数据（无论是正常数据还是恶意篡改的数据）在成功读取后都不会经过验证直接被使用。</t>
+  </si>
+  <si>
+    <t>https://github.com/TTY-flag/community_reports/blob/main/openeuler/ubs-io/scan-results/details/CLUSTER-INPUTVAL-002.md</t>
+  </si>
+  <si>
+    <t>使用 ZOO_OPEN_ACL_UNSAFE，任何客户端可读写</t>
+  </si>
+  <si>
+    <t>https://github.com/TTY-flag/community_reports/blob/main/openeuler/ubs-io/scan-results/details/CLUSTER-TRUSTBOUND-005.md</t>
+  </si>
+  <si>
+    <t>BdmUpdate() 函数绕过了 IsDiskFile() 块设备验证检查，允许将任意文件路径添加为磁盘设备。相比之下，BdmStart() 函数正确地在调用 BdmDevicesCreate() 前执行了 IsDiskFile() 检查以确保路径是合法的块设备</t>
+  </si>
+  <si>
+    <t>https://github.com/TTY-flag/community_reports/blob/main/openeuler/ubs-io/scan-results/details/DISK-008.md</t>
+  </si>
+  <si>
+    <t>RDMA 网络响应中的地址字段 (respMsg.address) 被直接通过 reinterpret_cast 转换为指针并使用，没有任何验证。恶意对端可以提供任意地址值</t>
+  </si>
+  <si>
+    <t>https://github.com/TTY-flag/community_reports/blob/main/openeuler/ubs-io/scan-results/details/NET-002.md</t>
+  </si>
+  <si>
+    <t>在SDK模块中，多个核心函数在日志输出中直接暴露用户提供的key参数</t>
+  </si>
+  <si>
+    <t>红线</t>
+  </si>
+  <si>
+    <t>https://github.com/TTY-flag/community_reports/blob/main/openeuler/ubs-io/scan-results/details/SDK-IL-001.md</t>
+  </si>
+  <si>
+    <t>https://github.com/TTY-flag/community_reports/blob/main/openeuler/ubs-io/scan-results/details/SDK-IL-003.md</t>
+  </si>
+  <si>
+    <t>验证不一致，存在路径遍历漏洞</t>
+  </si>
+  <si>
+    <t>https://github.com/TTY-flag/community_reports/blob/main/openeuler/ubs-io/scan-results/details/VUL-UNDERFS-008.md</t>
+  </si>
+  <si>
+    <t>static inline void CloseTlsLib() 存在uaf漏洞</t>
+  </si>
+  <si>
+    <t>https://github.com/TTY-flag/community_reports/blob/main/openeuler/ubs-io/scan-results/details/VULN-COMMON-002.md</t>
+  </si>
+  <si>
+    <t>EndWith 函数边界检查缺失</t>
+  </si>
+  <si>
+    <t>提示</t>
+  </si>
+  <si>
+    <t>貌似没地方调用</t>
+  </si>
+  <si>
+    <t>https://github.com/TTY-flag/community_reports/blob/main/openeuler/ubs-io/scan-results/details/VULN-COMMON-006.md</t>
+  </si>
+  <si>
+    <t>CheckPath不安全的路径验证函数</t>
+  </si>
+  <si>
+    <t>https://github.com/TTY-flag/community_reports/blob/main/openeuler/ubs-io/scan-results/details/VULN-IO-001.md</t>
+  </si>
+  <si>
+    <t>同问题VULN-IO-001</t>
+  </si>
+  <si>
+    <t>https://github.com/TTY-flag/community_reports/blob/main/openeuler/ubs-io/scan-results/details/VULN-IO-011.md</t>
+  </si>
+  <si>
+    <t>https://github.com/TTY-flag/community_reports/blob/main/openeuler/ubs-io/scan-results/details/VULN-IO-012.md</t>
+  </si>
+  <si>
+    <t>https://github.com/TTY-flag/community_reports/blob/main/openeuler/ubs-io/scan-results/details/VULN-IO-015.md</t>
+  </si>
+  <si>
+    <t>https://github.com/TTY-flag/community_reports/blob/main/openeuler/ubs-io/scan-results/details/VULN-IO-016.md</t>
+  </si>
+  <si>
+    <t>https://github.com/TTY-flag/community_reports/blob/main/openeuler/ubs-io/scan-results/details/VULN-IO-017.md</t>
   </si>
 </sst>
 </file>
@@ -3209,14 +3293,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
@@ -3588,10 +3672,10 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C2" t="s">
@@ -3605,8 +3689,8 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="2"/>
-      <c r="B3" s="3"/>
+      <c r="A3" s="3"/>
+      <c r="B3" s="4"/>
       <c r="C3" t="s">
         <v>14</v>
       </c>
@@ -3621,8 +3705,8 @@
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="2"/>
-      <c r="B4" s="3"/>
+      <c r="A4" s="3"/>
+      <c r="B4" s="4"/>
       <c r="C4" t="s">
         <v>17</v>
       </c>
@@ -3637,8 +3721,8 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="2"/>
-      <c r="B5" s="3"/>
+      <c r="A5" s="3"/>
+      <c r="B5" s="4"/>
       <c r="C5" t="s">
         <v>19</v>
       </c>
@@ -3653,12 +3737,12 @@
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="2"/>
-      <c r="B6" s="3"/>
+      <c r="A6" s="3"/>
+      <c r="B6" s="4"/>
       <c r="C6" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E6" t="s">
@@ -3666,8 +3750,8 @@
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="2"/>
-      <c r="B7" s="3" t="s">
+      <c r="A7" s="3"/>
+      <c r="B7" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C7" t="s">
@@ -3681,8 +3765,8 @@
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="2"/>
-      <c r="B8" s="3"/>
+      <c r="A8" s="3"/>
+      <c r="B8" s="4"/>
       <c r="C8" t="s">
         <v>26</v>
       </c>
@@ -3697,8 +3781,8 @@
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="2"/>
-      <c r="B9" s="3"/>
+      <c r="A9" s="3"/>
+      <c r="B9" s="4"/>
       <c r="C9" t="s">
         <v>29</v>
       </c>
@@ -3713,8 +3797,8 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="2"/>
-      <c r="B10" s="3"/>
+      <c r="A10" s="3"/>
+      <c r="B10" s="4"/>
       <c r="C10" t="s">
         <v>31</v>
       </c>
@@ -3729,8 +3813,8 @@
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="2"/>
-      <c r="B11" s="3"/>
+      <c r="A11" s="3"/>
+      <c r="B11" s="4"/>
       <c r="C11" t="s">
         <v>33</v>
       </c>
@@ -3745,8 +3829,8 @@
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3"/>
+      <c r="A12" s="3"/>
+      <c r="B12" s="4"/>
       <c r="C12" t="s">
         <v>35</v>
       </c>
@@ -3761,8 +3845,8 @@
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="2"/>
-      <c r="B13" s="3" t="s">
+      <c r="A13" s="3"/>
+      <c r="B13" s="4" t="s">
         <v>38</v>
       </c>
       <c r="C13" t="s">
@@ -3779,8 +3863,8 @@
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="2"/>
-      <c r="B14" s="3"/>
+      <c r="A14" s="3"/>
+      <c r="B14" s="4"/>
       <c r="C14" t="s">
         <v>42</v>
       </c>
@@ -3792,8 +3876,8 @@
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="2"/>
-      <c r="B15" s="3"/>
+      <c r="A15" s="3"/>
+      <c r="B15" s="4"/>
       <c r="C15" t="s">
         <v>44</v>
       </c>
@@ -3805,8 +3889,8 @@
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="2"/>
-      <c r="B16" s="3" t="s">
+      <c r="A16" s="3"/>
+      <c r="B16" s="4" t="s">
         <v>47</v>
       </c>
       <c r="C16" t="s">
@@ -3823,8 +3907,8 @@
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="2"/>
-      <c r="B17" s="3"/>
+      <c r="A17" s="3"/>
+      <c r="B17" s="4"/>
       <c r="C17" t="s">
         <v>51</v>
       </c>
@@ -3839,8 +3923,8 @@
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="2"/>
-      <c r="B18" s="3" t="s">
+      <c r="A18" s="3"/>
+      <c r="B18" s="4" t="s">
         <v>53</v>
       </c>
       <c r="C18" t="s">
@@ -3854,8 +3938,8 @@
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="2"/>
-      <c r="B19" s="3"/>
+      <c r="A19" s="3"/>
+      <c r="B19" s="4"/>
       <c r="C19" t="s">
         <v>57</v>
       </c>
@@ -3867,8 +3951,8 @@
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="2"/>
-      <c r="B20" s="3" t="s">
+      <c r="A20" s="3"/>
+      <c r="B20" s="4" t="s">
         <v>60</v>
       </c>
       <c r="C20" t="s">
@@ -3885,8 +3969,8 @@
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="2"/>
-      <c r="B21" s="3"/>
+      <c r="A21" s="3"/>
+      <c r="B21" s="4"/>
       <c r="C21" t="s">
         <v>64</v>
       </c>
@@ -3898,8 +3982,8 @@
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="2"/>
-      <c r="B22" s="3"/>
+      <c r="A22" s="3"/>
+      <c r="B22" s="4"/>
       <c r="C22" t="s">
         <v>66</v>
       </c>
@@ -3911,14 +3995,14 @@
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="2"/>
-      <c r="B23" s="3" t="s">
+      <c r="A23" s="3"/>
+      <c r="B23" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C23" t="s">
         <v>69</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="2" t="s">
         <v>70</v>
       </c>
       <c r="E23" t="s">
@@ -3929,8 +4013,8 @@
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="2"/>
-      <c r="B24" s="3"/>
+      <c r="A24" s="3"/>
+      <c r="B24" s="4"/>
       <c r="C24" t="s">
         <v>71</v>
       </c>
@@ -3945,8 +4029,8 @@
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="2"/>
-      <c r="B25" s="3"/>
+      <c r="A25" s="3"/>
+      <c r="B25" s="4"/>
       <c r="C25" t="s">
         <v>73</v>
       </c>
@@ -3961,8 +4045,8 @@
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="2"/>
-      <c r="B26" s="3" t="s">
+      <c r="A26" s="3"/>
+      <c r="B26" s="4" t="s">
         <v>75</v>
       </c>
       <c r="C26" t="s">
@@ -3979,14 +4063,14 @@
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="2"/>
-      <c r="B27" s="3" t="s">
+      <c r="A27" s="3"/>
+      <c r="B27" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C27" t="s">
         <v>79</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="2" t="s">
         <v>80</v>
       </c>
       <c r="E27" t="s">
@@ -3997,8 +4081,8 @@
       </c>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="2"/>
-      <c r="B28" s="3" t="s">
+      <c r="A28" s="3"/>
+      <c r="B28" s="4" t="s">
         <v>82</v>
       </c>
       <c r="C28" t="s">
@@ -4012,12 +4096,12 @@
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="2"/>
-      <c r="B29" s="3"/>
+      <c r="A29" s="3"/>
+      <c r="B29" s="4"/>
       <c r="C29" t="s">
         <v>85</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="2" t="s">
         <v>86</v>
       </c>
       <c r="E29" t="s">
@@ -4028,14 +4112,14 @@
       </c>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="2"/>
-      <c r="B30" s="3" t="s">
+      <c r="A30" s="3"/>
+      <c r="B30" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C30" t="s">
         <v>88</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="2" t="s">
         <v>89</v>
       </c>
       <c r="E30" t="s">
@@ -4043,8 +4127,8 @@
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="2"/>
-      <c r="B31" s="3" t="s">
+      <c r="A31" s="3"/>
+      <c r="B31" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C31" t="s">
@@ -4061,13 +4145,13 @@
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="2"/>
+      <c r="A32" s="3"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="3" t="s">
         <v>93</v>
       </c>
       <c r="B33" s="7" t="s">
@@ -4081,7 +4165,7 @@
       </c>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="2"/>
+      <c r="A34" s="3"/>
       <c r="B34" s="7" t="s">
         <v>96</v>
       </c>
@@ -4093,7 +4177,7 @@
       </c>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="2"/>
+      <c r="A35" s="3"/>
       <c r="B35" s="7" t="s">
         <v>98</v>
       </c>
@@ -4105,7 +4189,7 @@
       </c>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="2"/>
+      <c r="A36" s="3"/>
       <c r="B36" s="7" t="s">
         <v>100</v>
       </c>
@@ -4123,7 +4207,7 @@
       </c>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="2"/>
+      <c r="A37" s="3"/>
       <c r="B37" s="7"/>
       <c r="C37" s="6" t="s">
         <v>103</v>
@@ -4139,7 +4223,7 @@
       </c>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="2"/>
+      <c r="A38" s="3"/>
       <c r="B38" s="7"/>
       <c r="C38" s="6" t="s">
         <v>105</v>
@@ -4155,7 +4239,7 @@
       </c>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="2"/>
+      <c r="A39" s="3"/>
       <c r="B39" s="7"/>
       <c r="C39" s="6" t="s">
         <v>107</v>
@@ -4171,7 +4255,7 @@
       </c>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="2"/>
+      <c r="A40" s="3"/>
       <c r="B40" s="7" t="s">
         <v>109</v>
       </c>
@@ -4186,7 +4270,7 @@
       </c>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="2"/>
+      <c r="A41" s="3"/>
       <c r="B41" s="7"/>
       <c r="C41" s="6" t="s">
         <v>112</v>
@@ -4199,7 +4283,7 @@
       </c>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="2"/>
+      <c r="A42" s="3"/>
       <c r="B42" s="7"/>
       <c r="C42" s="6" t="s">
         <v>114</v>
@@ -4212,7 +4296,7 @@
       </c>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="2"/>
+      <c r="A43" s="3"/>
       <c r="B43" s="7"/>
       <c r="C43" s="6" t="s">
         <v>116</v>
@@ -4225,7 +4309,7 @@
       </c>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="2"/>
+      <c r="A44" s="3"/>
       <c r="B44" s="7"/>
       <c r="C44" s="6" t="s">
         <v>118</v>
@@ -4238,7 +4322,7 @@
       </c>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="2"/>
+      <c r="A45" s="3"/>
       <c r="B45" s="7" t="s">
         <v>120</v>
       </c>
@@ -4253,7 +4337,7 @@
       </c>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="2"/>
+      <c r="A46" s="3"/>
       <c r="B46" s="7"/>
       <c r="C46" s="6" t="s">
         <v>123</v>
@@ -4266,7 +4350,7 @@
       </c>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="2"/>
+      <c r="A47" s="3"/>
       <c r="B47" s="7"/>
       <c r="C47" s="6" t="s">
         <v>125</v>
@@ -4279,7 +4363,7 @@
       </c>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="2"/>
+      <c r="A48" s="3"/>
       <c r="B48" s="7"/>
       <c r="C48" s="6" t="s">
         <v>127</v>
@@ -4292,7 +4376,7 @@
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="2"/>
+      <c r="A49" s="3"/>
       <c r="B49" s="7"/>
       <c r="C49" s="6" t="s">
         <v>129</v>
@@ -4305,7 +4389,7 @@
       </c>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="2"/>
+      <c r="A50" s="3"/>
       <c r="B50" s="7"/>
       <c r="C50" s="6" t="s">
         <v>131</v>
@@ -4318,7 +4402,7 @@
       </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="2"/>
+      <c r="A51" s="3"/>
       <c r="B51" s="7"/>
       <c r="C51" s="6" t="s">
         <v>133</v>
@@ -4331,7 +4415,7 @@
       </c>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="2"/>
+      <c r="A52" s="3"/>
       <c r="B52" s="7"/>
       <c r="C52" s="6" t="s">
         <v>135</v>
@@ -4344,7 +4428,7 @@
       </c>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="2"/>
+      <c r="A53" s="3"/>
       <c r="B53" s="7" t="s">
         <v>137</v>
       </c>
@@ -4359,7 +4443,7 @@
       </c>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="2"/>
+      <c r="A54" s="3"/>
       <c r="B54" s="7"/>
       <c r="C54" s="6" t="s">
         <v>140</v>
@@ -4372,7 +4456,7 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="2"/>
+      <c r="A55" s="3"/>
       <c r="B55" s="7"/>
       <c r="C55" s="6" t="s">
         <v>142</v>
@@ -4385,7 +4469,7 @@
       </c>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" s="2"/>
+      <c r="A56" s="3"/>
       <c r="B56" s="7"/>
       <c r="C56" s="8" t="s">
         <v>144</v>
@@ -4398,7 +4482,7 @@
       </c>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="2"/>
+      <c r="A57" s="3"/>
       <c r="B57" s="7"/>
       <c r="C57" s="8" t="s">
         <v>146</v>
@@ -4411,7 +4495,7 @@
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="2"/>
+      <c r="A58" s="3"/>
       <c r="B58" s="7"/>
       <c r="C58" s="8" t="s">
         <v>148</v>
@@ -4424,7 +4508,7 @@
       </c>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="2"/>
+      <c r="A59" s="3"/>
       <c r="B59" s="7"/>
       <c r="C59" s="8" t="s">
         <v>150</v>
@@ -4437,7 +4521,7 @@
       </c>
     </row>
     <row r="60" spans="1:7">
-      <c r="A60" s="2"/>
+      <c r="A60" s="3"/>
       <c r="B60" s="7"/>
       <c r="C60" s="8" t="s">
         <v>152</v>
@@ -4450,7 +4534,7 @@
       </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="2"/>
+      <c r="A61" s="3"/>
       <c r="B61" s="7"/>
       <c r="C61" s="8" t="s">
         <v>154</v>
@@ -4463,7 +4547,7 @@
       </c>
     </row>
     <row r="62" spans="1:7">
-      <c r="A62" s="2"/>
+      <c r="A62" s="3"/>
       <c r="B62" s="7"/>
       <c r="C62" s="8" t="s">
         <v>156</v>
@@ -4476,7 +4560,7 @@
       </c>
     </row>
     <row r="63" spans="1:7">
-      <c r="A63" s="2"/>
+      <c r="A63" s="3"/>
       <c r="B63" s="7"/>
       <c r="C63" s="8" t="s">
         <v>158</v>
@@ -4489,7 +4573,7 @@
       </c>
     </row>
     <row r="64" spans="1:7">
-      <c r="A64" s="2"/>
+      <c r="A64" s="3"/>
       <c r="B64" s="7"/>
       <c r="C64" s="8" t="s">
         <v>160</v>
@@ -4502,7 +4586,7 @@
       </c>
     </row>
     <row r="65" spans="1:7">
-      <c r="A65" s="2"/>
+      <c r="A65" s="3"/>
       <c r="B65" s="7"/>
       <c r="C65" s="8" t="s">
         <v>162</v>
@@ -4515,7 +4599,7 @@
       </c>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="2"/>
+      <c r="A66" s="3"/>
       <c r="B66" s="7"/>
       <c r="C66" s="8" t="s">
         <v>164</v>
@@ -4528,12 +4612,12 @@
       </c>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="2"/>
+      <c r="A67" s="3"/>
       <c r="B67" s="7"/>
       <c r="C67" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="D67" s="2" t="s">
         <v>167</v>
       </c>
       <c r="G67">
@@ -4541,7 +4625,7 @@
       </c>
     </row>
     <row r="68" spans="1:7">
-      <c r="A68" s="2"/>
+      <c r="A68" s="3"/>
       <c r="B68" s="7"/>
       <c r="C68" s="8" t="s">
         <v>168</v>
@@ -4554,7 +4638,7 @@
       </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="2"/>
+      <c r="A69" s="3"/>
       <c r="B69" s="7"/>
       <c r="C69" s="8" t="s">
         <v>170</v>
@@ -4567,7 +4651,7 @@
       </c>
     </row>
     <row r="70" spans="1:7">
-      <c r="A70" s="2"/>
+      <c r="A70" s="3"/>
       <c r="B70" s="7"/>
       <c r="C70" s="8" t="s">
         <v>172</v>
@@ -4580,7 +4664,7 @@
       </c>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="2"/>
+      <c r="A71" s="3"/>
       <c r="B71" s="7"/>
       <c r="C71" s="8" t="s">
         <v>174</v>
@@ -4593,7 +4677,7 @@
       </c>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="2"/>
+      <c r="A72" s="3"/>
       <c r="B72" s="7"/>
       <c r="C72" s="8" t="s">
         <v>176</v>
@@ -4606,7 +4690,7 @@
       </c>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="2"/>
+      <c r="A73" s="3"/>
       <c r="B73" s="7"/>
       <c r="C73" s="8" t="s">
         <v>178</v>
@@ -4619,7 +4703,7 @@
       </c>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="2"/>
+      <c r="A74" s="3"/>
       <c r="B74" s="7"/>
       <c r="C74" s="8" t="s">
         <v>180</v>
@@ -4632,12 +4716,12 @@
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="2"/>
+      <c r="A75" s="3"/>
       <c r="B75" s="7"/>
       <c r="C75" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="D75" s="4" t="s">
+      <c r="D75" s="2" t="s">
         <v>183</v>
       </c>
       <c r="G75">
@@ -4645,12 +4729,12 @@
       </c>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="2"/>
+      <c r="A76" s="3"/>
       <c r="B76" s="7"/>
       <c r="C76" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="D76" s="4" t="s">
+      <c r="D76" s="2" t="s">
         <v>185</v>
       </c>
       <c r="G76">
@@ -4658,7 +4742,7 @@
       </c>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="2"/>
+      <c r="A77" s="3"/>
       <c r="B77" s="7"/>
       <c r="C77" s="8" t="s">
         <v>186</v>
@@ -4671,14 +4755,14 @@
       </c>
     </row>
     <row r="78" spans="1:7">
-      <c r="A78" s="2"/>
+      <c r="A78" s="3"/>
       <c r="B78" s="7" t="s">
         <v>188</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="D78" s="4" t="s">
+      <c r="D78" s="2" t="s">
         <v>189</v>
       </c>
       <c r="E78" t="s">
@@ -4689,12 +4773,12 @@
       </c>
     </row>
     <row r="79" spans="1:7">
-      <c r="A79" s="2"/>
+      <c r="A79" s="3"/>
       <c r="B79" s="7"/>
       <c r="C79" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="D79" s="4" t="s">
+      <c r="D79" s="2" t="s">
         <v>192</v>
       </c>
       <c r="E79" t="s">
@@ -4705,7 +4789,7 @@
       </c>
     </row>
     <row r="80" spans="1:7">
-      <c r="A80" s="2"/>
+      <c r="A80" s="3"/>
       <c r="B80" s="7"/>
       <c r="C80" s="6" t="s">
         <v>193</v>
@@ -4718,12 +4802,12 @@
       </c>
     </row>
     <row r="81" spans="1:7">
-      <c r="A81" s="2"/>
+      <c r="A81" s="3"/>
       <c r="B81" s="7"/>
       <c r="C81" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="D81" s="4" t="s">
+      <c r="D81" s="2" t="s">
         <v>196</v>
       </c>
       <c r="G81">
@@ -4731,12 +4815,12 @@
       </c>
     </row>
     <row r="82" spans="1:7">
-      <c r="A82" s="2"/>
+      <c r="A82" s="3"/>
       <c r="B82" s="7"/>
       <c r="C82" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="D82" s="4" t="s">
+      <c r="D82" s="2" t="s">
         <v>198</v>
       </c>
       <c r="G82">
@@ -4744,12 +4828,12 @@
       </c>
     </row>
     <row r="83" spans="1:7">
-      <c r="A83" s="2"/>
+      <c r="A83" s="3"/>
       <c r="B83" s="7"/>
       <c r="C83" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="D83" s="4" t="s">
+      <c r="D83" s="2" t="s">
         <v>200</v>
       </c>
       <c r="G83">
@@ -4757,7 +4841,7 @@
       </c>
     </row>
     <row r="85" spans="1:7">
-      <c r="A85" s="2" t="s">
+      <c r="A85" s="3" t="s">
         <v>201</v>
       </c>
       <c r="B85" s="9" t="s">
@@ -4774,7 +4858,7 @@
       </c>
     </row>
     <row r="86" spans="1:7">
-      <c r="A86" s="2"/>
+      <c r="A86" s="3"/>
       <c r="B86" s="9"/>
       <c r="C86" s="10" t="s">
         <v>206</v>
@@ -4787,7 +4871,7 @@
       </c>
     </row>
     <row r="87" spans="1:7">
-      <c r="A87" s="2"/>
+      <c r="A87" s="3"/>
       <c r="B87" s="9"/>
       <c r="C87" s="10" t="s">
         <v>208</v>
@@ -4800,7 +4884,7 @@
       </c>
     </row>
     <row r="88" spans="1:7">
-      <c r="A88" s="2"/>
+      <c r="A88" s="3"/>
       <c r="B88" s="9"/>
       <c r="C88" s="10" t="s">
         <v>210</v>
@@ -4813,7 +4897,7 @@
       </c>
     </row>
     <row r="89" spans="1:7">
-      <c r="A89" s="2"/>
+      <c r="A89" s="3"/>
       <c r="B89" s="9" t="s">
         <v>212</v>
       </c>
@@ -4828,7 +4912,7 @@
       </c>
     </row>
     <row r="90" spans="1:7">
-      <c r="A90" s="2"/>
+      <c r="A90" s="3"/>
       <c r="B90" s="9"/>
       <c r="C90" s="10" t="s">
         <v>216</v>
@@ -4841,7 +4925,7 @@
       </c>
     </row>
     <row r="91" spans="1:7">
-      <c r="A91" s="2"/>
+      <c r="A91" s="3"/>
       <c r="B91" s="9"/>
       <c r="C91" s="10" t="s">
         <v>218</v>
@@ -4854,7 +4938,7 @@
       </c>
     </row>
     <row r="92" spans="1:7">
-      <c r="A92" s="2"/>
+      <c r="A92" s="3"/>
       <c r="B92" s="9"/>
       <c r="C92" s="10" t="s">
         <v>221</v>
@@ -4867,7 +4951,7 @@
       </c>
     </row>
     <row r="93" spans="1:7">
-      <c r="A93" s="2"/>
+      <c r="A93" s="3"/>
       <c r="B93" s="9" t="s">
         <v>224</v>
       </c>
@@ -4882,7 +4966,7 @@
       </c>
     </row>
     <row r="94" spans="1:7">
-      <c r="A94" s="2"/>
+      <c r="A94" s="3"/>
       <c r="B94" s="9"/>
       <c r="C94" s="10" t="s">
         <v>227</v>
@@ -4895,7 +4979,7 @@
       </c>
     </row>
     <row r="95" spans="1:7">
-      <c r="A95" s="2"/>
+      <c r="A95" s="3"/>
       <c r="B95" s="9" t="s">
         <v>229</v>
       </c>
@@ -4910,7 +4994,7 @@
       </c>
     </row>
     <row r="96" spans="1:7">
-      <c r="A96" s="2"/>
+      <c r="A96" s="3"/>
       <c r="B96" s="9"/>
       <c r="C96" s="10" t="s">
         <v>233</v>
@@ -4923,7 +5007,7 @@
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="A97" s="2"/>
+      <c r="A97" s="3"/>
       <c r="B97" s="9"/>
       <c r="C97" s="10" t="s">
         <v>236</v>
@@ -4936,7 +5020,7 @@
       </c>
     </row>
     <row r="98" spans="1:5">
-      <c r="A98" s="2"/>
+      <c r="A98" s="3"/>
       <c r="B98" s="9"/>
       <c r="C98" s="10" t="s">
         <v>239</v>
@@ -4949,7 +5033,7 @@
       </c>
     </row>
     <row r="99" spans="1:5">
-      <c r="A99" s="2"/>
+      <c r="A99" s="3"/>
       <c r="B99" s="9" t="s">
         <v>242</v>
       </c>
@@ -4964,7 +5048,7 @@
       </c>
     </row>
     <row r="100" spans="1:5">
-      <c r="A100" s="2"/>
+      <c r="A100" s="3"/>
       <c r="B100" s="9"/>
       <c r="C100" s="10" t="s">
         <v>245</v>
@@ -4977,7 +5061,7 @@
       </c>
     </row>
     <row r="101" spans="1:5">
-      <c r="A101" s="2"/>
+      <c r="A101" s="3"/>
       <c r="B101" s="9"/>
       <c r="C101" s="10" t="s">
         <v>247</v>
@@ -4990,7 +5074,7 @@
       </c>
     </row>
     <row r="102" spans="1:5">
-      <c r="A102" s="2"/>
+      <c r="A102" s="3"/>
       <c r="B102" s="9"/>
       <c r="C102" s="10" t="s">
         <v>250</v>
@@ -5003,7 +5087,7 @@
       </c>
     </row>
     <row r="103" spans="1:5">
-      <c r="A103" s="2"/>
+      <c r="A103" s="3"/>
       <c r="B103" s="9"/>
       <c r="C103" s="10" t="s">
         <v>252</v>
@@ -5016,7 +5100,7 @@
       </c>
     </row>
     <row r="104" spans="1:5">
-      <c r="A104" s="2"/>
+      <c r="A104" s="3"/>
       <c r="B104" s="9"/>
       <c r="C104" s="10" t="s">
         <v>255</v>
@@ -5029,7 +5113,7 @@
       </c>
     </row>
     <row r="105" spans="1:5">
-      <c r="A105" s="2"/>
+      <c r="A105" s="3"/>
       <c r="B105" s="9" t="s">
         <v>257</v>
       </c>
@@ -5044,7 +5128,7 @@
       </c>
     </row>
     <row r="106" spans="1:5">
-      <c r="A106" s="2"/>
+      <c r="A106" s="3"/>
       <c r="B106" s="9" t="s">
         <v>260</v>
       </c>
@@ -5059,7 +5143,7 @@
       </c>
     </row>
     <row r="107" spans="1:5">
-      <c r="A107" s="2"/>
+      <c r="A107" s="3"/>
       <c r="B107" s="9" t="s">
         <v>264</v>
       </c>
@@ -5074,7 +5158,7 @@
       </c>
     </row>
     <row r="108" spans="1:5">
-      <c r="A108" s="2"/>
+      <c r="A108" s="3"/>
       <c r="B108" s="9"/>
       <c r="C108" s="10" t="s">
         <v>268</v>
@@ -5087,7 +5171,7 @@
       </c>
     </row>
     <row r="109" spans="1:5">
-      <c r="A109" s="2"/>
+      <c r="A109" s="3"/>
       <c r="B109" s="9"/>
       <c r="C109" s="10" t="s">
         <v>270</v>
@@ -5100,7 +5184,7 @@
       </c>
     </row>
     <row r="111" spans="1:5">
-      <c r="A111" s="2" t="s">
+      <c r="A111" s="3" t="s">
         <v>273</v>
       </c>
       <c r="B111" s="10"/>
@@ -5115,7 +5199,7 @@
       </c>
     </row>
     <row r="112" spans="1:5">
-      <c r="A112" s="2"/>
+      <c r="A112" s="3"/>
       <c r="B112" s="10"/>
       <c r="C112" s="10" t="s">
         <v>277</v>
@@ -5128,7 +5212,7 @@
       </c>
     </row>
     <row r="113" spans="1:5">
-      <c r="A113" s="2"/>
+      <c r="A113" s="3"/>
       <c r="B113" s="10"/>
       <c r="C113" s="10" t="s">
         <v>280</v>
@@ -5141,7 +5225,7 @@
       </c>
     </row>
     <row r="114" spans="1:5">
-      <c r="A114" s="2"/>
+      <c r="A114" s="3"/>
       <c r="B114" s="10"/>
       <c r="C114" s="10" t="s">
         <v>283</v>
@@ -5154,7 +5238,7 @@
       </c>
     </row>
     <row r="115" spans="1:5">
-      <c r="A115" s="2"/>
+      <c r="A115" s="3"/>
       <c r="B115" s="10"/>
       <c r="C115" s="10" t="s">
         <v>286</v>
@@ -5167,7 +5251,7 @@
       </c>
     </row>
     <row r="116" spans="1:5">
-      <c r="A116" s="2"/>
+      <c r="A116" s="3"/>
       <c r="B116" s="10"/>
       <c r="C116" s="10" t="s">
         <v>289</v>
@@ -5180,7 +5264,7 @@
       </c>
     </row>
     <row r="117" spans="1:5">
-      <c r="A117" s="2"/>
+      <c r="A117" s="3"/>
       <c r="B117" s="10"/>
       <c r="C117" s="10" t="s">
         <v>291</v>
@@ -5193,7 +5277,7 @@
       </c>
     </row>
     <row r="118" spans="1:5">
-      <c r="A118" s="2"/>
+      <c r="A118" s="3"/>
       <c r="B118" s="10"/>
       <c r="C118" s="10" t="s">
         <v>294</v>
@@ -5206,7 +5290,7 @@
       </c>
     </row>
     <row r="119" spans="1:5">
-      <c r="A119" s="2"/>
+      <c r="A119" s="3"/>
       <c r="B119" s="10"/>
       <c r="C119" s="10" t="s">
         <v>297</v>
@@ -5219,7 +5303,7 @@
       </c>
     </row>
     <row r="120" spans="1:5">
-      <c r="A120" s="2"/>
+      <c r="A120" s="3"/>
       <c r="B120" s="10"/>
       <c r="C120" s="10" t="s">
         <v>299</v>
@@ -5232,7 +5316,7 @@
       </c>
     </row>
     <row r="121" spans="1:5">
-      <c r="A121" s="2"/>
+      <c r="A121" s="3"/>
       <c r="B121" s="10"/>
       <c r="C121" s="10" t="s">
         <v>302</v>
@@ -5245,7 +5329,7 @@
       </c>
     </row>
     <row r="122" spans="1:5">
-      <c r="A122" s="2"/>
+      <c r="A122" s="3"/>
       <c r="B122" s="10"/>
       <c r="C122" s="10" t="s">
         <v>305</v>
@@ -5258,7 +5342,7 @@
       </c>
     </row>
     <row r="123" spans="1:5">
-      <c r="A123" s="2"/>
+      <c r="A123" s="3"/>
       <c r="B123" s="10"/>
       <c r="C123" s="10" t="s">
         <v>308</v>
@@ -5271,7 +5355,7 @@
       </c>
     </row>
     <row r="124" spans="1:5">
-      <c r="A124" s="2"/>
+      <c r="A124" s="3"/>
       <c r="B124" s="10"/>
       <c r="C124" s="10" t="s">
         <v>311</v>
@@ -5284,7 +5368,7 @@
       </c>
     </row>
     <row r="125" spans="1:5">
-      <c r="A125" s="2"/>
+      <c r="A125" s="3"/>
       <c r="B125" s="10"/>
       <c r="C125" s="10" t="s">
         <v>314</v>
@@ -5297,7 +5381,7 @@
       </c>
     </row>
     <row r="126" spans="1:5">
-      <c r="A126" s="2"/>
+      <c r="A126" s="3"/>
       <c r="B126" s="10"/>
       <c r="C126" s="10" t="s">
         <v>317</v>
@@ -5310,7 +5394,7 @@
       </c>
     </row>
     <row r="127" spans="1:5">
-      <c r="A127" s="2"/>
+      <c r="A127" s="3"/>
       <c r="B127" s="10"/>
       <c r="C127" s="10" t="s">
         <v>320</v>
@@ -5323,7 +5407,7 @@
       </c>
     </row>
     <row r="128" spans="1:5">
-      <c r="A128" s="2"/>
+      <c r="A128" s="3"/>
       <c r="B128" s="10"/>
       <c r="C128" s="10" t="s">
         <v>323</v>
@@ -5336,7 +5420,7 @@
       </c>
     </row>
     <row r="129" spans="1:5">
-      <c r="A129" s="2"/>
+      <c r="A129" s="3"/>
       <c r="B129" s="10"/>
       <c r="C129" s="10" t="s">
         <v>326</v>
@@ -5349,7 +5433,7 @@
       </c>
     </row>
     <row r="130" spans="1:5">
-      <c r="A130" s="2"/>
+      <c r="A130" s="3"/>
       <c r="B130" s="10"/>
       <c r="C130" s="10" t="s">
         <v>329</v>
@@ -5362,7 +5446,7 @@
       </c>
     </row>
     <row r="131" spans="1:5">
-      <c r="A131" s="2"/>
+      <c r="A131" s="3"/>
       <c r="B131" s="10"/>
       <c r="C131" s="10" t="s">
         <v>332</v>
@@ -5375,7 +5459,7 @@
       </c>
     </row>
     <row r="132" spans="1:5">
-      <c r="A132" s="2"/>
+      <c r="A132" s="3"/>
       <c r="B132" s="10"/>
       <c r="C132" s="10" t="s">
         <v>335</v>
@@ -5388,7 +5472,7 @@
       </c>
     </row>
     <row r="133" spans="1:5">
-      <c r="A133" s="2"/>
+      <c r="A133" s="3"/>
       <c r="B133" s="10"/>
       <c r="C133" s="10" t="s">
         <v>338</v>
@@ -5401,7 +5485,7 @@
       </c>
     </row>
     <row r="134" spans="1:5">
-      <c r="A134" s="2"/>
+      <c r="A134" s="3"/>
       <c r="B134" s="10"/>
       <c r="C134" s="10" t="s">
         <v>341</v>
@@ -5414,7 +5498,7 @@
       </c>
     </row>
     <row r="135" spans="1:5">
-      <c r="A135" s="2"/>
+      <c r="A135" s="3"/>
       <c r="B135" s="10"/>
       <c r="C135" s="10" t="s">
         <v>344</v>
@@ -5427,7 +5511,7 @@
       </c>
     </row>
     <row r="136" spans="1:5">
-      <c r="A136" s="2"/>
+      <c r="A136" s="3"/>
       <c r="B136" s="10"/>
       <c r="C136" s="10" t="s">
         <v>347</v>
@@ -5440,7 +5524,7 @@
       </c>
     </row>
     <row r="137" spans="1:5">
-      <c r="A137" s="2"/>
+      <c r="A137" s="3"/>
       <c r="B137" s="10"/>
       <c r="C137" s="10" t="s">
         <v>350</v>
@@ -5453,7 +5537,7 @@
       </c>
     </row>
     <row r="138" spans="1:5">
-      <c r="A138" s="2"/>
+      <c r="A138" s="3"/>
       <c r="B138" s="10"/>
       <c r="C138" s="10" t="s">
         <v>353</v>
@@ -5466,7 +5550,7 @@
       </c>
     </row>
     <row r="139" spans="1:5">
-      <c r="A139" s="2"/>
+      <c r="A139" s="3"/>
       <c r="B139" s="10"/>
       <c r="C139" s="10" t="s">
         <v>356</v>
@@ -5479,7 +5563,7 @@
       </c>
     </row>
     <row r="140" spans="1:5">
-      <c r="A140" s="2"/>
+      <c r="A140" s="3"/>
       <c r="B140" s="10"/>
       <c r="C140" s="10" t="s">
         <v>359</v>
@@ -5492,7 +5576,7 @@
       </c>
     </row>
     <row r="141" spans="1:5">
-      <c r="A141" s="2"/>
+      <c r="A141" s="3"/>
       <c r="B141" s="10"/>
       <c r="C141" s="10" t="s">
         <v>362</v>
@@ -5505,7 +5589,7 @@
       </c>
     </row>
     <row r="142" spans="1:5">
-      <c r="A142" s="2"/>
+      <c r="A142" s="3"/>
       <c r="B142" s="10"/>
       <c r="C142" s="10" t="s">
         <v>365</v>
@@ -5518,7 +5602,7 @@
       </c>
     </row>
     <row r="143" spans="1:5">
-      <c r="A143" s="2"/>
+      <c r="A143" s="3"/>
       <c r="B143" s="10"/>
       <c r="C143" s="10" t="s">
         <v>367</v>
@@ -5531,7 +5615,7 @@
       </c>
     </row>
     <row r="144" spans="1:5">
-      <c r="A144" s="2"/>
+      <c r="A144" s="3"/>
       <c r="B144" s="10"/>
       <c r="C144" s="10" t="s">
         <v>370</v>
@@ -5544,7 +5628,7 @@
       </c>
     </row>
     <row r="145" spans="1:5">
-      <c r="A145" s="2"/>
+      <c r="A145" s="3"/>
       <c r="B145" s="10"/>
       <c r="C145" s="10" t="s">
         <v>373</v>
@@ -5557,7 +5641,7 @@
       </c>
     </row>
     <row r="146" spans="1:5">
-      <c r="A146" s="2"/>
+      <c r="A146" s="3"/>
       <c r="B146" s="10"/>
       <c r="C146" s="10" t="s">
         <v>376</v>
@@ -5570,7 +5654,7 @@
       </c>
     </row>
     <row r="147" spans="1:5">
-      <c r="A147" s="2"/>
+      <c r="A147" s="3"/>
       <c r="B147" s="10"/>
       <c r="C147" s="10" t="s">
         <v>379</v>
@@ -5583,7 +5667,7 @@
       </c>
     </row>
     <row r="148" spans="1:5">
-      <c r="A148" s="2"/>
+      <c r="A148" s="3"/>
       <c r="B148" s="10"/>
       <c r="C148" s="10" t="s">
         <v>382</v>
@@ -5596,7 +5680,7 @@
       </c>
     </row>
     <row r="149" spans="1:5">
-      <c r="A149" s="2"/>
+      <c r="A149" s="3"/>
       <c r="B149" s="10"/>
       <c r="C149" s="10" t="s">
         <v>385</v>
@@ -5609,7 +5693,7 @@
       </c>
     </row>
     <row r="150" spans="1:5">
-      <c r="A150" s="2"/>
+      <c r="A150" s="3"/>
       <c r="B150" s="10"/>
       <c r="C150" s="10" t="s">
         <v>388</v>
@@ -5622,7 +5706,7 @@
       </c>
     </row>
     <row r="151" spans="1:5">
-      <c r="A151" s="2"/>
+      <c r="A151" s="3"/>
       <c r="B151" s="10"/>
       <c r="C151" s="10" t="s">
         <v>391</v>
@@ -5635,7 +5719,7 @@
       </c>
     </row>
     <row r="152" spans="1:5">
-      <c r="A152" s="2"/>
+      <c r="A152" s="3"/>
       <c r="B152" s="10"/>
       <c r="C152" s="10" t="s">
         <v>394</v>
@@ -5648,7 +5732,7 @@
       </c>
     </row>
     <row r="153" spans="1:5">
-      <c r="A153" s="2"/>
+      <c r="A153" s="3"/>
       <c r="B153" s="10"/>
       <c r="C153" s="10" t="s">
         <v>397</v>
@@ -5661,7 +5745,7 @@
       </c>
     </row>
     <row r="154" spans="1:5">
-      <c r="A154" s="2"/>
+      <c r="A154" s="3"/>
       <c r="B154" s="10"/>
       <c r="C154" s="10" t="s">
         <v>400</v>
@@ -5674,7 +5758,7 @@
       </c>
     </row>
     <row r="155" spans="1:5">
-      <c r="A155" s="2"/>
+      <c r="A155" s="3"/>
       <c r="B155" s="10"/>
       <c r="C155" s="10" t="s">
         <v>403</v>
@@ -5687,7 +5771,7 @@
       </c>
     </row>
     <row r="156" spans="1:5">
-      <c r="A156" s="2"/>
+      <c r="A156" s="3"/>
       <c r="B156" s="10"/>
       <c r="C156" s="10" t="s">
         <v>406</v>
@@ -5700,7 +5784,7 @@
       </c>
     </row>
     <row r="157" spans="1:5">
-      <c r="A157" s="2"/>
+      <c r="A157" s="3"/>
       <c r="B157" s="10"/>
       <c r="C157" s="10" t="s">
         <v>409</v>
@@ -5713,7 +5797,7 @@
       </c>
     </row>
     <row r="158" spans="1:5">
-      <c r="A158" s="2"/>
+      <c r="A158" s="3"/>
       <c r="B158" s="10"/>
       <c r="C158" s="10" t="s">
         <v>412</v>
@@ -5726,7 +5810,7 @@
       </c>
     </row>
     <row r="159" spans="1:5">
-      <c r="A159" s="2"/>
+      <c r="A159" s="3"/>
       <c r="B159" s="10"/>
       <c r="C159" s="10" t="s">
         <v>415</v>
@@ -5739,7 +5823,7 @@
       </c>
     </row>
     <row r="160" spans="1:5">
-      <c r="A160" s="2"/>
+      <c r="A160" s="3"/>
       <c r="B160" s="10"/>
       <c r="C160" s="10" t="s">
         <v>418</v>
@@ -5752,7 +5836,7 @@
       </c>
     </row>
     <row r="161" spans="1:5">
-      <c r="A161" s="2"/>
+      <c r="A161" s="3"/>
       <c r="B161" s="10"/>
       <c r="C161" s="10" t="s">
         <v>420</v>
@@ -5765,7 +5849,7 @@
       </c>
     </row>
     <row r="162" spans="1:5">
-      <c r="A162" s="2"/>
+      <c r="A162" s="3"/>
       <c r="B162" s="10"/>
       <c r="C162" s="10" t="s">
         <v>422</v>
@@ -5778,7 +5862,7 @@
       </c>
     </row>
     <row r="163" spans="1:5">
-      <c r="A163" s="2"/>
+      <c r="A163" s="3"/>
       <c r="B163" s="10"/>
       <c r="C163" s="10" t="s">
         <v>425</v>
@@ -5791,7 +5875,7 @@
       </c>
     </row>
     <row r="164" spans="1:5">
-      <c r="A164" s="2"/>
+      <c r="A164" s="3"/>
       <c r="B164" s="10"/>
       <c r="C164" s="10" t="s">
         <v>428</v>
@@ -5804,7 +5888,7 @@
       </c>
     </row>
     <row r="165" spans="1:5">
-      <c r="A165" s="2"/>
+      <c r="A165" s="3"/>
       <c r="B165" s="10"/>
       <c r="C165" s="10" t="s">
         <v>430</v>
@@ -5817,7 +5901,7 @@
       </c>
     </row>
     <row r="166" spans="1:5">
-      <c r="A166" s="2"/>
+      <c r="A166" s="3"/>
       <c r="B166" s="10"/>
       <c r="C166" s="10" t="s">
         <v>433</v>
@@ -5830,7 +5914,7 @@
       </c>
     </row>
     <row r="167" spans="1:5">
-      <c r="A167" s="2"/>
+      <c r="A167" s="3"/>
       <c r="B167" s="10"/>
       <c r="C167" s="10" t="s">
         <v>435</v>
@@ -5843,7 +5927,7 @@
       </c>
     </row>
     <row r="168" spans="1:5">
-      <c r="A168" s="2"/>
+      <c r="A168" s="3"/>
       <c r="B168" s="10"/>
       <c r="C168" s="10" t="s">
         <v>437</v>
@@ -5856,7 +5940,7 @@
       </c>
     </row>
     <row r="169" spans="1:5">
-      <c r="A169" s="2"/>
+      <c r="A169" s="3"/>
       <c r="B169" s="10"/>
       <c r="C169" s="10" t="s">
         <v>440</v>
@@ -5869,7 +5953,7 @@
       </c>
     </row>
     <row r="170" spans="1:5">
-      <c r="A170" s="2"/>
+      <c r="A170" s="3"/>
       <c r="B170" s="10"/>
       <c r="C170" s="10" t="s">
         <v>443</v>
@@ -5887,10 +5971,10 @@
       <c r="D171" s="10"/>
     </row>
     <row r="172" spans="1:5">
-      <c r="A172" s="2" t="s">
+      <c r="A172" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="B172" s="2" t="s">
+      <c r="B172" s="3" t="s">
         <v>446</v>
       </c>
       <c r="C172" s="6" t="s">
@@ -5904,8 +5988,8 @@
       </c>
     </row>
     <row r="173" spans="1:5">
-      <c r="A173" s="2"/>
-      <c r="B173" s="2"/>
+      <c r="A173" s="3"/>
+      <c r="B173" s="3"/>
       <c r="C173" s="6" t="s">
         <v>448</v>
       </c>
@@ -5917,8 +6001,8 @@
       </c>
     </row>
     <row r="174" spans="1:5">
-      <c r="A174" s="2"/>
-      <c r="B174" s="2"/>
+      <c r="A174" s="3"/>
+      <c r="B174" s="3"/>
       <c r="C174" s="6" t="s">
         <v>450</v>
       </c>
@@ -5930,8 +6014,8 @@
       </c>
     </row>
     <row r="175" spans="1:5">
-      <c r="A175" s="2"/>
-      <c r="B175" s="2"/>
+      <c r="A175" s="3"/>
+      <c r="B175" s="3"/>
       <c r="C175" s="6" t="s">
         <v>453</v>
       </c>
@@ -5943,8 +6027,8 @@
       </c>
     </row>
     <row r="176" spans="1:5">
-      <c r="A176" s="2"/>
-      <c r="B176" s="2"/>
+      <c r="A176" s="3"/>
+      <c r="B176" s="3"/>
       <c r="C176" s="6" t="s">
         <v>455</v>
       </c>
@@ -5956,8 +6040,8 @@
       </c>
     </row>
     <row r="177" spans="1:5">
-      <c r="A177" s="2"/>
-      <c r="B177" s="2"/>
+      <c r="A177" s="3"/>
+      <c r="B177" s="3"/>
       <c r="C177" s="6" t="s">
         <v>458</v>
       </c>
@@ -5969,8 +6053,8 @@
       </c>
     </row>
     <row r="178" spans="1:5">
-      <c r="A178" s="2"/>
-      <c r="B178" s="2"/>
+      <c r="A178" s="3"/>
+      <c r="B178" s="3"/>
       <c r="C178" s="6" t="s">
         <v>286</v>
       </c>
@@ -5982,8 +6066,8 @@
       </c>
     </row>
     <row r="179" spans="1:5">
-      <c r="A179" s="2"/>
-      <c r="B179" s="2"/>
+      <c r="A179" s="3"/>
+      <c r="B179" s="3"/>
       <c r="C179" s="6" t="s">
         <v>461</v>
       </c>
@@ -5995,8 +6079,8 @@
       </c>
     </row>
     <row r="180" spans="1:5">
-      <c r="A180" s="2"/>
-      <c r="B180" s="2"/>
+      <c r="A180" s="3"/>
+      <c r="B180" s="3"/>
       <c r="C180" s="6" t="s">
         <v>463</v>
       </c>
@@ -6008,8 +6092,8 @@
       </c>
     </row>
     <row r="181" spans="1:5">
-      <c r="A181" s="2"/>
-      <c r="B181" s="2"/>
+      <c r="A181" s="3"/>
+      <c r="B181" s="3"/>
       <c r="C181" s="6" t="s">
         <v>297</v>
       </c>
@@ -6021,8 +6105,8 @@
       </c>
     </row>
     <row r="182" spans="1:5">
-      <c r="A182" s="2"/>
-      <c r="B182" s="2"/>
+      <c r="A182" s="3"/>
+      <c r="B182" s="3"/>
       <c r="C182" s="6" t="s">
         <v>467</v>
       </c>
@@ -6034,8 +6118,8 @@
       </c>
     </row>
     <row r="183" spans="1:5">
-      <c r="A183" s="2"/>
-      <c r="B183" s="2"/>
+      <c r="A183" s="3"/>
+      <c r="B183" s="3"/>
       <c r="C183" s="6" t="s">
         <v>469</v>
       </c>
@@ -6047,8 +6131,8 @@
       </c>
     </row>
     <row r="184" spans="1:5">
-      <c r="A184" s="2"/>
-      <c r="B184" s="2"/>
+      <c r="A184" s="3"/>
+      <c r="B184" s="3"/>
       <c r="C184" s="6" t="s">
         <v>471</v>
       </c>
@@ -6060,8 +6144,8 @@
       </c>
     </row>
     <row r="185" spans="1:5">
-      <c r="A185" s="2"/>
-      <c r="B185" s="2"/>
+      <c r="A185" s="3"/>
+      <c r="B185" s="3"/>
       <c r="C185" s="6" t="s">
         <v>473</v>
       </c>
@@ -6073,8 +6157,8 @@
       </c>
     </row>
     <row r="186" spans="1:5">
-      <c r="A186" s="2"/>
-      <c r="B186" s="2"/>
+      <c r="A186" s="3"/>
+      <c r="B186" s="3"/>
       <c r="C186" s="6" t="s">
         <v>476</v>
       </c>
@@ -6086,8 +6170,8 @@
       </c>
     </row>
     <row r="187" spans="1:5">
-      <c r="A187" s="2"/>
-      <c r="B187" s="2"/>
+      <c r="A187" s="3"/>
+      <c r="B187" s="3"/>
       <c r="C187" s="6" t="s">
         <v>443</v>
       </c>
@@ -6099,8 +6183,8 @@
       </c>
     </row>
     <row r="188" spans="1:5">
-      <c r="A188" s="2"/>
-      <c r="B188" s="2" t="s">
+      <c r="A188" s="3"/>
+      <c r="B188" s="3" t="s">
         <v>480</v>
       </c>
       <c r="C188" s="6" t="s">
@@ -6114,8 +6198,8 @@
       </c>
     </row>
     <row r="189" spans="1:5">
-      <c r="A189" s="2"/>
-      <c r="B189" s="2"/>
+      <c r="A189" s="3"/>
+      <c r="B189" s="3"/>
       <c r="C189" s="6" t="s">
         <v>484</v>
       </c>
@@ -6127,8 +6211,8 @@
       </c>
     </row>
     <row r="190" spans="1:5">
-      <c r="A190" s="2"/>
-      <c r="B190" s="2"/>
+      <c r="A190" s="3"/>
+      <c r="B190" s="3"/>
       <c r="C190" s="6" t="s">
         <v>486</v>
       </c>
@@ -6140,8 +6224,8 @@
       </c>
     </row>
     <row r="191" spans="1:5">
-      <c r="A191" s="2"/>
-      <c r="B191" s="2"/>
+      <c r="A191" s="3"/>
+      <c r="B191" s="3"/>
       <c r="C191" s="6" t="s">
         <v>488</v>
       </c>
@@ -6153,8 +6237,8 @@
       </c>
     </row>
     <row r="192" spans="1:5">
-      <c r="A192" s="2"/>
-      <c r="B192" s="2"/>
+      <c r="A192" s="3"/>
+      <c r="B192" s="3"/>
       <c r="C192" s="6" t="s">
         <v>491</v>
       </c>
@@ -6166,8 +6250,8 @@
       </c>
     </row>
     <row r="193" spans="1:5">
-      <c r="A193" s="2"/>
-      <c r="B193" s="2"/>
+      <c r="A193" s="3"/>
+      <c r="B193" s="3"/>
       <c r="C193" s="6" t="s">
         <v>494</v>
       </c>
@@ -6179,8 +6263,8 @@
       </c>
     </row>
     <row r="194" spans="1:5">
-      <c r="A194" s="2"/>
-      <c r="B194" s="2"/>
+      <c r="A194" s="3"/>
+      <c r="B194" s="3"/>
       <c r="C194" s="6" t="s">
         <v>496</v>
       </c>
@@ -6192,8 +6276,8 @@
       </c>
     </row>
     <row r="195" spans="1:5">
-      <c r="A195" s="2"/>
-      <c r="B195" s="2"/>
+      <c r="A195" s="3"/>
+      <c r="B195" s="3"/>
       <c r="C195" s="6" t="s">
         <v>498</v>
       </c>
@@ -6205,8 +6289,8 @@
       </c>
     </row>
     <row r="196" spans="1:5">
-      <c r="A196" s="2"/>
-      <c r="B196" s="2"/>
+      <c r="A196" s="3"/>
+      <c r="B196" s="3"/>
       <c r="C196" s="6" t="s">
         <v>500</v>
       </c>
@@ -6218,8 +6302,8 @@
       </c>
     </row>
     <row r="197" spans="1:5">
-      <c r="A197" s="2"/>
-      <c r="B197" s="2"/>
+      <c r="A197" s="3"/>
+      <c r="B197" s="3"/>
       <c r="C197" s="6" t="s">
         <v>502</v>
       </c>
@@ -6231,8 +6315,8 @@
       </c>
     </row>
     <row r="198" spans="1:5">
-      <c r="A198" s="2"/>
-      <c r="B198" s="2"/>
+      <c r="A198" s="3"/>
+      <c r="B198" s="3"/>
       <c r="C198" s="6" t="s">
         <v>476</v>
       </c>
@@ -6244,8 +6328,8 @@
       </c>
     </row>
     <row r="199" spans="1:5">
-      <c r="A199" s="2"/>
-      <c r="B199" s="2"/>
+      <c r="A199" s="3"/>
+      <c r="B199" s="3"/>
       <c r="C199" s="6" t="s">
         <v>505</v>
       </c>
@@ -6257,8 +6341,8 @@
       </c>
     </row>
     <row r="200" spans="1:5">
-      <c r="A200" s="2"/>
-      <c r="B200" s="2"/>
+      <c r="A200" s="3"/>
+      <c r="B200" s="3"/>
       <c r="C200" s="6" t="s">
         <v>507</v>
       </c>
@@ -6270,8 +6354,8 @@
       </c>
     </row>
     <row r="201" spans="1:5">
-      <c r="A201" s="2"/>
-      <c r="B201" s="2"/>
+      <c r="A201" s="3"/>
+      <c r="B201" s="3"/>
       <c r="C201" s="6" t="s">
         <v>510</v>
       </c>
@@ -6283,8 +6367,8 @@
       </c>
     </row>
     <row r="202" spans="1:5">
-      <c r="A202" s="2"/>
-      <c r="B202" s="2"/>
+      <c r="A202" s="3"/>
+      <c r="B202" s="3"/>
       <c r="C202" s="6" t="s">
         <v>512</v>
       </c>
@@ -6296,8 +6380,8 @@
       </c>
     </row>
     <row r="203" spans="1:5">
-      <c r="A203" s="2"/>
-      <c r="B203" s="2"/>
+      <c r="A203" s="3"/>
+      <c r="B203" s="3"/>
       <c r="C203" s="6" t="s">
         <v>320</v>
       </c>
@@ -6309,8 +6393,8 @@
       </c>
     </row>
     <row r="204" spans="1:5">
-      <c r="A204" s="2"/>
-      <c r="B204" s="2"/>
+      <c r="A204" s="3"/>
+      <c r="B204" s="3"/>
       <c r="C204" s="6" t="s">
         <v>516</v>
       </c>
@@ -6322,8 +6406,8 @@
       </c>
     </row>
     <row r="205" spans="1:5">
-      <c r="A205" s="2"/>
-      <c r="B205" s="2"/>
+      <c r="A205" s="3"/>
+      <c r="B205" s="3"/>
       <c r="C205" s="6" t="s">
         <v>518</v>
       </c>
@@ -6341,7 +6425,7 @@
       <c r="E206" s="6"/>
     </row>
     <row r="207" spans="1:5">
-      <c r="A207" s="2" t="s">
+      <c r="A207" s="3" t="s">
         <v>520</v>
       </c>
       <c r="B207" s="6"/>
@@ -6356,7 +6440,7 @@
       </c>
     </row>
     <row r="208" spans="1:5">
-      <c r="A208" s="2"/>
+      <c r="A208" s="3"/>
       <c r="B208" s="6"/>
       <c r="C208" s="6" t="s">
         <v>524</v>
@@ -6369,7 +6453,7 @@
       </c>
     </row>
     <row r="209" spans="1:5">
-      <c r="A209" s="2"/>
+      <c r="A209" s="3"/>
       <c r="B209" s="6"/>
       <c r="C209" s="6" t="s">
         <v>526</v>
@@ -6382,7 +6466,7 @@
       </c>
     </row>
     <row r="210" spans="1:5">
-      <c r="A210" s="2"/>
+      <c r="A210" s="3"/>
       <c r="B210" s="6"/>
       <c r="C210" s="6" t="s">
         <v>529</v>
@@ -6395,7 +6479,7 @@
       </c>
     </row>
     <row r="211" spans="1:5">
-      <c r="A211" s="2"/>
+      <c r="A211" s="3"/>
       <c r="B211" s="6"/>
       <c r="C211" s="6" t="s">
         <v>532</v>
@@ -6408,7 +6492,7 @@
       </c>
     </row>
     <row r="212" spans="1:5">
-      <c r="A212" s="2"/>
+      <c r="A212" s="3"/>
       <c r="B212" s="6"/>
       <c r="C212" s="6" t="s">
         <v>534</v>
@@ -6421,7 +6505,7 @@
       </c>
     </row>
     <row r="213" spans="1:5">
-      <c r="A213" s="2"/>
+      <c r="A213" s="3"/>
       <c r="B213" s="6"/>
       <c r="C213" s="6" t="s">
         <v>286</v>
@@ -6434,7 +6518,7 @@
       </c>
     </row>
     <row r="214" spans="1:5">
-      <c r="A214" s="2"/>
+      <c r="A214" s="3"/>
       <c r="B214" s="6"/>
       <c r="C214" s="6" t="s">
         <v>538</v>
@@ -6447,7 +6531,7 @@
       </c>
     </row>
     <row r="215" spans="1:5">
-      <c r="A215" s="2"/>
+      <c r="A215" s="3"/>
       <c r="B215" s="6"/>
       <c r="C215" s="6" t="s">
         <v>541</v>
@@ -6460,7 +6544,7 @@
       </c>
     </row>
     <row r="216" spans="1:5">
-      <c r="A216" s="2"/>
+      <c r="A216" s="3"/>
       <c r="B216" s="6"/>
       <c r="C216" s="6" t="s">
         <v>544</v>
@@ -6473,7 +6557,7 @@
       </c>
     </row>
     <row r="217" spans="1:5">
-      <c r="A217" s="2"/>
+      <c r="A217" s="3"/>
       <c r="B217" s="6"/>
       <c r="C217" s="6" t="s">
         <v>546</v>
@@ -6486,7 +6570,7 @@
       </c>
     </row>
     <row r="218" spans="1:5">
-      <c r="A218" s="2"/>
+      <c r="A218" s="3"/>
       <c r="B218" s="6"/>
       <c r="C218" s="6" t="s">
         <v>548</v>
@@ -6499,7 +6583,7 @@
       </c>
     </row>
     <row r="219" spans="1:5">
-      <c r="A219" s="2"/>
+      <c r="A219" s="3"/>
       <c r="B219" s="6"/>
       <c r="C219" s="6" t="s">
         <v>551</v>
@@ -6512,7 +6596,7 @@
       </c>
     </row>
     <row r="220" spans="1:5">
-      <c r="A220" s="2"/>
+      <c r="A220" s="3"/>
       <c r="B220" s="6"/>
       <c r="C220" s="6" t="s">
         <v>554</v>
@@ -6525,7 +6609,7 @@
       </c>
     </row>
     <row r="221" spans="1:5">
-      <c r="A221" s="2"/>
+      <c r="A221" s="3"/>
       <c r="B221" s="6"/>
       <c r="C221" s="6" t="s">
         <v>556</v>
@@ -6538,7 +6622,7 @@
       </c>
     </row>
     <row r="222" spans="1:5">
-      <c r="A222" s="2"/>
+      <c r="A222" s="3"/>
       <c r="B222" s="6"/>
       <c r="C222" s="6" t="s">
         <v>558</v>
@@ -6551,7 +6635,7 @@
       </c>
     </row>
     <row r="223" spans="1:5">
-      <c r="A223" s="2"/>
+      <c r="A223" s="3"/>
       <c r="B223" s="6"/>
       <c r="C223" s="6" t="s">
         <v>561</v>
@@ -6564,7 +6648,7 @@
       </c>
     </row>
     <row r="224" spans="1:5">
-      <c r="A224" s="2"/>
+      <c r="A224" s="3"/>
       <c r="B224" s="6"/>
       <c r="C224" s="6" t="s">
         <v>564</v>
@@ -6577,7 +6661,7 @@
       </c>
     </row>
     <row r="225" spans="1:5">
-      <c r="A225" s="2"/>
+      <c r="A225" s="3"/>
       <c r="B225" s="6"/>
       <c r="C225" s="6" t="s">
         <v>567</v>
@@ -6590,7 +6674,7 @@
       </c>
     </row>
     <row r="226" spans="1:5">
-      <c r="A226" s="2"/>
+      <c r="A226" s="3"/>
       <c r="B226" s="6"/>
       <c r="C226" s="6" t="s">
         <v>326</v>
@@ -6603,7 +6687,7 @@
       </c>
     </row>
     <row r="227" spans="1:5">
-      <c r="A227" s="2"/>
+      <c r="A227" s="3"/>
       <c r="B227" s="6"/>
       <c r="C227" s="6" t="s">
         <v>571</v>
@@ -6616,7 +6700,7 @@
       </c>
     </row>
     <row r="228" spans="1:5">
-      <c r="A228" s="2"/>
+      <c r="A228" s="3"/>
       <c r="B228" s="6"/>
       <c r="C228" s="6" t="s">
         <v>574</v>
@@ -6629,7 +6713,7 @@
       </c>
     </row>
     <row r="229" spans="1:5">
-      <c r="A229" s="2"/>
+      <c r="A229" s="3"/>
       <c r="B229" s="6"/>
       <c r="C229" s="6" t="s">
         <v>577</v>
@@ -6642,7 +6726,7 @@
       </c>
     </row>
     <row r="230" spans="1:5">
-      <c r="A230" s="2"/>
+      <c r="A230" s="3"/>
       <c r="B230" s="6"/>
       <c r="C230" s="6" t="s">
         <v>579</v>
@@ -6655,7 +6739,7 @@
       </c>
     </row>
     <row r="231" spans="1:5">
-      <c r="A231" s="2"/>
+      <c r="A231" s="3"/>
       <c r="B231" s="6"/>
       <c r="C231" s="6" t="s">
         <v>297</v>
@@ -6668,7 +6752,7 @@
       </c>
     </row>
     <row r="232" spans="1:5">
-      <c r="A232" s="2"/>
+      <c r="A232" s="3"/>
       <c r="B232" s="6"/>
       <c r="C232" s="6" t="s">
         <v>583</v>
@@ -6681,7 +6765,7 @@
       </c>
     </row>
     <row r="233" spans="1:5">
-      <c r="A233" s="2"/>
+      <c r="A233" s="3"/>
       <c r="B233" s="6"/>
       <c r="C233" s="6" t="s">
         <v>585</v>
@@ -6694,7 +6778,7 @@
       </c>
     </row>
     <row r="234" spans="1:5">
-      <c r="A234" s="2"/>
+      <c r="A234" s="3"/>
       <c r="B234" s="6"/>
       <c r="C234" s="6" t="s">
         <v>588</v>
@@ -6707,7 +6791,7 @@
       </c>
     </row>
     <row r="235" spans="1:5">
-      <c r="A235" s="2"/>
+      <c r="A235" s="3"/>
       <c r="B235" s="6"/>
       <c r="C235" s="6" t="s">
         <v>590</v>
@@ -6720,7 +6804,7 @@
       </c>
     </row>
     <row r="236" spans="1:5">
-      <c r="A236" s="2"/>
+      <c r="A236" s="3"/>
       <c r="B236" s="6"/>
       <c r="C236" s="6" t="s">
         <v>592</v>
@@ -6733,7 +6817,7 @@
       </c>
     </row>
     <row r="237" spans="1:5">
-      <c r="A237" s="2"/>
+      <c r="A237" s="3"/>
       <c r="B237" s="6"/>
       <c r="C237" s="6" t="s">
         <v>594</v>
@@ -6746,7 +6830,7 @@
       </c>
     </row>
     <row r="238" spans="1:5">
-      <c r="A238" s="2"/>
+      <c r="A238" s="3"/>
       <c r="B238" s="6"/>
       <c r="C238" s="6" t="s">
         <v>596</v>
@@ -6759,7 +6843,7 @@
       </c>
     </row>
     <row r="239" spans="1:5">
-      <c r="A239" s="2"/>
+      <c r="A239" s="3"/>
       <c r="B239" s="6"/>
       <c r="C239" s="6" t="s">
         <v>598</v>
@@ -6772,7 +6856,7 @@
       </c>
     </row>
     <row r="240" spans="1:5">
-      <c r="A240" s="2"/>
+      <c r="A240" s="3"/>
       <c r="B240" s="6"/>
       <c r="C240" s="6" t="s">
         <v>601</v>
@@ -6785,7 +6869,7 @@
       </c>
     </row>
     <row r="241" spans="1:5">
-      <c r="A241" s="2"/>
+      <c r="A241" s="3"/>
       <c r="B241" s="6"/>
       <c r="C241" s="6" t="s">
         <v>603</v>
@@ -6798,7 +6882,7 @@
       </c>
     </row>
     <row r="242" spans="1:5">
-      <c r="A242" s="2"/>
+      <c r="A242" s="3"/>
       <c r="B242" s="6"/>
       <c r="C242" s="6" t="s">
         <v>606</v>
@@ -6811,7 +6895,7 @@
       </c>
     </row>
     <row r="243" spans="1:5">
-      <c r="A243" s="2"/>
+      <c r="A243" s="3"/>
       <c r="B243" s="6"/>
       <c r="C243" s="6" t="s">
         <v>609</v>
@@ -6824,7 +6908,7 @@
       </c>
     </row>
     <row r="244" spans="1:5">
-      <c r="A244" s="2"/>
+      <c r="A244" s="3"/>
       <c r="B244" s="6"/>
       <c r="C244" s="6" t="s">
         <v>612</v>
@@ -6837,7 +6921,7 @@
       </c>
     </row>
     <row r="245" spans="1:5">
-      <c r="A245" s="2"/>
+      <c r="A245" s="3"/>
       <c r="B245" s="6"/>
       <c r="C245" s="6" t="s">
         <v>614</v>
@@ -6850,7 +6934,7 @@
       </c>
     </row>
     <row r="246" spans="1:5">
-      <c r="A246" s="2"/>
+      <c r="A246" s="3"/>
       <c r="B246" s="6"/>
       <c r="C246" s="6" t="s">
         <v>616</v>
@@ -6863,7 +6947,7 @@
       </c>
     </row>
     <row r="247" spans="1:5">
-      <c r="A247" s="2"/>
+      <c r="A247" s="3"/>
       <c r="B247" s="6"/>
       <c r="C247" s="6" t="s">
         <v>619</v>
@@ -6876,7 +6960,7 @@
       </c>
     </row>
     <row r="248" spans="1:5">
-      <c r="A248" s="2"/>
+      <c r="A248" s="3"/>
       <c r="B248" s="6"/>
       <c r="C248" s="6" t="s">
         <v>622</v>
@@ -6889,7 +6973,7 @@
       </c>
     </row>
     <row r="249" spans="1:5">
-      <c r="A249" s="2"/>
+      <c r="A249" s="3"/>
       <c r="B249" s="6"/>
       <c r="C249" s="6" t="s">
         <v>624</v>
@@ -6902,7 +6986,7 @@
       </c>
     </row>
     <row r="250" spans="1:5">
-      <c r="A250" s="2"/>
+      <c r="A250" s="3"/>
       <c r="B250" s="6"/>
       <c r="C250" s="6" t="s">
         <v>627</v>
@@ -6915,7 +6999,7 @@
       </c>
     </row>
     <row r="251" spans="1:5">
-      <c r="A251" s="2"/>
+      <c r="A251" s="3"/>
       <c r="B251" s="6"/>
       <c r="C251" s="6" t="s">
         <v>629</v>
@@ -6928,7 +7012,7 @@
       </c>
     </row>
     <row r="252" spans="1:5">
-      <c r="A252" s="2"/>
+      <c r="A252" s="3"/>
       <c r="B252" s="6"/>
       <c r="C252" s="6" t="s">
         <v>632</v>
@@ -6941,7 +7025,7 @@
       </c>
     </row>
     <row r="253" spans="1:5">
-      <c r="A253" s="2"/>
+      <c r="A253" s="3"/>
       <c r="B253" s="6"/>
       <c r="C253" s="6" t="s">
         <v>635</v>
@@ -6954,7 +7038,7 @@
       </c>
     </row>
     <row r="254" spans="1:5">
-      <c r="A254" s="2"/>
+      <c r="A254" s="3"/>
       <c r="B254" s="6"/>
       <c r="C254" s="6" t="s">
         <v>637</v>
@@ -6967,7 +7051,7 @@
       </c>
     </row>
     <row r="255" spans="1:5">
-      <c r="A255" s="2"/>
+      <c r="A255" s="3"/>
       <c r="B255" s="6"/>
       <c r="C255" s="6" t="s">
         <v>640</v>
@@ -6980,7 +7064,7 @@
       </c>
     </row>
     <row r="256" spans="1:5">
-      <c r="A256" s="2"/>
+      <c r="A256" s="3"/>
       <c r="B256" s="6"/>
       <c r="C256" s="6" t="s">
         <v>642</v>
@@ -6993,7 +7077,7 @@
       </c>
     </row>
     <row r="257" spans="1:5">
-      <c r="A257" s="2"/>
+      <c r="A257" s="3"/>
       <c r="B257" s="6"/>
       <c r="C257" s="6" t="s">
         <v>644</v>
@@ -7006,7 +7090,7 @@
       </c>
     </row>
     <row r="258" spans="1:5">
-      <c r="A258" s="2"/>
+      <c r="A258" s="3"/>
       <c r="B258" s="6"/>
       <c r="C258" s="6" t="s">
         <v>646</v>
@@ -7019,7 +7103,7 @@
       </c>
     </row>
     <row r="259" spans="1:5">
-      <c r="A259" s="2"/>
+      <c r="A259" s="3"/>
       <c r="B259" s="6"/>
       <c r="C259" s="6" t="s">
         <v>648</v>
@@ -7032,7 +7116,7 @@
       </c>
     </row>
     <row r="260" spans="1:5">
-      <c r="A260" s="2"/>
+      <c r="A260" s="3"/>
       <c r="B260" s="6"/>
       <c r="C260" s="6" t="s">
         <v>651</v>
@@ -7045,7 +7129,7 @@
       </c>
     </row>
     <row r="261" spans="1:5">
-      <c r="A261" s="2"/>
+      <c r="A261" s="3"/>
       <c r="B261" s="6"/>
       <c r="C261" s="6" t="s">
         <v>653</v>
@@ -7058,7 +7142,7 @@
       </c>
     </row>
     <row r="262" spans="1:5">
-      <c r="A262" s="2"/>
+      <c r="A262" s="3"/>
       <c r="B262" s="6"/>
       <c r="C262" s="6" t="s">
         <v>656</v>
@@ -7071,7 +7155,7 @@
       </c>
     </row>
     <row r="263" spans="1:5">
-      <c r="A263" s="2"/>
+      <c r="A263" s="3"/>
       <c r="B263" s="6"/>
       <c r="C263" s="6" t="s">
         <v>658</v>
@@ -7084,7 +7168,7 @@
       </c>
     </row>
     <row r="264" spans="1:5">
-      <c r="A264" s="2"/>
+      <c r="A264" s="3"/>
       <c r="B264" s="6"/>
       <c r="C264" s="6" t="s">
         <v>661</v>
@@ -7097,7 +7181,7 @@
       </c>
     </row>
     <row r="265" spans="1:5">
-      <c r="A265" s="2"/>
+      <c r="A265" s="3"/>
       <c r="B265" s="6"/>
       <c r="C265" s="6" t="s">
         <v>664</v>
@@ -7110,7 +7194,7 @@
       </c>
     </row>
     <row r="266" spans="1:5">
-      <c r="A266" s="2"/>
+      <c r="A266" s="3"/>
       <c r="B266" s="6"/>
       <c r="C266" s="6" t="s">
         <v>667</v>
@@ -7123,7 +7207,7 @@
       </c>
     </row>
     <row r="267" spans="1:5">
-      <c r="A267" s="2"/>
+      <c r="A267" s="3"/>
       <c r="B267" s="6"/>
       <c r="C267" s="6" t="s">
         <v>670</v>
@@ -7136,7 +7220,7 @@
       </c>
     </row>
     <row r="268" spans="1:5">
-      <c r="A268" s="2"/>
+      <c r="A268" s="3"/>
       <c r="B268" s="6"/>
       <c r="C268" s="6" t="s">
         <v>673</v>
@@ -7149,7 +7233,7 @@
       </c>
     </row>
     <row r="269" spans="1:5">
-      <c r="A269" s="2"/>
+      <c r="A269" s="3"/>
       <c r="B269" s="6"/>
       <c r="C269" s="6" t="s">
         <v>675</v>
@@ -7162,7 +7246,7 @@
       </c>
     </row>
     <row r="270" spans="1:5">
-      <c r="A270" s="2"/>
+      <c r="A270" s="3"/>
       <c r="B270" s="6"/>
       <c r="C270" s="6" t="s">
         <v>677</v>
@@ -7175,7 +7259,7 @@
       </c>
     </row>
     <row r="271" spans="1:5">
-      <c r="A271" s="2"/>
+      <c r="A271" s="3"/>
       <c r="B271" s="6"/>
       <c r="C271" s="6" t="s">
         <v>680</v>
@@ -7188,7 +7272,7 @@
       </c>
     </row>
     <row r="272" spans="1:5">
-      <c r="A272" s="2"/>
+      <c r="A272" s="3"/>
       <c r="B272" s="6"/>
       <c r="C272" s="6" t="s">
         <v>683</v>
@@ -7201,7 +7285,7 @@
       </c>
     </row>
     <row r="273" spans="1:5">
-      <c r="A273" s="2"/>
+      <c r="A273" s="3"/>
       <c r="B273" s="6"/>
       <c r="C273" s="6" t="s">
         <v>685</v>
@@ -7214,7 +7298,7 @@
       </c>
     </row>
     <row r="274" spans="1:5">
-      <c r="A274" s="2"/>
+      <c r="A274" s="3"/>
       <c r="B274" s="6"/>
       <c r="C274" s="6" t="s">
         <v>687</v>
@@ -7227,7 +7311,7 @@
       </c>
     </row>
     <row r="275" spans="1:5">
-      <c r="A275" s="2"/>
+      <c r="A275" s="3"/>
       <c r="B275" s="6"/>
       <c r="C275" s="6" t="s">
         <v>689</v>
@@ -7240,7 +7324,7 @@
       </c>
     </row>
     <row r="276" spans="1:5">
-      <c r="A276" s="2"/>
+      <c r="A276" s="3"/>
       <c r="B276" s="6"/>
       <c r="C276" s="6" t="s">
         <v>691</v>
@@ -7253,7 +7337,7 @@
       </c>
     </row>
     <row r="277" spans="1:5">
-      <c r="A277" s="2"/>
+      <c r="A277" s="3"/>
       <c r="B277" s="6"/>
       <c r="C277" s="6" t="s">
         <v>694</v>
@@ -7266,7 +7350,7 @@
       </c>
     </row>
     <row r="278" spans="1:5">
-      <c r="A278" s="2"/>
+      <c r="A278" s="3"/>
       <c r="B278" s="6"/>
       <c r="C278" s="6" t="s">
         <v>443</v>
@@ -7279,7 +7363,7 @@
       </c>
     </row>
     <row r="279" spans="1:5">
-      <c r="A279" s="2"/>
+      <c r="A279" s="3"/>
       <c r="B279" s="6"/>
       <c r="C279" s="6" t="s">
         <v>697</v>
@@ -7292,7 +7376,7 @@
       </c>
     </row>
     <row r="280" spans="1:5">
-      <c r="A280" s="2"/>
+      <c r="A280" s="3"/>
       <c r="B280" s="6"/>
       <c r="C280" s="6" t="s">
         <v>700</v>
@@ -7305,7 +7389,7 @@
       </c>
     </row>
     <row r="281" spans="1:5">
-      <c r="A281" s="2"/>
+      <c r="A281" s="3"/>
       <c r="B281" s="6"/>
       <c r="C281" s="6" t="s">
         <v>702</v>
@@ -7318,7 +7402,7 @@
       </c>
     </row>
     <row r="282" spans="1:5">
-      <c r="A282" s="2"/>
+      <c r="A282" s="3"/>
       <c r="B282" s="6"/>
       <c r="C282" s="6" t="s">
         <v>704</v>
@@ -7331,7 +7415,7 @@
       </c>
     </row>
     <row r="283" spans="1:5">
-      <c r="A283" s="2"/>
+      <c r="A283" s="3"/>
       <c r="B283" s="6"/>
       <c r="C283" s="6" t="s">
         <v>706</v>
@@ -7344,7 +7428,7 @@
       </c>
     </row>
     <row r="284" spans="1:5">
-      <c r="A284" s="2"/>
+      <c r="A284" s="3"/>
       <c r="B284" s="6"/>
       <c r="C284" s="6" t="s">
         <v>709</v>
@@ -7357,7 +7441,7 @@
       </c>
     </row>
     <row r="285" spans="1:5">
-      <c r="A285" s="2"/>
+      <c r="A285" s="3"/>
       <c r="B285" s="6"/>
       <c r="C285" s="6" t="s">
         <v>711</v>
@@ -7370,7 +7454,7 @@
       </c>
     </row>
     <row r="286" spans="1:5">
-      <c r="A286" s="2"/>
+      <c r="A286" s="3"/>
       <c r="B286" s="6"/>
       <c r="C286" s="6" t="s">
         <v>713</v>
@@ -7383,7 +7467,7 @@
       </c>
     </row>
     <row r="287" spans="1:5">
-      <c r="A287" s="2"/>
+      <c r="A287" s="3"/>
       <c r="B287" s="6"/>
       <c r="C287" s="6" t="s">
         <v>716</v>
@@ -7396,7 +7480,7 @@
       </c>
     </row>
     <row r="288" spans="1:5">
-      <c r="A288" s="2"/>
+      <c r="A288" s="3"/>
       <c r="B288" s="6"/>
       <c r="C288" s="6" t="s">
         <v>719</v>
@@ -7409,7 +7493,7 @@
       </c>
     </row>
     <row r="289" spans="1:5">
-      <c r="A289" s="2"/>
+      <c r="A289" s="3"/>
       <c r="B289" s="6"/>
       <c r="C289" s="6" t="s">
         <v>722</v>
@@ -7422,7 +7506,7 @@
       </c>
     </row>
     <row r="290" spans="1:5">
-      <c r="A290" s="2"/>
+      <c r="A290" s="3"/>
       <c r="B290" s="6"/>
       <c r="C290" s="6" t="s">
         <v>724</v>
@@ -7435,7 +7519,7 @@
       </c>
     </row>
     <row r="291" spans="1:5">
-      <c r="A291" s="2"/>
+      <c r="A291" s="3"/>
       <c r="B291" s="6"/>
       <c r="C291" s="6" t="s">
         <v>726</v>
@@ -7448,7 +7532,7 @@
       </c>
     </row>
     <row r="292" spans="1:5">
-      <c r="A292" s="2"/>
+      <c r="A292" s="3"/>
       <c r="B292" s="6"/>
       <c r="C292" s="6" t="s">
         <v>728</v>
@@ -7461,7 +7545,7 @@
       </c>
     </row>
     <row r="293" spans="1:5">
-      <c r="A293" s="2"/>
+      <c r="A293" s="3"/>
       <c r="B293" s="6"/>
       <c r="C293" s="6" t="s">
         <v>731</v>
@@ -7474,7 +7558,7 @@
       </c>
     </row>
     <row r="294" spans="1:5">
-      <c r="A294" s="2"/>
+      <c r="A294" s="3"/>
       <c r="B294" s="6"/>
       <c r="C294" s="6" t="s">
         <v>733</v>
@@ -7487,7 +7571,7 @@
       </c>
     </row>
     <row r="295" spans="1:5">
-      <c r="A295" s="2"/>
+      <c r="A295" s="3"/>
       <c r="B295" s="6"/>
       <c r="C295" s="6" t="s">
         <v>735</v>
@@ -7500,7 +7584,7 @@
       </c>
     </row>
     <row r="296" spans="1:5">
-      <c r="A296" s="2"/>
+      <c r="A296" s="3"/>
       <c r="B296" s="6"/>
       <c r="C296" s="6" t="s">
         <v>738</v>
@@ -7513,7 +7597,7 @@
       </c>
     </row>
     <row r="297" spans="1:5">
-      <c r="A297" s="2"/>
+      <c r="A297" s="3"/>
       <c r="B297" s="6"/>
       <c r="C297" s="6" t="s">
         <v>741</v>
@@ -7526,7 +7610,7 @@
       </c>
     </row>
     <row r="298" spans="1:5">
-      <c r="A298" s="2"/>
+      <c r="A298" s="3"/>
       <c r="B298" s="6"/>
       <c r="C298" s="6" t="s">
         <v>744</v>
@@ -7539,7 +7623,7 @@
       </c>
     </row>
     <row r="299" spans="1:5">
-      <c r="A299" s="2"/>
+      <c r="A299" s="3"/>
       <c r="B299" s="6"/>
       <c r="C299" s="6" t="s">
         <v>747</v>
@@ -7552,7 +7636,7 @@
       </c>
     </row>
     <row r="300" spans="1:5">
-      <c r="A300" s="2"/>
+      <c r="A300" s="3"/>
       <c r="B300" s="6"/>
       <c r="C300" s="6" t="s">
         <v>749</v>
@@ -7565,7 +7649,7 @@
       </c>
     </row>
     <row r="301" spans="1:5">
-      <c r="A301" s="2"/>
+      <c r="A301" s="3"/>
       <c r="B301" s="6"/>
       <c r="C301" s="6" t="s">
         <v>752</v>
@@ -7578,7 +7662,7 @@
       </c>
     </row>
     <row r="302" spans="1:5">
-      <c r="A302" s="2"/>
+      <c r="A302" s="3"/>
       <c r="B302" s="6"/>
       <c r="C302" s="6" t="s">
         <v>754</v>
@@ -7591,7 +7675,7 @@
       </c>
     </row>
     <row r="303" spans="1:5">
-      <c r="A303" s="2"/>
+      <c r="A303" s="3"/>
       <c r="B303" s="6"/>
       <c r="C303" s="6" t="s">
         <v>756</v>
@@ -7604,7 +7688,7 @@
       </c>
     </row>
     <row r="304" spans="1:5">
-      <c r="A304" s="2"/>
+      <c r="A304" s="3"/>
       <c r="B304" s="6"/>
       <c r="C304" s="6" t="s">
         <v>758</v>
@@ -7617,7 +7701,7 @@
       </c>
     </row>
     <row r="305" spans="1:5">
-      <c r="A305" s="2"/>
+      <c r="A305" s="3"/>
       <c r="B305" s="6"/>
       <c r="C305" s="6" t="s">
         <v>760</v>
@@ -7630,7 +7714,7 @@
       </c>
     </row>
     <row r="306" spans="1:5">
-      <c r="A306" s="2"/>
+      <c r="A306" s="3"/>
       <c r="B306" s="6"/>
       <c r="C306" s="6" t="s">
         <v>763</v>
@@ -7643,7 +7727,7 @@
       </c>
     </row>
     <row r="307" spans="1:5">
-      <c r="A307" s="2"/>
+      <c r="A307" s="3"/>
       <c r="B307" s="6"/>
       <c r="C307" s="6" t="s">
         <v>766</v>
@@ -7656,7 +7740,7 @@
       </c>
     </row>
     <row r="308" spans="1:5">
-      <c r="A308" s="2"/>
+      <c r="A308" s="3"/>
       <c r="B308" s="6"/>
       <c r="C308" s="6" t="s">
         <v>768</v>
@@ -7669,7 +7753,7 @@
       </c>
     </row>
     <row r="309" spans="1:5">
-      <c r="A309" s="2"/>
+      <c r="A309" s="3"/>
       <c r="B309" s="6"/>
       <c r="C309" s="6" t="s">
         <v>770</v>
@@ -7682,7 +7766,7 @@
       </c>
     </row>
     <row r="310" spans="1:5">
-      <c r="A310" s="2"/>
+      <c r="A310" s="3"/>
       <c r="B310" s="6"/>
       <c r="C310" s="6" t="s">
         <v>773</v>
@@ -7695,7 +7779,7 @@
       </c>
     </row>
     <row r="311" spans="1:5">
-      <c r="A311" s="2"/>
+      <c r="A311" s="3"/>
       <c r="B311" s="6"/>
       <c r="C311" s="6" t="s">
         <v>776</v>
@@ -7708,7 +7792,7 @@
       </c>
     </row>
     <row r="312" spans="1:5">
-      <c r="A312" s="2"/>
+      <c r="A312" s="3"/>
       <c r="B312" s="6"/>
       <c r="C312" s="6" t="s">
         <v>778</v>
@@ -7721,7 +7805,7 @@
       </c>
     </row>
     <row r="313" spans="1:5">
-      <c r="A313" s="2"/>
+      <c r="A313" s="3"/>
       <c r="B313" s="6"/>
       <c r="C313" s="6" t="s">
         <v>780</v>
@@ -7734,7 +7818,7 @@
       </c>
     </row>
     <row r="314" spans="1:5">
-      <c r="A314" s="2"/>
+      <c r="A314" s="3"/>
       <c r="B314" s="6"/>
       <c r="C314" s="6" t="s">
         <v>782</v>
@@ -7747,7 +7831,7 @@
       </c>
     </row>
     <row r="315" spans="1:5">
-      <c r="A315" s="2"/>
+      <c r="A315" s="3"/>
       <c r="B315" s="6"/>
       <c r="C315" s="6" t="s">
         <v>785</v>
@@ -7760,7 +7844,7 @@
       </c>
     </row>
     <row r="316" spans="1:5">
-      <c r="A316" s="2"/>
+      <c r="A316" s="3"/>
       <c r="B316" s="6"/>
       <c r="C316" s="6" t="s">
         <v>787</v>
@@ -7773,7 +7857,7 @@
       </c>
     </row>
     <row r="317" spans="1:5">
-      <c r="A317" s="2"/>
+      <c r="A317" s="3"/>
       <c r="B317" s="6"/>
       <c r="C317" s="6" t="s">
         <v>789</v>
@@ -7786,7 +7870,7 @@
       </c>
     </row>
     <row r="318" spans="1:5">
-      <c r="A318" s="2"/>
+      <c r="A318" s="3"/>
       <c r="B318" s="6"/>
       <c r="C318" s="6" t="s">
         <v>792</v>
@@ -7799,7 +7883,7 @@
       </c>
     </row>
     <row r="319" spans="1:5">
-      <c r="A319" s="2"/>
+      <c r="A319" s="3"/>
       <c r="B319" s="6"/>
       <c r="C319" s="6" t="s">
         <v>795</v>
@@ -7812,7 +7896,7 @@
       </c>
     </row>
     <row r="320" spans="1:5">
-      <c r="A320" s="2"/>
+      <c r="A320" s="3"/>
       <c r="B320" s="6"/>
       <c r="C320" s="6" t="s">
         <v>798</v>
@@ -7825,7 +7909,7 @@
       </c>
     </row>
     <row r="321" spans="1:5">
-      <c r="A321" s="2"/>
+      <c r="A321" s="3"/>
       <c r="B321" s="6"/>
       <c r="C321" s="6" t="s">
         <v>800</v>
@@ -7838,7 +7922,7 @@
       </c>
     </row>
     <row r="322" spans="1:5">
-      <c r="A322" s="2"/>
+      <c r="A322" s="3"/>
       <c r="B322" s="6"/>
       <c r="C322" s="6" t="s">
         <v>802</v>
@@ -7851,7 +7935,7 @@
       </c>
     </row>
     <row r="323" spans="1:5">
-      <c r="A323" s="2"/>
+      <c r="A323" s="3"/>
       <c r="B323" s="6"/>
       <c r="C323" s="6" t="s">
         <v>804</v>
@@ -7870,7 +7954,7 @@
       <c r="E324" s="6"/>
     </row>
     <row r="325" spans="1:5">
-      <c r="A325" s="2" t="s">
+      <c r="A325" s="3" t="s">
         <v>807</v>
       </c>
       <c r="C325" s="6" t="s">
@@ -7884,7 +7968,7 @@
       </c>
     </row>
     <row r="326" spans="1:5">
-      <c r="A326" s="2"/>
+      <c r="A326" s="3"/>
       <c r="C326" s="6" t="s">
         <v>811</v>
       </c>
@@ -7896,7 +7980,7 @@
       </c>
     </row>
     <row r="327" spans="1:5">
-      <c r="A327" s="2"/>
+      <c r="A327" s="3"/>
       <c r="C327" s="6" t="s">
         <v>814</v>
       </c>
@@ -8018,10 +8102,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="10.6666666666667" customWidth="1"/>
+    <col min="1" max="1" width="15.2222222222222" customWidth="1"/>
     <col min="2" max="2" width="17.7777777777778" customWidth="1"/>
     <col min="3" max="3" width="61.8888888888889" customWidth="1"/>
     <col min="4" max="4" width="15.6666666666667" customWidth="1"/>
@@ -8219,7 +8303,268 @@
         <v>849</v>
       </c>
     </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>817</v>
+      </c>
+      <c r="B12" t="s">
+        <v>818</v>
+      </c>
+      <c r="C12" t="s">
+        <v>850</v>
+      </c>
+      <c r="D12" t="s">
+        <v>828</v>
+      </c>
+      <c r="F12" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>817</v>
+      </c>
+      <c r="B13" t="s">
+        <v>818</v>
+      </c>
+      <c r="C13" t="s">
+        <v>852</v>
+      </c>
+      <c r="D13" t="s">
+        <v>828</v>
+      </c>
+      <c r="F13" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>817</v>
+      </c>
+      <c r="B14" t="s">
+        <v>818</v>
+      </c>
+      <c r="C14" t="s">
+        <v>854</v>
+      </c>
+      <c r="D14" t="s">
+        <v>828</v>
+      </c>
+      <c r="F14" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>817</v>
+      </c>
+      <c r="B15" t="s">
+        <v>818</v>
+      </c>
+      <c r="C15" t="s">
+        <v>856</v>
+      </c>
+      <c r="D15" t="s">
+        <v>828</v>
+      </c>
+      <c r="F15" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>817</v>
+      </c>
+      <c r="B16" t="s">
+        <v>818</v>
+      </c>
+      <c r="C16" t="s">
+        <v>858</v>
+      </c>
+      <c r="D16" t="s">
+        <v>859</v>
+      </c>
+      <c r="F16" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>817</v>
+      </c>
+      <c r="B17" t="s">
+        <v>818</v>
+      </c>
+      <c r="C17" t="s">
+        <v>858</v>
+      </c>
+      <c r="D17" t="s">
+        <v>859</v>
+      </c>
+      <c r="F17" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>817</v>
+      </c>
+      <c r="B18" t="s">
+        <v>818</v>
+      </c>
+      <c r="C18" t="s">
+        <v>862</v>
+      </c>
+      <c r="D18" t="s">
+        <v>828</v>
+      </c>
+      <c r="F18" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" t="s">
+        <v>817</v>
+      </c>
+      <c r="B19" t="s">
+        <v>818</v>
+      </c>
+      <c r="C19" t="s">
+        <v>864</v>
+      </c>
+      <c r="D19" t="s">
+        <v>832</v>
+      </c>
+      <c r="F19" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>817</v>
+      </c>
+      <c r="B20" t="s">
+        <v>818</v>
+      </c>
+      <c r="C20" t="s">
+        <v>866</v>
+      </c>
+      <c r="D20" t="s">
+        <v>867</v>
+      </c>
+      <c r="E20" t="s">
+        <v>868</v>
+      </c>
+      <c r="F20" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>817</v>
+      </c>
+      <c r="B21" t="s">
+        <v>818</v>
+      </c>
+      <c r="C21" t="s">
+        <v>870</v>
+      </c>
+      <c r="D21" t="s">
+        <v>832</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
+        <v>817</v>
+      </c>
+      <c r="B22" t="s">
+        <v>818</v>
+      </c>
+      <c r="C22" t="s">
+        <v>872</v>
+      </c>
+      <c r="D22" t="s">
+        <v>832</v>
+      </c>
+      <c r="F22" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>817</v>
+      </c>
+      <c r="B23" t="s">
+        <v>818</v>
+      </c>
+      <c r="C23" t="s">
+        <v>872</v>
+      </c>
+      <c r="D23" t="s">
+        <v>832</v>
+      </c>
+      <c r="F23" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>817</v>
+      </c>
+      <c r="B24" t="s">
+        <v>818</v>
+      </c>
+      <c r="C24" t="s">
+        <v>872</v>
+      </c>
+      <c r="D24" t="s">
+        <v>832</v>
+      </c>
+      <c r="F24" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
+        <v>817</v>
+      </c>
+      <c r="B25" t="s">
+        <v>818</v>
+      </c>
+      <c r="C25" t="s">
+        <v>872</v>
+      </c>
+      <c r="D25" t="s">
+        <v>832</v>
+      </c>
+      <c r="F25" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
+        <v>817</v>
+      </c>
+      <c r="B26" t="s">
+        <v>818</v>
+      </c>
+      <c r="C26" t="s">
+        <v>872</v>
+      </c>
+      <c r="D26" t="s">
+        <v>832</v>
+      </c>
+      <c r="F26" t="s">
+        <v>877</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F21" r:id="rId1" display="https://github.com/TTY-flag/community_reports/blob/main/openeuler/ubs-io/scan-results/details/VULN-IO-001.md"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/社区代码仓列表.xlsx
+++ b/社区代码仓列表.xlsx
@@ -103,7 +103,7 @@
     <t>Gluten</t>
   </si>
   <si>
-    <t>https://gitee.com/openeuler/Gluten</t>
+    <t>https://atomgit.com/openeuler/Gluten</t>
   </si>
   <si>
     <t>BoostSRA 搜推广套件</t>
@@ -3905,7 +3905,9 @@
         <v>17</v>
       </c>
       <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+      <c r="G7" s="3">
+        <v>4</v>
+      </c>
       <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:10">
@@ -4031,7 +4033,9 @@
         <v>17</v>
       </c>
       <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
+      <c r="G14" s="3">
+        <v>2</v>
+      </c>
       <c r="H14" s="3"/>
     </row>
     <row r="15" spans="1:10">
@@ -9235,7 +9239,7 @@
     <hyperlink ref="D9" r:id="rId44" display="https://gitcode.com/boostkit/tensorflow-serving"/>
     <hyperlink ref="D8" r:id="rId45" display="https://gitcode.com/boostkit/tensorflow"/>
     <hyperlink ref="D7" r:id="rId46" display="https://gitcode.com/boostkit/kvecturbo" tooltip="https://gitcode.com/boostkit/kvecturbo"/>
-    <hyperlink ref="D6" r:id="rId47" display="https://gitee.com/openeuler/Gluten"/>
+    <hyperlink ref="D6" r:id="rId47" display="https://atomgit.com/openeuler/Gluten" tooltip="https://atomgit.com/openeuler/Gluten"/>
     <hyperlink ref="D105" r:id="rId48" display="https://gitcode.com/cann/runtime"/>
     <hyperlink ref="D15" r:id="rId49" display="https://gitcode.com/boostkit/hadoop/tree/hdfs-ec-24.0.0/"/>
   </hyperlinks>

--- a/社区代码仓列表.xlsx
+++ b/社区代码仓列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18960" windowHeight="12851"/>
+    <workbookView windowWidth="27083" windowHeight="12851"/>
   </bookViews>
   <sheets>
     <sheet name="社区开源仓列表" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
     <t>OmniAdaptor</t>
   </si>
   <si>
-    <t>https://gitee.com/openeuler/OmniAdaptor</t>
+    <t>https://atomgit.com/openeuler/OmniAdaptor</t>
   </si>
   <si>
     <t>Scala</t>
@@ -82,7 +82,7 @@
     <t>OmniOperator</t>
   </si>
   <si>
-    <t>https://gitee.com/openeuler/OmniOperator</t>
+    <t>https://atomgit.com/openeuler/OmniOperator</t>
   </si>
   <si>
     <t>C++</t>
@@ -91,13 +91,13 @@
     <t>OmniStream</t>
   </si>
   <si>
-    <t>https://gitee.com/openeuler/OmniStream</t>
+    <t>https://atomgit.com/openeuler/OmniStream</t>
   </si>
   <si>
     <t>OmniStateStore</t>
   </si>
   <si>
-    <t>https://gitee.com/openeuler/OmniStateStore</t>
+    <t>https://atomgit.com/openeuler/OmniStateStore</t>
   </si>
   <si>
     <t>Gluten</t>
@@ -3343,7 +3343,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3361,6 +3361,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="6" applyFill="1">
       <alignment vertical="center"/>
@@ -3810,7 +3813,7 @@
       <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="3" t="s">
@@ -3826,7 +3829,7 @@
       <c r="C3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -3844,7 +3847,7 @@
       <c r="C4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="6" t="s">
         <v>19</v>
       </c>
       <c r="E4" s="3" t="s">
@@ -3862,7 +3865,7 @@
       <c r="C5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E5" s="3" t="s">
@@ -3880,7 +3883,7 @@
       <c r="C6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>23</v>
       </c>
       <c r="E6" s="3" t="s">
@@ -3898,7 +3901,7 @@
       <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>26</v>
       </c>
       <c r="E7" s="3" t="s">
@@ -3916,7 +3919,7 @@
       <c r="C8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="8" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="3" t="s">
@@ -3934,7 +3937,7 @@
       <c r="C9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>31</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -3952,7 +3955,7 @@
       <c r="C10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="8" t="s">
         <v>33</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -3970,7 +3973,7 @@
       <c r="C11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="8" t="s">
         <v>35</v>
       </c>
       <c r="E11" s="3" t="s">
@@ -3988,7 +3991,7 @@
       <c r="C12" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="8" t="s">
         <v>37</v>
       </c>
       <c r="E12" s="3" t="s">
@@ -4008,7 +4011,7 @@
       <c r="C13" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="8" t="s">
         <v>41</v>
       </c>
       <c r="E13" s="3" t="s">
@@ -4026,7 +4029,7 @@
       <c r="C14" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="8" t="s">
         <v>44</v>
       </c>
       <c r="E14" s="3" t="s">
@@ -4044,7 +4047,7 @@
       <c r="C15" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="9" t="s">
         <v>46</v>
       </c>
       <c r="E15" s="3" t="s">
@@ -4062,7 +4065,7 @@
       <c r="C16" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="8" t="s">
         <v>50</v>
       </c>
       <c r="E16" s="3" t="s">
@@ -4080,7 +4083,7 @@
       <c r="C17" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="8" t="s">
         <v>53</v>
       </c>
       <c r="E17" s="3" t="s">
@@ -4100,7 +4103,7 @@
       <c r="C18" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="8" t="s">
         <v>56</v>
       </c>
       <c r="E18" s="3" t="s">
@@ -4118,7 +4121,7 @@
       <c r="C19" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="8" t="s">
         <v>59</v>
       </c>
       <c r="E19" s="3" t="s">
@@ -4136,7 +4139,7 @@
       <c r="C20" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="8" t="s">
         <v>63</v>
       </c>
       <c r="E20" s="3" t="s">
@@ -4154,7 +4157,7 @@
       <c r="C21" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="8" t="s">
         <v>66</v>
       </c>
       <c r="E21" s="3" t="s">
@@ -4172,7 +4175,7 @@
       <c r="C22" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="8" t="s">
         <v>68</v>
       </c>
       <c r="E22" s="3" t="s">
@@ -4192,7 +4195,7 @@
       <c r="C23" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="7" t="s">
         <v>71</v>
       </c>
       <c r="E23" s="3" t="s">
@@ -4210,7 +4213,7 @@
       <c r="C24" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="8" t="s">
         <v>73</v>
       </c>
       <c r="E24" s="3" t="s">
@@ -4228,7 +4231,7 @@
       <c r="C25" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="8" t="s">
         <v>75</v>
       </c>
       <c r="E25" s="3" t="s">
@@ -4248,7 +4251,7 @@
       <c r="C26" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="8" t="s">
         <v>78</v>
       </c>
       <c r="E26" s="3" t="s">
@@ -4270,7 +4273,7 @@
       <c r="C27" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="7" t="s">
         <v>81</v>
       </c>
       <c r="E27" s="3" t="s">
@@ -4290,7 +4293,7 @@
       <c r="C28" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="8" t="s">
         <v>85</v>
       </c>
       <c r="E28" s="3" t="s">
@@ -4308,7 +4311,7 @@
       <c r="C29" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="7" t="s">
         <v>87</v>
       </c>
       <c r="E29" s="3" t="s">
@@ -4328,7 +4331,7 @@
       <c r="C30" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="7" t="s">
         <v>90</v>
       </c>
       <c r="E30" s="3" t="s">
@@ -4348,7 +4351,7 @@
       <c r="C31" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="8" t="s">
         <v>93</v>
       </c>
       <c r="E31" s="3" t="s">
@@ -4361,4790 +4364,4790 @@
       <c r="H31" s="3"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="9"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
+      <c r="A32" s="10"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="11" t="s">
+      <c r="A33" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D33" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="11"/>
-      <c r="B34" s="12" t="s">
+      <c r="A34" s="12"/>
+      <c r="B34" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D34" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="11"/>
-      <c r="B35" s="12" t="s">
+      <c r="A35" s="12"/>
+      <c r="B35" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="11"/>
-      <c r="B36" s="12" t="s">
+      <c r="A36" s="12"/>
+      <c r="B36" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="D36" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13">
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14">
         <v>2</v>
       </c>
-      <c r="H36" s="13">
+      <c r="H36" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="11"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="13" t="s">
+      <c r="A37" s="12"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D37" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13">
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14">
         <v>23</v>
       </c>
-      <c r="H37" s="13">
+      <c r="H37" s="14">
         <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="11"/>
-      <c r="B38" s="12"/>
-      <c r="C38" s="13" t="s">
+      <c r="A38" s="12"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="D38" s="13" t="s">
+      <c r="D38" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13">
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14">
         <v>3</v>
       </c>
-      <c r="H38" s="13">
+      <c r="H38" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="11"/>
-      <c r="B39" s="12"/>
-      <c r="C39" s="13" t="s">
+      <c r="A39" s="12"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="D39" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13">
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14">
         <v>1</v>
       </c>
-      <c r="H39" s="13">
+      <c r="H39" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="11"/>
-      <c r="B40" s="12" t="s">
+      <c r="A40" s="12"/>
+      <c r="B40" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="D40" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13">
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14">
         <v>11</v>
       </c>
-      <c r="H40" s="13"/>
+      <c r="H40" s="14"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="11"/>
-      <c r="B41" s="12"/>
-      <c r="C41" s="13" t="s">
+      <c r="A41" s="12"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="D41" s="13" t="s">
+      <c r="D41" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13">
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14">
         <v>25</v>
       </c>
-      <c r="H41" s="13"/>
+      <c r="H41" s="14"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="11"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="13" t="s">
+      <c r="A42" s="12"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="D42" s="13" t="s">
+      <c r="D42" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13">
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14">
         <v>22</v>
       </c>
-      <c r="H42" s="13"/>
+      <c r="H42" s="14"/>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="11"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="13" t="s">
+      <c r="A43" s="12"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D43" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13">
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14">
         <v>6</v>
       </c>
-      <c r="H43" s="13"/>
+      <c r="H43" s="14"/>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="11"/>
-      <c r="B44" s="12"/>
-      <c r="C44" s="13" t="s">
+      <c r="A44" s="12"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D44" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13">
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14">
         <v>4</v>
       </c>
-      <c r="H44" s="13"/>
+      <c r="H44" s="14"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="11"/>
-      <c r="B45" s="12" t="s">
+      <c r="A45" s="12"/>
+      <c r="B45" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="D45" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13">
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14">
         <v>0</v>
       </c>
-      <c r="H45" s="13">
+      <c r="H45" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="11"/>
-      <c r="B46" s="12"/>
-      <c r="C46" s="13" t="s">
+      <c r="A46" s="12"/>
+      <c r="B46" s="13"/>
+      <c r="C46" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="D46" s="13" t="s">
+      <c r="D46" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13">
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14">
         <v>2</v>
       </c>
-      <c r="H46" s="13"/>
+      <c r="H46" s="14"/>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="11"/>
-      <c r="B47" s="12"/>
-      <c r="C47" s="13" t="s">
+      <c r="A47" s="12"/>
+      <c r="B47" s="13"/>
+      <c r="C47" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="D47" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13">
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14">
         <v>2</v>
       </c>
-      <c r="H47" s="13"/>
+      <c r="H47" s="14"/>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="11"/>
-      <c r="B48" s="12"/>
-      <c r="C48" s="13" t="s">
+      <c r="A48" s="12"/>
+      <c r="B48" s="13"/>
+      <c r="C48" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="D48" s="13" t="s">
+      <c r="D48" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13">
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14">
         <v>1</v>
       </c>
-      <c r="H48" s="13">
+      <c r="H48" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="11"/>
-      <c r="B49" s="12"/>
-      <c r="C49" s="13" t="s">
+      <c r="A49" s="12"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="D49" s="13" t="s">
+      <c r="D49" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13">
+      <c r="E49" s="14"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14">
         <v>0</v>
       </c>
-      <c r="H49" s="13"/>
+      <c r="H49" s="14"/>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="11"/>
-      <c r="B50" s="12"/>
-      <c r="C50" s="13" t="s">
+      <c r="A50" s="12"/>
+      <c r="B50" s="13"/>
+      <c r="C50" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="D50" s="13" t="s">
+      <c r="D50" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13">
+      <c r="E50" s="14"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="14">
         <v>6</v>
       </c>
-      <c r="H50" s="13"/>
+      <c r="H50" s="14"/>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="11"/>
-      <c r="B51" s="12"/>
-      <c r="C51" s="13" t="s">
+      <c r="A51" s="12"/>
+      <c r="B51" s="13"/>
+      <c r="C51" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="D51" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13">
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14">
         <v>8</v>
       </c>
-      <c r="H51" s="13"/>
+      <c r="H51" s="14"/>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="11"/>
-      <c r="B52" s="12"/>
-      <c r="C52" s="13" t="s">
+      <c r="A52" s="12"/>
+      <c r="B52" s="13"/>
+      <c r="C52" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="D52" s="13" t="s">
+      <c r="D52" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13">
+      <c r="E52" s="14"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14">
         <v>0</v>
       </c>
-      <c r="H52" s="13"/>
+      <c r="H52" s="14"/>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="11"/>
-      <c r="B53" s="12" t="s">
+      <c r="A53" s="12"/>
+      <c r="B53" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="D53" s="13" t="s">
+      <c r="D53" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13">
+      <c r="E53" s="14"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14">
         <v>1</v>
       </c>
-      <c r="H53" s="13"/>
+      <c r="H53" s="14"/>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="11"/>
-      <c r="B54" s="12"/>
-      <c r="C54" s="13" t="s">
+      <c r="A54" s="12"/>
+      <c r="B54" s="13"/>
+      <c r="C54" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="D54" s="13" t="s">
+      <c r="D54" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13">
+      <c r="E54" s="14"/>
+      <c r="F54" s="14"/>
+      <c r="G54" s="14">
         <v>0</v>
       </c>
-      <c r="H54" s="13"/>
+      <c r="H54" s="14"/>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="11"/>
-      <c r="B55" s="12"/>
-      <c r="C55" s="13" t="s">
+      <c r="A55" s="12"/>
+      <c r="B55" s="13"/>
+      <c r="C55" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="D55" s="13" t="s">
+      <c r="D55" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="13">
+      <c r="E55" s="14"/>
+      <c r="F55" s="14"/>
+      <c r="G55" s="14">
         <v>6</v>
       </c>
-      <c r="H55" s="13"/>
+      <c r="H55" s="14"/>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="11"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="14" t="s">
+      <c r="A56" s="12"/>
+      <c r="B56" s="13"/>
+      <c r="C56" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="D56" s="13" t="s">
+      <c r="D56" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="E56" s="13"/>
-      <c r="F56" s="13"/>
-      <c r="G56" s="13">
+      <c r="E56" s="14"/>
+      <c r="F56" s="14"/>
+      <c r="G56" s="14">
         <v>1</v>
       </c>
-      <c r="H56" s="13"/>
+      <c r="H56" s="14"/>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="11"/>
-      <c r="B57" s="12"/>
-      <c r="C57" s="14" t="s">
+      <c r="A57" s="12"/>
+      <c r="B57" s="13"/>
+      <c r="C57" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="D57" s="13" t="s">
+      <c r="D57" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13">
+      <c r="E57" s="14"/>
+      <c r="F57" s="14"/>
+      <c r="G57" s="14">
         <v>2</v>
       </c>
-      <c r="H57" s="13"/>
+      <c r="H57" s="14"/>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="11"/>
-      <c r="B58" s="12"/>
-      <c r="C58" s="14" t="s">
+      <c r="A58" s="12"/>
+      <c r="B58" s="13"/>
+      <c r="C58" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="D58" s="13" t="s">
+      <c r="D58" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13">
+      <c r="E58" s="14"/>
+      <c r="F58" s="14"/>
+      <c r="G58" s="14">
         <v>7</v>
       </c>
-      <c r="H58" s="13"/>
+      <c r="H58" s="14"/>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="11"/>
-      <c r="B59" s="12"/>
-      <c r="C59" s="14" t="s">
+      <c r="A59" s="12"/>
+      <c r="B59" s="13"/>
+      <c r="C59" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="D59" s="13" t="s">
+      <c r="D59" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="13">
+      <c r="E59" s="14"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14">
         <v>9</v>
       </c>
-      <c r="H59" s="13"/>
+      <c r="H59" s="14"/>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="11"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="14" t="s">
+      <c r="A60" s="12"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="D60" s="13" t="s">
+      <c r="D60" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="13">
+      <c r="E60" s="14"/>
+      <c r="F60" s="14"/>
+      <c r="G60" s="14">
         <v>0</v>
       </c>
-      <c r="H60" s="13"/>
+      <c r="H60" s="14"/>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="11"/>
-      <c r="B61" s="12"/>
-      <c r="C61" s="14" t="s">
+      <c r="A61" s="12"/>
+      <c r="B61" s="13"/>
+      <c r="C61" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="D61" s="13" t="s">
+      <c r="D61" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="E61" s="13"/>
-      <c r="F61" s="13"/>
-      <c r="G61" s="13">
+      <c r="E61" s="14"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="14">
         <v>3</v>
       </c>
-      <c r="H61" s="13"/>
+      <c r="H61" s="14"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="11"/>
-      <c r="B62" s="12"/>
-      <c r="C62" s="14" t="s">
+      <c r="A62" s="12"/>
+      <c r="B62" s="13"/>
+      <c r="C62" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="D62" s="13" t="s">
+      <c r="D62" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="E62" s="13"/>
-      <c r="F62" s="13"/>
-      <c r="G62" s="13">
+      <c r="E62" s="14"/>
+      <c r="F62" s="14"/>
+      <c r="G62" s="14">
         <v>7</v>
       </c>
-      <c r="H62" s="13"/>
+      <c r="H62" s="14"/>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="11"/>
-      <c r="B63" s="12"/>
-      <c r="C63" s="14" t="s">
+      <c r="A63" s="12"/>
+      <c r="B63" s="13"/>
+      <c r="C63" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="D63" s="13" t="s">
+      <c r="D63" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="E63" s="13"/>
-      <c r="F63" s="13"/>
-      <c r="G63" s="13">
+      <c r="E63" s="14"/>
+      <c r="F63" s="14"/>
+      <c r="G63" s="14">
         <v>8</v>
       </c>
-      <c r="H63" s="13"/>
+      <c r="H63" s="14"/>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="11"/>
-      <c r="B64" s="12"/>
-      <c r="C64" s="14" t="s">
+      <c r="A64" s="12"/>
+      <c r="B64" s="13"/>
+      <c r="C64" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="D64" s="13" t="s">
+      <c r="D64" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="E64" s="13"/>
-      <c r="F64" s="13"/>
-      <c r="G64" s="13">
+      <c r="E64" s="14"/>
+      <c r="F64" s="14"/>
+      <c r="G64" s="14">
         <v>0</v>
       </c>
-      <c r="H64" s="13"/>
+      <c r="H64" s="14"/>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65" s="11"/>
-      <c r="B65" s="12"/>
-      <c r="C65" s="14" t="s">
+      <c r="A65" s="12"/>
+      <c r="B65" s="13"/>
+      <c r="C65" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="D65" s="13" t="s">
+      <c r="D65" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="E65" s="13"/>
-      <c r="F65" s="13"/>
-      <c r="G65" s="13">
+      <c r="E65" s="14"/>
+      <c r="F65" s="14"/>
+      <c r="G65" s="14">
         <v>7</v>
       </c>
-      <c r="H65" s="13"/>
+      <c r="H65" s="14"/>
     </row>
     <row r="66" spans="1:8">
-      <c r="A66" s="11"/>
-      <c r="B66" s="12"/>
-      <c r="C66" s="14" t="s">
+      <c r="A66" s="12"/>
+      <c r="B66" s="13"/>
+      <c r="C66" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="D66" s="13" t="s">
+      <c r="D66" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="13">
+      <c r="E66" s="14"/>
+      <c r="F66" s="14"/>
+      <c r="G66" s="14">
         <v>3</v>
       </c>
-      <c r="H66" s="13"/>
+      <c r="H66" s="14"/>
     </row>
     <row r="67" spans="1:8">
-      <c r="A67" s="11"/>
-      <c r="B67" s="12"/>
-      <c r="C67" s="14" t="s">
+      <c r="A67" s="12"/>
+      <c r="B67" s="13"/>
+      <c r="C67" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="D67" s="15" t="s">
+      <c r="D67" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="E67" s="13"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="13">
+      <c r="E67" s="14"/>
+      <c r="F67" s="14"/>
+      <c r="G67" s="14">
         <v>8</v>
       </c>
-      <c r="H67" s="13"/>
+      <c r="H67" s="14"/>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" s="11"/>
-      <c r="B68" s="12"/>
-      <c r="C68" s="14" t="s">
+      <c r="A68" s="12"/>
+      <c r="B68" s="13"/>
+      <c r="C68" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="D68" s="13" t="s">
+      <c r="D68" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13">
+      <c r="E68" s="14"/>
+      <c r="F68" s="14"/>
+      <c r="G68" s="14">
         <v>0</v>
       </c>
-      <c r="H68" s="13"/>
+      <c r="H68" s="14"/>
     </row>
     <row r="69" spans="1:8">
-      <c r="A69" s="11"/>
-      <c r="B69" s="12"/>
-      <c r="C69" s="14" t="s">
+      <c r="A69" s="12"/>
+      <c r="B69" s="13"/>
+      <c r="C69" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="D69" s="13" t="s">
+      <c r="D69" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="E69" s="13"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13">
+      <c r="E69" s="14"/>
+      <c r="F69" s="14"/>
+      <c r="G69" s="14">
         <v>1</v>
       </c>
-      <c r="H69" s="13"/>
+      <c r="H69" s="14"/>
     </row>
     <row r="70" spans="1:8">
-      <c r="A70" s="11"/>
-      <c r="B70" s="12"/>
-      <c r="C70" s="14" t="s">
+      <c r="A70" s="12"/>
+      <c r="B70" s="13"/>
+      <c r="C70" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="D70" s="13" t="s">
+      <c r="D70" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="E70" s="13"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13">
+      <c r="E70" s="14"/>
+      <c r="F70" s="14"/>
+      <c r="G70" s="14">
         <v>0</v>
       </c>
-      <c r="H70" s="13"/>
+      <c r="H70" s="14"/>
     </row>
     <row r="71" spans="1:8">
-      <c r="A71" s="11"/>
-      <c r="B71" s="12"/>
-      <c r="C71" s="14" t="s">
+      <c r="A71" s="12"/>
+      <c r="B71" s="13"/>
+      <c r="C71" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="D71" s="13" t="s">
+      <c r="D71" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="13">
+      <c r="E71" s="14"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="14">
         <v>0</v>
       </c>
-      <c r="H71" s="13"/>
+      <c r="H71" s="14"/>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="11"/>
-      <c r="B72" s="12"/>
-      <c r="C72" s="14" t="s">
+      <c r="A72" s="12"/>
+      <c r="B72" s="13"/>
+      <c r="C72" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="D72" s="13" t="s">
+      <c r="D72" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="13">
+      <c r="E72" s="14"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="14">
         <v>0</v>
       </c>
-      <c r="H72" s="13"/>
+      <c r="H72" s="14"/>
     </row>
     <row r="73" spans="1:8">
-      <c r="A73" s="11"/>
-      <c r="B73" s="12"/>
-      <c r="C73" s="14" t="s">
+      <c r="A73" s="12"/>
+      <c r="B73" s="13"/>
+      <c r="C73" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="D73" s="16" t="s">
+      <c r="D73" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="E73" s="13"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="13">
+      <c r="E73" s="14"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14">
         <v>9</v>
       </c>
-      <c r="H73" s="13"/>
+      <c r="H73" s="14"/>
     </row>
     <row r="74" spans="1:8">
-      <c r="A74" s="11"/>
-      <c r="B74" s="12"/>
-      <c r="C74" s="14" t="s">
+      <c r="A74" s="12"/>
+      <c r="B74" s="13"/>
+      <c r="C74" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="D74" s="16" t="s">
+      <c r="D74" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="E74" s="13"/>
-      <c r="F74" s="13"/>
-      <c r="G74" s="13">
+      <c r="E74" s="14"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="14">
         <v>2</v>
       </c>
-      <c r="H74" s="13"/>
+      <c r="H74" s="14"/>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="11"/>
-      <c r="B75" s="12"/>
-      <c r="C75" s="14" t="s">
+      <c r="A75" s="12"/>
+      <c r="B75" s="13"/>
+      <c r="C75" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="D75" s="15" t="s">
+      <c r="D75" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="E75" s="13"/>
-      <c r="F75" s="13"/>
-      <c r="G75" s="13">
+      <c r="E75" s="14"/>
+      <c r="F75" s="14"/>
+      <c r="G75" s="14">
         <v>2</v>
       </c>
-      <c r="H75" s="13"/>
+      <c r="H75" s="14"/>
     </row>
     <row r="76" spans="1:8">
-      <c r="A76" s="11"/>
-      <c r="B76" s="12"/>
-      <c r="C76" s="14" t="s">
+      <c r="A76" s="12"/>
+      <c r="B76" s="13"/>
+      <c r="C76" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="D76" s="15" t="s">
+      <c r="D76" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="E76" s="13"/>
-      <c r="F76" s="13"/>
-      <c r="G76" s="13">
+      <c r="E76" s="14"/>
+      <c r="F76" s="14"/>
+      <c r="G76" s="14">
         <v>3</v>
       </c>
-      <c r="H76" s="13"/>
+      <c r="H76" s="14"/>
     </row>
     <row r="77" spans="1:8">
-      <c r="A77" s="11"/>
-      <c r="B77" s="12"/>
-      <c r="C77" s="14" t="s">
+      <c r="A77" s="12"/>
+      <c r="B77" s="13"/>
+      <c r="C77" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="D77" s="16" t="s">
+      <c r="D77" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="E77" s="13"/>
-      <c r="F77" s="13"/>
-      <c r="G77" s="13">
+      <c r="E77" s="14"/>
+      <c r="F77" s="14"/>
+      <c r="G77" s="14">
         <v>0</v>
       </c>
-      <c r="H77" s="13"/>
+      <c r="H77" s="14"/>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="11"/>
-      <c r="B78" s="12" t="s">
+      <c r="A78" s="12"/>
+      <c r="B78" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="C78" s="13" t="s">
+      <c r="C78" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="D78" s="15" t="s">
+      <c r="D78" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="E78" s="13" t="s">
+      <c r="E78" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="F78" s="13"/>
-      <c r="G78" s="13">
+      <c r="F78" s="14"/>
+      <c r="G78" s="14">
         <v>0</v>
       </c>
-      <c r="H78" s="13"/>
+      <c r="H78" s="14"/>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="11"/>
-      <c r="B79" s="12"/>
-      <c r="C79" s="13" t="s">
+      <c r="A79" s="12"/>
+      <c r="B79" s="13"/>
+      <c r="C79" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="D79" s="15" t="s">
+      <c r="D79" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="E79" s="13" t="s">
+      <c r="E79" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="F79" s="13"/>
-      <c r="G79" s="13">
+      <c r="F79" s="14"/>
+      <c r="G79" s="14">
         <v>0</v>
       </c>
-      <c r="H79" s="13"/>
+      <c r="H79" s="14"/>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="11"/>
-      <c r="B80" s="12"/>
-      <c r="C80" s="13" t="s">
+      <c r="A80" s="12"/>
+      <c r="B80" s="13"/>
+      <c r="C80" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="D80" s="16" t="s">
+      <c r="D80" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="E80" s="13"/>
-      <c r="F80" s="13"/>
-      <c r="G80" s="13">
+      <c r="E80" s="14"/>
+      <c r="F80" s="14"/>
+      <c r="G80" s="14">
         <v>4</v>
       </c>
-      <c r="H80" s="13"/>
+      <c r="H80" s="14"/>
     </row>
     <row r="81" spans="1:8">
-      <c r="A81" s="11"/>
-      <c r="B81" s="12"/>
-      <c r="C81" s="13" t="s">
+      <c r="A81" s="12"/>
+      <c r="B81" s="13"/>
+      <c r="C81" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="D81" s="15" t="s">
+      <c r="D81" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="E81" s="13"/>
-      <c r="F81" s="13"/>
-      <c r="G81" s="13">
+      <c r="E81" s="14"/>
+      <c r="F81" s="14"/>
+      <c r="G81" s="14">
         <v>1</v>
       </c>
-      <c r="H81" s="13"/>
+      <c r="H81" s="14"/>
     </row>
     <row r="82" spans="1:8">
-      <c r="A82" s="11"/>
-      <c r="B82" s="12"/>
-      <c r="C82" s="13" t="s">
+      <c r="A82" s="12"/>
+      <c r="B82" s="13"/>
+      <c r="C82" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="D82" s="15" t="s">
+      <c r="D82" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="E82" s="13"/>
-      <c r="F82" s="13"/>
-      <c r="G82" s="13">
+      <c r="E82" s="14"/>
+      <c r="F82" s="14"/>
+      <c r="G82" s="14">
         <v>0</v>
       </c>
-      <c r="H82" s="13"/>
+      <c r="H82" s="14"/>
     </row>
     <row r="83" spans="1:8">
-      <c r="A83" s="11"/>
-      <c r="B83" s="12"/>
-      <c r="C83" s="13" t="s">
+      <c r="A83" s="12"/>
+      <c r="B83" s="13"/>
+      <c r="C83" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="D83" s="15" t="s">
+      <c r="D83" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="E83" s="13"/>
-      <c r="F83" s="13"/>
-      <c r="G83" s="13">
+      <c r="E83" s="14"/>
+      <c r="F83" s="14"/>
+      <c r="G83" s="14">
         <v>0</v>
       </c>
-      <c r="H83" s="13"/>
+      <c r="H83" s="14"/>
     </row>
     <row r="85" spans="1:8">
-      <c r="A85" s="17" t="s">
+      <c r="A85" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="B85" s="18" t="s">
+      <c r="B85" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="C85" s="19" t="s">
+      <c r="C85" s="20" t="s">
         <v>204</v>
       </c>
-      <c r="D85" s="19" t="s">
+      <c r="D85" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="E85" s="19" t="s">
+      <c r="E85" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F85" s="20"/>
-      <c r="G85" s="20">
+      <c r="F85" s="21"/>
+      <c r="G85" s="21">
         <v>0</v>
       </c>
-      <c r="H85" s="20"/>
+      <c r="H85" s="21"/>
     </row>
     <row r="86" spans="1:8">
-      <c r="A86" s="17"/>
-      <c r="B86" s="18"/>
-      <c r="C86" s="19" t="s">
+      <c r="A86" s="18"/>
+      <c r="B86" s="19"/>
+      <c r="C86" s="20" t="s">
         <v>206</v>
       </c>
-      <c r="D86" s="19" t="s">
+      <c r="D86" s="20" t="s">
         <v>207</v>
       </c>
-      <c r="E86" s="19" t="s">
+      <c r="E86" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F86" s="20"/>
-      <c r="G86" s="20">
+      <c r="F86" s="21"/>
+      <c r="G86" s="21">
         <v>7</v>
       </c>
-      <c r="H86" s="20"/>
+      <c r="H86" s="21"/>
     </row>
     <row r="87" spans="1:8">
-      <c r="A87" s="17"/>
-      <c r="B87" s="18"/>
-      <c r="C87" s="19" t="s">
+      <c r="A87" s="18"/>
+      <c r="B87" s="19"/>
+      <c r="C87" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="D87" s="19" t="s">
+      <c r="D87" s="20" t="s">
         <v>209</v>
       </c>
-      <c r="E87" s="19" t="s">
+      <c r="E87" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F87" s="20"/>
-      <c r="G87" s="20">
+      <c r="F87" s="21"/>
+      <c r="G87" s="21">
         <v>8</v>
       </c>
-      <c r="H87" s="20"/>
+      <c r="H87" s="21"/>
     </row>
     <row r="88" spans="1:8">
-      <c r="A88" s="17"/>
-      <c r="B88" s="18"/>
-      <c r="C88" s="19" t="s">
+      <c r="A88" s="18"/>
+      <c r="B88" s="19"/>
+      <c r="C88" s="20" t="s">
         <v>210</v>
       </c>
-      <c r="D88" s="19" t="s">
+      <c r="D88" s="20" t="s">
         <v>211</v>
       </c>
-      <c r="E88" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="F88" s="20"/>
-      <c r="G88" s="20">
+      <c r="E88" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="F88" s="21"/>
+      <c r="G88" s="21">
         <v>8</v>
       </c>
-      <c r="H88" s="20"/>
+      <c r="H88" s="21"/>
     </row>
     <row r="89" spans="1:8">
-      <c r="A89" s="17"/>
-      <c r="B89" s="18" t="s">
+      <c r="A89" s="18"/>
+      <c r="B89" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="C89" s="19" t="s">
+      <c r="C89" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="D89" s="19" t="s">
+      <c r="D89" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="E89" s="19" t="s">
+      <c r="E89" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="F89" s="20"/>
-      <c r="G89" s="20">
+      <c r="F89" s="21"/>
+      <c r="G89" s="21">
         <v>4</v>
       </c>
-      <c r="H89" s="20"/>
+      <c r="H89" s="21"/>
     </row>
     <row r="90" spans="1:8">
-      <c r="A90" s="17"/>
-      <c r="B90" s="18"/>
-      <c r="C90" s="19" t="s">
+      <c r="A90" s="18"/>
+      <c r="B90" s="19"/>
+      <c r="C90" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="D90" s="19" t="s">
+      <c r="D90" s="20" t="s">
         <v>218</v>
       </c>
-      <c r="E90" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="F90" s="20"/>
-      <c r="G90" s="20">
+      <c r="E90" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="F90" s="21"/>
+      <c r="G90" s="21">
         <v>0</v>
       </c>
-      <c r="H90" s="20"/>
+      <c r="H90" s="21"/>
     </row>
     <row r="91" spans="1:8">
-      <c r="A91" s="17"/>
-      <c r="B91" s="18"/>
-      <c r="C91" s="19" t="s">
+      <c r="A91" s="18"/>
+      <c r="B91" s="19"/>
+      <c r="C91" s="20" t="s">
         <v>219</v>
       </c>
-      <c r="D91" s="19" t="s">
+      <c r="D91" s="20" t="s">
         <v>220</v>
       </c>
-      <c r="E91" s="19" t="s">
+      <c r="E91" s="20" t="s">
         <v>221</v>
       </c>
-      <c r="F91" s="20"/>
-      <c r="G91" s="20">
+      <c r="F91" s="21"/>
+      <c r="G91" s="21">
         <v>5</v>
       </c>
-      <c r="H91" s="20"/>
+      <c r="H91" s="21"/>
     </row>
     <row r="92" spans="1:8">
-      <c r="A92" s="17"/>
-      <c r="B92" s="18"/>
-      <c r="C92" s="19" t="s">
+      <c r="A92" s="18"/>
+      <c r="B92" s="19"/>
+      <c r="C92" s="20" t="s">
         <v>222</v>
       </c>
-      <c r="D92" s="19" t="s">
+      <c r="D92" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="E92" s="19" t="s">
+      <c r="E92" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="F92" s="20"/>
-      <c r="G92" s="20">
+      <c r="F92" s="21"/>
+      <c r="G92" s="21">
         <v>3</v>
       </c>
-      <c r="H92" s="20"/>
+      <c r="H92" s="21"/>
     </row>
     <row r="93" spans="1:8">
-      <c r="A93" s="17"/>
-      <c r="B93" s="18" t="s">
+      <c r="A93" s="18"/>
+      <c r="B93" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="C93" s="19" t="s">
+      <c r="C93" s="20" t="s">
         <v>226</v>
       </c>
-      <c r="D93" s="19" t="s">
+      <c r="D93" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="E93" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="F93" s="20"/>
-      <c r="G93" s="20">
+      <c r="E93" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="F93" s="21"/>
+      <c r="G93" s="21">
         <v>3</v>
       </c>
-      <c r="H93" s="20"/>
+      <c r="H93" s="21"/>
     </row>
     <row r="94" spans="1:8">
-      <c r="A94" s="17"/>
-      <c r="B94" s="18"/>
-      <c r="C94" s="19" t="s">
+      <c r="A94" s="18"/>
+      <c r="B94" s="19"/>
+      <c r="C94" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="D94" s="19" t="s">
+      <c r="D94" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="E94" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="F94" s="20"/>
-      <c r="G94" s="20">
+      <c r="E94" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="F94" s="21"/>
+      <c r="G94" s="21">
         <v>4</v>
       </c>
-      <c r="H94" s="20"/>
+      <c r="H94" s="21"/>
     </row>
     <row r="95" spans="1:8">
-      <c r="A95" s="17"/>
-      <c r="B95" s="18" t="s">
+      <c r="A95" s="18"/>
+      <c r="B95" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="C95" s="19" t="s">
+      <c r="C95" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="D95" s="19" t="s">
+      <c r="D95" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="E95" s="19" t="s">
+      <c r="E95" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="F95" s="20" t="s">
+      <c r="F95" s="21" t="s">
         <v>234</v>
       </c>
-      <c r="G95" s="20">
+      <c r="G95" s="21">
         <v>7</v>
       </c>
-      <c r="H95" s="20"/>
+      <c r="H95" s="21"/>
     </row>
     <row r="96" spans="1:8">
-      <c r="A96" s="17"/>
-      <c r="B96" s="18"/>
-      <c r="C96" s="19" t="s">
+      <c r="A96" s="18"/>
+      <c r="B96" s="19"/>
+      <c r="C96" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="D96" s="19" t="s">
+      <c r="D96" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="E96" s="19" t="s">
+      <c r="E96" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="F96" s="20"/>
-      <c r="G96" s="20">
+      <c r="F96" s="21"/>
+      <c r="G96" s="21">
         <v>2</v>
       </c>
-      <c r="H96" s="20"/>
+      <c r="H96" s="21"/>
     </row>
     <row r="97" spans="1:8">
-      <c r="A97" s="17"/>
-      <c r="B97" s="18"/>
-      <c r="C97" s="19" t="s">
+      <c r="A97" s="18"/>
+      <c r="B97" s="19"/>
+      <c r="C97" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="D97" s="19" t="s">
+      <c r="D97" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="E97" s="19" t="s">
+      <c r="E97" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="F97" s="20"/>
-      <c r="G97" s="20">
+      <c r="F97" s="21"/>
+      <c r="G97" s="21">
         <v>0</v>
       </c>
-      <c r="H97" s="20"/>
+      <c r="H97" s="21"/>
     </row>
     <row r="98" spans="1:8">
-      <c r="A98" s="17"/>
-      <c r="B98" s="18"/>
-      <c r="C98" s="19" t="s">
+      <c r="A98" s="18"/>
+      <c r="B98" s="19"/>
+      <c r="C98" s="20" t="s">
         <v>241</v>
       </c>
-      <c r="D98" s="19" t="s">
+      <c r="D98" s="20" t="s">
         <v>242</v>
       </c>
-      <c r="E98" s="19" t="s">
+      <c r="E98" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="F98" s="20"/>
-      <c r="G98" s="20">
+      <c r="F98" s="21"/>
+      <c r="G98" s="21">
         <v>1</v>
       </c>
-      <c r="H98" s="20"/>
+      <c r="H98" s="21"/>
     </row>
     <row r="99" spans="1:8">
-      <c r="A99" s="17"/>
-      <c r="B99" s="18" t="s">
+      <c r="A99" s="18"/>
+      <c r="B99" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="C99" s="19" t="s">
+      <c r="C99" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="D99" s="19" t="s">
+      <c r="D99" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="E99" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="F99" s="20"/>
-      <c r="G99" s="20">
+      <c r="E99" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="F99" s="21"/>
+      <c r="G99" s="21">
         <v>3</v>
       </c>
-      <c r="H99" s="20"/>
+      <c r="H99" s="21"/>
     </row>
     <row r="100" spans="1:8">
-      <c r="A100" s="17"/>
-      <c r="B100" s="18"/>
-      <c r="C100" s="19" t="s">
+      <c r="A100" s="18"/>
+      <c r="B100" s="19"/>
+      <c r="C100" s="20" t="s">
         <v>247</v>
       </c>
-      <c r="D100" s="19" t="s">
+      <c r="D100" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="E100" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="F100" s="20"/>
-      <c r="G100" s="20">
+      <c r="E100" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="F100" s="21"/>
+      <c r="G100" s="21">
         <v>19</v>
       </c>
-      <c r="H100" s="20"/>
+      <c r="H100" s="21"/>
     </row>
     <row r="101" spans="1:8">
-      <c r="A101" s="17"/>
-      <c r="B101" s="18"/>
-      <c r="C101" s="19" t="s">
+      <c r="A101" s="18"/>
+      <c r="B101" s="19"/>
+      <c r="C101" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="D101" s="19" t="s">
+      <c r="D101" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="E101" s="19" t="s">
+      <c r="E101" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="F101" s="20"/>
-      <c r="G101" s="20">
+      <c r="F101" s="21"/>
+      <c r="G101" s="21">
         <v>7</v>
       </c>
-      <c r="H101" s="20"/>
+      <c r="H101" s="21"/>
     </row>
     <row r="102" spans="1:8">
-      <c r="A102" s="17"/>
-      <c r="B102" s="18"/>
-      <c r="C102" s="19" t="s">
+      <c r="A102" s="18"/>
+      <c r="B102" s="19"/>
+      <c r="C102" s="20" t="s">
         <v>252</v>
       </c>
-      <c r="D102" s="19" t="s">
+      <c r="D102" s="20" t="s">
         <v>253</v>
       </c>
-      <c r="E102" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="F102" s="20"/>
-      <c r="G102" s="20">
+      <c r="E102" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="F102" s="21"/>
+      <c r="G102" s="21">
         <v>2</v>
       </c>
-      <c r="H102" s="20"/>
+      <c r="H102" s="21"/>
     </row>
     <row r="103" spans="1:8">
-      <c r="A103" s="17"/>
-      <c r="B103" s="18"/>
-      <c r="C103" s="19" t="s">
+      <c r="A103" s="18"/>
+      <c r="B103" s="19"/>
+      <c r="C103" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="D103" s="19" t="s">
+      <c r="D103" s="20" t="s">
         <v>255</v>
       </c>
-      <c r="E103" s="19" t="s">
+      <c r="E103" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="F103" s="20"/>
-      <c r="G103" s="20">
+      <c r="F103" s="21"/>
+      <c r="G103" s="21">
         <v>1</v>
       </c>
-      <c r="H103" s="20"/>
+      <c r="H103" s="21"/>
     </row>
     <row r="104" spans="1:8">
-      <c r="A104" s="17"/>
-      <c r="B104" s="18"/>
-      <c r="C104" s="19" t="s">
+      <c r="A104" s="18"/>
+      <c r="B104" s="19"/>
+      <c r="C104" s="20" t="s">
         <v>257</v>
       </c>
-      <c r="D104" s="19" t="s">
+      <c r="D104" s="20" t="s">
         <v>258</v>
       </c>
-      <c r="E104" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="F104" s="20"/>
-      <c r="G104" s="20">
+      <c r="E104" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="F104" s="21"/>
+      <c r="G104" s="21">
         <v>3</v>
       </c>
-      <c r="H104" s="20"/>
+      <c r="H104" s="21"/>
     </row>
     <row r="105" spans="1:8">
-      <c r="A105" s="17"/>
-      <c r="B105" s="18" t="s">
+      <c r="A105" s="18"/>
+      <c r="B105" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="C105" s="19" t="s">
+      <c r="C105" s="20" t="s">
         <v>260</v>
       </c>
-      <c r="D105" s="19" t="s">
+      <c r="D105" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="E105" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="F105" s="20"/>
-      <c r="G105" s="20">
+      <c r="E105" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="F105" s="21"/>
+      <c r="G105" s="21">
         <v>0</v>
       </c>
-      <c r="H105" s="20"/>
+      <c r="H105" s="21"/>
     </row>
     <row r="106" spans="1:8">
-      <c r="A106" s="17"/>
-      <c r="B106" s="18" t="s">
+      <c r="A106" s="18"/>
+      <c r="B106" s="19" t="s">
         <v>262</v>
       </c>
-      <c r="C106" s="19" t="s">
+      <c r="C106" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="D106" s="19" t="s">
+      <c r="D106" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="E106" s="19" t="s">
+      <c r="E106" s="20" t="s">
         <v>265</v>
       </c>
-      <c r="F106" s="20"/>
-      <c r="G106" s="20">
+      <c r="F106" s="21"/>
+      <c r="G106" s="21">
         <v>21</v>
       </c>
-      <c r="H106" s="20"/>
+      <c r="H106" s="21"/>
     </row>
     <row r="107" spans="1:8">
-      <c r="A107" s="17"/>
-      <c r="B107" s="18" t="s">
+      <c r="A107" s="18"/>
+      <c r="B107" s="19" t="s">
         <v>266</v>
       </c>
-      <c r="C107" s="19" t="s">
+      <c r="C107" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="D107" s="19" t="s">
+      <c r="D107" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="E107" s="19" t="s">
+      <c r="E107" s="20" t="s">
         <v>269</v>
       </c>
-      <c r="F107" s="20"/>
-      <c r="G107" s="20">
+      <c r="F107" s="21"/>
+      <c r="G107" s="21">
         <v>2</v>
       </c>
-      <c r="H107" s="20"/>
+      <c r="H107" s="21"/>
     </row>
     <row r="108" spans="1:8">
-      <c r="A108" s="17"/>
-      <c r="B108" s="18"/>
-      <c r="C108" s="19" t="s">
+      <c r="A108" s="18"/>
+      <c r="B108" s="19"/>
+      <c r="C108" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="D108" s="19" t="s">
+      <c r="D108" s="20" t="s">
         <v>271</v>
       </c>
-      <c r="E108" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="F108" s="20"/>
-      <c r="G108" s="20">
+      <c r="E108" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="F108" s="21"/>
+      <c r="G108" s="21">
         <v>1</v>
       </c>
-      <c r="H108" s="20"/>
+      <c r="H108" s="21"/>
     </row>
     <row r="109" spans="1:8">
-      <c r="A109" s="17"/>
-      <c r="B109" s="18"/>
-      <c r="C109" s="19" t="s">
+      <c r="A109" s="18"/>
+      <c r="B109" s="19"/>
+      <c r="C109" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="D109" s="19" t="s">
+      <c r="D109" s="20" t="s">
         <v>273</v>
       </c>
-      <c r="E109" s="19" t="s">
+      <c r="E109" s="20" t="s">
         <v>274</v>
       </c>
-      <c r="F109" s="20"/>
-      <c r="G109" s="20">
+      <c r="F109" s="21"/>
+      <c r="G109" s="21">
         <v>2</v>
       </c>
-      <c r="H109" s="20"/>
+      <c r="H109" s="21"/>
     </row>
     <row r="111" spans="1:8">
-      <c r="A111" s="21" t="s">
+      <c r="A111" s="22" t="s">
         <v>275</v>
       </c>
-      <c r="B111" s="22"/>
-      <c r="C111" s="22" t="s">
+      <c r="B111" s="23"/>
+      <c r="C111" s="23" t="s">
         <v>276</v>
       </c>
-      <c r="D111" s="22" t="s">
+      <c r="D111" s="23" t="s">
         <v>277</v>
       </c>
-      <c r="E111" s="23" t="s">
+      <c r="E111" s="24" t="s">
         <v>278</v>
       </c>
-      <c r="F111" s="23"/>
-      <c r="G111" s="23"/>
-      <c r="H111" s="23"/>
+      <c r="F111" s="24"/>
+      <c r="G111" s="24"/>
+      <c r="H111" s="24"/>
     </row>
     <row r="112" spans="1:8">
-      <c r="A112" s="21"/>
-      <c r="B112" s="22"/>
-      <c r="C112" s="22" t="s">
+      <c r="A112" s="22"/>
+      <c r="B112" s="23"/>
+      <c r="C112" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="D112" s="22" t="s">
+      <c r="D112" s="23" t="s">
         <v>280</v>
       </c>
-      <c r="E112" s="23" t="s">
+      <c r="E112" s="24" t="s">
         <v>281</v>
       </c>
-      <c r="F112" s="23"/>
-      <c r="G112" s="23"/>
-      <c r="H112" s="23"/>
+      <c r="F112" s="24"/>
+      <c r="G112" s="24"/>
+      <c r="H112" s="24"/>
     </row>
     <row r="113" spans="1:8">
-      <c r="A113" s="21"/>
-      <c r="B113" s="22"/>
-      <c r="C113" s="22" t="s">
+      <c r="A113" s="22"/>
+      <c r="B113" s="23"/>
+      <c r="C113" s="23" t="s">
         <v>282</v>
       </c>
-      <c r="D113" s="22" t="s">
+      <c r="D113" s="23" t="s">
         <v>283</v>
       </c>
-      <c r="E113" s="23" t="s">
+      <c r="E113" s="24" t="s">
         <v>284</v>
       </c>
-      <c r="F113" s="23"/>
-      <c r="G113" s="23"/>
-      <c r="H113" s="23"/>
+      <c r="F113" s="24"/>
+      <c r="G113" s="24"/>
+      <c r="H113" s="24"/>
     </row>
     <row r="114" spans="1:8">
-      <c r="A114" s="21"/>
-      <c r="B114" s="22"/>
-      <c r="C114" s="22" t="s">
+      <c r="A114" s="22"/>
+      <c r="B114" s="23"/>
+      <c r="C114" s="23" t="s">
         <v>285</v>
       </c>
-      <c r="D114" s="22" t="s">
+      <c r="D114" s="23" t="s">
         <v>286</v>
       </c>
-      <c r="E114" s="23" t="s">
+      <c r="E114" s="24" t="s">
         <v>287</v>
       </c>
-      <c r="F114" s="23"/>
-      <c r="G114" s="23"/>
-      <c r="H114" s="23"/>
+      <c r="F114" s="24"/>
+      <c r="G114" s="24"/>
+      <c r="H114" s="24"/>
     </row>
     <row r="115" spans="1:8">
-      <c r="A115" s="21"/>
-      <c r="B115" s="22"/>
-      <c r="C115" s="22" t="s">
+      <c r="A115" s="22"/>
+      <c r="B115" s="23"/>
+      <c r="C115" s="23" t="s">
         <v>288</v>
       </c>
-      <c r="D115" s="22" t="s">
+      <c r="D115" s="23" t="s">
         <v>289</v>
       </c>
-      <c r="E115" s="23" t="s">
+      <c r="E115" s="24" t="s">
         <v>290</v>
       </c>
-      <c r="F115" s="23"/>
-      <c r="G115" s="23"/>
-      <c r="H115" s="23"/>
+      <c r="F115" s="24"/>
+      <c r="G115" s="24"/>
+      <c r="H115" s="24"/>
     </row>
     <row r="116" spans="1:8">
-      <c r="A116" s="21"/>
-      <c r="B116" s="22"/>
-      <c r="C116" s="22" t="s">
+      <c r="A116" s="22"/>
+      <c r="B116" s="23"/>
+      <c r="C116" s="23" t="s">
         <v>291</v>
       </c>
-      <c r="D116" s="22" t="s">
+      <c r="D116" s="23" t="s">
         <v>292</v>
       </c>
-      <c r="E116" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="F116" s="23"/>
-      <c r="G116" s="23"/>
-      <c r="H116" s="23"/>
+      <c r="E116" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="F116" s="24"/>
+      <c r="G116" s="24"/>
+      <c r="H116" s="24"/>
     </row>
     <row r="117" spans="1:8">
-      <c r="A117" s="21"/>
-      <c r="B117" s="22"/>
-      <c r="C117" s="22" t="s">
+      <c r="A117" s="22"/>
+      <c r="B117" s="23"/>
+      <c r="C117" s="23" t="s">
         <v>293</v>
       </c>
-      <c r="D117" s="22" t="s">
+      <c r="D117" s="23" t="s">
         <v>294</v>
       </c>
-      <c r="E117" s="23" t="s">
+      <c r="E117" s="24" t="s">
         <v>295</v>
       </c>
-      <c r="F117" s="23"/>
-      <c r="G117" s="23"/>
-      <c r="H117" s="23"/>
+      <c r="F117" s="24"/>
+      <c r="G117" s="24"/>
+      <c r="H117" s="24"/>
     </row>
     <row r="118" spans="1:8">
-      <c r="A118" s="21"/>
-      <c r="B118" s="22"/>
-      <c r="C118" s="22" t="s">
+      <c r="A118" s="22"/>
+      <c r="B118" s="23"/>
+      <c r="C118" s="23" t="s">
         <v>296</v>
       </c>
-      <c r="D118" s="22" t="s">
+      <c r="D118" s="23" t="s">
         <v>297</v>
       </c>
-      <c r="E118" s="23" t="s">
+      <c r="E118" s="24" t="s">
         <v>298</v>
       </c>
-      <c r="F118" s="23"/>
-      <c r="G118" s="23"/>
-      <c r="H118" s="23"/>
+      <c r="F118" s="24"/>
+      <c r="G118" s="24"/>
+      <c r="H118" s="24"/>
     </row>
     <row r="119" spans="1:8">
-      <c r="A119" s="21"/>
-      <c r="B119" s="22"/>
-      <c r="C119" s="22" t="s">
+      <c r="A119" s="22"/>
+      <c r="B119" s="23"/>
+      <c r="C119" s="23" t="s">
         <v>299</v>
       </c>
-      <c r="D119" s="22" t="s">
+      <c r="D119" s="23" t="s">
         <v>300</v>
       </c>
-      <c r="E119" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="F119" s="23"/>
-      <c r="G119" s="23"/>
-      <c r="H119" s="23"/>
+      <c r="E119" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="F119" s="24"/>
+      <c r="G119" s="24"/>
+      <c r="H119" s="24"/>
     </row>
     <row r="120" spans="1:8">
-      <c r="A120" s="21"/>
-      <c r="B120" s="22"/>
-      <c r="C120" s="22" t="s">
+      <c r="A120" s="22"/>
+      <c r="B120" s="23"/>
+      <c r="C120" s="23" t="s">
         <v>301</v>
       </c>
-      <c r="D120" s="22" t="s">
+      <c r="D120" s="23" t="s">
         <v>302</v>
       </c>
-      <c r="E120" s="23" t="s">
+      <c r="E120" s="24" t="s">
         <v>303</v>
       </c>
-      <c r="F120" s="23"/>
-      <c r="G120" s="23"/>
-      <c r="H120" s="23"/>
+      <c r="F120" s="24"/>
+      <c r="G120" s="24"/>
+      <c r="H120" s="24"/>
     </row>
     <row r="121" spans="1:8">
-      <c r="A121" s="21"/>
-      <c r="B121" s="22"/>
-      <c r="C121" s="22" t="s">
+      <c r="A121" s="22"/>
+      <c r="B121" s="23"/>
+      <c r="C121" s="23" t="s">
         <v>304</v>
       </c>
-      <c r="D121" s="22" t="s">
+      <c r="D121" s="23" t="s">
         <v>305</v>
       </c>
-      <c r="E121" s="23" t="s">
+      <c r="E121" s="24" t="s">
         <v>306</v>
       </c>
-      <c r="F121" s="23"/>
-      <c r="G121" s="23"/>
-      <c r="H121" s="23"/>
+      <c r="F121" s="24"/>
+      <c r="G121" s="24"/>
+      <c r="H121" s="24"/>
     </row>
     <row r="122" spans="1:8">
-      <c r="A122" s="21"/>
-      <c r="B122" s="22"/>
-      <c r="C122" s="22" t="s">
+      <c r="A122" s="22"/>
+      <c r="B122" s="23"/>
+      <c r="C122" s="23" t="s">
         <v>307</v>
       </c>
-      <c r="D122" s="22" t="s">
+      <c r="D122" s="23" t="s">
         <v>308</v>
       </c>
-      <c r="E122" s="23" t="s">
+      <c r="E122" s="24" t="s">
         <v>309</v>
       </c>
-      <c r="F122" s="23"/>
-      <c r="G122" s="23"/>
-      <c r="H122" s="23"/>
+      <c r="F122" s="24"/>
+      <c r="G122" s="24"/>
+      <c r="H122" s="24"/>
     </row>
     <row r="123" spans="1:8">
-      <c r="A123" s="21"/>
-      <c r="B123" s="22"/>
-      <c r="C123" s="22" t="s">
+      <c r="A123" s="22"/>
+      <c r="B123" s="23"/>
+      <c r="C123" s="23" t="s">
         <v>310</v>
       </c>
-      <c r="D123" s="22" t="s">
+      <c r="D123" s="23" t="s">
         <v>311</v>
       </c>
-      <c r="E123" s="23" t="s">
+      <c r="E123" s="24" t="s">
         <v>312</v>
       </c>
-      <c r="F123" s="23"/>
-      <c r="G123" s="23"/>
-      <c r="H123" s="23"/>
+      <c r="F123" s="24"/>
+      <c r="G123" s="24"/>
+      <c r="H123" s="24"/>
     </row>
     <row r="124" spans="1:8">
-      <c r="A124" s="21"/>
-      <c r="B124" s="22"/>
-      <c r="C124" s="22" t="s">
+      <c r="A124" s="22"/>
+      <c r="B124" s="23"/>
+      <c r="C124" s="23" t="s">
         <v>313</v>
       </c>
-      <c r="D124" s="22" t="s">
+      <c r="D124" s="23" t="s">
         <v>314</v>
       </c>
-      <c r="E124" s="23" t="s">
+      <c r="E124" s="24" t="s">
         <v>315</v>
       </c>
-      <c r="F124" s="23"/>
-      <c r="G124" s="23"/>
-      <c r="H124" s="23"/>
+      <c r="F124" s="24"/>
+      <c r="G124" s="24"/>
+      <c r="H124" s="24"/>
     </row>
     <row r="125" spans="1:8">
-      <c r="A125" s="21"/>
-      <c r="B125" s="22"/>
-      <c r="C125" s="22" t="s">
+      <c r="A125" s="22"/>
+      <c r="B125" s="23"/>
+      <c r="C125" s="23" t="s">
         <v>316</v>
       </c>
-      <c r="D125" s="22" t="s">
+      <c r="D125" s="23" t="s">
         <v>317</v>
       </c>
-      <c r="E125" s="23" t="s">
+      <c r="E125" s="24" t="s">
         <v>318</v>
       </c>
-      <c r="F125" s="23"/>
-      <c r="G125" s="23"/>
-      <c r="H125" s="23"/>
+      <c r="F125" s="24"/>
+      <c r="G125" s="24"/>
+      <c r="H125" s="24"/>
     </row>
     <row r="126" spans="1:8">
-      <c r="A126" s="21"/>
-      <c r="B126" s="22"/>
-      <c r="C126" s="22" t="s">
+      <c r="A126" s="22"/>
+      <c r="B126" s="23"/>
+      <c r="C126" s="23" t="s">
         <v>319</v>
       </c>
-      <c r="D126" s="22" t="s">
+      <c r="D126" s="23" t="s">
         <v>320</v>
       </c>
-      <c r="E126" s="23" t="s">
+      <c r="E126" s="24" t="s">
         <v>321</v>
       </c>
-      <c r="F126" s="23"/>
-      <c r="G126" s="23"/>
-      <c r="H126" s="23"/>
+      <c r="F126" s="24"/>
+      <c r="G126" s="24"/>
+      <c r="H126" s="24"/>
     </row>
     <row r="127" spans="1:8">
-      <c r="A127" s="21"/>
-      <c r="B127" s="22"/>
-      <c r="C127" s="22" t="s">
+      <c r="A127" s="22"/>
+      <c r="B127" s="23"/>
+      <c r="C127" s="23" t="s">
         <v>322</v>
       </c>
-      <c r="D127" s="22" t="s">
+      <c r="D127" s="23" t="s">
         <v>323</v>
       </c>
-      <c r="E127" s="23" t="s">
+      <c r="E127" s="24" t="s">
         <v>324</v>
       </c>
-      <c r="F127" s="23"/>
-      <c r="G127" s="23"/>
-      <c r="H127" s="23"/>
+      <c r="F127" s="24"/>
+      <c r="G127" s="24"/>
+      <c r="H127" s="24"/>
     </row>
     <row r="128" spans="1:8">
-      <c r="A128" s="21"/>
-      <c r="B128" s="22"/>
-      <c r="C128" s="22" t="s">
+      <c r="A128" s="22"/>
+      <c r="B128" s="23"/>
+      <c r="C128" s="23" t="s">
         <v>325</v>
       </c>
-      <c r="D128" s="22" t="s">
+      <c r="D128" s="23" t="s">
         <v>326</v>
       </c>
-      <c r="E128" s="23" t="s">
+      <c r="E128" s="24" t="s">
         <v>327</v>
       </c>
-      <c r="F128" s="23"/>
-      <c r="G128" s="23"/>
-      <c r="H128" s="23"/>
+      <c r="F128" s="24"/>
+      <c r="G128" s="24"/>
+      <c r="H128" s="24"/>
     </row>
     <row r="129" spans="1:8">
-      <c r="A129" s="21"/>
-      <c r="B129" s="22"/>
-      <c r="C129" s="22" t="s">
+      <c r="A129" s="22"/>
+      <c r="B129" s="23"/>
+      <c r="C129" s="23" t="s">
         <v>328</v>
       </c>
-      <c r="D129" s="22" t="s">
+      <c r="D129" s="23" t="s">
         <v>329</v>
       </c>
-      <c r="E129" s="23" t="s">
+      <c r="E129" s="24" t="s">
         <v>330</v>
       </c>
-      <c r="F129" s="23"/>
-      <c r="G129" s="23"/>
-      <c r="H129" s="23"/>
+      <c r="F129" s="24"/>
+      <c r="G129" s="24"/>
+      <c r="H129" s="24"/>
     </row>
     <row r="130" spans="1:8">
-      <c r="A130" s="21"/>
-      <c r="B130" s="22"/>
-      <c r="C130" s="22" t="s">
+      <c r="A130" s="22"/>
+      <c r="B130" s="23"/>
+      <c r="C130" s="23" t="s">
         <v>331</v>
       </c>
-      <c r="D130" s="22" t="s">
+      <c r="D130" s="23" t="s">
         <v>332</v>
       </c>
-      <c r="E130" s="23" t="s">
+      <c r="E130" s="24" t="s">
         <v>333</v>
       </c>
-      <c r="F130" s="23"/>
-      <c r="G130" s="23"/>
-      <c r="H130" s="23"/>
+      <c r="F130" s="24"/>
+      <c r="G130" s="24"/>
+      <c r="H130" s="24"/>
     </row>
     <row r="131" spans="1:8">
-      <c r="A131" s="21"/>
-      <c r="B131" s="22"/>
-      <c r="C131" s="22" t="s">
+      <c r="A131" s="22"/>
+      <c r="B131" s="23"/>
+      <c r="C131" s="23" t="s">
         <v>334</v>
       </c>
-      <c r="D131" s="22" t="s">
+      <c r="D131" s="23" t="s">
         <v>335</v>
       </c>
-      <c r="E131" s="23" t="s">
+      <c r="E131" s="24" t="s">
         <v>336</v>
       </c>
-      <c r="F131" s="23"/>
-      <c r="G131" s="23"/>
-      <c r="H131" s="23"/>
+      <c r="F131" s="24"/>
+      <c r="G131" s="24"/>
+      <c r="H131" s="24"/>
     </row>
     <row r="132" spans="1:8">
-      <c r="A132" s="21"/>
-      <c r="B132" s="22"/>
-      <c r="C132" s="22" t="s">
+      <c r="A132" s="22"/>
+      <c r="B132" s="23"/>
+      <c r="C132" s="23" t="s">
         <v>337</v>
       </c>
-      <c r="D132" s="22" t="s">
+      <c r="D132" s="23" t="s">
         <v>338</v>
       </c>
-      <c r="E132" s="23" t="s">
+      <c r="E132" s="24" t="s">
         <v>339</v>
       </c>
-      <c r="F132" s="23"/>
-      <c r="G132" s="23"/>
-      <c r="H132" s="23"/>
+      <c r="F132" s="24"/>
+      <c r="G132" s="24"/>
+      <c r="H132" s="24"/>
     </row>
     <row r="133" spans="1:8">
-      <c r="A133" s="21"/>
-      <c r="B133" s="22"/>
-      <c r="C133" s="22" t="s">
+      <c r="A133" s="22"/>
+      <c r="B133" s="23"/>
+      <c r="C133" s="23" t="s">
         <v>340</v>
       </c>
-      <c r="D133" s="22" t="s">
+      <c r="D133" s="23" t="s">
         <v>341</v>
       </c>
-      <c r="E133" s="23" t="s">
+      <c r="E133" s="24" t="s">
         <v>342</v>
       </c>
-      <c r="F133" s="23"/>
-      <c r="G133" s="23"/>
-      <c r="H133" s="23"/>
+      <c r="F133" s="24"/>
+      <c r="G133" s="24"/>
+      <c r="H133" s="24"/>
     </row>
     <row r="134" spans="1:8">
-      <c r="A134" s="21"/>
-      <c r="B134" s="22"/>
-      <c r="C134" s="22" t="s">
+      <c r="A134" s="22"/>
+      <c r="B134" s="23"/>
+      <c r="C134" s="23" t="s">
         <v>343</v>
       </c>
-      <c r="D134" s="22" t="s">
+      <c r="D134" s="23" t="s">
         <v>344</v>
       </c>
-      <c r="E134" s="23" t="s">
+      <c r="E134" s="24" t="s">
         <v>345</v>
       </c>
-      <c r="F134" s="23"/>
-      <c r="G134" s="23"/>
-      <c r="H134" s="23"/>
+      <c r="F134" s="24"/>
+      <c r="G134" s="24"/>
+      <c r="H134" s="24"/>
     </row>
     <row r="135" spans="1:8">
-      <c r="A135" s="21"/>
-      <c r="B135" s="22"/>
-      <c r="C135" s="22" t="s">
+      <c r="A135" s="22"/>
+      <c r="B135" s="23"/>
+      <c r="C135" s="23" t="s">
         <v>346</v>
       </c>
-      <c r="D135" s="22" t="s">
+      <c r="D135" s="23" t="s">
         <v>347</v>
       </c>
-      <c r="E135" s="23" t="s">
+      <c r="E135" s="24" t="s">
         <v>348</v>
       </c>
-      <c r="F135" s="23"/>
-      <c r="G135" s="23"/>
-      <c r="H135" s="23"/>
+      <c r="F135" s="24"/>
+      <c r="G135" s="24"/>
+      <c r="H135" s="24"/>
     </row>
     <row r="136" spans="1:8">
-      <c r="A136" s="21"/>
-      <c r="B136" s="22"/>
-      <c r="C136" s="22" t="s">
+      <c r="A136" s="22"/>
+      <c r="B136" s="23"/>
+      <c r="C136" s="23" t="s">
         <v>349</v>
       </c>
-      <c r="D136" s="22" t="s">
+      <c r="D136" s="23" t="s">
         <v>350</v>
       </c>
-      <c r="E136" s="23" t="s">
+      <c r="E136" s="24" t="s">
         <v>351</v>
       </c>
-      <c r="F136" s="23"/>
-      <c r="G136" s="23"/>
-      <c r="H136" s="23"/>
+      <c r="F136" s="24"/>
+      <c r="G136" s="24"/>
+      <c r="H136" s="24"/>
     </row>
     <row r="137" spans="1:8">
-      <c r="A137" s="21"/>
-      <c r="B137" s="22"/>
-      <c r="C137" s="22" t="s">
+      <c r="A137" s="22"/>
+      <c r="B137" s="23"/>
+      <c r="C137" s="23" t="s">
         <v>352</v>
       </c>
-      <c r="D137" s="22" t="s">
+      <c r="D137" s="23" t="s">
         <v>353</v>
       </c>
-      <c r="E137" s="23" t="s">
+      <c r="E137" s="24" t="s">
         <v>354</v>
       </c>
-      <c r="F137" s="23"/>
-      <c r="G137" s="23"/>
-      <c r="H137" s="23"/>
+      <c r="F137" s="24"/>
+      <c r="G137" s="24"/>
+      <c r="H137" s="24"/>
     </row>
     <row r="138" spans="1:8">
-      <c r="A138" s="21"/>
-      <c r="B138" s="22"/>
-      <c r="C138" s="22" t="s">
+      <c r="A138" s="22"/>
+      <c r="B138" s="23"/>
+      <c r="C138" s="23" t="s">
         <v>355</v>
       </c>
-      <c r="D138" s="22" t="s">
+      <c r="D138" s="23" t="s">
         <v>356</v>
       </c>
-      <c r="E138" s="23" t="s">
+      <c r="E138" s="24" t="s">
         <v>357</v>
       </c>
-      <c r="F138" s="23"/>
-      <c r="G138" s="23"/>
-      <c r="H138" s="23"/>
+      <c r="F138" s="24"/>
+      <c r="G138" s="24"/>
+      <c r="H138" s="24"/>
     </row>
     <row r="139" spans="1:8">
-      <c r="A139" s="21"/>
-      <c r="B139" s="22"/>
-      <c r="C139" s="22" t="s">
+      <c r="A139" s="22"/>
+      <c r="B139" s="23"/>
+      <c r="C139" s="23" t="s">
         <v>358</v>
       </c>
-      <c r="D139" s="22" t="s">
+      <c r="D139" s="23" t="s">
         <v>359</v>
       </c>
-      <c r="E139" s="23" t="s">
+      <c r="E139" s="24" t="s">
         <v>360</v>
       </c>
-      <c r="F139" s="23"/>
-      <c r="G139" s="23"/>
-      <c r="H139" s="23"/>
+      <c r="F139" s="24"/>
+      <c r="G139" s="24"/>
+      <c r="H139" s="24"/>
     </row>
     <row r="140" spans="1:8">
-      <c r="A140" s="21"/>
-      <c r="B140" s="22"/>
-      <c r="C140" s="22" t="s">
+      <c r="A140" s="22"/>
+      <c r="B140" s="23"/>
+      <c r="C140" s="23" t="s">
         <v>361</v>
       </c>
-      <c r="D140" s="22" t="s">
+      <c r="D140" s="23" t="s">
         <v>362</v>
       </c>
-      <c r="E140" s="23" t="s">
+      <c r="E140" s="24" t="s">
         <v>363</v>
       </c>
-      <c r="F140" s="23"/>
-      <c r="G140" s="23"/>
-      <c r="H140" s="23"/>
+      <c r="F140" s="24"/>
+      <c r="G140" s="24"/>
+      <c r="H140" s="24"/>
     </row>
     <row r="141" spans="1:8">
-      <c r="A141" s="21"/>
-      <c r="B141" s="22"/>
-      <c r="C141" s="22" t="s">
+      <c r="A141" s="22"/>
+      <c r="B141" s="23"/>
+      <c r="C141" s="23" t="s">
         <v>364</v>
       </c>
-      <c r="D141" s="22" t="s">
+      <c r="D141" s="23" t="s">
         <v>365</v>
       </c>
-      <c r="E141" s="23" t="s">
+      <c r="E141" s="24" t="s">
         <v>366</v>
       </c>
-      <c r="F141" s="23"/>
-      <c r="G141" s="23"/>
-      <c r="H141" s="23"/>
+      <c r="F141" s="24"/>
+      <c r="G141" s="24"/>
+      <c r="H141" s="24"/>
     </row>
     <row r="142" spans="1:8">
-      <c r="A142" s="21"/>
-      <c r="B142" s="22"/>
-      <c r="C142" s="22" t="s">
+      <c r="A142" s="22"/>
+      <c r="B142" s="23"/>
+      <c r="C142" s="23" t="s">
         <v>367</v>
       </c>
-      <c r="D142" s="22" t="s">
+      <c r="D142" s="23" t="s">
         <v>368</v>
       </c>
-      <c r="E142" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="F142" s="23"/>
-      <c r="G142" s="23"/>
-      <c r="H142" s="23"/>
+      <c r="E142" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="F142" s="24"/>
+      <c r="G142" s="24"/>
+      <c r="H142" s="24"/>
     </row>
     <row r="143" spans="1:8">
-      <c r="A143" s="21"/>
-      <c r="B143" s="22"/>
-      <c r="C143" s="22" t="s">
+      <c r="A143" s="22"/>
+      <c r="B143" s="23"/>
+      <c r="C143" s="23" t="s">
         <v>369</v>
       </c>
-      <c r="D143" s="22" t="s">
+      <c r="D143" s="23" t="s">
         <v>370</v>
       </c>
-      <c r="E143" s="23" t="s">
+      <c r="E143" s="24" t="s">
         <v>371</v>
       </c>
-      <c r="F143" s="23"/>
-      <c r="G143" s="23"/>
-      <c r="H143" s="23"/>
+      <c r="F143" s="24"/>
+      <c r="G143" s="24"/>
+      <c r="H143" s="24"/>
     </row>
     <row r="144" spans="1:8">
-      <c r="A144" s="21"/>
-      <c r="B144" s="22"/>
-      <c r="C144" s="22" t="s">
+      <c r="A144" s="22"/>
+      <c r="B144" s="23"/>
+      <c r="C144" s="23" t="s">
         <v>372</v>
       </c>
-      <c r="D144" s="22" t="s">
+      <c r="D144" s="23" t="s">
         <v>373</v>
       </c>
-      <c r="E144" s="23" t="s">
+      <c r="E144" s="24" t="s">
         <v>374</v>
       </c>
-      <c r="F144" s="23"/>
-      <c r="G144" s="23"/>
-      <c r="H144" s="23"/>
+      <c r="F144" s="24"/>
+      <c r="G144" s="24"/>
+      <c r="H144" s="24"/>
     </row>
     <row r="145" spans="1:8">
-      <c r="A145" s="21"/>
-      <c r="B145" s="22"/>
-      <c r="C145" s="22" t="s">
+      <c r="A145" s="22"/>
+      <c r="B145" s="23"/>
+      <c r="C145" s="23" t="s">
         <v>375</v>
       </c>
-      <c r="D145" s="22" t="s">
+      <c r="D145" s="23" t="s">
         <v>376</v>
       </c>
-      <c r="E145" s="23" t="s">
+      <c r="E145" s="24" t="s">
         <v>377</v>
       </c>
-      <c r="F145" s="23"/>
-      <c r="G145" s="23"/>
-      <c r="H145" s="23"/>
+      <c r="F145" s="24"/>
+      <c r="G145" s="24"/>
+      <c r="H145" s="24"/>
     </row>
     <row r="146" spans="1:8">
-      <c r="A146" s="21"/>
-      <c r="B146" s="22"/>
-      <c r="C146" s="22" t="s">
+      <c r="A146" s="22"/>
+      <c r="B146" s="23"/>
+      <c r="C146" s="23" t="s">
         <v>378</v>
       </c>
-      <c r="D146" s="22" t="s">
+      <c r="D146" s="23" t="s">
         <v>379</v>
       </c>
-      <c r="E146" s="23" t="s">
+      <c r="E146" s="24" t="s">
         <v>380</v>
       </c>
-      <c r="F146" s="23"/>
-      <c r="G146" s="23"/>
-      <c r="H146" s="23"/>
+      <c r="F146" s="24"/>
+      <c r="G146" s="24"/>
+      <c r="H146" s="24"/>
     </row>
     <row r="147" spans="1:8">
-      <c r="A147" s="21"/>
-      <c r="B147" s="22"/>
-      <c r="C147" s="22" t="s">
+      <c r="A147" s="22"/>
+      <c r="B147" s="23"/>
+      <c r="C147" s="23" t="s">
         <v>381</v>
       </c>
-      <c r="D147" s="22" t="s">
+      <c r="D147" s="23" t="s">
         <v>382</v>
       </c>
-      <c r="E147" s="23" t="s">
+      <c r="E147" s="24" t="s">
         <v>383</v>
       </c>
-      <c r="F147" s="23"/>
-      <c r="G147" s="23"/>
-      <c r="H147" s="23"/>
+      <c r="F147" s="24"/>
+      <c r="G147" s="24"/>
+      <c r="H147" s="24"/>
     </row>
     <row r="148" spans="1:8">
-      <c r="A148" s="21"/>
-      <c r="B148" s="22"/>
-      <c r="C148" s="22" t="s">
+      <c r="A148" s="22"/>
+      <c r="B148" s="23"/>
+      <c r="C148" s="23" t="s">
         <v>384</v>
       </c>
-      <c r="D148" s="22" t="s">
+      <c r="D148" s="23" t="s">
         <v>385</v>
       </c>
-      <c r="E148" s="23" t="s">
+      <c r="E148" s="24" t="s">
         <v>386</v>
       </c>
-      <c r="F148" s="23"/>
-      <c r="G148" s="23"/>
-      <c r="H148" s="23"/>
+      <c r="F148" s="24"/>
+      <c r="G148" s="24"/>
+      <c r="H148" s="24"/>
     </row>
     <row r="149" spans="1:8">
-      <c r="A149" s="21"/>
-      <c r="B149" s="22"/>
-      <c r="C149" s="22" t="s">
+      <c r="A149" s="22"/>
+      <c r="B149" s="23"/>
+      <c r="C149" s="23" t="s">
         <v>387</v>
       </c>
-      <c r="D149" s="22" t="s">
+      <c r="D149" s="23" t="s">
         <v>388</v>
       </c>
-      <c r="E149" s="23" t="s">
+      <c r="E149" s="24" t="s">
         <v>389</v>
       </c>
-      <c r="F149" s="23"/>
-      <c r="G149" s="23"/>
-      <c r="H149" s="23"/>
+      <c r="F149" s="24"/>
+      <c r="G149" s="24"/>
+      <c r="H149" s="24"/>
     </row>
     <row r="150" spans="1:8">
-      <c r="A150" s="21"/>
-      <c r="B150" s="22"/>
-      <c r="C150" s="22" t="s">
+      <c r="A150" s="22"/>
+      <c r="B150" s="23"/>
+      <c r="C150" s="23" t="s">
         <v>390</v>
       </c>
-      <c r="D150" s="22" t="s">
+      <c r="D150" s="23" t="s">
         <v>391</v>
       </c>
-      <c r="E150" s="23" t="s">
+      <c r="E150" s="24" t="s">
         <v>392</v>
       </c>
-      <c r="F150" s="23"/>
-      <c r="G150" s="23"/>
-      <c r="H150" s="23"/>
+      <c r="F150" s="24"/>
+      <c r="G150" s="24"/>
+      <c r="H150" s="24"/>
     </row>
     <row r="151" spans="1:8">
-      <c r="A151" s="21"/>
-      <c r="B151" s="22"/>
-      <c r="C151" s="22" t="s">
+      <c r="A151" s="22"/>
+      <c r="B151" s="23"/>
+      <c r="C151" s="23" t="s">
         <v>393</v>
       </c>
-      <c r="D151" s="22" t="s">
+      <c r="D151" s="23" t="s">
         <v>394</v>
       </c>
-      <c r="E151" s="23" t="s">
+      <c r="E151" s="24" t="s">
         <v>395</v>
       </c>
-      <c r="F151" s="23"/>
-      <c r="G151" s="23"/>
-      <c r="H151" s="23"/>
+      <c r="F151" s="24"/>
+      <c r="G151" s="24"/>
+      <c r="H151" s="24"/>
     </row>
     <row r="152" spans="1:8">
-      <c r="A152" s="21"/>
-      <c r="B152" s="22"/>
-      <c r="C152" s="22" t="s">
+      <c r="A152" s="22"/>
+      <c r="B152" s="23"/>
+      <c r="C152" s="23" t="s">
         <v>396</v>
       </c>
-      <c r="D152" s="22" t="s">
+      <c r="D152" s="23" t="s">
         <v>397</v>
       </c>
-      <c r="E152" s="23" t="s">
+      <c r="E152" s="24" t="s">
         <v>398</v>
       </c>
-      <c r="F152" s="23"/>
-      <c r="G152" s="23"/>
-      <c r="H152" s="23"/>
+      <c r="F152" s="24"/>
+      <c r="G152" s="24"/>
+      <c r="H152" s="24"/>
     </row>
     <row r="153" spans="1:8">
-      <c r="A153" s="21"/>
-      <c r="B153" s="22"/>
-      <c r="C153" s="22" t="s">
+      <c r="A153" s="22"/>
+      <c r="B153" s="23"/>
+      <c r="C153" s="23" t="s">
         <v>399</v>
       </c>
-      <c r="D153" s="22" t="s">
+      <c r="D153" s="23" t="s">
         <v>400</v>
       </c>
-      <c r="E153" s="23" t="s">
+      <c r="E153" s="24" t="s">
         <v>401</v>
       </c>
-      <c r="F153" s="23"/>
-      <c r="G153" s="23"/>
-      <c r="H153" s="23"/>
+      <c r="F153" s="24"/>
+      <c r="G153" s="24"/>
+      <c r="H153" s="24"/>
     </row>
     <row r="154" spans="1:8">
-      <c r="A154" s="21"/>
-      <c r="B154" s="22"/>
-      <c r="C154" s="22" t="s">
+      <c r="A154" s="22"/>
+      <c r="B154" s="23"/>
+      <c r="C154" s="23" t="s">
         <v>402</v>
       </c>
-      <c r="D154" s="22" t="s">
+      <c r="D154" s="23" t="s">
         <v>403</v>
       </c>
-      <c r="E154" s="23" t="s">
+      <c r="E154" s="24" t="s">
         <v>404</v>
       </c>
-      <c r="F154" s="23"/>
-      <c r="G154" s="23"/>
-      <c r="H154" s="23"/>
+      <c r="F154" s="24"/>
+      <c r="G154" s="24"/>
+      <c r="H154" s="24"/>
     </row>
     <row r="155" spans="1:8">
-      <c r="A155" s="21"/>
-      <c r="B155" s="22"/>
-      <c r="C155" s="22" t="s">
+      <c r="A155" s="22"/>
+      <c r="B155" s="23"/>
+      <c r="C155" s="23" t="s">
         <v>405</v>
       </c>
-      <c r="D155" s="22" t="s">
+      <c r="D155" s="23" t="s">
         <v>406</v>
       </c>
-      <c r="E155" s="23" t="s">
+      <c r="E155" s="24" t="s">
         <v>407</v>
       </c>
-      <c r="F155" s="23"/>
-      <c r="G155" s="23"/>
-      <c r="H155" s="23"/>
+      <c r="F155" s="24"/>
+      <c r="G155" s="24"/>
+      <c r="H155" s="24"/>
     </row>
     <row r="156" spans="1:8">
-      <c r="A156" s="21"/>
-      <c r="B156" s="22"/>
-      <c r="C156" s="22" t="s">
+      <c r="A156" s="22"/>
+      <c r="B156" s="23"/>
+      <c r="C156" s="23" t="s">
         <v>408</v>
       </c>
-      <c r="D156" s="22" t="s">
+      <c r="D156" s="23" t="s">
         <v>409</v>
       </c>
-      <c r="E156" s="23" t="s">
+      <c r="E156" s="24" t="s">
         <v>410</v>
       </c>
-      <c r="F156" s="23"/>
-      <c r="G156" s="23"/>
-      <c r="H156" s="23"/>
+      <c r="F156" s="24"/>
+      <c r="G156" s="24"/>
+      <c r="H156" s="24"/>
     </row>
     <row r="157" spans="1:8">
-      <c r="A157" s="21"/>
-      <c r="B157" s="22"/>
-      <c r="C157" s="22" t="s">
+      <c r="A157" s="22"/>
+      <c r="B157" s="23"/>
+      <c r="C157" s="23" t="s">
         <v>411</v>
       </c>
-      <c r="D157" s="22" t="s">
+      <c r="D157" s="23" t="s">
         <v>412</v>
       </c>
-      <c r="E157" s="23" t="s">
+      <c r="E157" s="24" t="s">
         <v>413</v>
       </c>
-      <c r="F157" s="23"/>
-      <c r="G157" s="23"/>
-      <c r="H157" s="23"/>
+      <c r="F157" s="24"/>
+      <c r="G157" s="24"/>
+      <c r="H157" s="24"/>
     </row>
     <row r="158" spans="1:8">
-      <c r="A158" s="21"/>
-      <c r="B158" s="22"/>
-      <c r="C158" s="22" t="s">
+      <c r="A158" s="22"/>
+      <c r="B158" s="23"/>
+      <c r="C158" s="23" t="s">
         <v>414</v>
       </c>
-      <c r="D158" s="22" t="s">
+      <c r="D158" s="23" t="s">
         <v>415</v>
       </c>
-      <c r="E158" s="23" t="s">
+      <c r="E158" s="24" t="s">
         <v>416</v>
       </c>
-      <c r="F158" s="23"/>
-      <c r="G158" s="23"/>
-      <c r="H158" s="23"/>
+      <c r="F158" s="24"/>
+      <c r="G158" s="24"/>
+      <c r="H158" s="24"/>
     </row>
     <row r="159" spans="1:8">
-      <c r="A159" s="21"/>
-      <c r="B159" s="22"/>
-      <c r="C159" s="22" t="s">
+      <c r="A159" s="22"/>
+      <c r="B159" s="23"/>
+      <c r="C159" s="23" t="s">
         <v>417</v>
       </c>
-      <c r="D159" s="22" t="s">
+      <c r="D159" s="23" t="s">
         <v>418</v>
       </c>
-      <c r="E159" s="23" t="s">
+      <c r="E159" s="24" t="s">
         <v>419</v>
       </c>
-      <c r="F159" s="23"/>
-      <c r="G159" s="23"/>
-      <c r="H159" s="23"/>
+      <c r="F159" s="24"/>
+      <c r="G159" s="24"/>
+      <c r="H159" s="24"/>
     </row>
     <row r="160" spans="1:8">
-      <c r="A160" s="21"/>
-      <c r="B160" s="22"/>
-      <c r="C160" s="22" t="s">
+      <c r="A160" s="22"/>
+      <c r="B160" s="23"/>
+      <c r="C160" s="23" t="s">
         <v>420</v>
       </c>
-      <c r="D160" s="22" t="s">
+      <c r="D160" s="23" t="s">
         <v>421</v>
       </c>
-      <c r="E160" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="F160" s="23"/>
-      <c r="G160" s="23"/>
-      <c r="H160" s="23"/>
+      <c r="E160" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="F160" s="24"/>
+      <c r="G160" s="24"/>
+      <c r="H160" s="24"/>
     </row>
     <row r="161" spans="1:8">
-      <c r="A161" s="21"/>
-      <c r="B161" s="22"/>
-      <c r="C161" s="22" t="s">
+      <c r="A161" s="22"/>
+      <c r="B161" s="23"/>
+      <c r="C161" s="23" t="s">
         <v>422</v>
       </c>
-      <c r="D161" s="22" t="s">
+      <c r="D161" s="23" t="s">
         <v>423</v>
       </c>
-      <c r="E161" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="F161" s="23"/>
-      <c r="G161" s="23"/>
-      <c r="H161" s="23"/>
+      <c r="E161" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="F161" s="24"/>
+      <c r="G161" s="24"/>
+      <c r="H161" s="24"/>
     </row>
     <row r="162" spans="1:8">
-      <c r="A162" s="21"/>
-      <c r="B162" s="22"/>
-      <c r="C162" s="22" t="s">
+      <c r="A162" s="22"/>
+      <c r="B162" s="23"/>
+      <c r="C162" s="23" t="s">
         <v>424</v>
       </c>
-      <c r="D162" s="22" t="s">
+      <c r="D162" s="23" t="s">
         <v>425</v>
       </c>
-      <c r="E162" s="23" t="s">
+      <c r="E162" s="24" t="s">
         <v>426</v>
       </c>
-      <c r="F162" s="23"/>
-      <c r="G162" s="23"/>
-      <c r="H162" s="23"/>
+      <c r="F162" s="24"/>
+      <c r="G162" s="24"/>
+      <c r="H162" s="24"/>
     </row>
     <row r="163" spans="1:8">
-      <c r="A163" s="21"/>
-      <c r="B163" s="22"/>
-      <c r="C163" s="22" t="s">
+      <c r="A163" s="22"/>
+      <c r="B163" s="23"/>
+      <c r="C163" s="23" t="s">
         <v>427</v>
       </c>
-      <c r="D163" s="22" t="s">
+      <c r="D163" s="23" t="s">
         <v>428</v>
       </c>
-      <c r="E163" s="23" t="s">
+      <c r="E163" s="24" t="s">
         <v>429</v>
       </c>
-      <c r="F163" s="23"/>
-      <c r="G163" s="23"/>
-      <c r="H163" s="23"/>
+      <c r="F163" s="24"/>
+      <c r="G163" s="24"/>
+      <c r="H163" s="24"/>
     </row>
     <row r="164" spans="1:8">
-      <c r="A164" s="21"/>
-      <c r="B164" s="22"/>
-      <c r="C164" s="22" t="s">
+      <c r="A164" s="22"/>
+      <c r="B164" s="23"/>
+      <c r="C164" s="23" t="s">
         <v>430</v>
       </c>
-      <c r="D164" s="22" t="s">
+      <c r="D164" s="23" t="s">
         <v>431</v>
       </c>
-      <c r="E164" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="F164" s="23"/>
-      <c r="G164" s="23"/>
-      <c r="H164" s="23"/>
+      <c r="E164" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="F164" s="24"/>
+      <c r="G164" s="24"/>
+      <c r="H164" s="24"/>
     </row>
     <row r="165" spans="1:8">
-      <c r="A165" s="21"/>
-      <c r="B165" s="22"/>
-      <c r="C165" s="22" t="s">
+      <c r="A165" s="22"/>
+      <c r="B165" s="23"/>
+      <c r="C165" s="23" t="s">
         <v>432</v>
       </c>
-      <c r="D165" s="22" t="s">
+      <c r="D165" s="23" t="s">
         <v>433</v>
       </c>
-      <c r="E165" s="23" t="s">
+      <c r="E165" s="24" t="s">
         <v>434</v>
       </c>
-      <c r="F165" s="23"/>
-      <c r="G165" s="23"/>
-      <c r="H165" s="23"/>
+      <c r="F165" s="24"/>
+      <c r="G165" s="24"/>
+      <c r="H165" s="24"/>
     </row>
     <row r="166" spans="1:8">
-      <c r="A166" s="21"/>
-      <c r="B166" s="22"/>
-      <c r="C166" s="22" t="s">
+      <c r="A166" s="22"/>
+      <c r="B166" s="23"/>
+      <c r="C166" s="23" t="s">
         <v>435</v>
       </c>
-      <c r="D166" s="22" t="s">
+      <c r="D166" s="23" t="s">
         <v>436</v>
       </c>
-      <c r="E166" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="F166" s="23"/>
-      <c r="G166" s="23"/>
-      <c r="H166" s="23"/>
+      <c r="E166" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="F166" s="24"/>
+      <c r="G166" s="24"/>
+      <c r="H166" s="24"/>
     </row>
     <row r="167" spans="1:8">
-      <c r="A167" s="21"/>
-      <c r="B167" s="22"/>
-      <c r="C167" s="22" t="s">
+      <c r="A167" s="22"/>
+      <c r="B167" s="23"/>
+      <c r="C167" s="23" t="s">
         <v>437</v>
       </c>
-      <c r="D167" s="22" t="s">
+      <c r="D167" s="23" t="s">
         <v>438</v>
       </c>
-      <c r="E167" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="F167" s="23"/>
-      <c r="G167" s="23"/>
-      <c r="H167" s="23"/>
+      <c r="E167" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="F167" s="24"/>
+      <c r="G167" s="24"/>
+      <c r="H167" s="24"/>
     </row>
     <row r="168" spans="1:8">
-      <c r="A168" s="21"/>
-      <c r="B168" s="22"/>
-      <c r="C168" s="22" t="s">
+      <c r="A168" s="22"/>
+      <c r="B168" s="23"/>
+      <c r="C168" s="23" t="s">
         <v>439</v>
       </c>
-      <c r="D168" s="22" t="s">
+      <c r="D168" s="23" t="s">
         <v>440</v>
       </c>
-      <c r="E168" s="23" t="s">
+      <c r="E168" s="24" t="s">
         <v>441</v>
       </c>
-      <c r="F168" s="23"/>
-      <c r="G168" s="23"/>
-      <c r="H168" s="23"/>
+      <c r="F168" s="24"/>
+      <c r="G168" s="24"/>
+      <c r="H168" s="24"/>
     </row>
     <row r="169" spans="1:8">
-      <c r="A169" s="21"/>
-      <c r="B169" s="22"/>
-      <c r="C169" s="22" t="s">
+      <c r="A169" s="22"/>
+      <c r="B169" s="23"/>
+      <c r="C169" s="23" t="s">
         <v>442</v>
       </c>
-      <c r="D169" s="22" t="s">
+      <c r="D169" s="23" t="s">
         <v>443</v>
       </c>
-      <c r="E169" s="23" t="s">
+      <c r="E169" s="24" t="s">
         <v>444</v>
       </c>
-      <c r="F169" s="23"/>
-      <c r="G169" s="23"/>
-      <c r="H169" s="23"/>
+      <c r="F169" s="24"/>
+      <c r="G169" s="24"/>
+      <c r="H169" s="24"/>
     </row>
     <row r="170" spans="1:8">
-      <c r="A170" s="21"/>
-      <c r="B170" s="22"/>
-      <c r="C170" s="22" t="s">
+      <c r="A170" s="22"/>
+      <c r="B170" s="23"/>
+      <c r="C170" s="23" t="s">
         <v>445</v>
       </c>
-      <c r="D170" s="22" t="s">
+      <c r="D170" s="23" t="s">
         <v>446</v>
       </c>
-      <c r="E170" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="F170" s="23"/>
-      <c r="G170" s="23"/>
-      <c r="H170" s="23"/>
+      <c r="E170" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="F170" s="24"/>
+      <c r="G170" s="24"/>
+      <c r="H170" s="24"/>
     </row>
     <row r="171" spans="1:8">
-      <c r="B171" s="24"/>
-      <c r="C171" s="24"/>
-      <c r="D171" s="24"/>
+      <c r="B171" s="25"/>
+      <c r="C171" s="25"/>
+      <c r="D171" s="25"/>
     </row>
     <row r="172" spans="1:8">
-      <c r="A172" s="25" t="s">
+      <c r="A172" s="26" t="s">
         <v>447</v>
       </c>
-      <c r="B172" s="25" t="s">
+      <c r="B172" s="26" t="s">
         <v>448</v>
       </c>
-      <c r="C172" s="26" t="s">
+      <c r="C172" s="27" t="s">
         <v>448</v>
       </c>
-      <c r="D172" s="26" t="s">
+      <c r="D172" s="27" t="s">
         <v>449</v>
       </c>
-      <c r="E172" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="F172" s="26"/>
-      <c r="G172" s="26"/>
-      <c r="H172" s="26"/>
+      <c r="E172" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F172" s="27"/>
+      <c r="G172" s="27"/>
+      <c r="H172" s="27"/>
     </row>
     <row r="173" spans="1:8">
-      <c r="A173" s="25"/>
-      <c r="B173" s="25"/>
-      <c r="C173" s="26" t="s">
+      <c r="A173" s="26"/>
+      <c r="B173" s="26"/>
+      <c r="C173" s="27" t="s">
         <v>450</v>
       </c>
-      <c r="D173" s="26" t="s">
+      <c r="D173" s="27" t="s">
         <v>451</v>
       </c>
-      <c r="E173" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="F173" s="26"/>
-      <c r="G173" s="26"/>
-      <c r="H173" s="26"/>
+      <c r="E173" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F173" s="27"/>
+      <c r="G173" s="27"/>
+      <c r="H173" s="27"/>
     </row>
     <row r="174" spans="1:8">
-      <c r="A174" s="25"/>
-      <c r="B174" s="25"/>
-      <c r="C174" s="26" t="s">
+      <c r="A174" s="26"/>
+      <c r="B174" s="26"/>
+      <c r="C174" s="27" t="s">
         <v>452</v>
       </c>
-      <c r="D174" s="26" t="s">
+      <c r="D174" s="27" t="s">
         <v>453</v>
       </c>
-      <c r="E174" s="26" t="s">
+      <c r="E174" s="27" t="s">
         <v>454</v>
       </c>
-      <c r="F174" s="26"/>
-      <c r="G174" s="26"/>
-      <c r="H174" s="26"/>
+      <c r="F174" s="27"/>
+      <c r="G174" s="27"/>
+      <c r="H174" s="27"/>
     </row>
     <row r="175" spans="1:8">
-      <c r="A175" s="25"/>
-      <c r="B175" s="25"/>
-      <c r="C175" s="26" t="s">
+      <c r="A175" s="26"/>
+      <c r="B175" s="26"/>
+      <c r="C175" s="27" t="s">
         <v>455</v>
       </c>
-      <c r="D175" s="26" t="s">
+      <c r="D175" s="27" t="s">
         <v>456</v>
       </c>
-      <c r="E175" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="F175" s="26"/>
-      <c r="G175" s="26"/>
-      <c r="H175" s="26"/>
+      <c r="E175" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F175" s="27"/>
+      <c r="G175" s="27"/>
+      <c r="H175" s="27"/>
     </row>
     <row r="176" spans="1:8">
-      <c r="A176" s="25"/>
-      <c r="B176" s="25"/>
-      <c r="C176" s="26" t="s">
+      <c r="A176" s="26"/>
+      <c r="B176" s="26"/>
+      <c r="C176" s="27" t="s">
         <v>457</v>
       </c>
-      <c r="D176" s="26" t="s">
+      <c r="D176" s="27" t="s">
         <v>458</v>
       </c>
-      <c r="E176" s="26" t="s">
+      <c r="E176" s="27" t="s">
         <v>459</v>
       </c>
-      <c r="F176" s="26"/>
-      <c r="G176" s="26"/>
-      <c r="H176" s="26"/>
+      <c r="F176" s="27"/>
+      <c r="G176" s="27"/>
+      <c r="H176" s="27"/>
     </row>
     <row r="177" spans="1:8">
-      <c r="A177" s="25"/>
-      <c r="B177" s="25"/>
-      <c r="C177" s="26" t="s">
+      <c r="A177" s="26"/>
+      <c r="B177" s="26"/>
+      <c r="C177" s="27" t="s">
         <v>460</v>
       </c>
-      <c r="D177" s="26" t="s">
+      <c r="D177" s="27" t="s">
         <v>461</v>
       </c>
-      <c r="E177" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="F177" s="26"/>
-      <c r="G177" s="26"/>
-      <c r="H177" s="26"/>
+      <c r="E177" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F177" s="27"/>
+      <c r="G177" s="27"/>
+      <c r="H177" s="27"/>
     </row>
     <row r="178" spans="1:8">
-      <c r="A178" s="25"/>
-      <c r="B178" s="25"/>
-      <c r="C178" s="26" t="s">
+      <c r="A178" s="26"/>
+      <c r="B178" s="26"/>
+      <c r="C178" s="27" t="s">
         <v>288</v>
       </c>
-      <c r="D178" s="26" t="s">
+      <c r="D178" s="27" t="s">
         <v>462</v>
       </c>
-      <c r="E178" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="F178" s="26"/>
-      <c r="G178" s="26"/>
-      <c r="H178" s="26"/>
+      <c r="E178" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F178" s="27"/>
+      <c r="G178" s="27"/>
+      <c r="H178" s="27"/>
     </row>
     <row r="179" spans="1:8">
-      <c r="A179" s="25"/>
-      <c r="B179" s="25"/>
-      <c r="C179" s="26" t="s">
+      <c r="A179" s="26"/>
+      <c r="B179" s="26"/>
+      <c r="C179" s="27" t="s">
         <v>463</v>
       </c>
-      <c r="D179" s="26" t="s">
+      <c r="D179" s="27" t="s">
         <v>464</v>
       </c>
-      <c r="E179" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="F179" s="26"/>
-      <c r="G179" s="26"/>
-      <c r="H179" s="26"/>
+      <c r="E179" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F179" s="27"/>
+      <c r="G179" s="27"/>
+      <c r="H179" s="27"/>
     </row>
     <row r="180" spans="1:8">
-      <c r="A180" s="25"/>
-      <c r="B180" s="25"/>
-      <c r="C180" s="26" t="s">
+      <c r="A180" s="26"/>
+      <c r="B180" s="26"/>
+      <c r="C180" s="27" t="s">
         <v>465</v>
       </c>
-      <c r="D180" s="26" t="s">
+      <c r="D180" s="27" t="s">
         <v>466</v>
       </c>
-      <c r="E180" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="F180" s="26"/>
-      <c r="G180" s="26"/>
-      <c r="H180" s="26"/>
+      <c r="E180" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F180" s="27"/>
+      <c r="G180" s="27"/>
+      <c r="H180" s="27"/>
     </row>
     <row r="181" spans="1:8">
-      <c r="A181" s="25"/>
-      <c r="B181" s="25"/>
-      <c r="C181" s="26" t="s">
+      <c r="A181" s="26"/>
+      <c r="B181" s="26"/>
+      <c r="C181" s="27" t="s">
         <v>299</v>
       </c>
-      <c r="D181" s="26" t="s">
+      <c r="D181" s="27" t="s">
         <v>467</v>
       </c>
-      <c r="E181" s="26" t="s">
+      <c r="E181" s="27" t="s">
         <v>468</v>
       </c>
-      <c r="F181" s="26"/>
-      <c r="G181" s="26"/>
-      <c r="H181" s="26"/>
+      <c r="F181" s="27"/>
+      <c r="G181" s="27"/>
+      <c r="H181" s="27"/>
     </row>
     <row r="182" spans="1:8">
-      <c r="A182" s="25"/>
-      <c r="B182" s="25"/>
-      <c r="C182" s="26" t="s">
+      <c r="A182" s="26"/>
+      <c r="B182" s="26"/>
+      <c r="C182" s="27" t="s">
         <v>469</v>
       </c>
-      <c r="D182" s="26" t="s">
+      <c r="D182" s="27" t="s">
         <v>470</v>
       </c>
-      <c r="E182" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="F182" s="26"/>
-      <c r="G182" s="26"/>
-      <c r="H182" s="26"/>
+      <c r="E182" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F182" s="27"/>
+      <c r="G182" s="27"/>
+      <c r="H182" s="27"/>
     </row>
     <row r="183" spans="1:8">
-      <c r="A183" s="25"/>
-      <c r="B183" s="25"/>
-      <c r="C183" s="26" t="s">
+      <c r="A183" s="26"/>
+      <c r="B183" s="26"/>
+      <c r="C183" s="27" t="s">
         <v>471</v>
       </c>
-      <c r="D183" s="26" t="s">
+      <c r="D183" s="27" t="s">
         <v>472</v>
       </c>
-      <c r="E183" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="F183" s="26"/>
-      <c r="G183" s="26"/>
-      <c r="H183" s="26"/>
+      <c r="E183" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F183" s="27"/>
+      <c r="G183" s="27"/>
+      <c r="H183" s="27"/>
     </row>
     <row r="184" spans="1:8">
-      <c r="A184" s="25"/>
-      <c r="B184" s="25"/>
-      <c r="C184" s="26" t="s">
+      <c r="A184" s="26"/>
+      <c r="B184" s="26"/>
+      <c r="C184" s="27" t="s">
         <v>473</v>
       </c>
-      <c r="D184" s="26" t="s">
+      <c r="D184" s="27" t="s">
         <v>474</v>
       </c>
-      <c r="E184" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="F184" s="26"/>
-      <c r="G184" s="26"/>
-      <c r="H184" s="26"/>
+      <c r="E184" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F184" s="27"/>
+      <c r="G184" s="27"/>
+      <c r="H184" s="27"/>
     </row>
     <row r="185" spans="1:8">
-      <c r="A185" s="25"/>
-      <c r="B185" s="25"/>
-      <c r="C185" s="26" t="s">
+      <c r="A185" s="26"/>
+      <c r="B185" s="26"/>
+      <c r="C185" s="27" t="s">
         <v>475</v>
       </c>
-      <c r="D185" s="26" t="s">
+      <c r="D185" s="27" t="s">
         <v>476</v>
       </c>
-      <c r="E185" s="26" t="s">
+      <c r="E185" s="27" t="s">
         <v>477</v>
       </c>
-      <c r="F185" s="26"/>
-      <c r="G185" s="26"/>
-      <c r="H185" s="26"/>
+      <c r="F185" s="27"/>
+      <c r="G185" s="27"/>
+      <c r="H185" s="27"/>
     </row>
     <row r="186" spans="1:8">
-      <c r="A186" s="25"/>
-      <c r="B186" s="25"/>
-      <c r="C186" s="26" t="s">
+      <c r="A186" s="26"/>
+      <c r="B186" s="26"/>
+      <c r="C186" s="27" t="s">
         <v>478</v>
       </c>
-      <c r="D186" s="26" t="s">
+      <c r="D186" s="27" t="s">
         <v>479</v>
       </c>
-      <c r="E186" s="26" t="s">
+      <c r="E186" s="27" t="s">
         <v>480</v>
       </c>
-      <c r="F186" s="26"/>
-      <c r="G186" s="26"/>
-      <c r="H186" s="26"/>
+      <c r="F186" s="27"/>
+      <c r="G186" s="27"/>
+      <c r="H186" s="27"/>
     </row>
     <row r="187" spans="1:8">
-      <c r="A187" s="25"/>
-      <c r="B187" s="25"/>
-      <c r="C187" s="26" t="s">
+      <c r="A187" s="26"/>
+      <c r="B187" s="26"/>
+      <c r="C187" s="27" t="s">
         <v>445</v>
       </c>
-      <c r="D187" s="26" t="s">
+      <c r="D187" s="27" t="s">
         <v>481</v>
       </c>
-      <c r="E187" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="F187" s="26"/>
-      <c r="G187" s="26"/>
-      <c r="H187" s="26"/>
+      <c r="E187" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F187" s="27"/>
+      <c r="G187" s="27"/>
+      <c r="H187" s="27"/>
     </row>
     <row r="188" spans="1:8">
-      <c r="A188" s="25"/>
-      <c r="B188" s="25" t="s">
+      <c r="A188" s="26"/>
+      <c r="B188" s="26" t="s">
         <v>482</v>
       </c>
-      <c r="C188" s="26" t="s">
+      <c r="C188" s="27" t="s">
         <v>483</v>
       </c>
-      <c r="D188" s="26" t="s">
+      <c r="D188" s="27" t="s">
         <v>484</v>
       </c>
-      <c r="E188" s="26" t="s">
+      <c r="E188" s="27" t="s">
         <v>485</v>
       </c>
-      <c r="F188" s="26"/>
-      <c r="G188" s="26"/>
-      <c r="H188" s="26"/>
+      <c r="F188" s="27"/>
+      <c r="G188" s="27"/>
+      <c r="H188" s="27"/>
     </row>
     <row r="189" spans="1:8">
-      <c r="A189" s="25"/>
-      <c r="B189" s="25"/>
-      <c r="C189" s="26" t="s">
+      <c r="A189" s="26"/>
+      <c r="B189" s="26"/>
+      <c r="C189" s="27" t="s">
         <v>486</v>
       </c>
-      <c r="D189" s="26" t="s">
+      <c r="D189" s="27" t="s">
         <v>487</v>
       </c>
-      <c r="E189" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="F189" s="26"/>
-      <c r="G189" s="26"/>
-      <c r="H189" s="26"/>
+      <c r="E189" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F189" s="27"/>
+      <c r="G189" s="27"/>
+      <c r="H189" s="27"/>
     </row>
     <row r="190" spans="1:8">
-      <c r="A190" s="25"/>
-      <c r="B190" s="25"/>
-      <c r="C190" s="26" t="s">
+      <c r="A190" s="26"/>
+      <c r="B190" s="26"/>
+      <c r="C190" s="27" t="s">
         <v>488</v>
       </c>
-      <c r="D190" s="26" t="s">
+      <c r="D190" s="27" t="s">
         <v>489</v>
       </c>
-      <c r="E190" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="F190" s="26"/>
-      <c r="G190" s="26"/>
-      <c r="H190" s="26"/>
+      <c r="E190" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F190" s="27"/>
+      <c r="G190" s="27"/>
+      <c r="H190" s="27"/>
     </row>
     <row r="191" spans="1:8">
-      <c r="A191" s="25"/>
-      <c r="B191" s="25"/>
-      <c r="C191" s="26" t="s">
+      <c r="A191" s="26"/>
+      <c r="B191" s="26"/>
+      <c r="C191" s="27" t="s">
         <v>490</v>
       </c>
-      <c r="D191" s="26" t="s">
+      <c r="D191" s="27" t="s">
         <v>491</v>
       </c>
-      <c r="E191" s="26" t="s">
+      <c r="E191" s="27" t="s">
         <v>492</v>
       </c>
-      <c r="F191" s="26"/>
-      <c r="G191" s="26"/>
-      <c r="H191" s="26"/>
+      <c r="F191" s="27"/>
+      <c r="G191" s="27"/>
+      <c r="H191" s="27"/>
     </row>
     <row r="192" spans="1:8">
-      <c r="A192" s="25"/>
-      <c r="B192" s="25"/>
-      <c r="C192" s="26" t="s">
+      <c r="A192" s="26"/>
+      <c r="B192" s="26"/>
+      <c r="C192" s="27" t="s">
         <v>493</v>
       </c>
-      <c r="D192" s="26" t="s">
+      <c r="D192" s="27" t="s">
         <v>494</v>
       </c>
-      <c r="E192" s="26" t="s">
+      <c r="E192" s="27" t="s">
         <v>495</v>
       </c>
-      <c r="F192" s="26"/>
-      <c r="G192" s="26"/>
-      <c r="H192" s="26"/>
+      <c r="F192" s="27"/>
+      <c r="G192" s="27"/>
+      <c r="H192" s="27"/>
     </row>
     <row r="193" spans="1:8">
-      <c r="A193" s="25"/>
-      <c r="B193" s="25"/>
-      <c r="C193" s="26" t="s">
+      <c r="A193" s="26"/>
+      <c r="B193" s="26"/>
+      <c r="C193" s="27" t="s">
         <v>496</v>
       </c>
-      <c r="D193" s="26" t="s">
+      <c r="D193" s="27" t="s">
         <v>497</v>
       </c>
-      <c r="E193" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="F193" s="26"/>
-      <c r="G193" s="26"/>
-      <c r="H193" s="26"/>
+      <c r="E193" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F193" s="27"/>
+      <c r="G193" s="27"/>
+      <c r="H193" s="27"/>
     </row>
     <row r="194" spans="1:8">
-      <c r="A194" s="25"/>
-      <c r="B194" s="25"/>
-      <c r="C194" s="26" t="s">
+      <c r="A194" s="26"/>
+      <c r="B194" s="26"/>
+      <c r="C194" s="27" t="s">
         <v>498</v>
       </c>
-      <c r="D194" s="26" t="s">
+      <c r="D194" s="27" t="s">
         <v>499</v>
       </c>
-      <c r="E194" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="F194" s="26"/>
-      <c r="G194" s="26"/>
-      <c r="H194" s="26"/>
+      <c r="E194" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F194" s="27"/>
+      <c r="G194" s="27"/>
+      <c r="H194" s="27"/>
     </row>
     <row r="195" spans="1:8">
-      <c r="A195" s="25"/>
-      <c r="B195" s="25"/>
-      <c r="C195" s="26" t="s">
+      <c r="A195" s="26"/>
+      <c r="B195" s="26"/>
+      <c r="C195" s="27" t="s">
         <v>500</v>
       </c>
-      <c r="D195" s="26" t="s">
+      <c r="D195" s="27" t="s">
         <v>501</v>
       </c>
-      <c r="E195" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="F195" s="26"/>
-      <c r="G195" s="26"/>
-      <c r="H195" s="26"/>
+      <c r="E195" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F195" s="27"/>
+      <c r="G195" s="27"/>
+      <c r="H195" s="27"/>
     </row>
     <row r="196" spans="1:8">
-      <c r="A196" s="25"/>
-      <c r="B196" s="25"/>
-      <c r="C196" s="26" t="s">
+      <c r="A196" s="26"/>
+      <c r="B196" s="26"/>
+      <c r="C196" s="27" t="s">
         <v>502</v>
       </c>
-      <c r="D196" s="26" t="s">
+      <c r="D196" s="27" t="s">
         <v>503</v>
       </c>
-      <c r="E196" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="F196" s="26"/>
-      <c r="G196" s="26"/>
-      <c r="H196" s="26"/>
+      <c r="E196" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F196" s="27"/>
+      <c r="G196" s="27"/>
+      <c r="H196" s="27"/>
     </row>
     <row r="197" spans="1:8">
-      <c r="A197" s="25"/>
-      <c r="B197" s="25"/>
-      <c r="C197" s="26" t="s">
+      <c r="A197" s="26"/>
+      <c r="B197" s="26"/>
+      <c r="C197" s="27" t="s">
         <v>504</v>
       </c>
-      <c r="D197" s="26" t="s">
+      <c r="D197" s="27" t="s">
         <v>505</v>
       </c>
-      <c r="E197" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="F197" s="26"/>
-      <c r="G197" s="26"/>
-      <c r="H197" s="26"/>
+      <c r="E197" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F197" s="27"/>
+      <c r="G197" s="27"/>
+      <c r="H197" s="27"/>
     </row>
     <row r="198" spans="1:8">
-      <c r="A198" s="25"/>
-      <c r="B198" s="25"/>
-      <c r="C198" s="26" t="s">
+      <c r="A198" s="26"/>
+      <c r="B198" s="26"/>
+      <c r="C198" s="27" t="s">
         <v>478</v>
       </c>
-      <c r="D198" s="26" t="s">
+      <c r="D198" s="27" t="s">
         <v>506</v>
       </c>
-      <c r="E198" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="F198" s="26"/>
-      <c r="G198" s="26"/>
-      <c r="H198" s="26"/>
+      <c r="E198" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F198" s="27"/>
+      <c r="G198" s="27"/>
+      <c r="H198" s="27"/>
     </row>
     <row r="199" spans="1:8">
-      <c r="A199" s="25"/>
-      <c r="B199" s="25"/>
-      <c r="C199" s="26" t="s">
+      <c r="A199" s="26"/>
+      <c r="B199" s="26"/>
+      <c r="C199" s="27" t="s">
         <v>507</v>
       </c>
-      <c r="D199" s="26" t="s">
+      <c r="D199" s="27" t="s">
         <v>508</v>
       </c>
-      <c r="E199" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="F199" s="26"/>
-      <c r="G199" s="26"/>
-      <c r="H199" s="26"/>
+      <c r="E199" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F199" s="27"/>
+      <c r="G199" s="27"/>
+      <c r="H199" s="27"/>
     </row>
     <row r="200" spans="1:8">
-      <c r="A200" s="25"/>
-      <c r="B200" s="25"/>
-      <c r="C200" s="26" t="s">
+      <c r="A200" s="26"/>
+      <c r="B200" s="26"/>
+      <c r="C200" s="27" t="s">
         <v>509</v>
       </c>
-      <c r="D200" s="26" t="s">
+      <c r="D200" s="27" t="s">
         <v>510</v>
       </c>
-      <c r="E200" s="26" t="s">
+      <c r="E200" s="27" t="s">
         <v>511</v>
       </c>
-      <c r="F200" s="26"/>
-      <c r="G200" s="26"/>
-      <c r="H200" s="26"/>
+      <c r="F200" s="27"/>
+      <c r="G200" s="27"/>
+      <c r="H200" s="27"/>
     </row>
     <row r="201" spans="1:8">
-      <c r="A201" s="25"/>
-      <c r="B201" s="25"/>
-      <c r="C201" s="26" t="s">
+      <c r="A201" s="26"/>
+      <c r="B201" s="26"/>
+      <c r="C201" s="27" t="s">
         <v>512</v>
       </c>
-      <c r="D201" s="26" t="s">
+      <c r="D201" s="27" t="s">
         <v>513</v>
       </c>
-      <c r="E201" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="F201" s="26"/>
-      <c r="G201" s="26"/>
-      <c r="H201" s="26"/>
+      <c r="E201" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F201" s="27"/>
+      <c r="G201" s="27"/>
+      <c r="H201" s="27"/>
     </row>
     <row r="202" spans="1:8">
-      <c r="A202" s="25"/>
-      <c r="B202" s="25"/>
-      <c r="C202" s="26" t="s">
+      <c r="A202" s="26"/>
+      <c r="B202" s="26"/>
+      <c r="C202" s="27" t="s">
         <v>514</v>
       </c>
-      <c r="D202" s="26" t="s">
+      <c r="D202" s="27" t="s">
         <v>515</v>
       </c>
-      <c r="E202" s="26" t="s">
+      <c r="E202" s="27" t="s">
         <v>516</v>
       </c>
-      <c r="F202" s="26"/>
-      <c r="G202" s="26"/>
-      <c r="H202" s="26"/>
+      <c r="F202" s="27"/>
+      <c r="G202" s="27"/>
+      <c r="H202" s="27"/>
     </row>
     <row r="203" spans="1:8">
-      <c r="A203" s="25"/>
-      <c r="B203" s="25"/>
-      <c r="C203" s="26" t="s">
+      <c r="A203" s="26"/>
+      <c r="B203" s="26"/>
+      <c r="C203" s="27" t="s">
         <v>322</v>
       </c>
-      <c r="D203" s="26" t="s">
+      <c r="D203" s="27" t="s">
         <v>517</v>
       </c>
-      <c r="E203" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="F203" s="26"/>
-      <c r="G203" s="26"/>
-      <c r="H203" s="26"/>
+      <c r="E203" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F203" s="27"/>
+      <c r="G203" s="27"/>
+      <c r="H203" s="27"/>
     </row>
     <row r="204" spans="1:8">
-      <c r="A204" s="25"/>
-      <c r="B204" s="25"/>
-      <c r="C204" s="26" t="s">
+      <c r="A204" s="26"/>
+      <c r="B204" s="26"/>
+      <c r="C204" s="27" t="s">
         <v>518</v>
       </c>
-      <c r="D204" s="26" t="s">
+      <c r="D204" s="27" t="s">
         <v>519</v>
       </c>
-      <c r="E204" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="F204" s="26"/>
-      <c r="G204" s="26"/>
-      <c r="H204" s="26"/>
+      <c r="E204" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F204" s="27"/>
+      <c r="G204" s="27"/>
+      <c r="H204" s="27"/>
     </row>
     <row r="205" spans="1:8">
-      <c r="A205" s="25"/>
-      <c r="B205" s="25"/>
-      <c r="C205" s="26" t="s">
+      <c r="A205" s="26"/>
+      <c r="B205" s="26"/>
+      <c r="C205" s="27" t="s">
         <v>520</v>
       </c>
-      <c r="D205" s="26" t="s">
+      <c r="D205" s="27" t="s">
         <v>521</v>
       </c>
-      <c r="E205" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="F205" s="26"/>
-      <c r="G205" s="26"/>
-      <c r="H205" s="26"/>
+      <c r="E205" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="F205" s="27"/>
+      <c r="G205" s="27"/>
+      <c r="H205" s="27"/>
     </row>
     <row r="206" spans="1:8">
-      <c r="B206" s="10"/>
-      <c r="C206" s="10"/>
-      <c r="D206" s="10"/>
-      <c r="E206" s="10"/>
+      <c r="B206" s="11"/>
+      <c r="C206" s="11"/>
+      <c r="D206" s="11"/>
+      <c r="E206" s="11"/>
     </row>
     <row r="207" spans="1:8">
-      <c r="A207" s="27" t="s">
+      <c r="A207" s="28" t="s">
         <v>522</v>
       </c>
-      <c r="B207" s="28"/>
-      <c r="C207" s="28" t="s">
+      <c r="B207" s="29"/>
+      <c r="C207" s="29" t="s">
         <v>523</v>
       </c>
-      <c r="D207" s="28" t="s">
+      <c r="D207" s="29" t="s">
         <v>524</v>
       </c>
-      <c r="E207" s="28" t="s">
+      <c r="E207" s="29" t="s">
         <v>525</v>
       </c>
-      <c r="F207" s="28"/>
-      <c r="G207" s="28"/>
-      <c r="H207" s="28"/>
+      <c r="F207" s="29"/>
+      <c r="G207" s="29"/>
+      <c r="H207" s="29"/>
     </row>
     <row r="208" spans="1:8">
-      <c r="A208" s="27"/>
-      <c r="B208" s="28"/>
-      <c r="C208" s="28" t="s">
+      <c r="A208" s="28"/>
+      <c r="B208" s="29"/>
+      <c r="C208" s="29" t="s">
         <v>526</v>
       </c>
-      <c r="D208" s="28" t="s">
+      <c r="D208" s="29" t="s">
         <v>527</v>
       </c>
-      <c r="E208" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F208" s="28"/>
-      <c r="G208" s="28"/>
-      <c r="H208" s="28"/>
+      <c r="E208" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F208" s="29"/>
+      <c r="G208" s="29"/>
+      <c r="H208" s="29"/>
     </row>
     <row r="209" spans="1:8">
-      <c r="A209" s="27"/>
-      <c r="B209" s="28"/>
-      <c r="C209" s="28" t="s">
+      <c r="A209" s="28"/>
+      <c r="B209" s="29"/>
+      <c r="C209" s="29" t="s">
         <v>528</v>
       </c>
-      <c r="D209" s="28" t="s">
+      <c r="D209" s="29" t="s">
         <v>529</v>
       </c>
-      <c r="E209" s="28" t="s">
+      <c r="E209" s="29" t="s">
         <v>530</v>
       </c>
-      <c r="F209" s="28"/>
-      <c r="G209" s="28"/>
-      <c r="H209" s="28"/>
+      <c r="F209" s="29"/>
+      <c r="G209" s="29"/>
+      <c r="H209" s="29"/>
     </row>
     <row r="210" spans="1:8">
-      <c r="A210" s="27"/>
-      <c r="B210" s="28"/>
-      <c r="C210" s="28" t="s">
+      <c r="A210" s="28"/>
+      <c r="B210" s="29"/>
+      <c r="C210" s="29" t="s">
         <v>531</v>
       </c>
-      <c r="D210" s="28" t="s">
+      <c r="D210" s="29" t="s">
         <v>532</v>
       </c>
-      <c r="E210" s="28" t="s">
+      <c r="E210" s="29" t="s">
         <v>533</v>
       </c>
-      <c r="F210" s="28"/>
-      <c r="G210" s="28"/>
-      <c r="H210" s="28"/>
+      <c r="F210" s="29"/>
+      <c r="G210" s="29"/>
+      <c r="H210" s="29"/>
     </row>
     <row r="211" spans="1:8">
-      <c r="A211" s="27"/>
-      <c r="B211" s="28"/>
-      <c r="C211" s="28" t="s">
+      <c r="A211" s="28"/>
+      <c r="B211" s="29"/>
+      <c r="C211" s="29" t="s">
         <v>534</v>
       </c>
-      <c r="D211" s="28" t="s">
+      <c r="D211" s="29" t="s">
         <v>535</v>
       </c>
-      <c r="E211" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F211" s="28"/>
-      <c r="G211" s="28"/>
-      <c r="H211" s="28"/>
+      <c r="E211" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F211" s="29"/>
+      <c r="G211" s="29"/>
+      <c r="H211" s="29"/>
     </row>
     <row r="212" spans="1:8">
-      <c r="A212" s="27"/>
-      <c r="B212" s="28"/>
-      <c r="C212" s="28" t="s">
+      <c r="A212" s="28"/>
+      <c r="B212" s="29"/>
+      <c r="C212" s="29" t="s">
         <v>536</v>
       </c>
-      <c r="D212" s="28" t="s">
+      <c r="D212" s="29" t="s">
         <v>537</v>
       </c>
-      <c r="E212" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F212" s="28"/>
-      <c r="G212" s="28"/>
-      <c r="H212" s="28"/>
+      <c r="E212" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F212" s="29"/>
+      <c r="G212" s="29"/>
+      <c r="H212" s="29"/>
     </row>
     <row r="213" spans="1:8">
-      <c r="A213" s="27"/>
-      <c r="B213" s="28"/>
-      <c r="C213" s="28" t="s">
+      <c r="A213" s="28"/>
+      <c r="B213" s="29"/>
+      <c r="C213" s="29" t="s">
         <v>288</v>
       </c>
-      <c r="D213" s="28" t="s">
+      <c r="D213" s="29" t="s">
         <v>538</v>
       </c>
-      <c r="E213" s="28" t="s">
+      <c r="E213" s="29" t="s">
         <v>539</v>
       </c>
-      <c r="F213" s="28"/>
-      <c r="G213" s="28"/>
-      <c r="H213" s="28"/>
+      <c r="F213" s="29"/>
+      <c r="G213" s="29"/>
+      <c r="H213" s="29"/>
     </row>
     <row r="214" spans="1:8">
-      <c r="A214" s="27"/>
-      <c r="B214" s="28"/>
-      <c r="C214" s="28" t="s">
+      <c r="A214" s="28"/>
+      <c r="B214" s="29"/>
+      <c r="C214" s="29" t="s">
         <v>540</v>
       </c>
-      <c r="D214" s="28" t="s">
+      <c r="D214" s="29" t="s">
         <v>541</v>
       </c>
-      <c r="E214" s="28" t="s">
+      <c r="E214" s="29" t="s">
         <v>542</v>
       </c>
-      <c r="F214" s="28"/>
-      <c r="G214" s="28"/>
-      <c r="H214" s="28"/>
+      <c r="F214" s="29"/>
+      <c r="G214" s="29"/>
+      <c r="H214" s="29"/>
     </row>
     <row r="215" spans="1:8">
-      <c r="A215" s="27"/>
-      <c r="B215" s="28"/>
-      <c r="C215" s="28" t="s">
+      <c r="A215" s="28"/>
+      <c r="B215" s="29"/>
+      <c r="C215" s="29" t="s">
         <v>543</v>
       </c>
-      <c r="D215" s="28" t="s">
+      <c r="D215" s="29" t="s">
         <v>544</v>
       </c>
-      <c r="E215" s="28" t="s">
+      <c r="E215" s="29" t="s">
         <v>545</v>
       </c>
-      <c r="F215" s="28"/>
-      <c r="G215" s="28"/>
-      <c r="H215" s="28"/>
+      <c r="F215" s="29"/>
+      <c r="G215" s="29"/>
+      <c r="H215" s="29"/>
     </row>
     <row r="216" spans="1:8">
-      <c r="A216" s="27"/>
-      <c r="B216" s="28"/>
-      <c r="C216" s="28" t="s">
+      <c r="A216" s="28"/>
+      <c r="B216" s="29"/>
+      <c r="C216" s="29" t="s">
         <v>546</v>
       </c>
-      <c r="D216" s="28" t="s">
+      <c r="D216" s="29" t="s">
         <v>547</v>
       </c>
-      <c r="E216" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F216" s="28"/>
-      <c r="G216" s="28"/>
-      <c r="H216" s="28"/>
+      <c r="E216" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F216" s="29"/>
+      <c r="G216" s="29"/>
+      <c r="H216" s="29"/>
     </row>
     <row r="217" spans="1:8">
-      <c r="A217" s="27"/>
-      <c r="B217" s="28"/>
-      <c r="C217" s="28" t="s">
+      <c r="A217" s="28"/>
+      <c r="B217" s="29"/>
+      <c r="C217" s="29" t="s">
         <v>548</v>
       </c>
-      <c r="D217" s="28" t="s">
+      <c r="D217" s="29" t="s">
         <v>549</v>
       </c>
-      <c r="E217" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F217" s="28"/>
-      <c r="G217" s="28"/>
-      <c r="H217" s="28"/>
+      <c r="E217" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F217" s="29"/>
+      <c r="G217" s="29"/>
+      <c r="H217" s="29"/>
     </row>
     <row r="218" spans="1:8">
-      <c r="A218" s="27"/>
-      <c r="B218" s="28"/>
-      <c r="C218" s="28" t="s">
+      <c r="A218" s="28"/>
+      <c r="B218" s="29"/>
+      <c r="C218" s="29" t="s">
         <v>550</v>
       </c>
-      <c r="D218" s="28" t="s">
+      <c r="D218" s="29" t="s">
         <v>551</v>
       </c>
-      <c r="E218" s="28" t="s">
+      <c r="E218" s="29" t="s">
         <v>552</v>
       </c>
-      <c r="F218" s="28"/>
-      <c r="G218" s="28"/>
-      <c r="H218" s="28"/>
+      <c r="F218" s="29"/>
+      <c r="G218" s="29"/>
+      <c r="H218" s="29"/>
     </row>
     <row r="219" spans="1:8">
-      <c r="A219" s="27"/>
-      <c r="B219" s="28"/>
-      <c r="C219" s="28" t="s">
+      <c r="A219" s="28"/>
+      <c r="B219" s="29"/>
+      <c r="C219" s="29" t="s">
         <v>553</v>
       </c>
-      <c r="D219" s="28" t="s">
+      <c r="D219" s="29" t="s">
         <v>554</v>
       </c>
-      <c r="E219" s="28" t="s">
+      <c r="E219" s="29" t="s">
         <v>555</v>
       </c>
-      <c r="F219" s="28"/>
-      <c r="G219" s="28"/>
-      <c r="H219" s="28"/>
+      <c r="F219" s="29"/>
+      <c r="G219" s="29"/>
+      <c r="H219" s="29"/>
     </row>
     <row r="220" spans="1:8">
-      <c r="A220" s="27"/>
-      <c r="B220" s="28"/>
-      <c r="C220" s="28" t="s">
+      <c r="A220" s="28"/>
+      <c r="B220" s="29"/>
+      <c r="C220" s="29" t="s">
         <v>556</v>
       </c>
-      <c r="D220" s="28" t="s">
+      <c r="D220" s="29" t="s">
         <v>557</v>
       </c>
-      <c r="E220" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F220" s="28"/>
-      <c r="G220" s="28"/>
-      <c r="H220" s="28"/>
+      <c r="E220" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F220" s="29"/>
+      <c r="G220" s="29"/>
+      <c r="H220" s="29"/>
     </row>
     <row r="221" spans="1:8">
-      <c r="A221" s="27"/>
-      <c r="B221" s="28"/>
-      <c r="C221" s="28" t="s">
+      <c r="A221" s="28"/>
+      <c r="B221" s="29"/>
+      <c r="C221" s="29" t="s">
         <v>558</v>
       </c>
-      <c r="D221" s="28" t="s">
+      <c r="D221" s="29" t="s">
         <v>559</v>
       </c>
-      <c r="E221" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F221" s="28"/>
-      <c r="G221" s="28"/>
-      <c r="H221" s="28"/>
+      <c r="E221" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F221" s="29"/>
+      <c r="G221" s="29"/>
+      <c r="H221" s="29"/>
     </row>
     <row r="222" spans="1:8">
-      <c r="A222" s="27"/>
-      <c r="B222" s="28"/>
-      <c r="C222" s="28" t="s">
+      <c r="A222" s="28"/>
+      <c r="B222" s="29"/>
+      <c r="C222" s="29" t="s">
         <v>560</v>
       </c>
-      <c r="D222" s="28" t="s">
+      <c r="D222" s="29" t="s">
         <v>561</v>
       </c>
-      <c r="E222" s="28" t="s">
+      <c r="E222" s="29" t="s">
         <v>562</v>
       </c>
-      <c r="F222" s="28"/>
-      <c r="G222" s="28"/>
-      <c r="H222" s="28"/>
+      <c r="F222" s="29"/>
+      <c r="G222" s="29"/>
+      <c r="H222" s="29"/>
     </row>
     <row r="223" spans="1:8">
-      <c r="A223" s="27"/>
-      <c r="B223" s="28"/>
-      <c r="C223" s="28" t="s">
+      <c r="A223" s="28"/>
+      <c r="B223" s="29"/>
+      <c r="C223" s="29" t="s">
         <v>563</v>
       </c>
-      <c r="D223" s="28" t="s">
+      <c r="D223" s="29" t="s">
         <v>564</v>
       </c>
-      <c r="E223" s="28" t="s">
+      <c r="E223" s="29" t="s">
         <v>565</v>
       </c>
-      <c r="F223" s="28"/>
-      <c r="G223" s="28"/>
-      <c r="H223" s="28"/>
+      <c r="F223" s="29"/>
+      <c r="G223" s="29"/>
+      <c r="H223" s="29"/>
     </row>
     <row r="224" spans="1:8">
-      <c r="A224" s="27"/>
-      <c r="B224" s="28"/>
-      <c r="C224" s="28" t="s">
+      <c r="A224" s="28"/>
+      <c r="B224" s="29"/>
+      <c r="C224" s="29" t="s">
         <v>566</v>
       </c>
-      <c r="D224" s="28" t="s">
+      <c r="D224" s="29" t="s">
         <v>567</v>
       </c>
-      <c r="E224" s="28" t="s">
+      <c r="E224" s="29" t="s">
         <v>568</v>
       </c>
-      <c r="F224" s="28"/>
-      <c r="G224" s="28"/>
-      <c r="H224" s="28"/>
+      <c r="F224" s="29"/>
+      <c r="G224" s="29"/>
+      <c r="H224" s="29"/>
     </row>
     <row r="225" spans="1:8">
-      <c r="A225" s="27"/>
-      <c r="B225" s="28"/>
-      <c r="C225" s="28" t="s">
+      <c r="A225" s="28"/>
+      <c r="B225" s="29"/>
+      <c r="C225" s="29" t="s">
         <v>569</v>
       </c>
-      <c r="D225" s="28" t="s">
+      <c r="D225" s="29" t="s">
         <v>570</v>
       </c>
-      <c r="E225" s="28" t="s">
+      <c r="E225" s="29" t="s">
         <v>571</v>
       </c>
-      <c r="F225" s="28"/>
-      <c r="G225" s="28"/>
-      <c r="H225" s="28"/>
+      <c r="F225" s="29"/>
+      <c r="G225" s="29"/>
+      <c r="H225" s="29"/>
     </row>
     <row r="226" spans="1:8">
-      <c r="A226" s="27"/>
-      <c r="B226" s="28"/>
-      <c r="C226" s="28" t="s">
+      <c r="A226" s="28"/>
+      <c r="B226" s="29"/>
+      <c r="C226" s="29" t="s">
         <v>328</v>
       </c>
-      <c r="D226" s="28" t="s">
+      <c r="D226" s="29" t="s">
         <v>572</v>
       </c>
-      <c r="E226" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F226" s="28"/>
-      <c r="G226" s="28"/>
-      <c r="H226" s="28"/>
+      <c r="E226" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F226" s="29"/>
+      <c r="G226" s="29"/>
+      <c r="H226" s="29"/>
     </row>
     <row r="227" spans="1:8">
-      <c r="A227" s="27"/>
-      <c r="B227" s="28"/>
-      <c r="C227" s="28" t="s">
+      <c r="A227" s="28"/>
+      <c r="B227" s="29"/>
+      <c r="C227" s="29" t="s">
         <v>573</v>
       </c>
-      <c r="D227" s="28" t="s">
+      <c r="D227" s="29" t="s">
         <v>574</v>
       </c>
-      <c r="E227" s="28" t="s">
+      <c r="E227" s="29" t="s">
         <v>575</v>
       </c>
-      <c r="F227" s="28"/>
-      <c r="G227" s="28"/>
-      <c r="H227" s="28"/>
+      <c r="F227" s="29"/>
+      <c r="G227" s="29"/>
+      <c r="H227" s="29"/>
     </row>
     <row r="228" spans="1:8">
-      <c r="A228" s="27"/>
-      <c r="B228" s="28"/>
-      <c r="C228" s="28" t="s">
+      <c r="A228" s="28"/>
+      <c r="B228" s="29"/>
+      <c r="C228" s="29" t="s">
         <v>576</v>
       </c>
-      <c r="D228" s="28" t="s">
+      <c r="D228" s="29" t="s">
         <v>577</v>
       </c>
-      <c r="E228" s="28" t="s">
+      <c r="E228" s="29" t="s">
         <v>578</v>
       </c>
-      <c r="F228" s="28"/>
-      <c r="G228" s="28"/>
-      <c r="H228" s="28"/>
+      <c r="F228" s="29"/>
+      <c r="G228" s="29"/>
+      <c r="H228" s="29"/>
     </row>
     <row r="229" spans="1:8">
-      <c r="A229" s="27"/>
-      <c r="B229" s="28"/>
-      <c r="C229" s="28" t="s">
+      <c r="A229" s="28"/>
+      <c r="B229" s="29"/>
+      <c r="C229" s="29" t="s">
         <v>579</v>
       </c>
-      <c r="D229" s="28" t="s">
+      <c r="D229" s="29" t="s">
         <v>580</v>
       </c>
-      <c r="E229" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F229" s="28"/>
-      <c r="G229" s="28"/>
-      <c r="H229" s="28"/>
+      <c r="E229" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F229" s="29"/>
+      <c r="G229" s="29"/>
+      <c r="H229" s="29"/>
     </row>
     <row r="230" spans="1:8">
-      <c r="A230" s="27"/>
-      <c r="B230" s="28"/>
-      <c r="C230" s="28" t="s">
+      <c r="A230" s="28"/>
+      <c r="B230" s="29"/>
+      <c r="C230" s="29" t="s">
         <v>581</v>
       </c>
-      <c r="D230" s="28" t="s">
+      <c r="D230" s="29" t="s">
         <v>582</v>
       </c>
-      <c r="E230" s="28" t="s">
+      <c r="E230" s="29" t="s">
         <v>583</v>
       </c>
-      <c r="F230" s="28"/>
-      <c r="G230" s="28"/>
-      <c r="H230" s="28"/>
+      <c r="F230" s="29"/>
+      <c r="G230" s="29"/>
+      <c r="H230" s="29"/>
     </row>
     <row r="231" spans="1:8">
-      <c r="A231" s="27"/>
-      <c r="B231" s="28"/>
-      <c r="C231" s="28" t="s">
+      <c r="A231" s="28"/>
+      <c r="B231" s="29"/>
+      <c r="C231" s="29" t="s">
         <v>299</v>
       </c>
-      <c r="D231" s="28" t="s">
+      <c r="D231" s="29" t="s">
         <v>584</v>
       </c>
-      <c r="E231" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F231" s="28"/>
-      <c r="G231" s="28"/>
-      <c r="H231" s="28"/>
+      <c r="E231" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F231" s="29"/>
+      <c r="G231" s="29"/>
+      <c r="H231" s="29"/>
     </row>
     <row r="232" spans="1:8">
-      <c r="A232" s="27"/>
-      <c r="B232" s="28"/>
-      <c r="C232" s="28" t="s">
+      <c r="A232" s="28"/>
+      <c r="B232" s="29"/>
+      <c r="C232" s="29" t="s">
         <v>585</v>
       </c>
-      <c r="D232" s="28" t="s">
+      <c r="D232" s="29" t="s">
         <v>586</v>
       </c>
-      <c r="E232" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F232" s="28"/>
-      <c r="G232" s="28"/>
-      <c r="H232" s="28"/>
+      <c r="E232" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F232" s="29"/>
+      <c r="G232" s="29"/>
+      <c r="H232" s="29"/>
     </row>
     <row r="233" spans="1:8">
-      <c r="A233" s="27"/>
-      <c r="B233" s="28"/>
-      <c r="C233" s="28" t="s">
+      <c r="A233" s="28"/>
+      <c r="B233" s="29"/>
+      <c r="C233" s="29" t="s">
         <v>587</v>
       </c>
-      <c r="D233" s="28" t="s">
+      <c r="D233" s="29" t="s">
         <v>588</v>
       </c>
-      <c r="E233" s="28" t="s">
+      <c r="E233" s="29" t="s">
         <v>589</v>
       </c>
-      <c r="F233" s="28"/>
-      <c r="G233" s="28"/>
-      <c r="H233" s="28"/>
+      <c r="F233" s="29"/>
+      <c r="G233" s="29"/>
+      <c r="H233" s="29"/>
     </row>
     <row r="234" spans="1:8">
-      <c r="A234" s="27"/>
-      <c r="B234" s="28"/>
-      <c r="C234" s="28" t="s">
+      <c r="A234" s="28"/>
+      <c r="B234" s="29"/>
+      <c r="C234" s="29" t="s">
         <v>590</v>
       </c>
-      <c r="D234" s="28" t="s">
+      <c r="D234" s="29" t="s">
         <v>591</v>
       </c>
-      <c r="E234" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F234" s="28"/>
-      <c r="G234" s="28"/>
-      <c r="H234" s="28"/>
+      <c r="E234" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F234" s="29"/>
+      <c r="G234" s="29"/>
+      <c r="H234" s="29"/>
     </row>
     <row r="235" spans="1:8">
-      <c r="A235" s="27"/>
-      <c r="B235" s="28"/>
-      <c r="C235" s="28" t="s">
+      <c r="A235" s="28"/>
+      <c r="B235" s="29"/>
+      <c r="C235" s="29" t="s">
         <v>592</v>
       </c>
-      <c r="D235" s="28" t="s">
+      <c r="D235" s="29" t="s">
         <v>593</v>
       </c>
-      <c r="E235" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F235" s="28"/>
-      <c r="G235" s="28"/>
-      <c r="H235" s="28"/>
+      <c r="E235" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F235" s="29"/>
+      <c r="G235" s="29"/>
+      <c r="H235" s="29"/>
     </row>
     <row r="236" spans="1:8">
-      <c r="A236" s="27"/>
-      <c r="B236" s="28"/>
-      <c r="C236" s="28" t="s">
+      <c r="A236" s="28"/>
+      <c r="B236" s="29"/>
+      <c r="C236" s="29" t="s">
         <v>594</v>
       </c>
-      <c r="D236" s="28" t="s">
+      <c r="D236" s="29" t="s">
         <v>595</v>
       </c>
-      <c r="E236" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F236" s="28"/>
-      <c r="G236" s="28"/>
-      <c r="H236" s="28"/>
+      <c r="E236" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F236" s="29"/>
+      <c r="G236" s="29"/>
+      <c r="H236" s="29"/>
     </row>
     <row r="237" spans="1:8">
-      <c r="A237" s="27"/>
-      <c r="B237" s="28"/>
-      <c r="C237" s="28" t="s">
+      <c r="A237" s="28"/>
+      <c r="B237" s="29"/>
+      <c r="C237" s="29" t="s">
         <v>596</v>
       </c>
-      <c r="D237" s="28" t="s">
+      <c r="D237" s="29" t="s">
         <v>597</v>
       </c>
-      <c r="E237" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F237" s="28"/>
-      <c r="G237" s="28"/>
-      <c r="H237" s="28"/>
+      <c r="E237" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F237" s="29"/>
+      <c r="G237" s="29"/>
+      <c r="H237" s="29"/>
     </row>
     <row r="238" spans="1:8">
-      <c r="A238" s="27"/>
-      <c r="B238" s="28"/>
-      <c r="C238" s="28" t="s">
+      <c r="A238" s="28"/>
+      <c r="B238" s="29"/>
+      <c r="C238" s="29" t="s">
         <v>598</v>
       </c>
-      <c r="D238" s="28" t="s">
+      <c r="D238" s="29" t="s">
         <v>599</v>
       </c>
-      <c r="E238" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F238" s="28"/>
-      <c r="G238" s="28"/>
-      <c r="H238" s="28"/>
+      <c r="E238" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F238" s="29"/>
+      <c r="G238" s="29"/>
+      <c r="H238" s="29"/>
     </row>
     <row r="239" spans="1:8">
-      <c r="A239" s="27"/>
-      <c r="B239" s="28"/>
-      <c r="C239" s="28" t="s">
+      <c r="A239" s="28"/>
+      <c r="B239" s="29"/>
+      <c r="C239" s="29" t="s">
         <v>600</v>
       </c>
-      <c r="D239" s="28" t="s">
+      <c r="D239" s="29" t="s">
         <v>601</v>
       </c>
-      <c r="E239" s="28" t="s">
+      <c r="E239" s="29" t="s">
         <v>602</v>
       </c>
-      <c r="F239" s="28"/>
-      <c r="G239" s="28"/>
-      <c r="H239" s="28"/>
+      <c r="F239" s="29"/>
+      <c r="G239" s="29"/>
+      <c r="H239" s="29"/>
     </row>
     <row r="240" spans="1:8">
-      <c r="A240" s="27"/>
-      <c r="B240" s="28"/>
-      <c r="C240" s="28" t="s">
+      <c r="A240" s="28"/>
+      <c r="B240" s="29"/>
+      <c r="C240" s="29" t="s">
         <v>603</v>
       </c>
-      <c r="D240" s="28" t="s">
+      <c r="D240" s="29" t="s">
         <v>604</v>
       </c>
-      <c r="E240" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F240" s="28"/>
-      <c r="G240" s="28"/>
-      <c r="H240" s="28"/>
+      <c r="E240" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F240" s="29"/>
+      <c r="G240" s="29"/>
+      <c r="H240" s="29"/>
     </row>
     <row r="241" spans="1:8">
-      <c r="A241" s="27"/>
-      <c r="B241" s="28"/>
-      <c r="C241" s="28" t="s">
+      <c r="A241" s="28"/>
+      <c r="B241" s="29"/>
+      <c r="C241" s="29" t="s">
         <v>605</v>
       </c>
-      <c r="D241" s="28" t="s">
+      <c r="D241" s="29" t="s">
         <v>606</v>
       </c>
-      <c r="E241" s="28" t="s">
+      <c r="E241" s="29" t="s">
         <v>607</v>
       </c>
-      <c r="F241" s="28"/>
-      <c r="G241" s="28"/>
-      <c r="H241" s="28"/>
+      <c r="F241" s="29"/>
+      <c r="G241" s="29"/>
+      <c r="H241" s="29"/>
     </row>
     <row r="242" spans="1:8">
-      <c r="A242" s="27"/>
-      <c r="B242" s="28"/>
-      <c r="C242" s="28" t="s">
+      <c r="A242" s="28"/>
+      <c r="B242" s="29"/>
+      <c r="C242" s="29" t="s">
         <v>608</v>
       </c>
-      <c r="D242" s="28" t="s">
+      <c r="D242" s="29" t="s">
         <v>609</v>
       </c>
-      <c r="E242" s="28" t="s">
+      <c r="E242" s="29" t="s">
         <v>610</v>
       </c>
-      <c r="F242" s="28"/>
-      <c r="G242" s="28"/>
-      <c r="H242" s="28"/>
+      <c r="F242" s="29"/>
+      <c r="G242" s="29"/>
+      <c r="H242" s="29"/>
     </row>
     <row r="243" spans="1:8">
-      <c r="A243" s="27"/>
-      <c r="B243" s="28"/>
-      <c r="C243" s="28" t="s">
+      <c r="A243" s="28"/>
+      <c r="B243" s="29"/>
+      <c r="C243" s="29" t="s">
         <v>611</v>
       </c>
-      <c r="D243" s="28" t="s">
+      <c r="D243" s="29" t="s">
         <v>612</v>
       </c>
-      <c r="E243" s="28" t="s">
+      <c r="E243" s="29" t="s">
         <v>613</v>
       </c>
-      <c r="F243" s="28"/>
-      <c r="G243" s="28"/>
-      <c r="H243" s="28"/>
+      <c r="F243" s="29"/>
+      <c r="G243" s="29"/>
+      <c r="H243" s="29"/>
     </row>
     <row r="244" spans="1:8">
-      <c r="A244" s="27"/>
-      <c r="B244" s="28"/>
-      <c r="C244" s="28" t="s">
+      <c r="A244" s="28"/>
+      <c r="B244" s="29"/>
+      <c r="C244" s="29" t="s">
         <v>614</v>
       </c>
-      <c r="D244" s="28" t="s">
+      <c r="D244" s="29" t="s">
         <v>615</v>
       </c>
-      <c r="E244" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F244" s="28"/>
-      <c r="G244" s="28"/>
-      <c r="H244" s="28"/>
+      <c r="E244" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F244" s="29"/>
+      <c r="G244" s="29"/>
+      <c r="H244" s="29"/>
     </row>
     <row r="245" spans="1:8">
-      <c r="A245" s="27"/>
-      <c r="B245" s="28"/>
-      <c r="C245" s="28" t="s">
+      <c r="A245" s="28"/>
+      <c r="B245" s="29"/>
+      <c r="C245" s="29" t="s">
         <v>616</v>
       </c>
-      <c r="D245" s="28" t="s">
+      <c r="D245" s="29" t="s">
         <v>617</v>
       </c>
-      <c r="E245" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F245" s="28"/>
-      <c r="G245" s="28"/>
-      <c r="H245" s="28"/>
+      <c r="E245" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F245" s="29"/>
+      <c r="G245" s="29"/>
+      <c r="H245" s="29"/>
     </row>
     <row r="246" spans="1:8">
-      <c r="A246" s="27"/>
-      <c r="B246" s="28"/>
-      <c r="C246" s="28" t="s">
+      <c r="A246" s="28"/>
+      <c r="B246" s="29"/>
+      <c r="C246" s="29" t="s">
         <v>618</v>
       </c>
-      <c r="D246" s="28" t="s">
+      <c r="D246" s="29" t="s">
         <v>619</v>
       </c>
-      <c r="E246" s="28" t="s">
+      <c r="E246" s="29" t="s">
         <v>620</v>
       </c>
-      <c r="F246" s="28"/>
-      <c r="G246" s="28"/>
-      <c r="H246" s="28"/>
+      <c r="F246" s="29"/>
+      <c r="G246" s="29"/>
+      <c r="H246" s="29"/>
     </row>
     <row r="247" spans="1:8">
-      <c r="A247" s="27"/>
-      <c r="B247" s="28"/>
-      <c r="C247" s="28" t="s">
+      <c r="A247" s="28"/>
+      <c r="B247" s="29"/>
+      <c r="C247" s="29" t="s">
         <v>621</v>
       </c>
-      <c r="D247" s="28" t="s">
+      <c r="D247" s="29" t="s">
         <v>622</v>
       </c>
-      <c r="E247" s="28" t="s">
+      <c r="E247" s="29" t="s">
         <v>623</v>
       </c>
-      <c r="F247" s="28"/>
-      <c r="G247" s="28"/>
-      <c r="H247" s="28"/>
+      <c r="F247" s="29"/>
+      <c r="G247" s="29"/>
+      <c r="H247" s="29"/>
     </row>
     <row r="248" spans="1:8">
-      <c r="A248" s="27"/>
-      <c r="B248" s="28"/>
-      <c r="C248" s="28" t="s">
+      <c r="A248" s="28"/>
+      <c r="B248" s="29"/>
+      <c r="C248" s="29" t="s">
         <v>624</v>
       </c>
-      <c r="D248" s="28" t="s">
+      <c r="D248" s="29" t="s">
         <v>625</v>
       </c>
-      <c r="E248" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F248" s="28"/>
-      <c r="G248" s="28"/>
-      <c r="H248" s="28"/>
+      <c r="E248" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F248" s="29"/>
+      <c r="G248" s="29"/>
+      <c r="H248" s="29"/>
     </row>
     <row r="249" spans="1:8">
-      <c r="A249" s="27"/>
-      <c r="B249" s="28"/>
-      <c r="C249" s="28" t="s">
+      <c r="A249" s="28"/>
+      <c r="B249" s="29"/>
+      <c r="C249" s="29" t="s">
         <v>626</v>
       </c>
-      <c r="D249" s="28" t="s">
+      <c r="D249" s="29" t="s">
         <v>627</v>
       </c>
-      <c r="E249" s="28" t="s">
+      <c r="E249" s="29" t="s">
         <v>628</v>
       </c>
-      <c r="F249" s="28"/>
-      <c r="G249" s="28"/>
-      <c r="H249" s="28"/>
+      <c r="F249" s="29"/>
+      <c r="G249" s="29"/>
+      <c r="H249" s="29"/>
     </row>
     <row r="250" spans="1:8">
-      <c r="A250" s="27"/>
-      <c r="B250" s="28"/>
-      <c r="C250" s="28" t="s">
+      <c r="A250" s="28"/>
+      <c r="B250" s="29"/>
+      <c r="C250" s="29" t="s">
         <v>629</v>
       </c>
-      <c r="D250" s="28" t="s">
+      <c r="D250" s="29" t="s">
         <v>630</v>
       </c>
-      <c r="E250" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F250" s="28"/>
-      <c r="G250" s="28"/>
-      <c r="H250" s="28"/>
+      <c r="E250" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F250" s="29"/>
+      <c r="G250" s="29"/>
+      <c r="H250" s="29"/>
     </row>
     <row r="251" spans="1:8">
-      <c r="A251" s="27"/>
-      <c r="B251" s="28"/>
-      <c r="C251" s="28" t="s">
+      <c r="A251" s="28"/>
+      <c r="B251" s="29"/>
+      <c r="C251" s="29" t="s">
         <v>631</v>
       </c>
-      <c r="D251" s="28" t="s">
+      <c r="D251" s="29" t="s">
         <v>632</v>
       </c>
-      <c r="E251" s="28" t="s">
+      <c r="E251" s="29" t="s">
         <v>633</v>
       </c>
-      <c r="F251" s="28"/>
-      <c r="G251" s="28"/>
-      <c r="H251" s="28"/>
+      <c r="F251" s="29"/>
+      <c r="G251" s="29"/>
+      <c r="H251" s="29"/>
     </row>
     <row r="252" spans="1:8">
-      <c r="A252" s="27"/>
-      <c r="B252" s="28"/>
-      <c r="C252" s="28" t="s">
+      <c r="A252" s="28"/>
+      <c r="B252" s="29"/>
+      <c r="C252" s="29" t="s">
         <v>634</v>
       </c>
-      <c r="D252" s="28" t="s">
+      <c r="D252" s="29" t="s">
         <v>635</v>
       </c>
-      <c r="E252" s="28" t="s">
+      <c r="E252" s="29" t="s">
         <v>636</v>
       </c>
-      <c r="F252" s="28"/>
-      <c r="G252" s="28"/>
-      <c r="H252" s="28"/>
+      <c r="F252" s="29"/>
+      <c r="G252" s="29"/>
+      <c r="H252" s="29"/>
     </row>
     <row r="253" spans="1:8">
-      <c r="A253" s="27"/>
-      <c r="B253" s="28"/>
-      <c r="C253" s="28" t="s">
+      <c r="A253" s="28"/>
+      <c r="B253" s="29"/>
+      <c r="C253" s="29" t="s">
         <v>637</v>
       </c>
-      <c r="D253" s="28" t="s">
+      <c r="D253" s="29" t="s">
         <v>638</v>
       </c>
-      <c r="E253" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F253" s="28"/>
-      <c r="G253" s="28"/>
-      <c r="H253" s="28"/>
+      <c r="E253" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F253" s="29"/>
+      <c r="G253" s="29"/>
+      <c r="H253" s="29"/>
     </row>
     <row r="254" spans="1:8">
-      <c r="A254" s="27"/>
-      <c r="B254" s="28"/>
-      <c r="C254" s="28" t="s">
+      <c r="A254" s="28"/>
+      <c r="B254" s="29"/>
+      <c r="C254" s="29" t="s">
         <v>639</v>
       </c>
-      <c r="D254" s="28" t="s">
+      <c r="D254" s="29" t="s">
         <v>640</v>
       </c>
-      <c r="E254" s="28" t="s">
+      <c r="E254" s="29" t="s">
         <v>641</v>
       </c>
-      <c r="F254" s="28"/>
-      <c r="G254" s="28"/>
-      <c r="H254" s="28"/>
+      <c r="F254" s="29"/>
+      <c r="G254" s="29"/>
+      <c r="H254" s="29"/>
     </row>
     <row r="255" spans="1:8">
-      <c r="A255" s="27"/>
-      <c r="B255" s="28"/>
-      <c r="C255" s="28" t="s">
+      <c r="A255" s="28"/>
+      <c r="B255" s="29"/>
+      <c r="C255" s="29" t="s">
         <v>642</v>
       </c>
-      <c r="D255" s="28" t="s">
+      <c r="D255" s="29" t="s">
         <v>643</v>
       </c>
-      <c r="E255" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F255" s="28"/>
-      <c r="G255" s="28"/>
-      <c r="H255" s="28"/>
+      <c r="E255" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F255" s="29"/>
+      <c r="G255" s="29"/>
+      <c r="H255" s="29"/>
     </row>
     <row r="256" spans="1:8">
-      <c r="A256" s="27"/>
-      <c r="B256" s="28"/>
-      <c r="C256" s="28" t="s">
+      <c r="A256" s="28"/>
+      <c r="B256" s="29"/>
+      <c r="C256" s="29" t="s">
         <v>644</v>
       </c>
-      <c r="D256" s="28" t="s">
+      <c r="D256" s="29" t="s">
         <v>645</v>
       </c>
-      <c r="E256" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F256" s="28"/>
-      <c r="G256" s="28"/>
-      <c r="H256" s="28"/>
+      <c r="E256" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F256" s="29"/>
+      <c r="G256" s="29"/>
+      <c r="H256" s="29"/>
     </row>
     <row r="257" spans="1:8">
-      <c r="A257" s="27"/>
-      <c r="B257" s="28"/>
-      <c r="C257" s="28" t="s">
+      <c r="A257" s="28"/>
+      <c r="B257" s="29"/>
+      <c r="C257" s="29" t="s">
         <v>646</v>
       </c>
-      <c r="D257" s="28" t="s">
+      <c r="D257" s="29" t="s">
         <v>647</v>
       </c>
-      <c r="E257" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F257" s="28"/>
-      <c r="G257" s="28"/>
-      <c r="H257" s="28"/>
+      <c r="E257" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F257" s="29"/>
+      <c r="G257" s="29"/>
+      <c r="H257" s="29"/>
     </row>
     <row r="258" spans="1:8">
-      <c r="A258" s="27"/>
-      <c r="B258" s="28"/>
-      <c r="C258" s="28" t="s">
+      <c r="A258" s="28"/>
+      <c r="B258" s="29"/>
+      <c r="C258" s="29" t="s">
         <v>648</v>
       </c>
-      <c r="D258" s="28" t="s">
+      <c r="D258" s="29" t="s">
         <v>649</v>
       </c>
-      <c r="E258" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F258" s="28"/>
-      <c r="G258" s="28"/>
-      <c r="H258" s="28"/>
+      <c r="E258" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F258" s="29"/>
+      <c r="G258" s="29"/>
+      <c r="H258" s="29"/>
     </row>
     <row r="259" spans="1:8">
-      <c r="A259" s="27"/>
-      <c r="B259" s="28"/>
-      <c r="C259" s="28" t="s">
+      <c r="A259" s="28"/>
+      <c r="B259" s="29"/>
+      <c r="C259" s="29" t="s">
         <v>650</v>
       </c>
-      <c r="D259" s="28" t="s">
+      <c r="D259" s="29" t="s">
         <v>651</v>
       </c>
-      <c r="E259" s="28" t="s">
+      <c r="E259" s="29" t="s">
         <v>652</v>
       </c>
-      <c r="F259" s="28"/>
-      <c r="G259" s="28"/>
-      <c r="H259" s="28"/>
+      <c r="F259" s="29"/>
+      <c r="G259" s="29"/>
+      <c r="H259" s="29"/>
     </row>
     <row r="260" spans="1:8">
-      <c r="A260" s="27"/>
-      <c r="B260" s="28"/>
-      <c r="C260" s="28" t="s">
+      <c r="A260" s="28"/>
+      <c r="B260" s="29"/>
+      <c r="C260" s="29" t="s">
         <v>653</v>
       </c>
-      <c r="D260" s="28" t="s">
+      <c r="D260" s="29" t="s">
         <v>654</v>
       </c>
-      <c r="E260" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F260" s="28"/>
-      <c r="G260" s="28"/>
-      <c r="H260" s="28"/>
+      <c r="E260" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F260" s="29"/>
+      <c r="G260" s="29"/>
+      <c r="H260" s="29"/>
     </row>
     <row r="261" spans="1:8">
-      <c r="A261" s="27"/>
-      <c r="B261" s="28"/>
-      <c r="C261" s="28" t="s">
+      <c r="A261" s="28"/>
+      <c r="B261" s="29"/>
+      <c r="C261" s="29" t="s">
         <v>655</v>
       </c>
-      <c r="D261" s="28" t="s">
+      <c r="D261" s="29" t="s">
         <v>656</v>
       </c>
-      <c r="E261" s="28" t="s">
+      <c r="E261" s="29" t="s">
         <v>657</v>
       </c>
-      <c r="F261" s="28"/>
-      <c r="G261" s="28"/>
-      <c r="H261" s="28"/>
+      <c r="F261" s="29"/>
+      <c r="G261" s="29"/>
+      <c r="H261" s="29"/>
     </row>
     <row r="262" spans="1:8">
-      <c r="A262" s="27"/>
-      <c r="B262" s="28"/>
-      <c r="C262" s="28" t="s">
+      <c r="A262" s="28"/>
+      <c r="B262" s="29"/>
+      <c r="C262" s="29" t="s">
         <v>658</v>
       </c>
-      <c r="D262" s="28" t="s">
+      <c r="D262" s="29" t="s">
         <v>659</v>
       </c>
-      <c r="E262" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F262" s="28"/>
-      <c r="G262" s="28"/>
-      <c r="H262" s="28"/>
+      <c r="E262" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F262" s="29"/>
+      <c r="G262" s="29"/>
+      <c r="H262" s="29"/>
     </row>
     <row r="263" spans="1:8">
-      <c r="A263" s="27"/>
-      <c r="B263" s="28"/>
-      <c r="C263" s="28" t="s">
+      <c r="A263" s="28"/>
+      <c r="B263" s="29"/>
+      <c r="C263" s="29" t="s">
         <v>660</v>
       </c>
-      <c r="D263" s="28" t="s">
+      <c r="D263" s="29" t="s">
         <v>661</v>
       </c>
-      <c r="E263" s="28" t="s">
+      <c r="E263" s="29" t="s">
         <v>662</v>
       </c>
-      <c r="F263" s="28"/>
-      <c r="G263" s="28"/>
-      <c r="H263" s="28"/>
+      <c r="F263" s="29"/>
+      <c r="G263" s="29"/>
+      <c r="H263" s="29"/>
     </row>
     <row r="264" spans="1:8">
-      <c r="A264" s="27"/>
-      <c r="B264" s="28"/>
-      <c r="C264" s="28" t="s">
+      <c r="A264" s="28"/>
+      <c r="B264" s="29"/>
+      <c r="C264" s="29" t="s">
         <v>663</v>
       </c>
-      <c r="D264" s="28" t="s">
+      <c r="D264" s="29" t="s">
         <v>664</v>
       </c>
-      <c r="E264" s="28" t="s">
+      <c r="E264" s="29" t="s">
         <v>665</v>
       </c>
-      <c r="F264" s="28"/>
-      <c r="G264" s="28"/>
-      <c r="H264" s="28"/>
+      <c r="F264" s="29"/>
+      <c r="G264" s="29"/>
+      <c r="H264" s="29"/>
     </row>
     <row r="265" spans="1:8">
-      <c r="A265" s="27"/>
-      <c r="B265" s="28"/>
-      <c r="C265" s="28" t="s">
+      <c r="A265" s="28"/>
+      <c r="B265" s="29"/>
+      <c r="C265" s="29" t="s">
         <v>666</v>
       </c>
-      <c r="D265" s="28" t="s">
+      <c r="D265" s="29" t="s">
         <v>667</v>
       </c>
-      <c r="E265" s="28" t="s">
+      <c r="E265" s="29" t="s">
         <v>668</v>
       </c>
-      <c r="F265" s="28"/>
-      <c r="G265" s="28"/>
-      <c r="H265" s="28"/>
+      <c r="F265" s="29"/>
+      <c r="G265" s="29"/>
+      <c r="H265" s="29"/>
     </row>
     <row r="266" spans="1:8">
-      <c r="A266" s="27"/>
-      <c r="B266" s="28"/>
-      <c r="C266" s="28" t="s">
+      <c r="A266" s="28"/>
+      <c r="B266" s="29"/>
+      <c r="C266" s="29" t="s">
         <v>669</v>
       </c>
-      <c r="D266" s="28" t="s">
+      <c r="D266" s="29" t="s">
         <v>670</v>
       </c>
-      <c r="E266" s="28" t="s">
+      <c r="E266" s="29" t="s">
         <v>671</v>
       </c>
-      <c r="F266" s="28"/>
-      <c r="G266" s="28"/>
-      <c r="H266" s="28"/>
+      <c r="F266" s="29"/>
+      <c r="G266" s="29"/>
+      <c r="H266" s="29"/>
     </row>
     <row r="267" spans="1:8">
-      <c r="A267" s="27"/>
-      <c r="B267" s="28"/>
-      <c r="C267" s="28" t="s">
+      <c r="A267" s="28"/>
+      <c r="B267" s="29"/>
+      <c r="C267" s="29" t="s">
         <v>672</v>
       </c>
-      <c r="D267" s="28" t="s">
+      <c r="D267" s="29" t="s">
         <v>673</v>
       </c>
-      <c r="E267" s="28" t="s">
+      <c r="E267" s="29" t="s">
         <v>674</v>
       </c>
-      <c r="F267" s="28"/>
-      <c r="G267" s="28"/>
-      <c r="H267" s="28"/>
+      <c r="F267" s="29"/>
+      <c r="G267" s="29"/>
+      <c r="H267" s="29"/>
     </row>
     <row r="268" spans="1:8">
-      <c r="A268" s="27"/>
-      <c r="B268" s="28"/>
-      <c r="C268" s="28" t="s">
+      <c r="A268" s="28"/>
+      <c r="B268" s="29"/>
+      <c r="C268" s="29" t="s">
         <v>675</v>
       </c>
-      <c r="D268" s="28" t="s">
+      <c r="D268" s="29" t="s">
         <v>676</v>
       </c>
-      <c r="E268" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F268" s="28"/>
-      <c r="G268" s="28"/>
-      <c r="H268" s="28"/>
+      <c r="E268" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F268" s="29"/>
+      <c r="G268" s="29"/>
+      <c r="H268" s="29"/>
     </row>
     <row r="269" spans="1:8">
-      <c r="A269" s="27"/>
-      <c r="B269" s="28"/>
-      <c r="C269" s="28" t="s">
+      <c r="A269" s="28"/>
+      <c r="B269" s="29"/>
+      <c r="C269" s="29" t="s">
         <v>677</v>
       </c>
-      <c r="D269" s="28" t="s">
+      <c r="D269" s="29" t="s">
         <v>678</v>
       </c>
-      <c r="E269" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F269" s="28"/>
-      <c r="G269" s="28"/>
-      <c r="H269" s="28"/>
+      <c r="E269" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F269" s="29"/>
+      <c r="G269" s="29"/>
+      <c r="H269" s="29"/>
     </row>
     <row r="270" spans="1:8">
-      <c r="A270" s="27"/>
-      <c r="B270" s="28"/>
-      <c r="C270" s="28" t="s">
+      <c r="A270" s="28"/>
+      <c r="B270" s="29"/>
+      <c r="C270" s="29" t="s">
         <v>679</v>
       </c>
-      <c r="D270" s="28" t="s">
+      <c r="D270" s="29" t="s">
         <v>680</v>
       </c>
-      <c r="E270" s="28" t="s">
+      <c r="E270" s="29" t="s">
         <v>681</v>
       </c>
-      <c r="F270" s="28"/>
-      <c r="G270" s="28"/>
-      <c r="H270" s="28"/>
+      <c r="F270" s="29"/>
+      <c r="G270" s="29"/>
+      <c r="H270" s="29"/>
     </row>
     <row r="271" spans="1:8">
-      <c r="A271" s="27"/>
-      <c r="B271" s="28"/>
-      <c r="C271" s="28" t="s">
+      <c r="A271" s="28"/>
+      <c r="B271" s="29"/>
+      <c r="C271" s="29" t="s">
         <v>682</v>
       </c>
-      <c r="D271" s="28" t="s">
+      <c r="D271" s="29" t="s">
         <v>683</v>
       </c>
-      <c r="E271" s="28" t="s">
+      <c r="E271" s="29" t="s">
         <v>684</v>
       </c>
-      <c r="F271" s="28"/>
-      <c r="G271" s="28"/>
-      <c r="H271" s="28"/>
+      <c r="F271" s="29"/>
+      <c r="G271" s="29"/>
+      <c r="H271" s="29"/>
     </row>
     <row r="272" spans="1:8">
-      <c r="A272" s="27"/>
-      <c r="B272" s="28"/>
-      <c r="C272" s="28" t="s">
+      <c r="A272" s="28"/>
+      <c r="B272" s="29"/>
+      <c r="C272" s="29" t="s">
         <v>685</v>
       </c>
-      <c r="D272" s="28" t="s">
+      <c r="D272" s="29" t="s">
         <v>686</v>
       </c>
-      <c r="E272" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F272" s="28"/>
-      <c r="G272" s="28"/>
-      <c r="H272" s="28"/>
+      <c r="E272" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F272" s="29"/>
+      <c r="G272" s="29"/>
+      <c r="H272" s="29"/>
     </row>
     <row r="273" spans="1:8">
-      <c r="A273" s="27"/>
-      <c r="B273" s="28"/>
-      <c r="C273" s="28" t="s">
+      <c r="A273" s="28"/>
+      <c r="B273" s="29"/>
+      <c r="C273" s="29" t="s">
         <v>687</v>
       </c>
-      <c r="D273" s="28" t="s">
+      <c r="D273" s="29" t="s">
         <v>688</v>
       </c>
-      <c r="E273" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F273" s="28"/>
-      <c r="G273" s="28"/>
-      <c r="H273" s="28"/>
+      <c r="E273" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F273" s="29"/>
+      <c r="G273" s="29"/>
+      <c r="H273" s="29"/>
     </row>
     <row r="274" spans="1:8">
-      <c r="A274" s="27"/>
-      <c r="B274" s="28"/>
-      <c r="C274" s="28" t="s">
+      <c r="A274" s="28"/>
+      <c r="B274" s="29"/>
+      <c r="C274" s="29" t="s">
         <v>689</v>
       </c>
-      <c r="D274" s="28" t="s">
+      <c r="D274" s="29" t="s">
         <v>690</v>
       </c>
-      <c r="E274" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F274" s="28"/>
-      <c r="G274" s="28"/>
-      <c r="H274" s="28"/>
+      <c r="E274" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F274" s="29"/>
+      <c r="G274" s="29"/>
+      <c r="H274" s="29"/>
     </row>
     <row r="275" spans="1:8">
-      <c r="A275" s="27"/>
-      <c r="B275" s="28"/>
-      <c r="C275" s="28" t="s">
+      <c r="A275" s="28"/>
+      <c r="B275" s="29"/>
+      <c r="C275" s="29" t="s">
         <v>691</v>
       </c>
-      <c r="D275" s="28" t="s">
+      <c r="D275" s="29" t="s">
         <v>692</v>
       </c>
-      <c r="E275" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F275" s="28"/>
-      <c r="G275" s="28"/>
-      <c r="H275" s="28"/>
+      <c r="E275" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F275" s="29"/>
+      <c r="G275" s="29"/>
+      <c r="H275" s="29"/>
     </row>
     <row r="276" spans="1:8">
-      <c r="A276" s="27"/>
-      <c r="B276" s="28"/>
-      <c r="C276" s="28" t="s">
+      <c r="A276" s="28"/>
+      <c r="B276" s="29"/>
+      <c r="C276" s="29" t="s">
         <v>693</v>
       </c>
-      <c r="D276" s="28" t="s">
+      <c r="D276" s="29" t="s">
         <v>694</v>
       </c>
-      <c r="E276" s="28" t="s">
+      <c r="E276" s="29" t="s">
         <v>695</v>
       </c>
-      <c r="F276" s="28"/>
-      <c r="G276" s="28"/>
-      <c r="H276" s="28"/>
+      <c r="F276" s="29"/>
+      <c r="G276" s="29"/>
+      <c r="H276" s="29"/>
     </row>
     <row r="277" spans="1:8">
-      <c r="A277" s="27"/>
-      <c r="B277" s="28"/>
-      <c r="C277" s="28" t="s">
+      <c r="A277" s="28"/>
+      <c r="B277" s="29"/>
+      <c r="C277" s="29" t="s">
         <v>696</v>
       </c>
-      <c r="D277" s="28" t="s">
+      <c r="D277" s="29" t="s">
         <v>697</v>
       </c>
-      <c r="E277" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F277" s="28"/>
-      <c r="G277" s="28"/>
-      <c r="H277" s="28"/>
+      <c r="E277" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F277" s="29"/>
+      <c r="G277" s="29"/>
+      <c r="H277" s="29"/>
     </row>
     <row r="278" spans="1:8">
-      <c r="A278" s="27"/>
-      <c r="B278" s="28"/>
-      <c r="C278" s="28" t="s">
+      <c r="A278" s="28"/>
+      <c r="B278" s="29"/>
+      <c r="C278" s="29" t="s">
         <v>445</v>
       </c>
-      <c r="D278" s="28" t="s">
+      <c r="D278" s="29" t="s">
         <v>698</v>
       </c>
-      <c r="E278" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F278" s="28"/>
-      <c r="G278" s="28"/>
-      <c r="H278" s="28"/>
+      <c r="E278" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F278" s="29"/>
+      <c r="G278" s="29"/>
+      <c r="H278" s="29"/>
     </row>
     <row r="279" spans="1:8">
-      <c r="A279" s="27"/>
-      <c r="B279" s="28"/>
-      <c r="C279" s="28" t="s">
+      <c r="A279" s="28"/>
+      <c r="B279" s="29"/>
+      <c r="C279" s="29" t="s">
         <v>699</v>
       </c>
-      <c r="D279" s="28" t="s">
+      <c r="D279" s="29" t="s">
         <v>700</v>
       </c>
-      <c r="E279" s="28" t="s">
+      <c r="E279" s="29" t="s">
         <v>701</v>
       </c>
-      <c r="F279" s="28"/>
-      <c r="G279" s="28"/>
-      <c r="H279" s="28"/>
+      <c r="F279" s="29"/>
+      <c r="G279" s="29"/>
+      <c r="H279" s="29"/>
     </row>
     <row r="280" spans="1:8">
-      <c r="A280" s="27"/>
-      <c r="B280" s="28"/>
-      <c r="C280" s="28" t="s">
+      <c r="A280" s="28"/>
+      <c r="B280" s="29"/>
+      <c r="C280" s="29" t="s">
         <v>702</v>
       </c>
-      <c r="D280" s="28" t="s">
+      <c r="D280" s="29" t="s">
         <v>703</v>
       </c>
-      <c r="E280" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F280" s="28"/>
-      <c r="G280" s="28"/>
-      <c r="H280" s="28"/>
+      <c r="E280" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F280" s="29"/>
+      <c r="G280" s="29"/>
+      <c r="H280" s="29"/>
     </row>
     <row r="281" spans="1:8">
-      <c r="A281" s="27"/>
-      <c r="B281" s="28"/>
-      <c r="C281" s="28" t="s">
+      <c r="A281" s="28"/>
+      <c r="B281" s="29"/>
+      <c r="C281" s="29" t="s">
         <v>704</v>
       </c>
-      <c r="D281" s="28" t="s">
+      <c r="D281" s="29" t="s">
         <v>705</v>
       </c>
-      <c r="E281" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F281" s="28"/>
-      <c r="G281" s="28"/>
-      <c r="H281" s="28"/>
+      <c r="E281" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F281" s="29"/>
+      <c r="G281" s="29"/>
+      <c r="H281" s="29"/>
     </row>
     <row r="282" spans="1:8">
-      <c r="A282" s="27"/>
-      <c r="B282" s="28"/>
-      <c r="C282" s="28" t="s">
+      <c r="A282" s="28"/>
+      <c r="B282" s="29"/>
+      <c r="C282" s="29" t="s">
         <v>706</v>
       </c>
-      <c r="D282" s="28" t="s">
+      <c r="D282" s="29" t="s">
         <v>707</v>
       </c>
-      <c r="E282" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F282" s="28"/>
-      <c r="G282" s="28"/>
-      <c r="H282" s="28"/>
+      <c r="E282" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F282" s="29"/>
+      <c r="G282" s="29"/>
+      <c r="H282" s="29"/>
     </row>
     <row r="283" spans="1:8">
-      <c r="A283" s="27"/>
-      <c r="B283" s="28"/>
-      <c r="C283" s="28" t="s">
+      <c r="A283" s="28"/>
+      <c r="B283" s="29"/>
+      <c r="C283" s="29" t="s">
         <v>708</v>
       </c>
-      <c r="D283" s="28" t="s">
+      <c r="D283" s="29" t="s">
         <v>709</v>
       </c>
-      <c r="E283" s="28" t="s">
+      <c r="E283" s="29" t="s">
         <v>710</v>
       </c>
-      <c r="F283" s="28"/>
-      <c r="G283" s="28"/>
-      <c r="H283" s="28"/>
+      <c r="F283" s="29"/>
+      <c r="G283" s="29"/>
+      <c r="H283" s="29"/>
     </row>
     <row r="284" spans="1:8">
-      <c r="A284" s="27"/>
-      <c r="B284" s="28"/>
-      <c r="C284" s="28" t="s">
+      <c r="A284" s="28"/>
+      <c r="B284" s="29"/>
+      <c r="C284" s="29" t="s">
         <v>711</v>
       </c>
-      <c r="D284" s="28" t="s">
+      <c r="D284" s="29" t="s">
         <v>712</v>
       </c>
-      <c r="E284" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F284" s="28"/>
-      <c r="G284" s="28"/>
-      <c r="H284" s="28"/>
+      <c r="E284" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F284" s="29"/>
+      <c r="G284" s="29"/>
+      <c r="H284" s="29"/>
     </row>
     <row r="285" spans="1:8">
-      <c r="A285" s="27"/>
-      <c r="B285" s="28"/>
-      <c r="C285" s="28" t="s">
+      <c r="A285" s="28"/>
+      <c r="B285" s="29"/>
+      <c r="C285" s="29" t="s">
         <v>713</v>
       </c>
-      <c r="D285" s="28" t="s">
+      <c r="D285" s="29" t="s">
         <v>714</v>
       </c>
-      <c r="E285" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F285" s="28"/>
-      <c r="G285" s="28"/>
-      <c r="H285" s="28"/>
+      <c r="E285" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F285" s="29"/>
+      <c r="G285" s="29"/>
+      <c r="H285" s="29"/>
     </row>
     <row r="286" spans="1:8">
-      <c r="A286" s="27"/>
-      <c r="B286" s="28"/>
-      <c r="C286" s="28" t="s">
+      <c r="A286" s="28"/>
+      <c r="B286" s="29"/>
+      <c r="C286" s="29" t="s">
         <v>715</v>
       </c>
-      <c r="D286" s="28" t="s">
+      <c r="D286" s="29" t="s">
         <v>716</v>
       </c>
-      <c r="E286" s="28" t="s">
+      <c r="E286" s="29" t="s">
         <v>717</v>
       </c>
-      <c r="F286" s="28"/>
-      <c r="G286" s="28"/>
-      <c r="H286" s="28"/>
+      <c r="F286" s="29"/>
+      <c r="G286" s="29"/>
+      <c r="H286" s="29"/>
     </row>
     <row r="287" spans="1:8">
-      <c r="A287" s="27"/>
-      <c r="B287" s="28"/>
-      <c r="C287" s="28" t="s">
+      <c r="A287" s="28"/>
+      <c r="B287" s="29"/>
+      <c r="C287" s="29" t="s">
         <v>718</v>
       </c>
-      <c r="D287" s="28" t="s">
+      <c r="D287" s="29" t="s">
         <v>719</v>
       </c>
-      <c r="E287" s="28" t="s">
+      <c r="E287" s="29" t="s">
         <v>720</v>
       </c>
-      <c r="F287" s="28"/>
-      <c r="G287" s="28"/>
-      <c r="H287" s="28"/>
+      <c r="F287" s="29"/>
+      <c r="G287" s="29"/>
+      <c r="H287" s="29"/>
     </row>
     <row r="288" spans="1:8">
-      <c r="A288" s="27"/>
-      <c r="B288" s="28"/>
-      <c r="C288" s="28" t="s">
+      <c r="A288" s="28"/>
+      <c r="B288" s="29"/>
+      <c r="C288" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="D288" s="28" t="s">
+      <c r="D288" s="29" t="s">
         <v>722</v>
       </c>
-      <c r="E288" s="28" t="s">
+      <c r="E288" s="29" t="s">
         <v>723</v>
       </c>
-      <c r="F288" s="28"/>
-      <c r="G288" s="28"/>
-      <c r="H288" s="28"/>
+      <c r="F288" s="29"/>
+      <c r="G288" s="29"/>
+      <c r="H288" s="29"/>
     </row>
     <row r="289" spans="1:8">
-      <c r="A289" s="27"/>
-      <c r="B289" s="28"/>
-      <c r="C289" s="28" t="s">
+      <c r="A289" s="28"/>
+      <c r="B289" s="29"/>
+      <c r="C289" s="29" t="s">
         <v>724</v>
       </c>
-      <c r="D289" s="28" t="s">
+      <c r="D289" s="29" t="s">
         <v>725</v>
       </c>
-      <c r="E289" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F289" s="28"/>
-      <c r="G289" s="28"/>
-      <c r="H289" s="28"/>
+      <c r="E289" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F289" s="29"/>
+      <c r="G289" s="29"/>
+      <c r="H289" s="29"/>
     </row>
     <row r="290" spans="1:8">
-      <c r="A290" s="27"/>
-      <c r="B290" s="28"/>
-      <c r="C290" s="28" t="s">
+      <c r="A290" s="28"/>
+      <c r="B290" s="29"/>
+      <c r="C290" s="29" t="s">
         <v>726</v>
       </c>
-      <c r="D290" s="28" t="s">
+      <c r="D290" s="29" t="s">
         <v>727</v>
       </c>
-      <c r="E290" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F290" s="28"/>
-      <c r="G290" s="28"/>
-      <c r="H290" s="28"/>
+      <c r="E290" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F290" s="29"/>
+      <c r="G290" s="29"/>
+      <c r="H290" s="29"/>
     </row>
     <row r="291" spans="1:8">
-      <c r="A291" s="27"/>
-      <c r="B291" s="28"/>
-      <c r="C291" s="28" t="s">
+      <c r="A291" s="28"/>
+      <c r="B291" s="29"/>
+      <c r="C291" s="29" t="s">
         <v>728</v>
       </c>
-      <c r="D291" s="28" t="s">
+      <c r="D291" s="29" t="s">
         <v>729</v>
       </c>
-      <c r="E291" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F291" s="28"/>
-      <c r="G291" s="28"/>
-      <c r="H291" s="28"/>
+      <c r="E291" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F291" s="29"/>
+      <c r="G291" s="29"/>
+      <c r="H291" s="29"/>
     </row>
     <row r="292" spans="1:8">
-      <c r="A292" s="27"/>
-      <c r="B292" s="28"/>
-      <c r="C292" s="28" t="s">
+      <c r="A292" s="28"/>
+      <c r="B292" s="29"/>
+      <c r="C292" s="29" t="s">
         <v>730</v>
       </c>
-      <c r="D292" s="28" t="s">
+      <c r="D292" s="29" t="s">
         <v>731</v>
       </c>
-      <c r="E292" s="28" t="s">
+      <c r="E292" s="29" t="s">
         <v>732</v>
       </c>
-      <c r="F292" s="28"/>
-      <c r="G292" s="28"/>
-      <c r="H292" s="28"/>
+      <c r="F292" s="29"/>
+      <c r="G292" s="29"/>
+      <c r="H292" s="29"/>
     </row>
     <row r="293" spans="1:8">
-      <c r="A293" s="27"/>
-      <c r="B293" s="28"/>
-      <c r="C293" s="28" t="s">
+      <c r="A293" s="28"/>
+      <c r="B293" s="29"/>
+      <c r="C293" s="29" t="s">
         <v>733</v>
       </c>
-      <c r="D293" s="28" t="s">
+      <c r="D293" s="29" t="s">
         <v>734</v>
       </c>
-      <c r="E293" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F293" s="28"/>
-      <c r="G293" s="28"/>
-      <c r="H293" s="28"/>
+      <c r="E293" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F293" s="29"/>
+      <c r="G293" s="29"/>
+      <c r="H293" s="29"/>
     </row>
     <row r="294" spans="1:8">
-      <c r="A294" s="27"/>
-      <c r="B294" s="28"/>
-      <c r="C294" s="28" t="s">
+      <c r="A294" s="28"/>
+      <c r="B294" s="29"/>
+      <c r="C294" s="29" t="s">
         <v>735</v>
       </c>
-      <c r="D294" s="28" t="s">
+      <c r="D294" s="29" t="s">
         <v>736</v>
       </c>
-      <c r="E294" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F294" s="28"/>
-      <c r="G294" s="28"/>
-      <c r="H294" s="28"/>
+      <c r="E294" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F294" s="29"/>
+      <c r="G294" s="29"/>
+      <c r="H294" s="29"/>
     </row>
     <row r="295" spans="1:8">
-      <c r="A295" s="27"/>
-      <c r="B295" s="28"/>
-      <c r="C295" s="28" t="s">
+      <c r="A295" s="28"/>
+      <c r="B295" s="29"/>
+      <c r="C295" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="D295" s="28" t="s">
+      <c r="D295" s="29" t="s">
         <v>738</v>
       </c>
-      <c r="E295" s="28" t="s">
+      <c r="E295" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="F295" s="28"/>
-      <c r="G295" s="28"/>
-      <c r="H295" s="28"/>
+      <c r="F295" s="29"/>
+      <c r="G295" s="29"/>
+      <c r="H295" s="29"/>
     </row>
     <row r="296" spans="1:8">
-      <c r="A296" s="27"/>
-      <c r="B296" s="28"/>
-      <c r="C296" s="28" t="s">
+      <c r="A296" s="28"/>
+      <c r="B296" s="29"/>
+      <c r="C296" s="29" t="s">
         <v>740</v>
       </c>
-      <c r="D296" s="28" t="s">
+      <c r="D296" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="E296" s="28" t="s">
+      <c r="E296" s="29" t="s">
         <v>742</v>
       </c>
-      <c r="F296" s="28"/>
-      <c r="G296" s="28"/>
-      <c r="H296" s="28"/>
+      <c r="F296" s="29"/>
+      <c r="G296" s="29"/>
+      <c r="H296" s="29"/>
     </row>
     <row r="297" spans="1:8">
-      <c r="A297" s="27"/>
-      <c r="B297" s="28"/>
-      <c r="C297" s="28" t="s">
+      <c r="A297" s="28"/>
+      <c r="B297" s="29"/>
+      <c r="C297" s="29" t="s">
         <v>743</v>
       </c>
-      <c r="D297" s="28" t="s">
+      <c r="D297" s="29" t="s">
         <v>744</v>
       </c>
-      <c r="E297" s="28" t="s">
+      <c r="E297" s="29" t="s">
         <v>745</v>
       </c>
-      <c r="F297" s="28"/>
-      <c r="G297" s="28"/>
-      <c r="H297" s="28"/>
+      <c r="F297" s="29"/>
+      <c r="G297" s="29"/>
+      <c r="H297" s="29"/>
     </row>
     <row r="298" spans="1:8">
-      <c r="A298" s="27"/>
-      <c r="B298" s="28"/>
-      <c r="C298" s="28" t="s">
+      <c r="A298" s="28"/>
+      <c r="B298" s="29"/>
+      <c r="C298" s="29" t="s">
         <v>746</v>
       </c>
-      <c r="D298" s="28" t="s">
+      <c r="D298" s="29" t="s">
         <v>747</v>
       </c>
-      <c r="E298" s="28" t="s">
+      <c r="E298" s="29" t="s">
         <v>748</v>
       </c>
-      <c r="F298" s="28"/>
-      <c r="G298" s="28"/>
-      <c r="H298" s="28"/>
+      <c r="F298" s="29"/>
+      <c r="G298" s="29"/>
+      <c r="H298" s="29"/>
     </row>
     <row r="299" spans="1:8">
-      <c r="A299" s="27"/>
-      <c r="B299" s="28"/>
-      <c r="C299" s="28" t="s">
+      <c r="A299" s="28"/>
+      <c r="B299" s="29"/>
+      <c r="C299" s="29" t="s">
         <v>749</v>
       </c>
-      <c r="D299" s="28" t="s">
+      <c r="D299" s="29" t="s">
         <v>750</v>
       </c>
-      <c r="E299" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F299" s="28"/>
-      <c r="G299" s="28"/>
-      <c r="H299" s="28"/>
+      <c r="E299" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F299" s="29"/>
+      <c r="G299" s="29"/>
+      <c r="H299" s="29"/>
     </row>
     <row r="300" spans="1:8">
-      <c r="A300" s="27"/>
-      <c r="B300" s="28"/>
-      <c r="C300" s="28" t="s">
+      <c r="A300" s="28"/>
+      <c r="B300" s="29"/>
+      <c r="C300" s="29" t="s">
         <v>751</v>
       </c>
-      <c r="D300" s="28" t="s">
+      <c r="D300" s="29" t="s">
         <v>752</v>
       </c>
-      <c r="E300" s="28" t="s">
+      <c r="E300" s="29" t="s">
         <v>753</v>
       </c>
-      <c r="F300" s="28"/>
-      <c r="G300" s="28"/>
-      <c r="H300" s="28"/>
+      <c r="F300" s="29"/>
+      <c r="G300" s="29"/>
+      <c r="H300" s="29"/>
     </row>
     <row r="301" spans="1:8">
-      <c r="A301" s="27"/>
-      <c r="B301" s="28"/>
-      <c r="C301" s="28" t="s">
+      <c r="A301" s="28"/>
+      <c r="B301" s="29"/>
+      <c r="C301" s="29" t="s">
         <v>754</v>
       </c>
-      <c r="D301" s="28" t="s">
+      <c r="D301" s="29" t="s">
         <v>755</v>
       </c>
-      <c r="E301" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F301" s="28"/>
-      <c r="G301" s="28"/>
-      <c r="H301" s="28"/>
+      <c r="E301" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F301" s="29"/>
+      <c r="G301" s="29"/>
+      <c r="H301" s="29"/>
     </row>
     <row r="302" spans="1:8">
-      <c r="A302" s="27"/>
-      <c r="B302" s="28"/>
-      <c r="C302" s="28" t="s">
+      <c r="A302" s="28"/>
+      <c r="B302" s="29"/>
+      <c r="C302" s="29" t="s">
         <v>756</v>
       </c>
-      <c r="D302" s="28" t="s">
+      <c r="D302" s="29" t="s">
         <v>757</v>
       </c>
-      <c r="E302" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F302" s="28"/>
-      <c r="G302" s="28"/>
-      <c r="H302" s="28"/>
+      <c r="E302" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F302" s="29"/>
+      <c r="G302" s="29"/>
+      <c r="H302" s="29"/>
     </row>
     <row r="303" spans="1:8">
-      <c r="A303" s="27"/>
-      <c r="B303" s="28"/>
-      <c r="C303" s="28" t="s">
+      <c r="A303" s="28"/>
+      <c r="B303" s="29"/>
+      <c r="C303" s="29" t="s">
         <v>758</v>
       </c>
-      <c r="D303" s="28" t="s">
+      <c r="D303" s="29" t="s">
         <v>759</v>
       </c>
-      <c r="E303" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F303" s="28"/>
-      <c r="G303" s="28"/>
-      <c r="H303" s="28"/>
+      <c r="E303" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F303" s="29"/>
+      <c r="G303" s="29"/>
+      <c r="H303" s="29"/>
     </row>
     <row r="304" spans="1:8">
-      <c r="A304" s="27"/>
-      <c r="B304" s="28"/>
-      <c r="C304" s="28" t="s">
+      <c r="A304" s="28"/>
+      <c r="B304" s="29"/>
+      <c r="C304" s="29" t="s">
         <v>760</v>
       </c>
-      <c r="D304" s="28" t="s">
+      <c r="D304" s="29" t="s">
         <v>761</v>
       </c>
-      <c r="E304" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F304" s="28"/>
-      <c r="G304" s="28"/>
-      <c r="H304" s="28"/>
+      <c r="E304" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F304" s="29"/>
+      <c r="G304" s="29"/>
+      <c r="H304" s="29"/>
     </row>
     <row r="305" spans="1:8">
-      <c r="A305" s="27"/>
-      <c r="B305" s="28"/>
-      <c r="C305" s="28" t="s">
+      <c r="A305" s="28"/>
+      <c r="B305" s="29"/>
+      <c r="C305" s="29" t="s">
         <v>762</v>
       </c>
-      <c r="D305" s="28" t="s">
+      <c r="D305" s="29" t="s">
         <v>763</v>
       </c>
-      <c r="E305" s="28" t="s">
+      <c r="E305" s="29" t="s">
         <v>764</v>
       </c>
-      <c r="F305" s="28"/>
-      <c r="G305" s="28"/>
-      <c r="H305" s="28"/>
+      <c r="F305" s="29"/>
+      <c r="G305" s="29"/>
+      <c r="H305" s="29"/>
     </row>
     <row r="306" spans="1:8">
-      <c r="A306" s="27"/>
-      <c r="B306" s="28"/>
-      <c r="C306" s="28" t="s">
+      <c r="A306" s="28"/>
+      <c r="B306" s="29"/>
+      <c r="C306" s="29" t="s">
         <v>765</v>
       </c>
-      <c r="D306" s="28" t="s">
+      <c r="D306" s="29" t="s">
         <v>766</v>
       </c>
-      <c r="E306" s="28" t="s">
+      <c r="E306" s="29" t="s">
         <v>767</v>
       </c>
-      <c r="F306" s="28"/>
-      <c r="G306" s="28"/>
-      <c r="H306" s="28"/>
+      <c r="F306" s="29"/>
+      <c r="G306" s="29"/>
+      <c r="H306" s="29"/>
     </row>
     <row r="307" spans="1:8">
-      <c r="A307" s="27"/>
-      <c r="B307" s="28"/>
-      <c r="C307" s="28" t="s">
+      <c r="A307" s="28"/>
+      <c r="B307" s="29"/>
+      <c r="C307" s="29" t="s">
         <v>768</v>
       </c>
-      <c r="D307" s="28" t="s">
+      <c r="D307" s="29" t="s">
         <v>769</v>
       </c>
-      <c r="E307" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F307" s="28"/>
-      <c r="G307" s="28"/>
-      <c r="H307" s="28"/>
+      <c r="E307" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F307" s="29"/>
+      <c r="G307" s="29"/>
+      <c r="H307" s="29"/>
     </row>
     <row r="308" spans="1:8">
-      <c r="A308" s="27"/>
-      <c r="B308" s="28"/>
-      <c r="C308" s="28" t="s">
+      <c r="A308" s="28"/>
+      <c r="B308" s="29"/>
+      <c r="C308" s="29" t="s">
         <v>770</v>
       </c>
-      <c r="D308" s="28" t="s">
+      <c r="D308" s="29" t="s">
         <v>771</v>
       </c>
-      <c r="E308" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F308" s="28"/>
-      <c r="G308" s="28"/>
-      <c r="H308" s="28"/>
+      <c r="E308" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F308" s="29"/>
+      <c r="G308" s="29"/>
+      <c r="H308" s="29"/>
     </row>
     <row r="309" spans="1:8">
-      <c r="A309" s="27"/>
-      <c r="B309" s="28"/>
-      <c r="C309" s="28" t="s">
+      <c r="A309" s="28"/>
+      <c r="B309" s="29"/>
+      <c r="C309" s="29" t="s">
         <v>772</v>
       </c>
-      <c r="D309" s="28" t="s">
+      <c r="D309" s="29" t="s">
         <v>773</v>
       </c>
-      <c r="E309" s="28" t="s">
+      <c r="E309" s="29" t="s">
         <v>774</v>
       </c>
-      <c r="F309" s="28"/>
-      <c r="G309" s="28"/>
-      <c r="H309" s="28"/>
+      <c r="F309" s="29"/>
+      <c r="G309" s="29"/>
+      <c r="H309" s="29"/>
     </row>
     <row r="310" spans="1:8">
-      <c r="A310" s="27"/>
-      <c r="B310" s="28"/>
-      <c r="C310" s="28" t="s">
+      <c r="A310" s="28"/>
+      <c r="B310" s="29"/>
+      <c r="C310" s="29" t="s">
         <v>775</v>
       </c>
-      <c r="D310" s="28" t="s">
+      <c r="D310" s="29" t="s">
         <v>776</v>
       </c>
-      <c r="E310" s="28" t="s">
+      <c r="E310" s="29" t="s">
         <v>777</v>
       </c>
-      <c r="F310" s="28"/>
-      <c r="G310" s="28"/>
-      <c r="H310" s="28"/>
+      <c r="F310" s="29"/>
+      <c r="G310" s="29"/>
+      <c r="H310" s="29"/>
     </row>
     <row r="311" spans="1:8">
-      <c r="A311" s="27"/>
-      <c r="B311" s="28"/>
-      <c r="C311" s="28" t="s">
+      <c r="A311" s="28"/>
+      <c r="B311" s="29"/>
+      <c r="C311" s="29" t="s">
         <v>778</v>
       </c>
-      <c r="D311" s="28" t="s">
+      <c r="D311" s="29" t="s">
         <v>779</v>
       </c>
-      <c r="E311" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F311" s="28"/>
-      <c r="G311" s="28"/>
-      <c r="H311" s="28"/>
+      <c r="E311" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F311" s="29"/>
+      <c r="G311" s="29"/>
+      <c r="H311" s="29"/>
     </row>
     <row r="312" spans="1:8">
-      <c r="A312" s="27"/>
-      <c r="B312" s="28"/>
-      <c r="C312" s="28" t="s">
+      <c r="A312" s="28"/>
+      <c r="B312" s="29"/>
+      <c r="C312" s="29" t="s">
         <v>780</v>
       </c>
-      <c r="D312" s="28" t="s">
+      <c r="D312" s="29" t="s">
         <v>781</v>
       </c>
-      <c r="E312" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F312" s="28"/>
-      <c r="G312" s="28"/>
-      <c r="H312" s="28"/>
+      <c r="E312" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F312" s="29"/>
+      <c r="G312" s="29"/>
+      <c r="H312" s="29"/>
     </row>
     <row r="313" spans="1:8">
-      <c r="A313" s="27"/>
-      <c r="B313" s="28"/>
-      <c r="C313" s="28" t="s">
+      <c r="A313" s="28"/>
+      <c r="B313" s="29"/>
+      <c r="C313" s="29" t="s">
         <v>782</v>
       </c>
-      <c r="D313" s="28" t="s">
+      <c r="D313" s="29" t="s">
         <v>783</v>
       </c>
-      <c r="E313" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F313" s="28"/>
-      <c r="G313" s="28"/>
-      <c r="H313" s="28"/>
+      <c r="E313" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F313" s="29"/>
+      <c r="G313" s="29"/>
+      <c r="H313" s="29"/>
     </row>
     <row r="314" spans="1:8">
-      <c r="A314" s="27"/>
-      <c r="B314" s="28"/>
-      <c r="C314" s="28" t="s">
+      <c r="A314" s="28"/>
+      <c r="B314" s="29"/>
+      <c r="C314" s="29" t="s">
         <v>784</v>
       </c>
-      <c r="D314" s="28" t="s">
+      <c r="D314" s="29" t="s">
         <v>785</v>
       </c>
-      <c r="E314" s="28" t="s">
+      <c r="E314" s="29" t="s">
         <v>786</v>
       </c>
-      <c r="F314" s="28"/>
-      <c r="G314" s="28"/>
-      <c r="H314" s="28"/>
+      <c r="F314" s="29"/>
+      <c r="G314" s="29"/>
+      <c r="H314" s="29"/>
     </row>
     <row r="315" spans="1:8">
-      <c r="A315" s="27"/>
-      <c r="B315" s="28"/>
-      <c r="C315" s="28" t="s">
+      <c r="A315" s="28"/>
+      <c r="B315" s="29"/>
+      <c r="C315" s="29" t="s">
         <v>787</v>
       </c>
-      <c r="D315" s="28" t="s">
+      <c r="D315" s="29" t="s">
         <v>788</v>
       </c>
-      <c r="E315" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F315" s="28"/>
-      <c r="G315" s="28"/>
-      <c r="H315" s="28"/>
+      <c r="E315" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F315" s="29"/>
+      <c r="G315" s="29"/>
+      <c r="H315" s="29"/>
     </row>
     <row r="316" spans="1:8">
-      <c r="A316" s="27"/>
-      <c r="B316" s="28"/>
-      <c r="C316" s="28" t="s">
+      <c r="A316" s="28"/>
+      <c r="B316" s="29"/>
+      <c r="C316" s="29" t="s">
         <v>789</v>
       </c>
-      <c r="D316" s="28" t="s">
+      <c r="D316" s="29" t="s">
         <v>790</v>
       </c>
-      <c r="E316" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F316" s="28"/>
-      <c r="G316" s="28"/>
-      <c r="H316" s="28"/>
+      <c r="E316" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F316" s="29"/>
+      <c r="G316" s="29"/>
+      <c r="H316" s="29"/>
     </row>
     <row r="317" spans="1:8">
-      <c r="A317" s="27"/>
-      <c r="B317" s="28"/>
-      <c r="C317" s="28" t="s">
+      <c r="A317" s="28"/>
+      <c r="B317" s="29"/>
+      <c r="C317" s="29" t="s">
         <v>791</v>
       </c>
-      <c r="D317" s="28" t="s">
+      <c r="D317" s="29" t="s">
         <v>792</v>
       </c>
-      <c r="E317" s="28" t="s">
+      <c r="E317" s="29" t="s">
         <v>793</v>
       </c>
-      <c r="F317" s="28"/>
-      <c r="G317" s="28"/>
-      <c r="H317" s="28"/>
+      <c r="F317" s="29"/>
+      <c r="G317" s="29"/>
+      <c r="H317" s="29"/>
     </row>
     <row r="318" spans="1:8">
-      <c r="A318" s="27"/>
-      <c r="B318" s="28"/>
-      <c r="C318" s="28" t="s">
+      <c r="A318" s="28"/>
+      <c r="B318" s="29"/>
+      <c r="C318" s="29" t="s">
         <v>794</v>
       </c>
-      <c r="D318" s="28" t="s">
+      <c r="D318" s="29" t="s">
         <v>795</v>
       </c>
-      <c r="E318" s="28" t="s">
+      <c r="E318" s="29" t="s">
         <v>796</v>
       </c>
-      <c r="F318" s="28"/>
-      <c r="G318" s="28"/>
-      <c r="H318" s="28"/>
+      <c r="F318" s="29"/>
+      <c r="G318" s="29"/>
+      <c r="H318" s="29"/>
     </row>
     <row r="319" spans="1:8">
-      <c r="A319" s="27"/>
-      <c r="B319" s="28"/>
-      <c r="C319" s="28" t="s">
+      <c r="A319" s="28"/>
+      <c r="B319" s="29"/>
+      <c r="C319" s="29" t="s">
         <v>797</v>
       </c>
-      <c r="D319" s="28" t="s">
+      <c r="D319" s="29" t="s">
         <v>798</v>
       </c>
-      <c r="E319" s="28" t="s">
+      <c r="E319" s="29" t="s">
         <v>799</v>
       </c>
-      <c r="F319" s="28"/>
-      <c r="G319" s="28"/>
-      <c r="H319" s="28"/>
+      <c r="F319" s="29"/>
+      <c r="G319" s="29"/>
+      <c r="H319" s="29"/>
     </row>
     <row r="320" spans="1:8">
-      <c r="A320" s="27"/>
-      <c r="B320" s="28"/>
-      <c r="C320" s="28" t="s">
+      <c r="A320" s="28"/>
+      <c r="B320" s="29"/>
+      <c r="C320" s="29" t="s">
         <v>800</v>
       </c>
-      <c r="D320" s="28" t="s">
+      <c r="D320" s="29" t="s">
         <v>801</v>
       </c>
-      <c r="E320" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F320" s="28"/>
-      <c r="G320" s="28"/>
-      <c r="H320" s="28"/>
+      <c r="E320" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F320" s="29"/>
+      <c r="G320" s="29"/>
+      <c r="H320" s="29"/>
     </row>
     <row r="321" spans="1:8">
-      <c r="A321" s="27"/>
-      <c r="B321" s="28"/>
-      <c r="C321" s="28" t="s">
+      <c r="A321" s="28"/>
+      <c r="B321" s="29"/>
+      <c r="C321" s="29" t="s">
         <v>802</v>
       </c>
-      <c r="D321" s="28" t="s">
+      <c r="D321" s="29" t="s">
         <v>803</v>
       </c>
-      <c r="E321" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F321" s="28"/>
-      <c r="G321" s="28"/>
-      <c r="H321" s="28"/>
+      <c r="E321" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F321" s="29"/>
+      <c r="G321" s="29"/>
+      <c r="H321" s="29"/>
     </row>
     <row r="322" spans="1:8">
-      <c r="A322" s="27"/>
-      <c r="B322" s="28"/>
-      <c r="C322" s="28" t="s">
+      <c r="A322" s="28"/>
+      <c r="B322" s="29"/>
+      <c r="C322" s="29" t="s">
         <v>804</v>
       </c>
-      <c r="D322" s="28" t="s">
+      <c r="D322" s="29" t="s">
         <v>805</v>
       </c>
-      <c r="E322" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="F322" s="28"/>
-      <c r="G322" s="28"/>
-      <c r="H322" s="28"/>
+      <c r="E322" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F322" s="29"/>
+      <c r="G322" s="29"/>
+      <c r="H322" s="29"/>
     </row>
     <row r="323" spans="1:8">
-      <c r="A323" s="27"/>
-      <c r="B323" s="28"/>
-      <c r="C323" s="28" t="s">
+      <c r="A323" s="28"/>
+      <c r="B323" s="29"/>
+      <c r="C323" s="29" t="s">
         <v>806</v>
       </c>
-      <c r="D323" s="28" t="s">
+      <c r="D323" s="29" t="s">
         <v>807</v>
       </c>
-      <c r="E323" s="28" t="s">
+      <c r="E323" s="29" t="s">
         <v>808</v>
       </c>
-      <c r="F323" s="28"/>
-      <c r="G323" s="28"/>
-      <c r="H323" s="28"/>
+      <c r="F323" s="29"/>
+      <c r="G323" s="29"/>
+      <c r="H323" s="29"/>
     </row>
     <row r="324" spans="1:8">
-      <c r="B324" s="10"/>
-      <c r="C324" s="10"/>
-      <c r="D324" s="10"/>
-      <c r="E324" s="10"/>
+      <c r="B324" s="11"/>
+      <c r="C324" s="11"/>
+      <c r="D324" s="11"/>
+      <c r="E324" s="11"/>
     </row>
     <row r="325" spans="1:8">
-      <c r="A325" s="29" t="s">
+      <c r="A325" s="30" t="s">
         <v>809</v>
       </c>
-      <c r="B325" s="30"/>
-      <c r="C325" s="30" t="s">
+      <c r="B325" s="31"/>
+      <c r="C325" s="31" t="s">
         <v>810</v>
       </c>
-      <c r="D325" s="30" t="s">
+      <c r="D325" s="31" t="s">
         <v>811</v>
       </c>
-      <c r="E325" s="30" t="s">
+      <c r="E325" s="31" t="s">
         <v>812</v>
       </c>
-      <c r="F325" s="30"/>
-      <c r="G325" s="30"/>
-      <c r="H325" s="30"/>
+      <c r="F325" s="31"/>
+      <c r="G325" s="31"/>
+      <c r="H325" s="31"/>
     </row>
     <row r="326" spans="1:8">
-      <c r="A326" s="29"/>
-      <c r="B326" s="30"/>
-      <c r="C326" s="30" t="s">
+      <c r="A326" s="30"/>
+      <c r="B326" s="31"/>
+      <c r="C326" s="31" t="s">
         <v>813</v>
       </c>
-      <c r="D326" s="30" t="s">
+      <c r="D326" s="31" t="s">
         <v>814</v>
       </c>
-      <c r="E326" s="30" t="s">
+      <c r="E326" s="31" t="s">
         <v>815</v>
       </c>
-      <c r="F326" s="30"/>
-      <c r="G326" s="30"/>
-      <c r="H326" s="30"/>
+      <c r="F326" s="31"/>
+      <c r="G326" s="31"/>
+      <c r="H326" s="31"/>
     </row>
     <row r="327" spans="1:8">
-      <c r="A327" s="29"/>
-      <c r="B327" s="30"/>
-      <c r="C327" s="30" t="s">
+      <c r="A327" s="30"/>
+      <c r="B327" s="31"/>
+      <c r="C327" s="31" t="s">
         <v>816</v>
       </c>
-      <c r="D327" s="30" t="s">
+      <c r="D327" s="31" t="s">
         <v>817</v>
       </c>
-      <c r="E327" s="30" t="s">
+      <c r="E327" s="31" t="s">
         <v>818</v>
       </c>
-      <c r="F327" s="30"/>
-      <c r="G327" s="30"/>
-      <c r="H327" s="30"/>
+      <c r="F327" s="31"/>
+      <c r="G327" s="31"/>
+      <c r="H327" s="31"/>
     </row>
     <row r="328" spans="1:8">
-      <c r="C328" s="10"/>
-      <c r="D328" s="10"/>
+      <c r="C328" s="11"/>
+      <c r="D328" s="11"/>
     </row>
     <row r="329" spans="1:8">
       <c r="A329" t="s">
         <v>819</v>
       </c>
-      <c r="C329" s="10" t="s">
+      <c r="C329" s="11" t="s">
         <v>820</v>
       </c>
-      <c r="D329" s="10" t="s">
+      <c r="D329" s="11" t="s">
         <v>821</v>
       </c>
       <c r="E329" t="s">
@@ -9158,8 +9161,8 @@
       </c>
     </row>
     <row r="330" spans="1:8">
-      <c r="C330" s="10"/>
-      <c r="D330" s="10"/>
+      <c r="C330" s="11"/>
+      <c r="D330" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="28">
@@ -9216,7 +9219,7 @@
     <hyperlink ref="D82" r:id="rId21" display="https://gitcode.com/Ascend/memfabric_hybrid"/>
     <hyperlink ref="D83" r:id="rId22" display="https://gitcode.com/Ascend/ascend-deployer"/>
     <hyperlink ref="D31" r:id="rId23" display="https://gitcode.com/boostkit/spdk"/>
-    <hyperlink ref="D30" r:id="rId24" display="https://gitcode.com/boostkit/kae"/>
+    <hyperlink ref="D30" r:id="rId24" display="https://gitcode.com/boostkit/kae" tooltip="https://gitcode.com/boostkit/kae"/>
     <hyperlink ref="D29" r:id="rId25" display="https://gitcode.com/boostkit/lz4"/>
     <hyperlink ref="D28" r:id="rId26" display="https://gitcode.com/boostkit/zstd"/>
     <hyperlink ref="D27" r:id="rId27" display="https://gitcode.com/boostkit/hyperscan"/>
@@ -9237,11 +9240,19 @@
     <hyperlink ref="D11" r:id="rId42" display="https://gitcode.com/boostkit/faiss"/>
     <hyperlink ref="D10" r:id="rId43" display="https://gitcode.com/boostkit/hnswlib"/>
     <hyperlink ref="D9" r:id="rId44" display="https://gitcode.com/boostkit/tensorflow-serving"/>
-    <hyperlink ref="D8" r:id="rId45" display="https://gitcode.com/boostkit/tensorflow"/>
+    <hyperlink ref="D8" r:id="rId45" display="https://gitcode.com/boostkit/tensorflow" tooltip="https://gitcode.com/boostkit/tensorflow"/>
     <hyperlink ref="D7" r:id="rId46" display="https://gitcode.com/boostkit/kvecturbo" tooltip="https://gitcode.com/boostkit/kvecturbo"/>
     <hyperlink ref="D6" r:id="rId47" display="https://atomgit.com/openeuler/Gluten" tooltip="https://atomgit.com/openeuler/Gluten"/>
     <hyperlink ref="D105" r:id="rId48" display="https://gitcode.com/cann/runtime"/>
     <hyperlink ref="D15" r:id="rId49" display="https://gitcode.com/boostkit/hadoop/tree/hdfs-ec-24.0.0/"/>
+    <hyperlink ref="D2" r:id="rId50" display="https://atomgit.com/openeuler/OmniAdaptor" tooltip="https://atomgit.com/openeuler/OmniAdaptor"/>
+    <hyperlink ref="D3" r:id="rId51" display="https://atomgit.com/openeuler/OmniOperator" tooltip="https://atomgit.com/openeuler/OmniOperator"/>
+    <hyperlink ref="D4" r:id="rId52" display="https://atomgit.com/openeuler/OmniStream" tooltip="https://atomgit.com/openeuler/OmniStream"/>
+    <hyperlink ref="D5" r:id="rId53" display="https://atomgit.com/openeuler/OmniStateStore" tooltip="https://atomgit.com/openeuler/OmniStateStore"/>
+    <hyperlink ref="D33" r:id="rId54" display="https://gitcode.com/Ascend/AscendNPU-IR" tooltip="https://gitcode.com/Ascend/AscendNPU-IR"/>
+    <hyperlink ref="D36" r:id="rId55" display="https://gitcode.com/Ascend/MindIE-SD"/>
+    <hyperlink ref="D104" r:id="rId56" display="https://gitcode.com/cann/catlass"/>
+    <hyperlink ref="D34" r:id="rId57" display="https://gitcode.com/Ascend/pytorch"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/社区代码仓列表.xlsx
+++ b/社区代码仓列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27083" windowHeight="12851"/>
+    <workbookView windowWidth="20255" windowHeight="12851"/>
   </bookViews>
   <sheets>
     <sheet name="社区开源仓列表" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="882">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="884">
   <si>
     <t>社区名</t>
   </si>
@@ -2501,6 +2501,12 @@
   </si>
   <si>
     <t>C++、C</t>
+  </si>
+  <si>
+    <t>ubs-mem</t>
+  </si>
+  <si>
+    <t>https://gitcode.com/openeuler/ubs-mem</t>
   </si>
   <si>
     <t>组件</t>
@@ -3343,7 +3349,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3365,13 +3371,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="6" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3432,6 +3438,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3820,7 +3829,9 @@
         <v>14</v>
       </c>
       <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
+      <c r="G2" s="3">
+        <v>2</v>
+      </c>
       <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:10">
@@ -3837,7 +3848,7 @@
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3" s="3"/>
     </row>
@@ -3855,7 +3866,7 @@
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H4" s="3"/>
     </row>
@@ -3865,7 +3876,7 @@
       <c r="C5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>21</v>
       </c>
       <c r="E5" s="3" t="s">
@@ -3883,14 +3894,16 @@
       <c r="C6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>23</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="G6" s="3">
+        <v>26</v>
+      </c>
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:10">
@@ -3901,7 +3914,7 @@
       <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="9" t="s">
         <v>26</v>
       </c>
       <c r="E7" s="3" t="s">
@@ -3919,7 +3932,7 @@
       <c r="C8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="9" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="3" t="s">
@@ -3937,7 +3950,7 @@
       <c r="C9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="9" t="s">
         <v>31</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -3955,7 +3968,7 @@
       <c r="C10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="9" t="s">
         <v>33</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -3973,7 +3986,7 @@
       <c r="C11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="9" t="s">
         <v>35</v>
       </c>
       <c r="E11" s="3" t="s">
@@ -3991,7 +4004,7 @@
       <c r="C12" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="9" t="s">
         <v>37</v>
       </c>
       <c r="E12" s="3" t="s">
@@ -4011,7 +4024,7 @@
       <c r="C13" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="9" t="s">
         <v>41</v>
       </c>
       <c r="E13" s="3" t="s">
@@ -4029,7 +4042,7 @@
       <c r="C14" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="9" t="s">
         <v>44</v>
       </c>
       <c r="E14" s="3" t="s">
@@ -4047,7 +4060,7 @@
       <c r="C15" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="6" t="s">
         <v>46</v>
       </c>
       <c r="E15" s="3" t="s">
@@ -4065,7 +4078,7 @@
       <c r="C16" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="9" t="s">
         <v>50</v>
       </c>
       <c r="E16" s="3" t="s">
@@ -4083,7 +4096,7 @@
       <c r="C17" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="9" t="s">
         <v>53</v>
       </c>
       <c r="E17" s="3" t="s">
@@ -4103,7 +4116,7 @@
       <c r="C18" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="9" t="s">
         <v>56</v>
       </c>
       <c r="E18" s="3" t="s">
@@ -4121,7 +4134,7 @@
       <c r="C19" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="9" t="s">
         <v>59</v>
       </c>
       <c r="E19" s="3" t="s">
@@ -4139,7 +4152,7 @@
       <c r="C20" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="9" t="s">
         <v>63</v>
       </c>
       <c r="E20" s="3" t="s">
@@ -4157,7 +4170,7 @@
       <c r="C21" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="9" t="s">
         <v>66</v>
       </c>
       <c r="E21" s="3" t="s">
@@ -4175,7 +4188,7 @@
       <c r="C22" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="9" t="s">
         <v>68</v>
       </c>
       <c r="E22" s="3" t="s">
@@ -4195,7 +4208,7 @@
       <c r="C23" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="8" t="s">
         <v>71</v>
       </c>
       <c r="E23" s="3" t="s">
@@ -4213,7 +4226,7 @@
       <c r="C24" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="9" t="s">
         <v>73</v>
       </c>
       <c r="E24" s="3" t="s">
@@ -4231,7 +4244,7 @@
       <c r="C25" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="9" t="s">
         <v>75</v>
       </c>
       <c r="E25" s="3" t="s">
@@ -4251,7 +4264,7 @@
       <c r="C26" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="9" t="s">
         <v>78</v>
       </c>
       <c r="E26" s="3" t="s">
@@ -4273,7 +4286,7 @@
       <c r="C27" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="8" t="s">
         <v>81</v>
       </c>
       <c r="E27" s="3" t="s">
@@ -4293,7 +4306,7 @@
       <c r="C28" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="9" t="s">
         <v>85</v>
       </c>
       <c r="E28" s="3" t="s">
@@ -4311,7 +4324,7 @@
       <c r="C29" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="8" t="s">
         <v>87</v>
       </c>
       <c r="E29" s="3" t="s">
@@ -4331,7 +4344,7 @@
       <c r="C30" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="8" t="s">
         <v>90</v>
       </c>
       <c r="E30" s="3" t="s">
@@ -4351,7 +4364,7 @@
       <c r="C31" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="9" t="s">
         <v>93</v>
       </c>
       <c r="E31" s="3" t="s">
@@ -4673,7 +4686,7 @@
       <c r="E50" s="14"/>
       <c r="F50" s="14"/>
       <c r="G50" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H50" s="14"/>
     </row>
@@ -9147,7 +9160,7 @@
       <c r="C329" s="11" t="s">
         <v>820</v>
       </c>
-      <c r="D329" s="11" t="s">
+      <c r="D329" s="2" t="s">
         <v>821</v>
       </c>
       <c r="E329" t="s">
@@ -9161,8 +9174,18 @@
       </c>
     </row>
     <row r="330" spans="1:8">
-      <c r="C330" s="11"/>
-      <c r="D330" s="11"/>
+      <c r="C330" s="11" t="s">
+        <v>823</v>
+      </c>
+      <c r="D330" s="32" t="s">
+        <v>824</v>
+      </c>
+      <c r="E330" t="s">
+        <v>822</v>
+      </c>
+      <c r="G330">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="28">
@@ -9253,6 +9276,8 @@
     <hyperlink ref="D36" r:id="rId55" display="https://gitcode.com/Ascend/MindIE-SD"/>
     <hyperlink ref="D104" r:id="rId56" display="https://gitcode.com/cann/catlass"/>
     <hyperlink ref="D34" r:id="rId57" display="https://gitcode.com/Ascend/pytorch"/>
+    <hyperlink ref="D329" r:id="rId58" display="https://gitcode.com/openeuler/ubs-io"/>
+    <hyperlink ref="D330" r:id="rId59" display="https://gitcode.com/openeuler/ubs-mem"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -9278,19 +9303,19 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -9298,16 +9323,16 @@
         <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C2" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="D2" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="F2" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -9315,16 +9340,16 @@
         <v>101</v>
       </c>
       <c r="B3" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C3" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="D3" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F3" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -9332,16 +9357,16 @@
         <v>101</v>
       </c>
       <c r="B4" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C4" t="s">
+        <v>837</v>
+      </c>
+      <c r="D4" t="s">
         <v>835</v>
       </c>
-      <c r="D4" t="s">
-        <v>833</v>
-      </c>
       <c r="F4" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -9349,16 +9374,16 @@
         <v>101</v>
       </c>
       <c r="B5" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C5" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="D5" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F5" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -9366,16 +9391,16 @@
         <v>101</v>
       </c>
       <c r="B6" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C6" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="D6" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F6" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -9383,16 +9408,16 @@
         <v>101</v>
       </c>
       <c r="B7" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C7" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="D7" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F7" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -9400,16 +9425,16 @@
         <v>101</v>
       </c>
       <c r="B8" t="s">
+        <v>833</v>
+      </c>
+      <c r="C8" t="s">
+        <v>845</v>
+      </c>
+      <c r="D8" t="s">
         <v>831</v>
       </c>
-      <c r="C8" t="s">
-        <v>843</v>
-      </c>
-      <c r="D8" t="s">
-        <v>829</v>
-      </c>
       <c r="F8" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -9417,16 +9442,16 @@
         <v>101</v>
       </c>
       <c r="B9" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C9" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="D9" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F9" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -9434,16 +9459,16 @@
         <v>101</v>
       </c>
       <c r="B10" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C10" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="D10" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F10" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -9451,16 +9476,16 @@
         <v>101</v>
       </c>
       <c r="B11" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C11" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="D11" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F11" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -9468,16 +9493,16 @@
         <v>121</v>
       </c>
       <c r="B12" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C12" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="D12" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="F12" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
     </row>
   </sheetData>
@@ -9506,19 +9531,19 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -9526,13 +9551,13 @@
         <v>820</v>
       </c>
       <c r="C2" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="D2" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="F2" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -9540,13 +9565,13 @@
         <v>820</v>
       </c>
       <c r="C3" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="D3" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="F3" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -9554,13 +9579,13 @@
         <v>820</v>
       </c>
       <c r="C4" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="D4" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="F4" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -9568,13 +9593,13 @@
         <v>820</v>
       </c>
       <c r="C5" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="D5" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="F5" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -9582,13 +9607,13 @@
         <v>820</v>
       </c>
       <c r="C6" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="D6" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="F6" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -9596,13 +9621,13 @@
         <v>820</v>
       </c>
       <c r="C7" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="D7" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="F7" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -9610,13 +9635,13 @@
         <v>820</v>
       </c>
       <c r="C8" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="D8" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="F8" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -9624,13 +9649,13 @@
         <v>820</v>
       </c>
       <c r="C9" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="D9" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F9" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -9638,16 +9663,16 @@
         <v>820</v>
       </c>
       <c r="C10" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="D10" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="E10" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="F10" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -9655,13 +9680,13 @@
         <v>820</v>
       </c>
       <c r="C11" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="D11" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -9669,13 +9694,13 @@
         <v>820</v>
       </c>
       <c r="C12" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="D12" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F12" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -9683,13 +9708,13 @@
         <v>820</v>
       </c>
       <c r="C13" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="D13" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F13" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -9697,13 +9722,13 @@
         <v>820</v>
       </c>
       <c r="C14" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="D14" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F14" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -9711,13 +9736,13 @@
         <v>820</v>
       </c>
       <c r="C15" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="D15" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F15" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -9725,13 +9750,13 @@
         <v>820</v>
       </c>
       <c r="C16" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="D16" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F16" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
     </row>
     <row r="21" spans="6:6">
@@ -9766,19 +9791,19 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
     </row>
     <row r="21" spans="6:6">
@@ -9810,19 +9835,19 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
     </row>
     <row r="21" spans="6:6">
@@ -9854,19 +9879,19 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
     </row>
     <row r="21" spans="6:6">

--- a/社区代码仓列表.xlsx
+++ b/社区代码仓列表.xlsx
@@ -9233,7 +9233,7 @@
         <v>823</v>
       </c>
       <c r="G330">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/社区代码仓列表.xlsx
+++ b/社区代码仓列表.xlsx
@@ -5220,7 +5220,9 @@
         <v>197</v>
       </c>
       <c r="F81" s="11"/>
-      <c r="G81" s="11"/>
+      <c r="G81" s="11">
+        <v>4</v>
+      </c>
       <c r="H81" s="11"/>
     </row>
     <row r="82" spans="1:8">
@@ -5236,7 +5238,9 @@
       </c>
       <c r="E82" s="11"/>
       <c r="F82" s="11"/>
-      <c r="G82" s="11"/>
+      <c r="G82" s="11">
+        <v>0</v>
+      </c>
       <c r="H82" s="11"/>
     </row>
     <row r="83" spans="1:8">
@@ -5252,7 +5256,9 @@
       </c>
       <c r="E83" s="11"/>
       <c r="F83" s="11"/>
-      <c r="G83" s="11"/>
+      <c r="G83" s="11">
+        <v>1</v>
+      </c>
       <c r="H83" s="11"/>
     </row>
     <row r="85" spans="1:8">

--- a/社区代码仓列表.xlsx
+++ b/社区代码仓列表.xlsx
@@ -5651,7 +5651,7 @@
       </c>
       <c r="F105" s="16"/>
       <c r="G105" s="16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H105" s="16"/>
     </row>
@@ -5734,7 +5734,7 @@
     <row r="110" spans="1:8">
       <c r="G110">
         <f>SUM(G85:G109)</f>
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="111" spans="1:8">

--- a/社区代码仓列表.xlsx
+++ b/社区代码仓列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20255" windowHeight="12851"/>
+    <workbookView windowWidth="21971" windowHeight="12851"/>
   </bookViews>
   <sheets>
     <sheet name="社区开源仓列表" sheetId="1" r:id="rId1"/>
@@ -5371,7 +5371,7 @@
       </c>
       <c r="F90" s="16"/>
       <c r="G90" s="16">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H90" s="16"/>
     </row>
@@ -5734,7 +5734,7 @@
     <row r="110" spans="1:8">
       <c r="G110">
         <f>SUM(G85:G109)</f>
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="111" spans="1:8">

--- a/社区代码仓列表.xlsx
+++ b/社区代码仓列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21971" windowHeight="12851"/>
+    <workbookView windowWidth="21971" windowHeight="14700"/>
   </bookViews>
   <sheets>
     <sheet name="社区开源仓列表" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="885">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="889">
   <si>
     <t>社区名</t>
   </si>
@@ -475,6 +475,9 @@
     <t>https://gitcode.com/Ascend/mstt</t>
   </si>
   <si>
+    <t>python</t>
+  </si>
+  <si>
     <t>msIT</t>
   </si>
   <si>
@@ -487,12 +490,29 @@
     <t>https://gitcode.com/Ascend/msot</t>
   </si>
   <si>
+    <t>shell、python、c++</t>
+  </si>
+  <si>
     <t>MindStudio-Debugger</t>
   </si>
   <si>
     <t>https://gitcode.com/Ascend/msdebug</t>
   </si>
   <si>
+    <r>
+      <t>LLVM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF252B3A"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、C++</t>
+    </r>
+  </si>
+  <si>
     <t>MindStudio-Monitor</t>
   </si>
   <si>
@@ -517,6 +537,9 @@
     <t>https://gitcode.com/Ascend/msprof</t>
   </si>
   <si>
+    <t>python、c++</t>
+  </si>
+  <si>
     <t>MindStudio-Service-Profiler</t>
   </si>
   <si>
@@ -553,6 +576,9 @@
     <t>https://gitcode.com/Ascend/mspti</t>
   </si>
   <si>
+    <t>C++、python</t>
+  </si>
+  <si>
     <t>MindStudio-Agent</t>
   </si>
   <si>
@@ -583,6 +609,9 @@
     <t>https://gitcode.com/Ascend/mstx</t>
   </si>
   <si>
+    <t>C、C++、python</t>
+  </si>
+  <si>
     <t>MindStudio-CommReport</t>
   </si>
   <si>
@@ -1384,16 +1413,10 @@
     <t>https://gitcode.com/mindspore/mindspore</t>
   </si>
   <si>
-    <t>C++、python</t>
-  </si>
-  <si>
     <t>vllm-mindspore</t>
   </si>
   <si>
     <t>https://gitcode.com/mindspore/vllm-mindspore</t>
-  </si>
-  <si>
-    <t>python</t>
   </si>
   <si>
     <t>akg</t>
@@ -2699,7 +2722,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2858,6 +2881,12 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF252B3A"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="40">
@@ -3406,6 +3435,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3414,9 +3446,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -4814,7 +4843,9 @@
       <c r="D56" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="E56" s="11"/>
+      <c r="E56" s="11" t="s">
+        <v>147</v>
+      </c>
       <c r="F56" s="11"/>
       <c r="G56" s="11">
         <v>1</v>
@@ -4825,12 +4856,14 @@
       <c r="A57" s="9"/>
       <c r="B57" s="10"/>
       <c r="C57" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E57" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="D57" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="11">
         <v>0</v>
@@ -4841,12 +4874,14 @@
       <c r="A58" s="9"/>
       <c r="B58" s="10"/>
       <c r="C58" s="11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="E58" s="11"/>
+        <v>151</v>
+      </c>
+      <c r="E58" s="11" t="s">
+        <v>152</v>
+      </c>
       <c r="F58" s="11"/>
       <c r="G58" s="11">
         <v>6</v>
@@ -4857,12 +4892,14 @@
       <c r="A59" s="9"/>
       <c r="B59" s="10"/>
       <c r="C59" s="12" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="E59" s="11"/>
+        <v>154</v>
+      </c>
+      <c r="E59" s="11" t="s">
+        <v>155</v>
+      </c>
       <c r="F59" s="11"/>
       <c r="G59" s="11">
         <v>1</v>
@@ -4873,12 +4910,14 @@
       <c r="A60" s="9"/>
       <c r="B60" s="10"/>
       <c r="C60" s="12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="E60" s="11"/>
+        <v>157</v>
+      </c>
+      <c r="E60" s="11" t="s">
+        <v>57</v>
+      </c>
       <c r="F60" s="11"/>
       <c r="G60" s="11">
         <v>2</v>
@@ -4889,12 +4928,14 @@
       <c r="A61" s="9"/>
       <c r="B61" s="10"/>
       <c r="C61" s="12" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="E61" s="11"/>
+        <v>159</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>57</v>
+      </c>
       <c r="F61" s="11"/>
       <c r="G61" s="11">
         <v>7</v>
@@ -4905,12 +4946,14 @@
       <c r="A62" s="9"/>
       <c r="B62" s="10"/>
       <c r="C62" s="12" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="E62" s="11"/>
+        <v>161</v>
+      </c>
+      <c r="E62" s="11" t="s">
+        <v>17</v>
+      </c>
       <c r="F62" s="11"/>
       <c r="G62" s="11">
         <v>9</v>
@@ -4921,12 +4964,14 @@
       <c r="A63" s="9"/>
       <c r="B63" s="10"/>
       <c r="C63" s="12" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="E63" s="11"/>
+        <v>163</v>
+      </c>
+      <c r="E63" s="11" t="s">
+        <v>164</v>
+      </c>
       <c r="F63" s="11"/>
       <c r="G63" s="11">
         <v>0</v>
@@ -4937,12 +4982,14 @@
       <c r="A64" s="9"/>
       <c r="B64" s="10"/>
       <c r="C64" s="12" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="E64" s="11"/>
+        <v>166</v>
+      </c>
+      <c r="E64" s="11" t="s">
+        <v>164</v>
+      </c>
       <c r="F64" s="11"/>
       <c r="G64" s="11">
         <v>3</v>
@@ -4953,12 +5000,14 @@
       <c r="A65" s="9"/>
       <c r="B65" s="10"/>
       <c r="C65" s="12" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="E65" s="11"/>
+        <v>168</v>
+      </c>
+      <c r="E65" s="11" t="s">
+        <v>147</v>
+      </c>
       <c r="F65" s="11"/>
       <c r="G65" s="11">
         <v>7</v>
@@ -4969,12 +5018,14 @@
       <c r="A66" s="9"/>
       <c r="B66" s="10"/>
       <c r="C66" s="12" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="E66" s="11"/>
+        <v>170</v>
+      </c>
+      <c r="E66" s="11" t="s">
+        <v>147</v>
+      </c>
       <c r="F66" s="11"/>
       <c r="G66" s="11">
         <v>8</v>
@@ -4985,12 +5036,14 @@
       <c r="A67" s="9"/>
       <c r="B67" s="10"/>
       <c r="C67" s="12" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="E67" s="11"/>
+        <v>172</v>
+      </c>
+      <c r="E67" s="11" t="s">
+        <v>17</v>
+      </c>
       <c r="F67" s="11"/>
       <c r="G67" s="11">
         <v>0</v>
@@ -5001,12 +5054,14 @@
       <c r="A68" s="9"/>
       <c r="B68" s="10"/>
       <c r="C68" s="12" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="E68" s="11"/>
+        <v>174</v>
+      </c>
+      <c r="E68" s="11" t="s">
+        <v>17</v>
+      </c>
       <c r="F68" s="11"/>
       <c r="G68" s="11">
         <v>7</v>
@@ -5017,12 +5072,14 @@
       <c r="A69" s="9"/>
       <c r="B69" s="10"/>
       <c r="C69" s="12" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="E69" s="11"/>
+        <v>176</v>
+      </c>
+      <c r="E69" s="11" t="s">
+        <v>177</v>
+      </c>
       <c r="F69" s="11"/>
       <c r="G69" s="11">
         <v>3</v>
@@ -5033,12 +5090,14 @@
       <c r="A70" s="9"/>
       <c r="B70" s="10"/>
       <c r="C70" s="12" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="E70" s="11"/>
+        <v>179</v>
+      </c>
+      <c r="E70" s="11" t="s">
+        <v>147</v>
+      </c>
       <c r="F70" s="11"/>
       <c r="G70" s="11">
         <v>8</v>
@@ -5049,12 +5108,14 @@
       <c r="A71" s="9"/>
       <c r="B71" s="10"/>
       <c r="C71" s="12" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="E71" s="11"/>
+        <v>181</v>
+      </c>
+      <c r="E71" s="11" t="s">
+        <v>17</v>
+      </c>
       <c r="F71" s="11"/>
       <c r="G71" s="11">
         <v>0</v>
@@ -5065,12 +5126,14 @@
       <c r="A72" s="9"/>
       <c r="B72" s="10"/>
       <c r="C72" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="E72" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="D72" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="E72" s="11"/>
       <c r="F72" s="11"/>
       <c r="G72" s="11">
         <v>1</v>
@@ -5081,12 +5144,14 @@
       <c r="A73" s="9"/>
       <c r="B73" s="10"/>
       <c r="C73" s="12" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="E73" s="11"/>
+        <v>185</v>
+      </c>
+      <c r="E73" s="11" t="s">
+        <v>57</v>
+      </c>
       <c r="F73" s="11"/>
       <c r="G73" s="11">
         <v>0</v>
@@ -5097,12 +5162,14 @@
       <c r="A74" s="9"/>
       <c r="B74" s="10"/>
       <c r="C74" s="12" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="E74" s="11"/>
+        <v>187</v>
+      </c>
+      <c r="E74" s="11" t="s">
+        <v>188</v>
+      </c>
       <c r="F74" s="11"/>
       <c r="G74" s="11">
         <v>0</v>
@@ -5113,12 +5180,14 @@
       <c r="A75" s="9"/>
       <c r="B75" s="10"/>
       <c r="C75" s="12" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="E75" s="11"/>
+        <v>190</v>
+      </c>
+      <c r="E75" s="11" t="s">
+        <v>57</v>
+      </c>
       <c r="F75" s="11"/>
       <c r="G75" s="11">
         <v>0</v>
@@ -5129,12 +5198,14 @@
       <c r="A76" s="9"/>
       <c r="B76" s="10"/>
       <c r="C76" s="12" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="E76" s="11"/>
+        <v>192</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>147</v>
+      </c>
       <c r="F76" s="11"/>
       <c r="G76" s="11">
         <v>9</v>
@@ -5145,12 +5216,14 @@
       <c r="A77" s="9"/>
       <c r="B77" s="10"/>
       <c r="C77" s="12" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="E77" s="11"/>
+        <v>194</v>
+      </c>
+      <c r="E77" s="11" t="s">
+        <v>177</v>
+      </c>
       <c r="F77" s="11"/>
       <c r="G77" s="11">
         <v>2</v>
@@ -5161,12 +5234,14 @@
       <c r="A78" s="9"/>
       <c r="B78" s="10"/>
       <c r="C78" s="12" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="E78" s="11"/>
+        <v>196</v>
+      </c>
+      <c r="E78" s="11" t="s">
+        <v>164</v>
+      </c>
       <c r="F78" s="11"/>
       <c r="G78" s="11">
         <v>2</v>
@@ -5177,12 +5252,14 @@
       <c r="A79" s="9"/>
       <c r="B79" s="10"/>
       <c r="C79" s="12" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="E79" s="11"/>
+        <v>198</v>
+      </c>
+      <c r="E79" s="11" t="s">
+        <v>177</v>
+      </c>
       <c r="F79" s="11"/>
       <c r="G79" s="11">
         <v>3</v>
@@ -5193,12 +5270,14 @@
       <c r="A80" s="9"/>
       <c r="B80" s="10"/>
       <c r="C80" s="12" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="E80" s="11"/>
+        <v>200</v>
+      </c>
+      <c r="E80" s="11" t="s">
+        <v>17</v>
+      </c>
       <c r="F80" s="11"/>
       <c r="G80" s="11">
         <v>0</v>
@@ -5208,16 +5287,16 @@
     <row r="81" spans="1:8">
       <c r="A81" s="9"/>
       <c r="B81" s="10" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="E81" s="11" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="F81" s="11"/>
       <c r="G81" s="11">
@@ -5228,13 +5307,13 @@
     <row r="82" spans="1:8">
       <c r="A82" s="9"/>
       <c r="B82" s="10" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="E82" s="11"/>
       <c r="F82" s="11"/>
@@ -5246,13 +5325,13 @@
     <row r="83" spans="1:8">
       <c r="A83" s="9"/>
       <c r="B83" s="10" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E83" s="11"/>
       <c r="F83" s="11"/>
@@ -5263,16 +5342,16 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="13" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B85" s="14" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E85" s="15" t="s">
         <v>17</v>
@@ -5287,10 +5366,10 @@
       <c r="A86" s="13"/>
       <c r="B86" s="14"/>
       <c r="C86" s="15" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="D86" s="15" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E86" s="15" t="s">
         <v>17</v>
@@ -5305,10 +5384,10 @@
       <c r="A87" s="13"/>
       <c r="B87" s="14"/>
       <c r="C87" s="15" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E87" s="15" t="s">
         <v>17</v>
@@ -5323,13 +5402,13 @@
       <c r="A88" s="13"/>
       <c r="B88" s="14"/>
       <c r="C88" s="15" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="D88" s="15" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F88" s="16"/>
       <c r="G88" s="16">
@@ -5340,16 +5419,16 @@
     <row r="89" spans="1:8">
       <c r="A89" s="13"/>
       <c r="B89" s="14" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D89" s="15" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="E89" s="15" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="F89" s="16"/>
       <c r="G89" s="16">
@@ -5361,13 +5440,13 @@
       <c r="A90" s="13"/>
       <c r="B90" s="14"/>
       <c r="C90" s="15" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="D90" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="E90" s="15" t="s">
         <v>218</v>
-      </c>
-      <c r="E90" s="15" t="s">
-        <v>212</v>
       </c>
       <c r="F90" s="16"/>
       <c r="G90" s="16">
@@ -5379,13 +5458,13 @@
       <c r="A91" s="13"/>
       <c r="B91" s="14"/>
       <c r="C91" s="15" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D91" s="15" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="E91" s="15" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="F91" s="16"/>
       <c r="G91" s="16">
@@ -5397,13 +5476,13 @@
       <c r="A92" s="13"/>
       <c r="B92" s="14"/>
       <c r="C92" s="15" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D92" s="15" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E92" s="15" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="F92" s="16"/>
       <c r="G92" s="16">
@@ -5414,16 +5493,16 @@
     <row r="93" spans="1:8">
       <c r="A93" s="13"/>
       <c r="B93" s="14" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D93" s="15" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="E93" s="15" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F93" s="16"/>
       <c r="G93" s="16">
@@ -5435,13 +5514,13 @@
       <c r="A94" s="13"/>
       <c r="B94" s="14"/>
       <c r="C94" s="15" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D94" s="15" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="E94" s="15" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F94" s="16"/>
       <c r="G94" s="16">
@@ -5452,19 +5531,19 @@
     <row r="95" spans="1:8">
       <c r="A95" s="13"/>
       <c r="B95" s="14" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="C95" s="15" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D95" s="15" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E95" s="15" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="F95" s="16" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="G95" s="16">
         <v>7</v>
@@ -5475,13 +5554,13 @@
       <c r="A96" s="13"/>
       <c r="B96" s="14"/>
       <c r="C96" s="15" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="D96" s="15" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E96" s="15" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="F96" s="16"/>
       <c r="G96" s="16">
@@ -5493,13 +5572,13 @@
       <c r="A97" s="13"/>
       <c r="B97" s="14"/>
       <c r="C97" s="15" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="D97" s="15" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="E97" s="15" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="F97" s="16"/>
       <c r="G97" s="16">
@@ -5511,13 +5590,13 @@
       <c r="A98" s="13"/>
       <c r="B98" s="14"/>
       <c r="C98" s="15" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="D98" s="15" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E98" s="15" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="F98" s="16"/>
       <c r="G98" s="16">
@@ -5528,16 +5607,16 @@
     <row r="99" spans="1:8">
       <c r="A99" s="13"/>
       <c r="B99" s="14" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="D99" s="15" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="E99" s="15" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F99" s="16"/>
       <c r="G99" s="16">
@@ -5549,13 +5628,13 @@
       <c r="A100" s="13"/>
       <c r="B100" s="14"/>
       <c r="C100" s="15" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="D100" s="15" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="E100" s="15" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F100" s="16"/>
       <c r="G100" s="16">
@@ -5567,13 +5646,13 @@
       <c r="A101" s="13"/>
       <c r="B101" s="14"/>
       <c r="C101" s="15" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="D101" s="15" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="E101" s="15" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="F101" s="16"/>
       <c r="G101" s="16">
@@ -5585,13 +5664,13 @@
       <c r="A102" s="13"/>
       <c r="B102" s="14"/>
       <c r="C102" s="15" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="D102" s="15" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E102" s="15" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F102" s="16"/>
       <c r="G102" s="16">
@@ -5603,13 +5682,13 @@
       <c r="A103" s="13"/>
       <c r="B103" s="14"/>
       <c r="C103" s="15" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="D103" s="15" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E103" s="15" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="F103" s="16"/>
       <c r="G103" s="16">
@@ -5621,13 +5700,13 @@
       <c r="A104" s="13"/>
       <c r="B104" s="14"/>
       <c r="C104" s="15" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="D104" s="15" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="E104" s="15" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F104" s="16"/>
       <c r="G104" s="16">
@@ -5638,16 +5717,16 @@
     <row r="105" spans="1:8">
       <c r="A105" s="13"/>
       <c r="B105" s="14" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C105" s="15" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D105" s="15" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E105" s="15" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F105" s="16"/>
       <c r="G105" s="16">
@@ -5658,16 +5737,16 @@
     <row r="106" spans="1:8">
       <c r="A106" s="13"/>
       <c r="B106" s="14" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="D106" s="15" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E106" s="15" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="F106" s="16"/>
       <c r="G106" s="16">
@@ -5678,16 +5757,16 @@
     <row r="107" spans="1:8">
       <c r="A107" s="13"/>
       <c r="B107" s="14" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C107" s="15" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="D107" s="15" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="E107" s="15" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="F107" s="16"/>
       <c r="G107" s="16">
@@ -5699,13 +5778,13 @@
       <c r="A108" s="13"/>
       <c r="B108" s="14"/>
       <c r="C108" s="15" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D108" s="15" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E108" s="15" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F108" s="16"/>
       <c r="G108" s="16">
@@ -5717,13 +5796,13 @@
       <c r="A109" s="13"/>
       <c r="B109" s="14"/>
       <c r="C109" s="15" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="D109" s="15" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="E109" s="15" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="F109" s="16"/>
       <c r="G109" s="16">
@@ -5739,1534 +5818,1534 @@
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="17" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B111" s="18"/>
       <c r="C111" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="D111" s="18" t="s">
-        <v>277</v>
-      </c>
-      <c r="E111" s="19" t="s">
-        <v>278</v>
-      </c>
-      <c r="F111" s="19"/>
-      <c r="G111" s="19"/>
-      <c r="H111" s="19"/>
+        <v>282</v>
+      </c>
+      <c r="D111" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="E111" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="F111" s="20"/>
+      <c r="G111" s="20"/>
+      <c r="H111" s="20"/>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="17"/>
       <c r="B112" s="18"/>
       <c r="C112" s="18" t="s">
-        <v>279</v>
-      </c>
-      <c r="D112" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="E112" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="F112" s="19"/>
-      <c r="G112" s="19"/>
-      <c r="H112" s="19"/>
+        <v>285</v>
+      </c>
+      <c r="D112" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="E112" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="F112" s="20"/>
+      <c r="G112" s="20"/>
+      <c r="H112" s="20"/>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="17"/>
       <c r="B113" s="18"/>
       <c r="C113" s="18" t="s">
-        <v>282</v>
-      </c>
-      <c r="D113" s="18" t="s">
-        <v>283</v>
-      </c>
-      <c r="E113" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="F113" s="19"/>
-      <c r="G113" s="19"/>
-      <c r="H113" s="19"/>
+        <v>288</v>
+      </c>
+      <c r="D113" s="19" t="s">
+        <v>289</v>
+      </c>
+      <c r="E113" s="20" t="s">
+        <v>290</v>
+      </c>
+      <c r="F113" s="20"/>
+      <c r="G113" s="20"/>
+      <c r="H113" s="20"/>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="17"/>
       <c r="B114" s="18"/>
       <c r="C114" s="18" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D114" s="18" t="s">
-        <v>286</v>
-      </c>
-      <c r="E114" s="19" t="s">
-        <v>287</v>
-      </c>
-      <c r="F114" s="19"/>
-      <c r="G114" s="19"/>
-      <c r="H114" s="19"/>
+        <v>292</v>
+      </c>
+      <c r="E114" s="20" t="s">
+        <v>293</v>
+      </c>
+      <c r="F114" s="20"/>
+      <c r="G114" s="20"/>
+      <c r="H114" s="20"/>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="17"/>
       <c r="B115" s="18"/>
       <c r="C115" s="18" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="D115" s="18" t="s">
-        <v>289</v>
-      </c>
-      <c r="E115" s="19" t="s">
-        <v>290</v>
-      </c>
-      <c r="F115" s="19"/>
-      <c r="G115" s="19"/>
-      <c r="H115" s="19"/>
+        <v>295</v>
+      </c>
+      <c r="E115" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="F115" s="20"/>
+      <c r="G115" s="20"/>
+      <c r="H115" s="20"/>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="17"/>
       <c r="B116" s="18"/>
       <c r="C116" s="18" t="s">
-        <v>291</v>
-      </c>
-      <c r="D116" s="18" t="s">
-        <v>292</v>
-      </c>
-      <c r="E116" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="F116" s="19"/>
-      <c r="G116" s="19"/>
-      <c r="H116" s="19"/>
+        <v>297</v>
+      </c>
+      <c r="D116" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="E116" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="F116" s="20"/>
+      <c r="G116" s="20"/>
+      <c r="H116" s="20"/>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="17"/>
       <c r="B117" s="18"/>
       <c r="C117" s="18" t="s">
-        <v>293</v>
-      </c>
-      <c r="D117" s="18" t="s">
-        <v>294</v>
-      </c>
-      <c r="E117" s="19" t="s">
-        <v>295</v>
-      </c>
-      <c r="F117" s="19"/>
-      <c r="G117" s="19"/>
-      <c r="H117" s="19"/>
+        <v>299</v>
+      </c>
+      <c r="D117" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="E117" s="20" t="s">
+        <v>301</v>
+      </c>
+      <c r="F117" s="20"/>
+      <c r="G117" s="20"/>
+      <c r="H117" s="20"/>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="17"/>
       <c r="B118" s="18"/>
       <c r="C118" s="18" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="D118" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="E118" s="19" t="s">
-        <v>298</v>
-      </c>
-      <c r="F118" s="19"/>
-      <c r="G118" s="19"/>
-      <c r="H118" s="19"/>
+        <v>303</v>
+      </c>
+      <c r="E118" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="F118" s="20"/>
+      <c r="G118" s="20"/>
+      <c r="H118" s="20"/>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="17"/>
       <c r="B119" s="18"/>
       <c r="C119" s="18" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="D119" s="18" t="s">
-        <v>300</v>
-      </c>
-      <c r="E119" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="F119" s="19"/>
-      <c r="G119" s="19"/>
-      <c r="H119" s="19"/>
+        <v>306</v>
+      </c>
+      <c r="E119" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="F119" s="20"/>
+      <c r="G119" s="20"/>
+      <c r="H119" s="20"/>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="17"/>
       <c r="B120" s="18"/>
       <c r="C120" s="18" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="D120" s="18" t="s">
-        <v>302</v>
-      </c>
-      <c r="E120" s="19" t="s">
-        <v>303</v>
-      </c>
-      <c r="F120" s="19"/>
-      <c r="G120" s="19"/>
-      <c r="H120" s="19"/>
+        <v>308</v>
+      </c>
+      <c r="E120" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="F120" s="20"/>
+      <c r="G120" s="20"/>
+      <c r="H120" s="20"/>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="17"/>
       <c r="B121" s="18"/>
       <c r="C121" s="18" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="D121" s="18" t="s">
-        <v>305</v>
-      </c>
-      <c r="E121" s="19" t="s">
-        <v>306</v>
-      </c>
-      <c r="F121" s="19"/>
-      <c r="G121" s="19"/>
-      <c r="H121" s="19"/>
+        <v>311</v>
+      </c>
+      <c r="E121" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="F121" s="20"/>
+      <c r="G121" s="20"/>
+      <c r="H121" s="20"/>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="17"/>
       <c r="B122" s="18"/>
       <c r="C122" s="18" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="D122" s="18" t="s">
-        <v>308</v>
-      </c>
-      <c r="E122" s="19" t="s">
-        <v>309</v>
-      </c>
-      <c r="F122" s="19"/>
-      <c r="G122" s="19"/>
-      <c r="H122" s="19"/>
+        <v>314</v>
+      </c>
+      <c r="E122" s="20" t="s">
+        <v>315</v>
+      </c>
+      <c r="F122" s="20"/>
+      <c r="G122" s="20"/>
+      <c r="H122" s="20"/>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="17"/>
       <c r="B123" s="18"/>
       <c r="C123" s="18" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="D123" s="18" t="s">
-        <v>311</v>
-      </c>
-      <c r="E123" s="19" t="s">
-        <v>312</v>
-      </c>
-      <c r="F123" s="19"/>
-      <c r="G123" s="19"/>
-      <c r="H123" s="19"/>
+        <v>317</v>
+      </c>
+      <c r="E123" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="F123" s="20"/>
+      <c r="G123" s="20"/>
+      <c r="H123" s="20"/>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="17"/>
       <c r="B124" s="18"/>
       <c r="C124" s="18" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="D124" s="18" t="s">
-        <v>314</v>
-      </c>
-      <c r="E124" s="19" t="s">
-        <v>315</v>
-      </c>
-      <c r="F124" s="19"/>
-      <c r="G124" s="19"/>
-      <c r="H124" s="19"/>
+        <v>320</v>
+      </c>
+      <c r="E124" s="20" t="s">
+        <v>321</v>
+      </c>
+      <c r="F124" s="20"/>
+      <c r="G124" s="20"/>
+      <c r="H124" s="20"/>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="17"/>
       <c r="B125" s="18"/>
       <c r="C125" s="18" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="D125" s="18" t="s">
-        <v>317</v>
-      </c>
-      <c r="E125" s="19" t="s">
-        <v>318</v>
-      </c>
-      <c r="F125" s="19"/>
-      <c r="G125" s="19"/>
-      <c r="H125" s="19"/>
+        <v>323</v>
+      </c>
+      <c r="E125" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="F125" s="20"/>
+      <c r="G125" s="20"/>
+      <c r="H125" s="20"/>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" s="17"/>
       <c r="B126" s="18"/>
       <c r="C126" s="18" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="D126" s="18" t="s">
-        <v>320</v>
-      </c>
-      <c r="E126" s="19" t="s">
-        <v>321</v>
-      </c>
-      <c r="F126" s="19"/>
-      <c r="G126" s="19"/>
-      <c r="H126" s="19"/>
+        <v>326</v>
+      </c>
+      <c r="E126" s="20" t="s">
+        <v>327</v>
+      </c>
+      <c r="F126" s="20"/>
+      <c r="G126" s="20"/>
+      <c r="H126" s="20"/>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" s="17"/>
       <c r="B127" s="18"/>
       <c r="C127" s="18" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="D127" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="E127" s="19" t="s">
-        <v>324</v>
-      </c>
-      <c r="F127" s="19"/>
-      <c r="G127" s="19"/>
-      <c r="H127" s="19"/>
+        <v>329</v>
+      </c>
+      <c r="E127" s="20" t="s">
+        <v>330</v>
+      </c>
+      <c r="F127" s="20"/>
+      <c r="G127" s="20"/>
+      <c r="H127" s="20"/>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="17"/>
       <c r="B128" s="18"/>
       <c r="C128" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="D128" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="E128" s="19" t="s">
-        <v>327</v>
-      </c>
-      <c r="F128" s="19"/>
-      <c r="G128" s="19"/>
-      <c r="H128" s="19"/>
+        <v>331</v>
+      </c>
+      <c r="D128" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="E128" s="20" t="s">
+        <v>333</v>
+      </c>
+      <c r="F128" s="20"/>
+      <c r="G128" s="20"/>
+      <c r="H128" s="20"/>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="17"/>
       <c r="B129" s="18"/>
       <c r="C129" s="18" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="D129" s="18" t="s">
-        <v>329</v>
-      </c>
-      <c r="E129" s="19" t="s">
-        <v>330</v>
-      </c>
-      <c r="F129" s="19"/>
-      <c r="G129" s="19"/>
-      <c r="H129" s="19"/>
+        <v>335</v>
+      </c>
+      <c r="E129" s="20" t="s">
+        <v>336</v>
+      </c>
+      <c r="F129" s="20"/>
+      <c r="G129" s="20"/>
+      <c r="H129" s="20"/>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="17"/>
       <c r="B130" s="18"/>
       <c r="C130" s="18" t="s">
-        <v>331</v>
-      </c>
-      <c r="D130" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="E130" s="19" t="s">
-        <v>333</v>
-      </c>
-      <c r="F130" s="19"/>
-      <c r="G130" s="19"/>
-      <c r="H130" s="19"/>
+        <v>337</v>
+      </c>
+      <c r="D130" s="19" t="s">
+        <v>338</v>
+      </c>
+      <c r="E130" s="20" t="s">
+        <v>339</v>
+      </c>
+      <c r="F130" s="20"/>
+      <c r="G130" s="20"/>
+      <c r="H130" s="20"/>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="17"/>
       <c r="B131" s="18"/>
       <c r="C131" s="18" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="D131" s="18" t="s">
-        <v>335</v>
-      </c>
-      <c r="E131" s="19" t="s">
-        <v>336</v>
-      </c>
-      <c r="F131" s="19"/>
-      <c r="G131" s="19"/>
-      <c r="H131" s="19"/>
+        <v>341</v>
+      </c>
+      <c r="E131" s="20" t="s">
+        <v>342</v>
+      </c>
+      <c r="F131" s="20"/>
+      <c r="G131" s="20"/>
+      <c r="H131" s="20"/>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="17"/>
       <c r="B132" s="18"/>
       <c r="C132" s="18" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="D132" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="E132" s="19" t="s">
-        <v>339</v>
-      </c>
-      <c r="F132" s="19"/>
-      <c r="G132" s="19"/>
-      <c r="H132" s="19"/>
+        <v>344</v>
+      </c>
+      <c r="E132" s="20" t="s">
+        <v>345</v>
+      </c>
+      <c r="F132" s="20"/>
+      <c r="G132" s="20"/>
+      <c r="H132" s="20"/>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="17"/>
       <c r="B133" s="18"/>
       <c r="C133" s="18" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="D133" s="18" t="s">
-        <v>341</v>
-      </c>
-      <c r="E133" s="19" t="s">
-        <v>342</v>
-      </c>
-      <c r="F133" s="19"/>
-      <c r="G133" s="19"/>
-      <c r="H133" s="19"/>
+        <v>347</v>
+      </c>
+      <c r="E133" s="20" t="s">
+        <v>348</v>
+      </c>
+      <c r="F133" s="20"/>
+      <c r="G133" s="20"/>
+      <c r="H133" s="20"/>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="17"/>
       <c r="B134" s="18"/>
       <c r="C134" s="18" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="D134" s="18" t="s">
-        <v>344</v>
-      </c>
-      <c r="E134" s="19" t="s">
-        <v>345</v>
-      </c>
-      <c r="F134" s="19"/>
-      <c r="G134" s="19"/>
-      <c r="H134" s="19"/>
+        <v>350</v>
+      </c>
+      <c r="E134" s="20" t="s">
+        <v>351</v>
+      </c>
+      <c r="F134" s="20"/>
+      <c r="G134" s="20"/>
+      <c r="H134" s="20"/>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="17"/>
       <c r="B135" s="18"/>
       <c r="C135" s="18" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="D135" s="18" t="s">
-        <v>347</v>
-      </c>
-      <c r="E135" s="19" t="s">
-        <v>348</v>
-      </c>
-      <c r="F135" s="19"/>
-      <c r="G135" s="19"/>
-      <c r="H135" s="19"/>
+        <v>353</v>
+      </c>
+      <c r="E135" s="20" t="s">
+        <v>354</v>
+      </c>
+      <c r="F135" s="20"/>
+      <c r="G135" s="20"/>
+      <c r="H135" s="20"/>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" s="17"/>
       <c r="B136" s="18"/>
       <c r="C136" s="18" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="D136" s="18" t="s">
-        <v>350</v>
-      </c>
-      <c r="E136" s="19" t="s">
-        <v>351</v>
-      </c>
-      <c r="F136" s="19"/>
-      <c r="G136" s="19"/>
-      <c r="H136" s="19"/>
+        <v>356</v>
+      </c>
+      <c r="E136" s="20" t="s">
+        <v>357</v>
+      </c>
+      <c r="F136" s="20"/>
+      <c r="G136" s="20"/>
+      <c r="H136" s="20"/>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="17"/>
       <c r="B137" s="18"/>
       <c r="C137" s="18" t="s">
-        <v>352</v>
-      </c>
-      <c r="D137" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="E137" s="19" t="s">
-        <v>354</v>
-      </c>
-      <c r="F137" s="19"/>
-      <c r="G137" s="19"/>
-      <c r="H137" s="19"/>
+        <v>358</v>
+      </c>
+      <c r="D137" s="19" t="s">
+        <v>359</v>
+      </c>
+      <c r="E137" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="F137" s="20"/>
+      <c r="G137" s="20"/>
+      <c r="H137" s="20"/>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="17"/>
       <c r="B138" s="18"/>
       <c r="C138" s="18" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="D138" s="18" t="s">
-        <v>356</v>
-      </c>
-      <c r="E138" s="19" t="s">
-        <v>357</v>
-      </c>
-      <c r="F138" s="19"/>
-      <c r="G138" s="19"/>
-      <c r="H138" s="19"/>
+        <v>362</v>
+      </c>
+      <c r="E138" s="20" t="s">
+        <v>363</v>
+      </c>
+      <c r="F138" s="20"/>
+      <c r="G138" s="20"/>
+      <c r="H138" s="20"/>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="17"/>
       <c r="B139" s="18"/>
       <c r="C139" s="18" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D139" s="18" t="s">
-        <v>359</v>
-      </c>
-      <c r="E139" s="19" t="s">
-        <v>360</v>
-      </c>
-      <c r="F139" s="19"/>
-      <c r="G139" s="19"/>
-      <c r="H139" s="19"/>
+        <v>365</v>
+      </c>
+      <c r="E139" s="20" t="s">
+        <v>366</v>
+      </c>
+      <c r="F139" s="20"/>
+      <c r="G139" s="20"/>
+      <c r="H139" s="20"/>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="17"/>
       <c r="B140" s="18"/>
       <c r="C140" s="18" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="D140" s="18" t="s">
-        <v>362</v>
-      </c>
-      <c r="E140" s="19" t="s">
-        <v>363</v>
-      </c>
-      <c r="F140" s="19"/>
-      <c r="G140" s="19"/>
-      <c r="H140" s="19"/>
+        <v>368</v>
+      </c>
+      <c r="E140" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="F140" s="20"/>
+      <c r="G140" s="20"/>
+      <c r="H140" s="20"/>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="17"/>
       <c r="B141" s="18"/>
       <c r="C141" s="18" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="D141" s="18" t="s">
-        <v>365</v>
-      </c>
-      <c r="E141" s="19" t="s">
-        <v>366</v>
-      </c>
-      <c r="F141" s="19"/>
-      <c r="G141" s="19"/>
-      <c r="H141" s="19"/>
+        <v>371</v>
+      </c>
+      <c r="E141" s="20" t="s">
+        <v>372</v>
+      </c>
+      <c r="F141" s="20"/>
+      <c r="G141" s="20"/>
+      <c r="H141" s="20"/>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="17"/>
       <c r="B142" s="18"/>
       <c r="C142" s="18" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="D142" s="18" t="s">
-        <v>368</v>
-      </c>
-      <c r="E142" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="F142" s="19"/>
-      <c r="G142" s="19"/>
-      <c r="H142" s="19"/>
+        <v>374</v>
+      </c>
+      <c r="E142" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="F142" s="20"/>
+      <c r="G142" s="20"/>
+      <c r="H142" s="20"/>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="17"/>
       <c r="B143" s="18"/>
       <c r="C143" s="18" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="D143" s="18" t="s">
-        <v>370</v>
-      </c>
-      <c r="E143" s="19" t="s">
-        <v>371</v>
-      </c>
-      <c r="F143" s="19"/>
-      <c r="G143" s="19"/>
-      <c r="H143" s="19"/>
+        <v>376</v>
+      </c>
+      <c r="E143" s="20" t="s">
+        <v>377</v>
+      </c>
+      <c r="F143" s="20"/>
+      <c r="G143" s="20"/>
+      <c r="H143" s="20"/>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="17"/>
       <c r="B144" s="18"/>
       <c r="C144" s="18" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="D144" s="18" t="s">
-        <v>373</v>
-      </c>
-      <c r="E144" s="19" t="s">
-        <v>374</v>
-      </c>
-      <c r="F144" s="19"/>
-      <c r="G144" s="19"/>
-      <c r="H144" s="19"/>
+        <v>379</v>
+      </c>
+      <c r="E144" s="20" t="s">
+        <v>380</v>
+      </c>
+      <c r="F144" s="20"/>
+      <c r="G144" s="20"/>
+      <c r="H144" s="20"/>
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="17"/>
       <c r="B145" s="18"/>
       <c r="C145" s="18" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="D145" s="18" t="s">
-        <v>376</v>
-      </c>
-      <c r="E145" s="19" t="s">
-        <v>377</v>
-      </c>
-      <c r="F145" s="19"/>
-      <c r="G145" s="19"/>
-      <c r="H145" s="19"/>
+        <v>382</v>
+      </c>
+      <c r="E145" s="20" t="s">
+        <v>383</v>
+      </c>
+      <c r="F145" s="20"/>
+      <c r="G145" s="20"/>
+      <c r="H145" s="20"/>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="17"/>
       <c r="B146" s="18"/>
       <c r="C146" s="18" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="D146" s="18" t="s">
-        <v>379</v>
-      </c>
-      <c r="E146" s="19" t="s">
-        <v>380</v>
-      </c>
-      <c r="F146" s="19"/>
-      <c r="G146" s="19"/>
-      <c r="H146" s="19"/>
+        <v>385</v>
+      </c>
+      <c r="E146" s="20" t="s">
+        <v>386</v>
+      </c>
+      <c r="F146" s="20"/>
+      <c r="G146" s="20"/>
+      <c r="H146" s="20"/>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="17"/>
       <c r="B147" s="18"/>
       <c r="C147" s="18" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="D147" s="18" t="s">
-        <v>382</v>
-      </c>
-      <c r="E147" s="19" t="s">
-        <v>383</v>
-      </c>
-      <c r="F147" s="19"/>
-      <c r="G147" s="19"/>
-      <c r="H147" s="19"/>
+        <v>388</v>
+      </c>
+      <c r="E147" s="20" t="s">
+        <v>389</v>
+      </c>
+      <c r="F147" s="20"/>
+      <c r="G147" s="20"/>
+      <c r="H147" s="20"/>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="17"/>
       <c r="B148" s="18"/>
       <c r="C148" s="18" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="D148" s="18" t="s">
-        <v>385</v>
-      </c>
-      <c r="E148" s="19" t="s">
-        <v>386</v>
-      </c>
-      <c r="F148" s="19"/>
-      <c r="G148" s="19"/>
-      <c r="H148" s="19"/>
+        <v>391</v>
+      </c>
+      <c r="E148" s="20" t="s">
+        <v>392</v>
+      </c>
+      <c r="F148" s="20"/>
+      <c r="G148" s="20"/>
+      <c r="H148" s="20"/>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="17"/>
       <c r="B149" s="18"/>
       <c r="C149" s="18" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="D149" s="18" t="s">
-        <v>388</v>
-      </c>
-      <c r="E149" s="19" t="s">
-        <v>389</v>
-      </c>
-      <c r="F149" s="19"/>
-      <c r="G149" s="19"/>
-      <c r="H149" s="19"/>
+        <v>394</v>
+      </c>
+      <c r="E149" s="20" t="s">
+        <v>395</v>
+      </c>
+      <c r="F149" s="20"/>
+      <c r="G149" s="20"/>
+      <c r="H149" s="20"/>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" s="17"/>
       <c r="B150" s="18"/>
       <c r="C150" s="18" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="D150" s="18" t="s">
-        <v>391</v>
-      </c>
-      <c r="E150" s="19" t="s">
-        <v>392</v>
-      </c>
-      <c r="F150" s="19"/>
-      <c r="G150" s="19"/>
-      <c r="H150" s="19"/>
+        <v>397</v>
+      </c>
+      <c r="E150" s="20" t="s">
+        <v>398</v>
+      </c>
+      <c r="F150" s="20"/>
+      <c r="G150" s="20"/>
+      <c r="H150" s="20"/>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="17"/>
       <c r="B151" s="18"/>
       <c r="C151" s="18" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="D151" s="18" t="s">
-        <v>394</v>
-      </c>
-      <c r="E151" s="19" t="s">
-        <v>395</v>
-      </c>
-      <c r="F151" s="19"/>
-      <c r="G151" s="19"/>
-      <c r="H151" s="19"/>
+        <v>400</v>
+      </c>
+      <c r="E151" s="20" t="s">
+        <v>401</v>
+      </c>
+      <c r="F151" s="20"/>
+      <c r="G151" s="20"/>
+      <c r="H151" s="20"/>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="17"/>
       <c r="B152" s="18"/>
       <c r="C152" s="18" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="D152" s="18" t="s">
-        <v>397</v>
-      </c>
-      <c r="E152" s="19" t="s">
-        <v>398</v>
-      </c>
-      <c r="F152" s="19"/>
-      <c r="G152" s="19"/>
-      <c r="H152" s="19"/>
+        <v>403</v>
+      </c>
+      <c r="E152" s="20" t="s">
+        <v>404</v>
+      </c>
+      <c r="F152" s="20"/>
+      <c r="G152" s="20"/>
+      <c r="H152" s="20"/>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" s="17"/>
       <c r="B153" s="18"/>
       <c r="C153" s="18" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="D153" s="18" t="s">
-        <v>400</v>
-      </c>
-      <c r="E153" s="19" t="s">
-        <v>401</v>
-      </c>
-      <c r="F153" s="19"/>
-      <c r="G153" s="19"/>
-      <c r="H153" s="19"/>
+        <v>406</v>
+      </c>
+      <c r="E153" s="20" t="s">
+        <v>407</v>
+      </c>
+      <c r="F153" s="20"/>
+      <c r="G153" s="20"/>
+      <c r="H153" s="20"/>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" s="17"/>
       <c r="B154" s="18"/>
       <c r="C154" s="18" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="D154" s="18" t="s">
-        <v>403</v>
-      </c>
-      <c r="E154" s="19" t="s">
-        <v>404</v>
-      </c>
-      <c r="F154" s="19"/>
-      <c r="G154" s="19"/>
-      <c r="H154" s="19"/>
+        <v>409</v>
+      </c>
+      <c r="E154" s="20" t="s">
+        <v>410</v>
+      </c>
+      <c r="F154" s="20"/>
+      <c r="G154" s="20"/>
+      <c r="H154" s="20"/>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" s="17"/>
       <c r="B155" s="18"/>
       <c r="C155" s="18" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="D155" s="18" t="s">
-        <v>406</v>
-      </c>
-      <c r="E155" s="19" t="s">
-        <v>407</v>
-      </c>
-      <c r="F155" s="19"/>
-      <c r="G155" s="19"/>
-      <c r="H155" s="19"/>
+        <v>412</v>
+      </c>
+      <c r="E155" s="20" t="s">
+        <v>413</v>
+      </c>
+      <c r="F155" s="20"/>
+      <c r="G155" s="20"/>
+      <c r="H155" s="20"/>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" s="17"/>
       <c r="B156" s="18"/>
       <c r="C156" s="18" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="D156" s="18" t="s">
-        <v>409</v>
-      </c>
-      <c r="E156" s="19" t="s">
-        <v>410</v>
-      </c>
-      <c r="F156" s="19"/>
-      <c r="G156" s="19"/>
-      <c r="H156" s="19"/>
+        <v>415</v>
+      </c>
+      <c r="E156" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="F156" s="20"/>
+      <c r="G156" s="20"/>
+      <c r="H156" s="20"/>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" s="17"/>
       <c r="B157" s="18"/>
       <c r="C157" s="18" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="D157" s="18" t="s">
-        <v>412</v>
-      </c>
-      <c r="E157" s="19" t="s">
-        <v>413</v>
-      </c>
-      <c r="F157" s="19"/>
-      <c r="G157" s="19"/>
-      <c r="H157" s="19"/>
+        <v>418</v>
+      </c>
+      <c r="E157" s="20" t="s">
+        <v>419</v>
+      </c>
+      <c r="F157" s="20"/>
+      <c r="G157" s="20"/>
+      <c r="H157" s="20"/>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="17"/>
       <c r="B158" s="18"/>
       <c r="C158" s="18" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="D158" s="18" t="s">
-        <v>415</v>
-      </c>
-      <c r="E158" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="F158" s="19"/>
-      <c r="G158" s="19"/>
-      <c r="H158" s="19"/>
+        <v>421</v>
+      </c>
+      <c r="E158" s="20" t="s">
+        <v>422</v>
+      </c>
+      <c r="F158" s="20"/>
+      <c r="G158" s="20"/>
+      <c r="H158" s="20"/>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" s="17"/>
       <c r="B159" s="18"/>
       <c r="C159" s="18" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="D159" s="18" t="s">
-        <v>418</v>
-      </c>
-      <c r="E159" s="19" t="s">
-        <v>419</v>
-      </c>
-      <c r="F159" s="19"/>
-      <c r="G159" s="19"/>
-      <c r="H159" s="19"/>
+        <v>424</v>
+      </c>
+      <c r="E159" s="20" t="s">
+        <v>425</v>
+      </c>
+      <c r="F159" s="20"/>
+      <c r="G159" s="20"/>
+      <c r="H159" s="20"/>
     </row>
     <row r="160" spans="1:8">
       <c r="A160" s="17"/>
       <c r="B160" s="18"/>
       <c r="C160" s="18" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="D160" s="18" t="s">
-        <v>421</v>
-      </c>
-      <c r="E160" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="F160" s="19"/>
-      <c r="G160" s="19"/>
-      <c r="H160" s="19"/>
+        <v>427</v>
+      </c>
+      <c r="E160" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="F160" s="20"/>
+      <c r="G160" s="20"/>
+      <c r="H160" s="20"/>
     </row>
     <row r="161" spans="1:8">
       <c r="A161" s="17"/>
       <c r="B161" s="18"/>
       <c r="C161" s="18" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="D161" s="18" t="s">
-        <v>423</v>
-      </c>
-      <c r="E161" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="F161" s="19"/>
-      <c r="G161" s="19"/>
-      <c r="H161" s="19"/>
+        <v>429</v>
+      </c>
+      <c r="E161" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="F161" s="20"/>
+      <c r="G161" s="20"/>
+      <c r="H161" s="20"/>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" s="17"/>
       <c r="B162" s="18"/>
       <c r="C162" s="18" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="D162" s="18" t="s">
-        <v>425</v>
-      </c>
-      <c r="E162" s="19" t="s">
-        <v>426</v>
-      </c>
-      <c r="F162" s="19"/>
-      <c r="G162" s="19"/>
-      <c r="H162" s="19"/>
+        <v>431</v>
+      </c>
+      <c r="E162" s="20" t="s">
+        <v>432</v>
+      </c>
+      <c r="F162" s="20"/>
+      <c r="G162" s="20"/>
+      <c r="H162" s="20"/>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" s="17"/>
       <c r="B163" s="18"/>
       <c r="C163" s="18" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="D163" s="18" t="s">
-        <v>428</v>
-      </c>
-      <c r="E163" s="19" t="s">
-        <v>429</v>
-      </c>
-      <c r="F163" s="19"/>
-      <c r="G163" s="19"/>
-      <c r="H163" s="19"/>
+        <v>434</v>
+      </c>
+      <c r="E163" s="20" t="s">
+        <v>435</v>
+      </c>
+      <c r="F163" s="20"/>
+      <c r="G163" s="20"/>
+      <c r="H163" s="20"/>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" s="17"/>
       <c r="B164" s="18"/>
       <c r="C164" s="18" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="D164" s="18" t="s">
-        <v>431</v>
-      </c>
-      <c r="E164" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="F164" s="19"/>
-      <c r="G164" s="19"/>
-      <c r="H164" s="19"/>
+        <v>437</v>
+      </c>
+      <c r="E164" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="F164" s="20"/>
+      <c r="G164" s="20"/>
+      <c r="H164" s="20"/>
     </row>
     <row r="165" spans="1:8">
       <c r="A165" s="17"/>
       <c r="B165" s="18"/>
       <c r="C165" s="18" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="D165" s="18" t="s">
-        <v>433</v>
-      </c>
-      <c r="E165" s="19" t="s">
-        <v>434</v>
-      </c>
-      <c r="F165" s="19"/>
-      <c r="G165" s="19"/>
-      <c r="H165" s="19"/>
+        <v>439</v>
+      </c>
+      <c r="E165" s="20" t="s">
+        <v>440</v>
+      </c>
+      <c r="F165" s="20"/>
+      <c r="G165" s="20"/>
+      <c r="H165" s="20"/>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" s="17"/>
       <c r="B166" s="18"/>
       <c r="C166" s="18" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="D166" s="18" t="s">
-        <v>436</v>
-      </c>
-      <c r="E166" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="F166" s="19"/>
-      <c r="G166" s="19"/>
-      <c r="H166" s="19"/>
+        <v>442</v>
+      </c>
+      <c r="E166" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="F166" s="20"/>
+      <c r="G166" s="20"/>
+      <c r="H166" s="20"/>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" s="17"/>
       <c r="B167" s="18"/>
       <c r="C167" s="18" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="D167" s="18" t="s">
-        <v>438</v>
-      </c>
-      <c r="E167" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="F167" s="19"/>
-      <c r="G167" s="19"/>
-      <c r="H167" s="19"/>
+        <v>444</v>
+      </c>
+      <c r="E167" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="F167" s="20"/>
+      <c r="G167" s="20"/>
+      <c r="H167" s="20"/>
     </row>
     <row r="168" spans="1:8">
       <c r="A168" s="17"/>
       <c r="B168" s="18"/>
       <c r="C168" s="18" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="D168" s="18" t="s">
-        <v>440</v>
-      </c>
-      <c r="E168" s="19" t="s">
-        <v>441</v>
-      </c>
-      <c r="F168" s="19"/>
-      <c r="G168" s="19"/>
-      <c r="H168" s="19"/>
+        <v>446</v>
+      </c>
+      <c r="E168" s="20" t="s">
+        <v>447</v>
+      </c>
+      <c r="F168" s="20"/>
+      <c r="G168" s="20"/>
+      <c r="H168" s="20"/>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" s="17"/>
       <c r="B169" s="18"/>
       <c r="C169" s="18" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="D169" s="18" t="s">
-        <v>443</v>
-      </c>
-      <c r="E169" s="19" t="s">
-        <v>444</v>
-      </c>
-      <c r="F169" s="19"/>
-      <c r="G169" s="19"/>
-      <c r="H169" s="19"/>
+        <v>449</v>
+      </c>
+      <c r="E169" s="20" t="s">
+        <v>450</v>
+      </c>
+      <c r="F169" s="20"/>
+      <c r="G169" s="20"/>
+      <c r="H169" s="20"/>
     </row>
     <row r="170" spans="1:8">
       <c r="A170" s="17"/>
       <c r="B170" s="18"/>
       <c r="C170" s="18" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="D170" s="18" t="s">
-        <v>446</v>
-      </c>
-      <c r="E170" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="F170" s="19"/>
-      <c r="G170" s="19"/>
-      <c r="H170" s="19"/>
+        <v>452</v>
+      </c>
+      <c r="E170" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="F170" s="20"/>
+      <c r="G170" s="20"/>
+      <c r="H170" s="20"/>
     </row>
     <row r="171" spans="1:8">
-      <c r="B171" s="20"/>
-      <c r="C171" s="20"/>
-      <c r="D171" s="20"/>
+      <c r="B171" s="21"/>
+      <c r="C171" s="21"/>
+      <c r="D171" s="21"/>
     </row>
     <row r="172" spans="1:8">
-      <c r="A172" s="21" t="s">
-        <v>447</v>
-      </c>
-      <c r="B172" s="21" t="s">
-        <v>448</v>
-      </c>
-      <c r="C172" s="22" t="s">
-        <v>448</v>
-      </c>
-      <c r="D172" s="23" t="s">
-        <v>449</v>
-      </c>
-      <c r="E172" s="22" t="s">
-        <v>450</v>
-      </c>
-      <c r="F172" s="22"/>
-      <c r="G172" s="22"/>
-      <c r="H172" s="22"/>
+      <c r="A172" s="22" t="s">
+        <v>453</v>
+      </c>
+      <c r="B172" s="22" t="s">
+        <v>454</v>
+      </c>
+      <c r="C172" s="23" t="s">
+        <v>454</v>
+      </c>
+      <c r="D172" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="E172" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="F172" s="23"/>
+      <c r="G172" s="23"/>
+      <c r="H172" s="23"/>
     </row>
     <row r="173" spans="1:8">
-      <c r="A173" s="21"/>
-      <c r="B173" s="21"/>
-      <c r="C173" s="22" t="s">
+      <c r="A173" s="22"/>
+      <c r="B173" s="22"/>
+      <c r="C173" s="23" t="s">
+        <v>456</v>
+      </c>
+      <c r="D173" s="19" t="s">
+        <v>457</v>
+      </c>
+      <c r="E173" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="F173" s="23"/>
+      <c r="G173" s="23"/>
+      <c r="H173" s="23"/>
+    </row>
+    <row r="174" spans="1:8">
+      <c r="A174" s="22"/>
+      <c r="B174" s="22"/>
+      <c r="C174" s="23" t="s">
+        <v>458</v>
+      </c>
+      <c r="D174" s="19" t="s">
+        <v>459</v>
+      </c>
+      <c r="E174" s="23" t="s">
+        <v>460</v>
+      </c>
+      <c r="F174" s="23"/>
+      <c r="G174" s="23"/>
+      <c r="H174" s="23"/>
+    </row>
+    <row r="175" spans="1:8">
+      <c r="A175" s="22"/>
+      <c r="B175" s="22"/>
+      <c r="C175" s="23" t="s">
+        <v>461</v>
+      </c>
+      <c r="D175" s="19" t="s">
+        <v>462</v>
+      </c>
+      <c r="E175" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="F175" s="23"/>
+      <c r="G175" s="23"/>
+      <c r="H175" s="23"/>
+    </row>
+    <row r="176" spans="1:8">
+      <c r="A176" s="22"/>
+      <c r="B176" s="22"/>
+      <c r="C176" s="23" t="s">
+        <v>463</v>
+      </c>
+      <c r="D176" s="19" t="s">
+        <v>464</v>
+      </c>
+      <c r="E176" s="23" t="s">
+        <v>465</v>
+      </c>
+      <c r="F176" s="23"/>
+      <c r="G176" s="23"/>
+      <c r="H176" s="23"/>
+    </row>
+    <row r="177" spans="1:8">
+      <c r="A177" s="22"/>
+      <c r="B177" s="22"/>
+      <c r="C177" s="23" t="s">
+        <v>466</v>
+      </c>
+      <c r="D177" s="19" t="s">
+        <v>467</v>
+      </c>
+      <c r="E177" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="F177" s="23"/>
+      <c r="G177" s="23"/>
+      <c r="H177" s="23"/>
+    </row>
+    <row r="178" spans="1:8">
+      <c r="A178" s="22"/>
+      <c r="B178" s="22"/>
+      <c r="C178" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="D178" s="19" t="s">
+        <v>468</v>
+      </c>
+      <c r="E178" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="F178" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="G178" s="23"/>
+      <c r="H178" s="23"/>
+    </row>
+    <row r="179" spans="1:8">
+      <c r="A179" s="22"/>
+      <c r="B179" s="22"/>
+      <c r="C179" s="23" t="s">
+        <v>469</v>
+      </c>
+      <c r="D179" s="19" t="s">
+        <v>470</v>
+      </c>
+      <c r="E179" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="F179" s="23"/>
+      <c r="G179" s="23"/>
+      <c r="H179" s="23"/>
+    </row>
+    <row r="180" spans="1:8">
+      <c r="A180" s="22"/>
+      <c r="B180" s="22"/>
+      <c r="C180" s="23" t="s">
+        <v>471</v>
+      </c>
+      <c r="D180" s="19" t="s">
+        <v>472</v>
+      </c>
+      <c r="E180" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="F180" s="23"/>
+      <c r="G180" s="23"/>
+      <c r="H180" s="23"/>
+    </row>
+    <row r="181" spans="1:8">
+      <c r="A181" s="22"/>
+      <c r="B181" s="22"/>
+      <c r="C181" s="23" t="s">
+        <v>305</v>
+      </c>
+      <c r="D181" s="19" t="s">
+        <v>473</v>
+      </c>
+      <c r="E181" s="23" t="s">
+        <v>474</v>
+      </c>
+      <c r="F181" s="23"/>
+      <c r="G181" s="23"/>
+      <c r="H181" s="23"/>
+    </row>
+    <row r="182" spans="1:8">
+      <c r="A182" s="22"/>
+      <c r="B182" s="22"/>
+      <c r="C182" s="23" t="s">
+        <v>475</v>
+      </c>
+      <c r="D182" s="19" t="s">
+        <v>476</v>
+      </c>
+      <c r="E182" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="F182" s="23"/>
+      <c r="G182" s="23"/>
+      <c r="H182" s="23"/>
+    </row>
+    <row r="183" spans="1:8">
+      <c r="A183" s="22"/>
+      <c r="B183" s="22"/>
+      <c r="C183" s="23" t="s">
+        <v>477</v>
+      </c>
+      <c r="D183" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="E183" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="F183" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="G183" s="23"/>
+      <c r="H183" s="23"/>
+    </row>
+    <row r="184" spans="1:8">
+      <c r="A184" s="22"/>
+      <c r="B184" s="22"/>
+      <c r="C184" s="23" t="s">
+        <v>479</v>
+      </c>
+      <c r="D184" s="19" t="s">
+        <v>480</v>
+      </c>
+      <c r="E184" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="F184" s="23"/>
+      <c r="G184" s="23"/>
+      <c r="H184" s="23"/>
+    </row>
+    <row r="185" spans="1:8">
+      <c r="A185" s="22"/>
+      <c r="B185" s="22"/>
+      <c r="C185" s="23" t="s">
+        <v>481</v>
+      </c>
+      <c r="D185" s="19" t="s">
+        <v>482</v>
+      </c>
+      <c r="E185" s="23" t="s">
+        <v>483</v>
+      </c>
+      <c r="F185" s="23"/>
+      <c r="G185" s="23"/>
+      <c r="H185" s="23"/>
+    </row>
+    <row r="186" spans="1:8">
+      <c r="A186" s="22"/>
+      <c r="B186" s="22"/>
+      <c r="C186" s="23" t="s">
+        <v>484</v>
+      </c>
+      <c r="D186" s="23" t="s">
+        <v>485</v>
+      </c>
+      <c r="E186" s="23" t="s">
+        <v>486</v>
+      </c>
+      <c r="F186" s="23"/>
+      <c r="G186" s="23"/>
+      <c r="H186" s="23"/>
+    </row>
+    <row r="187" spans="1:8">
+      <c r="A187" s="22"/>
+      <c r="B187" s="22"/>
+      <c r="C187" s="23" t="s">
         <v>451</v>
       </c>
-      <c r="D173" s="23" t="s">
-        <v>452</v>
-      </c>
-      <c r="E173" s="22" t="s">
-        <v>453</v>
-      </c>
-      <c r="F173" s="22"/>
-      <c r="G173" s="22"/>
-      <c r="H173" s="22"/>
-    </row>
-    <row r="174" spans="1:8">
-      <c r="A174" s="21"/>
-      <c r="B174" s="21"/>
-      <c r="C174" s="22" t="s">
-        <v>454</v>
-      </c>
-      <c r="D174" s="23" t="s">
-        <v>455</v>
-      </c>
-      <c r="E174" s="22" t="s">
-        <v>456</v>
-      </c>
-      <c r="F174" s="22"/>
-      <c r="G174" s="22"/>
-      <c r="H174" s="22"/>
-    </row>
-    <row r="175" spans="1:8">
-      <c r="A175" s="21"/>
-      <c r="B175" s="21"/>
-      <c r="C175" s="22" t="s">
-        <v>457</v>
-      </c>
-      <c r="D175" s="23" t="s">
-        <v>458</v>
-      </c>
-      <c r="E175" s="22" t="s">
-        <v>453</v>
-      </c>
-      <c r="F175" s="22"/>
-      <c r="G175" s="22"/>
-      <c r="H175" s="22"/>
-    </row>
-    <row r="176" spans="1:8">
-      <c r="A176" s="21"/>
-      <c r="B176" s="21"/>
-      <c r="C176" s="22" t="s">
-        <v>459</v>
-      </c>
-      <c r="D176" s="23" t="s">
-        <v>460</v>
-      </c>
-      <c r="E176" s="22" t="s">
-        <v>461</v>
-      </c>
-      <c r="F176" s="22"/>
-      <c r="G176" s="22"/>
-      <c r="H176" s="22"/>
-    </row>
-    <row r="177" spans="1:8">
-      <c r="A177" s="21"/>
-      <c r="B177" s="21"/>
-      <c r="C177" s="22" t="s">
-        <v>462</v>
-      </c>
-      <c r="D177" s="23" t="s">
-        <v>463</v>
-      </c>
-      <c r="E177" s="22" t="s">
-        <v>453</v>
-      </c>
-      <c r="F177" s="22"/>
-      <c r="G177" s="22"/>
-      <c r="H177" s="22"/>
-    </row>
-    <row r="178" spans="1:8">
-      <c r="A178" s="21"/>
-      <c r="B178" s="21"/>
-      <c r="C178" s="22" t="s">
-        <v>288</v>
-      </c>
-      <c r="D178" s="23" t="s">
-        <v>464</v>
-      </c>
-      <c r="E178" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="F178" s="22" t="s">
+      <c r="D187" s="19" t="s">
+        <v>487</v>
+      </c>
+      <c r="E187" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="F187" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="G178" s="22"/>
-      <c r="H178" s="22"/>
-    </row>
-    <row r="179" spans="1:8">
-      <c r="A179" s="21"/>
-      <c r="B179" s="21"/>
-      <c r="C179" s="22" t="s">
-        <v>465</v>
-      </c>
-      <c r="D179" s="23" t="s">
-        <v>466</v>
-      </c>
-      <c r="E179" s="22" t="s">
-        <v>453</v>
-      </c>
-      <c r="F179" s="22"/>
-      <c r="G179" s="22"/>
-      <c r="H179" s="22"/>
-    </row>
-    <row r="180" spans="1:8">
-      <c r="A180" s="21"/>
-      <c r="B180" s="21"/>
-      <c r="C180" s="22" t="s">
-        <v>467</v>
-      </c>
-      <c r="D180" s="23" t="s">
-        <v>468</v>
-      </c>
-      <c r="E180" s="22" t="s">
-        <v>450</v>
-      </c>
-      <c r="F180" s="22"/>
-      <c r="G180" s="22"/>
-      <c r="H180" s="22"/>
-    </row>
-    <row r="181" spans="1:8">
-      <c r="A181" s="21"/>
-      <c r="B181" s="21"/>
-      <c r="C181" s="22" t="s">
-        <v>299</v>
-      </c>
-      <c r="D181" s="23" t="s">
-        <v>469</v>
-      </c>
-      <c r="E181" s="22" t="s">
-        <v>470</v>
-      </c>
-      <c r="F181" s="22"/>
-      <c r="G181" s="22"/>
-      <c r="H181" s="22"/>
-    </row>
-    <row r="182" spans="1:8">
-      <c r="A182" s="21"/>
-      <c r="B182" s="21"/>
-      <c r="C182" s="22" t="s">
-        <v>471</v>
-      </c>
-      <c r="D182" s="23" t="s">
-        <v>472</v>
-      </c>
-      <c r="E182" s="22" t="s">
-        <v>450</v>
-      </c>
-      <c r="F182" s="22"/>
-      <c r="G182" s="22"/>
-      <c r="H182" s="22"/>
-    </row>
-    <row r="183" spans="1:8">
-      <c r="A183" s="21"/>
-      <c r="B183" s="21"/>
-      <c r="C183" s="22" t="s">
-        <v>473</v>
-      </c>
-      <c r="D183" s="23" t="s">
-        <v>474</v>
-      </c>
-      <c r="E183" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="F183" s="22" t="s">
+      <c r="G187" s="23"/>
+      <c r="H187" s="23"/>
+    </row>
+    <row r="188" spans="1:8">
+      <c r="A188" s="22"/>
+      <c r="B188" s="22" t="s">
+        <v>488</v>
+      </c>
+      <c r="C188" s="23" t="s">
+        <v>489</v>
+      </c>
+      <c r="D188" s="23" t="s">
+        <v>490</v>
+      </c>
+      <c r="E188" s="23" t="s">
+        <v>491</v>
+      </c>
+      <c r="F188" s="23"/>
+      <c r="G188" s="23"/>
+      <c r="H188" s="23"/>
+    </row>
+    <row r="189" spans="1:8">
+      <c r="A189" s="22"/>
+      <c r="B189" s="22"/>
+      <c r="C189" s="23" t="s">
+        <v>492</v>
+      </c>
+      <c r="D189" s="19" t="s">
+        <v>493</v>
+      </c>
+      <c r="E189" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="F189" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="G189" s="23"/>
+      <c r="H189" s="23"/>
+    </row>
+    <row r="190" spans="1:8">
+      <c r="A190" s="22"/>
+      <c r="B190" s="22"/>
+      <c r="C190" s="23" t="s">
+        <v>494</v>
+      </c>
+      <c r="D190" s="19" t="s">
+        <v>495</v>
+      </c>
+      <c r="E190" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="F190" s="23"/>
+      <c r="G190" s="23"/>
+      <c r="H190" s="23"/>
+    </row>
+    <row r="191" spans="1:8">
+      <c r="A191" s="22"/>
+      <c r="B191" s="22"/>
+      <c r="C191" s="23" t="s">
+        <v>496</v>
+      </c>
+      <c r="D191" s="23" t="s">
+        <v>497</v>
+      </c>
+      <c r="E191" s="23" t="s">
+        <v>498</v>
+      </c>
+      <c r="F191" s="23"/>
+      <c r="G191" s="23"/>
+      <c r="H191" s="23"/>
+    </row>
+    <row r="192" spans="1:8">
+      <c r="A192" s="22"/>
+      <c r="B192" s="22"/>
+      <c r="C192" s="23" t="s">
+        <v>499</v>
+      </c>
+      <c r="D192" s="23" t="s">
+        <v>500</v>
+      </c>
+      <c r="E192" s="23" t="s">
+        <v>501</v>
+      </c>
+      <c r="F192" s="23"/>
+      <c r="G192" s="23"/>
+      <c r="H192" s="23"/>
+    </row>
+    <row r="193" spans="1:8">
+      <c r="A193" s="22"/>
+      <c r="B193" s="22"/>
+      <c r="C193" s="23" t="s">
+        <v>502</v>
+      </c>
+      <c r="D193" s="19" t="s">
+        <v>503</v>
+      </c>
+      <c r="E193" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="F193" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="G183" s="22"/>
-      <c r="H183" s="22"/>
-    </row>
-    <row r="184" spans="1:8">
-      <c r="A184" s="21"/>
-      <c r="B184" s="21"/>
-      <c r="C184" s="22" t="s">
-        <v>475</v>
-      </c>
-      <c r="D184" s="23" t="s">
-        <v>476</v>
-      </c>
-      <c r="E184" s="22" t="s">
+      <c r="G193" s="23"/>
+      <c r="H193" s="23"/>
+    </row>
+    <row r="194" spans="1:8">
+      <c r="A194" s="22"/>
+      <c r="B194" s="22"/>
+      <c r="C194" s="23" t="s">
+        <v>504</v>
+      </c>
+      <c r="D194" s="19" t="s">
+        <v>505</v>
+      </c>
+      <c r="E194" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="F194" s="23"/>
+      <c r="G194" s="23"/>
+      <c r="H194" s="23"/>
+    </row>
+    <row r="195" spans="1:8">
+      <c r="A195" s="22"/>
+      <c r="B195" s="22"/>
+      <c r="C195" s="23" t="s">
+        <v>506</v>
+      </c>
+      <c r="D195" s="19" t="s">
+        <v>507</v>
+      </c>
+      <c r="E195" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="F195" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="G195" s="23"/>
+      <c r="H195" s="23"/>
+    </row>
+    <row r="196" spans="1:8">
+      <c r="A196" s="22"/>
+      <c r="B196" s="22"/>
+      <c r="C196" s="23" t="s">
+        <v>508</v>
+      </c>
+      <c r="D196" s="19" t="s">
+        <v>509</v>
+      </c>
+      <c r="E196" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="F196" s="23"/>
+      <c r="G196" s="23"/>
+      <c r="H196" s="23"/>
+    </row>
+    <row r="197" spans="1:8">
+      <c r="A197" s="22"/>
+      <c r="B197" s="22"/>
+      <c r="C197" s="23" t="s">
+        <v>510</v>
+      </c>
+      <c r="D197" s="19" t="s">
+        <v>511</v>
+      </c>
+      <c r="E197" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="F197" s="23"/>
+      <c r="G197" s="23"/>
+      <c r="H197" s="23"/>
+    </row>
+    <row r="198" spans="1:8">
+      <c r="A198" s="22"/>
+      <c r="B198" s="22"/>
+      <c r="C198" s="23" t="s">
+        <v>484</v>
+      </c>
+      <c r="D198" s="19" t="s">
+        <v>512</v>
+      </c>
+      <c r="E198" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="F198" s="23"/>
+      <c r="G198" s="23"/>
+      <c r="H198" s="23"/>
+    </row>
+    <row r="199" spans="1:8">
+      <c r="A199" s="22"/>
+      <c r="B199" s="22"/>
+      <c r="C199" s="23" t="s">
+        <v>513</v>
+      </c>
+      <c r="D199" s="19" t="s">
+        <v>514</v>
+      </c>
+      <c r="E199" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="F199" s="23"/>
+      <c r="G199" s="23"/>
+      <c r="H199" s="23"/>
+    </row>
+    <row r="200" spans="1:8">
+      <c r="A200" s="22"/>
+      <c r="B200" s="22"/>
+      <c r="C200" s="23" t="s">
+        <v>515</v>
+      </c>
+      <c r="D200" s="23" t="s">
+        <v>516</v>
+      </c>
+      <c r="E200" s="23" t="s">
+        <v>517</v>
+      </c>
+      <c r="F200" s="23"/>
+      <c r="G200" s="23"/>
+      <c r="H200" s="23"/>
+    </row>
+    <row r="201" spans="1:8">
+      <c r="A201" s="22"/>
+      <c r="B201" s="22"/>
+      <c r="C201" s="23" t="s">
+        <v>518</v>
+      </c>
+      <c r="D201" s="19" t="s">
+        <v>519</v>
+      </c>
+      <c r="E201" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="F201" s="23"/>
+      <c r="G201" s="23"/>
+      <c r="H201" s="23"/>
+    </row>
+    <row r="202" spans="1:8">
+      <c r="A202" s="22"/>
+      <c r="B202" s="22"/>
+      <c r="C202" s="23" t="s">
+        <v>520</v>
+      </c>
+      <c r="D202" s="23" t="s">
+        <v>521</v>
+      </c>
+      <c r="E202" s="23" t="s">
+        <v>522</v>
+      </c>
+      <c r="F202" s="23"/>
+      <c r="G202" s="23"/>
+      <c r="H202" s="23"/>
+    </row>
+    <row r="203" spans="1:8">
+      <c r="A203" s="22"/>
+      <c r="B203" s="22"/>
+      <c r="C203" s="23" t="s">
+        <v>328</v>
+      </c>
+      <c r="D203" s="19" t="s">
+        <v>523</v>
+      </c>
+      <c r="E203" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="F203" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="G203" s="23"/>
+      <c r="H203" s="23"/>
+    </row>
+    <row r="204" spans="1:8">
+      <c r="A204" s="22"/>
+      <c r="B204" s="22"/>
+      <c r="C204" s="23" t="s">
+        <v>524</v>
+      </c>
+      <c r="D204" s="19" t="s">
+        <v>525</v>
+      </c>
+      <c r="E204" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="F204" s="23"/>
+      <c r="G204" s="23"/>
+      <c r="H204" s="23"/>
+    </row>
+    <row r="205" spans="1:8">
+      <c r="A205" s="22"/>
+      <c r="B205" s="22"/>
+      <c r="C205" s="23" t="s">
+        <v>526</v>
+      </c>
+      <c r="D205" s="19" t="s">
+        <v>527</v>
+      </c>
+      <c r="E205" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="F184" s="22"/>
-      <c r="G184" s="22"/>
-      <c r="H184" s="22"/>
-    </row>
-    <row r="185" spans="1:8">
-      <c r="A185" s="21"/>
-      <c r="B185" s="21"/>
-      <c r="C185" s="22" t="s">
-        <v>477</v>
-      </c>
-      <c r="D185" s="23" t="s">
-        <v>478</v>
-      </c>
-      <c r="E185" s="22" t="s">
-        <v>479</v>
-      </c>
-      <c r="F185" s="22"/>
-      <c r="G185" s="22"/>
-      <c r="H185" s="22"/>
-    </row>
-    <row r="186" spans="1:8">
-      <c r="A186" s="21"/>
-      <c r="B186" s="21"/>
-      <c r="C186" s="22" t="s">
-        <v>480</v>
-      </c>
-      <c r="D186" s="22" t="s">
-        <v>481</v>
-      </c>
-      <c r="E186" s="22" t="s">
-        <v>482</v>
-      </c>
-      <c r="F186" s="22"/>
-      <c r="G186" s="22"/>
-      <c r="H186" s="22"/>
-    </row>
-    <row r="187" spans="1:8">
-      <c r="A187" s="21"/>
-      <c r="B187" s="21"/>
-      <c r="C187" s="22" t="s">
-        <v>445</v>
-      </c>
-      <c r="D187" s="23" t="s">
-        <v>483</v>
-      </c>
-      <c r="E187" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="F187" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="G187" s="22"/>
-      <c r="H187" s="22"/>
-    </row>
-    <row r="188" spans="1:8">
-      <c r="A188" s="21"/>
-      <c r="B188" s="21" t="s">
-        <v>484</v>
-      </c>
-      <c r="C188" s="22" t="s">
-        <v>485</v>
-      </c>
-      <c r="D188" s="22" t="s">
-        <v>486</v>
-      </c>
-      <c r="E188" s="22" t="s">
-        <v>487</v>
-      </c>
-      <c r="F188" s="22"/>
-      <c r="G188" s="22"/>
-      <c r="H188" s="22"/>
-    </row>
-    <row r="189" spans="1:8">
-      <c r="A189" s="21"/>
-      <c r="B189" s="21"/>
-      <c r="C189" s="22" t="s">
-        <v>488</v>
-      </c>
-      <c r="D189" s="23" t="s">
-        <v>489</v>
-      </c>
-      <c r="E189" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="F189" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="G189" s="22"/>
-      <c r="H189" s="22"/>
-    </row>
-    <row r="190" spans="1:8">
-      <c r="A190" s="21"/>
-      <c r="B190" s="21"/>
-      <c r="C190" s="22" t="s">
-        <v>490</v>
-      </c>
-      <c r="D190" s="23" t="s">
-        <v>491</v>
-      </c>
-      <c r="E190" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="F190" s="22"/>
-      <c r="G190" s="22"/>
-      <c r="H190" s="22"/>
-    </row>
-    <row r="191" spans="1:8">
-      <c r="A191" s="21"/>
-      <c r="B191" s="21"/>
-      <c r="C191" s="22" t="s">
-        <v>492</v>
-      </c>
-      <c r="D191" s="22" t="s">
-        <v>493</v>
-      </c>
-      <c r="E191" s="22" t="s">
-        <v>494</v>
-      </c>
-      <c r="F191" s="22"/>
-      <c r="G191" s="22"/>
-      <c r="H191" s="22"/>
-    </row>
-    <row r="192" spans="1:8">
-      <c r="A192" s="21"/>
-      <c r="B192" s="21"/>
-      <c r="C192" s="22" t="s">
-        <v>495</v>
-      </c>
-      <c r="D192" s="22" t="s">
-        <v>496</v>
-      </c>
-      <c r="E192" s="22" t="s">
-        <v>497</v>
-      </c>
-      <c r="F192" s="22"/>
-      <c r="G192" s="22"/>
-      <c r="H192" s="22"/>
-    </row>
-    <row r="193" spans="1:8">
-      <c r="A193" s="21"/>
-      <c r="B193" s="21"/>
-      <c r="C193" s="22" t="s">
-        <v>498</v>
-      </c>
-      <c r="D193" s="23" t="s">
-        <v>499</v>
-      </c>
-      <c r="E193" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="F193" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="G193" s="22"/>
-      <c r="H193" s="22"/>
-    </row>
-    <row r="194" spans="1:8">
-      <c r="A194" s="21"/>
-      <c r="B194" s="21"/>
-      <c r="C194" s="22" t="s">
-        <v>500</v>
-      </c>
-      <c r="D194" s="23" t="s">
-        <v>501</v>
-      </c>
-      <c r="E194" s="22" t="s">
-        <v>453</v>
-      </c>
-      <c r="F194" s="22"/>
-      <c r="G194" s="22"/>
-      <c r="H194" s="22"/>
-    </row>
-    <row r="195" spans="1:8">
-      <c r="A195" s="21"/>
-      <c r="B195" s="21"/>
-      <c r="C195" s="22" t="s">
-        <v>502</v>
-      </c>
-      <c r="D195" s="23" t="s">
-        <v>503</v>
-      </c>
-      <c r="E195" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="F195" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="G195" s="22"/>
-      <c r="H195" s="22"/>
-    </row>
-    <row r="196" spans="1:8">
-      <c r="A196" s="21"/>
-      <c r="B196" s="21"/>
-      <c r="C196" s="22" t="s">
-        <v>504</v>
-      </c>
-      <c r="D196" s="23" t="s">
-        <v>505</v>
-      </c>
-      <c r="E196" s="22" t="s">
-        <v>453</v>
-      </c>
-      <c r="F196" s="22"/>
-      <c r="G196" s="22"/>
-      <c r="H196" s="22"/>
-    </row>
-    <row r="197" spans="1:8">
-      <c r="A197" s="21"/>
-      <c r="B197" s="21"/>
-      <c r="C197" s="22" t="s">
-        <v>506</v>
-      </c>
-      <c r="D197" s="23" t="s">
-        <v>507</v>
-      </c>
-      <c r="E197" s="22" t="s">
-        <v>453</v>
-      </c>
-      <c r="F197" s="22"/>
-      <c r="G197" s="22"/>
-      <c r="H197" s="22"/>
-    </row>
-    <row r="198" spans="1:8">
-      <c r="A198" s="21"/>
-      <c r="B198" s="21"/>
-      <c r="C198" s="22" t="s">
-        <v>480</v>
-      </c>
-      <c r="D198" s="23" t="s">
-        <v>508</v>
-      </c>
-      <c r="E198" s="22" t="s">
-        <v>453</v>
-      </c>
-      <c r="F198" s="22"/>
-      <c r="G198" s="22"/>
-      <c r="H198" s="22"/>
-    </row>
-    <row r="199" spans="1:8">
-      <c r="A199" s="21"/>
-      <c r="B199" s="21"/>
-      <c r="C199" s="22" t="s">
-        <v>509</v>
-      </c>
-      <c r="D199" s="23" t="s">
-        <v>510</v>
-      </c>
-      <c r="E199" s="22" t="s">
-        <v>453</v>
-      </c>
-      <c r="F199" s="22"/>
-      <c r="G199" s="22"/>
-      <c r="H199" s="22"/>
-    </row>
-    <row r="200" spans="1:8">
-      <c r="A200" s="21"/>
-      <c r="B200" s="21"/>
-      <c r="C200" s="22" t="s">
-        <v>511</v>
-      </c>
-      <c r="D200" s="22" t="s">
-        <v>512</v>
-      </c>
-      <c r="E200" s="22" t="s">
-        <v>513</v>
-      </c>
-      <c r="F200" s="22"/>
-      <c r="G200" s="22"/>
-      <c r="H200" s="22"/>
-    </row>
-    <row r="201" spans="1:8">
-      <c r="A201" s="21"/>
-      <c r="B201" s="21"/>
-      <c r="C201" s="22" t="s">
-        <v>514</v>
-      </c>
-      <c r="D201" s="23" t="s">
-        <v>515</v>
-      </c>
-      <c r="E201" s="22" t="s">
-        <v>453</v>
-      </c>
-      <c r="F201" s="22"/>
-      <c r="G201" s="22"/>
-      <c r="H201" s="22"/>
-    </row>
-    <row r="202" spans="1:8">
-      <c r="A202" s="21"/>
-      <c r="B202" s="21"/>
-      <c r="C202" s="22" t="s">
-        <v>516</v>
-      </c>
-      <c r="D202" s="22" t="s">
-        <v>517</v>
-      </c>
-      <c r="E202" s="22" t="s">
-        <v>518</v>
-      </c>
-      <c r="F202" s="22"/>
-      <c r="G202" s="22"/>
-      <c r="H202" s="22"/>
-    </row>
-    <row r="203" spans="1:8">
-      <c r="A203" s="21"/>
-      <c r="B203" s="21"/>
-      <c r="C203" s="22" t="s">
-        <v>322</v>
-      </c>
-      <c r="D203" s="23" t="s">
-        <v>519</v>
-      </c>
-      <c r="E203" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="F203" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="G203" s="22"/>
-      <c r="H203" s="22"/>
-    </row>
-    <row r="204" spans="1:8">
-      <c r="A204" s="21"/>
-      <c r="B204" s="21"/>
-      <c r="C204" s="22" t="s">
-        <v>520</v>
-      </c>
-      <c r="D204" s="23" t="s">
-        <v>521</v>
-      </c>
-      <c r="E204" s="22" t="s">
-        <v>453</v>
-      </c>
-      <c r="F204" s="22"/>
-      <c r="G204" s="22"/>
-      <c r="H204" s="22"/>
-    </row>
-    <row r="205" spans="1:8">
-      <c r="A205" s="21"/>
-      <c r="B205" s="21"/>
-      <c r="C205" s="22" t="s">
-        <v>522</v>
-      </c>
-      <c r="D205" s="23" t="s">
-        <v>523</v>
-      </c>
-      <c r="E205" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="F205" s="22"/>
-      <c r="G205" s="22"/>
-      <c r="H205" s="22"/>
+      <c r="F205" s="23"/>
+      <c r="G205" s="23"/>
+      <c r="H205" s="23"/>
     </row>
     <row r="206" spans="1:8">
       <c r="B206" s="8"/>
@@ -7276,17 +7355,17 @@
     </row>
     <row r="207" spans="1:8">
       <c r="A207" s="24" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B207" s="25"/>
       <c r="C207" s="25" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="D207" s="25" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="E207" s="25" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="F207" s="25"/>
       <c r="G207" s="25"/>
@@ -7296,13 +7375,13 @@
       <c r="A208" s="24"/>
       <c r="B208" s="25"/>
       <c r="C208" s="25" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="D208" s="25" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="E208" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F208" s="25"/>
       <c r="G208" s="25"/>
@@ -7312,13 +7391,13 @@
       <c r="A209" s="24"/>
       <c r="B209" s="25"/>
       <c r="C209" s="25" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D209" s="25" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="E209" s="25" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="F209" s="25"/>
       <c r="G209" s="25"/>
@@ -7328,13 +7407,13 @@
       <c r="A210" s="24"/>
       <c r="B210" s="25"/>
       <c r="C210" s="25" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="D210" s="25" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="E210" s="25" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="F210" s="25"/>
       <c r="G210" s="25"/>
@@ -7344,13 +7423,13 @@
       <c r="A211" s="24"/>
       <c r="B211" s="25"/>
       <c r="C211" s="25" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D211" s="25" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="E211" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F211" s="25"/>
       <c r="G211" s="25"/>
@@ -7360,13 +7439,13 @@
       <c r="A212" s="24"/>
       <c r="B212" s="25"/>
       <c r="C212" s="25" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="D212" s="25" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="E212" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F212" s="25"/>
       <c r="G212" s="25"/>
@@ -7376,13 +7455,13 @@
       <c r="A213" s="24"/>
       <c r="B213" s="25"/>
       <c r="C213" s="25" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="D213" s="25" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="E213" s="25" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="F213" s="25"/>
       <c r="G213" s="25"/>
@@ -7392,13 +7471,13 @@
       <c r="A214" s="24"/>
       <c r="B214" s="25"/>
       <c r="C214" s="25" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="D214" s="25" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="E214" s="25" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="F214" s="25"/>
       <c r="G214" s="25"/>
@@ -7408,13 +7487,13 @@
       <c r="A215" s="24"/>
       <c r="B215" s="25"/>
       <c r="C215" s="25" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="D215" s="25" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="E215" s="25" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="F215" s="25"/>
       <c r="G215" s="25"/>
@@ -7424,13 +7503,13 @@
       <c r="A216" s="24"/>
       <c r="B216" s="25"/>
       <c r="C216" s="25" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="D216" s="25" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="E216" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F216" s="25"/>
       <c r="G216" s="25"/>
@@ -7440,13 +7519,13 @@
       <c r="A217" s="24"/>
       <c r="B217" s="25"/>
       <c r="C217" s="25" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="D217" s="25" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="E217" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F217" s="25"/>
       <c r="G217" s="25"/>
@@ -7456,13 +7535,13 @@
       <c r="A218" s="24"/>
       <c r="B218" s="25"/>
       <c r="C218" s="25" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="D218" s="25" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="E218" s="25" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="F218" s="25"/>
       <c r="G218" s="25"/>
@@ -7472,13 +7551,13 @@
       <c r="A219" s="24"/>
       <c r="B219" s="25"/>
       <c r="C219" s="25" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="D219" s="25" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="E219" s="25" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="F219" s="25"/>
       <c r="G219" s="25"/>
@@ -7488,13 +7567,13 @@
       <c r="A220" s="24"/>
       <c r="B220" s="25"/>
       <c r="C220" s="25" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="D220" s="25" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="E220" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F220" s="25"/>
       <c r="G220" s="25"/>
@@ -7504,13 +7583,13 @@
       <c r="A221" s="24"/>
       <c r="B221" s="25"/>
       <c r="C221" s="25" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="D221" s="25" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="E221" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F221" s="25"/>
       <c r="G221" s="25"/>
@@ -7520,13 +7599,13 @@
       <c r="A222" s="24"/>
       <c r="B222" s="25"/>
       <c r="C222" s="25" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="D222" s="25" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="E222" s="25" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F222" s="25"/>
       <c r="G222" s="25"/>
@@ -7536,13 +7615,13 @@
       <c r="A223" s="24"/>
       <c r="B223" s="25"/>
       <c r="C223" s="25" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="D223" s="25" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="E223" s="25" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F223" s="25"/>
       <c r="G223" s="25"/>
@@ -7552,13 +7631,13 @@
       <c r="A224" s="24"/>
       <c r="B224" s="25"/>
       <c r="C224" s="25" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="D224" s="25" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="E224" s="25" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="F224" s="25"/>
       <c r="G224" s="25"/>
@@ -7568,13 +7647,13 @@
       <c r="A225" s="24"/>
       <c r="B225" s="25"/>
       <c r="C225" s="25" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="D225" s="25" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="E225" s="25" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="F225" s="25"/>
       <c r="G225" s="25"/>
@@ -7584,13 +7663,13 @@
       <c r="A226" s="24"/>
       <c r="B226" s="25"/>
       <c r="C226" s="25" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="D226" s="25" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="E226" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F226" s="25"/>
       <c r="G226" s="25"/>
@@ -7600,13 +7679,13 @@
       <c r="A227" s="24"/>
       <c r="B227" s="25"/>
       <c r="C227" s="25" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="D227" s="25" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="E227" s="25" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="F227" s="25"/>
       <c r="G227" s="25"/>
@@ -7616,13 +7695,13 @@
       <c r="A228" s="24"/>
       <c r="B228" s="25"/>
       <c r="C228" s="25" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="D228" s="25" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="E228" s="25" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="F228" s="25"/>
       <c r="G228" s="25"/>
@@ -7632,13 +7711,13 @@
       <c r="A229" s="24"/>
       <c r="B229" s="25"/>
       <c r="C229" s="25" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="D229" s="25" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="E229" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F229" s="25"/>
       <c r="G229" s="25"/>
@@ -7648,13 +7727,13 @@
       <c r="A230" s="24"/>
       <c r="B230" s="25"/>
       <c r="C230" s="25" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="D230" s="25" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="E230" s="25" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="F230" s="25"/>
       <c r="G230" s="25"/>
@@ -7664,13 +7743,13 @@
       <c r="A231" s="24"/>
       <c r="B231" s="25"/>
       <c r="C231" s="25" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="D231" s="25" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="E231" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F231" s="25"/>
       <c r="G231" s="25"/>
@@ -7680,13 +7759,13 @@
       <c r="A232" s="24"/>
       <c r="B232" s="25"/>
       <c r="C232" s="25" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="D232" s="25" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="E232" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F232" s="25"/>
       <c r="G232" s="25"/>
@@ -7696,13 +7775,13 @@
       <c r="A233" s="24"/>
       <c r="B233" s="25"/>
       <c r="C233" s="25" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="D233" s="25" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="E233" s="25" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="F233" s="25"/>
       <c r="G233" s="25"/>
@@ -7712,13 +7791,13 @@
       <c r="A234" s="24"/>
       <c r="B234" s="25"/>
       <c r="C234" s="25" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="D234" s="25" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="E234" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F234" s="25"/>
       <c r="G234" s="25"/>
@@ -7728,13 +7807,13 @@
       <c r="A235" s="24"/>
       <c r="B235" s="25"/>
       <c r="C235" s="25" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="D235" s="25" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="E235" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F235" s="25"/>
       <c r="G235" s="25"/>
@@ -7744,13 +7823,13 @@
       <c r="A236" s="24"/>
       <c r="B236" s="25"/>
       <c r="C236" s="25" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="D236" s="25" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="E236" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F236" s="25"/>
       <c r="G236" s="25"/>
@@ -7760,13 +7839,13 @@
       <c r="A237" s="24"/>
       <c r="B237" s="25"/>
       <c r="C237" s="25" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="D237" s="25" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="E237" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F237" s="25"/>
       <c r="G237" s="25"/>
@@ -7776,13 +7855,13 @@
       <c r="A238" s="24"/>
       <c r="B238" s="25"/>
       <c r="C238" s="25" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="D238" s="25" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="E238" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F238" s="25"/>
       <c r="G238" s="25"/>
@@ -7792,13 +7871,13 @@
       <c r="A239" s="24"/>
       <c r="B239" s="25"/>
       <c r="C239" s="25" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="D239" s="25" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="E239" s="25" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="F239" s="25"/>
       <c r="G239" s="25"/>
@@ -7808,13 +7887,13 @@
       <c r="A240" s="24"/>
       <c r="B240" s="25"/>
       <c r="C240" s="25" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="D240" s="25" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="E240" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F240" s="25"/>
       <c r="G240" s="25"/>
@@ -7824,13 +7903,13 @@
       <c r="A241" s="24"/>
       <c r="B241" s="25"/>
       <c r="C241" s="25" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="D241" s="25" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="E241" s="25" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="F241" s="25"/>
       <c r="G241" s="25"/>
@@ -7840,13 +7919,13 @@
       <c r="A242" s="24"/>
       <c r="B242" s="25"/>
       <c r="C242" s="25" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="D242" s="25" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="E242" s="25" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="F242" s="25"/>
       <c r="G242" s="25"/>
@@ -7856,13 +7935,13 @@
       <c r="A243" s="24"/>
       <c r="B243" s="25"/>
       <c r="C243" s="25" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="D243" s="25" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="E243" s="25" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="F243" s="25"/>
       <c r="G243" s="25"/>
@@ -7872,13 +7951,13 @@
       <c r="A244" s="24"/>
       <c r="B244" s="25"/>
       <c r="C244" s="25" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="D244" s="25" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="E244" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F244" s="25"/>
       <c r="G244" s="25"/>
@@ -7888,13 +7967,13 @@
       <c r="A245" s="24"/>
       <c r="B245" s="25"/>
       <c r="C245" s="25" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D245" s="25" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E245" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F245" s="25"/>
       <c r="G245" s="25"/>
@@ -7904,13 +7983,13 @@
       <c r="A246" s="24"/>
       <c r="B246" s="25"/>
       <c r="C246" s="25" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D246" s="25" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="E246" s="25" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="F246" s="25"/>
       <c r="G246" s="25"/>
@@ -7920,13 +7999,13 @@
       <c r="A247" s="24"/>
       <c r="B247" s="25"/>
       <c r="C247" s="25" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D247" s="25" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="E247" s="25" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="F247" s="25"/>
       <c r="G247" s="25"/>
@@ -7936,13 +8015,13 @@
       <c r="A248" s="24"/>
       <c r="B248" s="25"/>
       <c r="C248" s="25" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D248" s="25" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="E248" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F248" s="25"/>
       <c r="G248" s="25"/>
@@ -7952,13 +8031,13 @@
       <c r="A249" s="24"/>
       <c r="B249" s="25"/>
       <c r="C249" s="25" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D249" s="25" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="E249" s="25" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="F249" s="25"/>
       <c r="G249" s="25"/>
@@ -7968,13 +8047,13 @@
       <c r="A250" s="24"/>
       <c r="B250" s="25"/>
       <c r="C250" s="25" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="D250" s="25" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="E250" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F250" s="25"/>
       <c r="G250" s="25"/>
@@ -7984,13 +8063,13 @@
       <c r="A251" s="24"/>
       <c r="B251" s="25"/>
       <c r="C251" s="25" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="D251" s="25" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="E251" s="25" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="F251" s="25"/>
       <c r="G251" s="25"/>
@@ -8000,13 +8079,13 @@
       <c r="A252" s="24"/>
       <c r="B252" s="25"/>
       <c r="C252" s="25" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="D252" s="25" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="E252" s="25" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="F252" s="25"/>
       <c r="G252" s="25"/>
@@ -8016,13 +8095,13 @@
       <c r="A253" s="24"/>
       <c r="B253" s="25"/>
       <c r="C253" s="25" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="D253" s="25" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="E253" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F253" s="25"/>
       <c r="G253" s="25"/>
@@ -8032,13 +8111,13 @@
       <c r="A254" s="24"/>
       <c r="B254" s="25"/>
       <c r="C254" s="25" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="D254" s="25" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="E254" s="25" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="F254" s="25"/>
       <c r="G254" s="25"/>
@@ -8048,13 +8127,13 @@
       <c r="A255" s="24"/>
       <c r="B255" s="25"/>
       <c r="C255" s="25" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="D255" s="25" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="E255" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F255" s="25"/>
       <c r="G255" s="25"/>
@@ -8064,13 +8143,13 @@
       <c r="A256" s="24"/>
       <c r="B256" s="25"/>
       <c r="C256" s="25" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="D256" s="25" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="E256" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F256" s="25"/>
       <c r="G256" s="25"/>
@@ -8080,13 +8159,13 @@
       <c r="A257" s="24"/>
       <c r="B257" s="25"/>
       <c r="C257" s="25" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="D257" s="25" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="E257" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F257" s="25"/>
       <c r="G257" s="25"/>
@@ -8096,13 +8175,13 @@
       <c r="A258" s="24"/>
       <c r="B258" s="25"/>
       <c r="C258" s="25" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="D258" s="25" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="E258" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F258" s="25"/>
       <c r="G258" s="25"/>
@@ -8112,13 +8191,13 @@
       <c r="A259" s="24"/>
       <c r="B259" s="25"/>
       <c r="C259" s="25" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="D259" s="25" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="E259" s="25" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="F259" s="25"/>
       <c r="G259" s="25"/>
@@ -8128,13 +8207,13 @@
       <c r="A260" s="24"/>
       <c r="B260" s="25"/>
       <c r="C260" s="25" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="D260" s="25" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="E260" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F260" s="25"/>
       <c r="G260" s="25"/>
@@ -8144,13 +8223,13 @@
       <c r="A261" s="24"/>
       <c r="B261" s="25"/>
       <c r="C261" s="25" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="D261" s="25" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="E261" s="25" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="F261" s="25"/>
       <c r="G261" s="25"/>
@@ -8160,13 +8239,13 @@
       <c r="A262" s="24"/>
       <c r="B262" s="25"/>
       <c r="C262" s="25" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="D262" s="25" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="E262" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F262" s="25"/>
       <c r="G262" s="25"/>
@@ -8176,13 +8255,13 @@
       <c r="A263" s="24"/>
       <c r="B263" s="25"/>
       <c r="C263" s="25" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="D263" s="25" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="E263" s="25" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="F263" s="25"/>
       <c r="G263" s="25"/>
@@ -8192,13 +8271,13 @@
       <c r="A264" s="24"/>
       <c r="B264" s="25"/>
       <c r="C264" s="25" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="D264" s="25" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="E264" s="25" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="F264" s="25"/>
       <c r="G264" s="25"/>
@@ -8208,13 +8287,13 @@
       <c r="A265" s="24"/>
       <c r="B265" s="25"/>
       <c r="C265" s="25" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="D265" s="25" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="E265" s="25" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="F265" s="25"/>
       <c r="G265" s="25"/>
@@ -8224,13 +8303,13 @@
       <c r="A266" s="24"/>
       <c r="B266" s="25"/>
       <c r="C266" s="25" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="D266" s="25" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="E266" s="25" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="F266" s="25"/>
       <c r="G266" s="25"/>
@@ -8240,13 +8319,13 @@
       <c r="A267" s="24"/>
       <c r="B267" s="25"/>
       <c r="C267" s="25" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="D267" s="25" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="E267" s="25" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="F267" s="25"/>
       <c r="G267" s="25"/>
@@ -8256,13 +8335,13 @@
       <c r="A268" s="24"/>
       <c r="B268" s="25"/>
       <c r="C268" s="25" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="D268" s="25" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="E268" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F268" s="25"/>
       <c r="G268" s="25"/>
@@ -8272,13 +8351,13 @@
       <c r="A269" s="24"/>
       <c r="B269" s="25"/>
       <c r="C269" s="25" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="D269" s="25" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="E269" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F269" s="25"/>
       <c r="G269" s="25"/>
@@ -8288,13 +8367,13 @@
       <c r="A270" s="24"/>
       <c r="B270" s="25"/>
       <c r="C270" s="25" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="D270" s="25" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E270" s="25" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="F270" s="25"/>
       <c r="G270" s="25"/>
@@ -8304,13 +8383,13 @@
       <c r="A271" s="24"/>
       <c r="B271" s="25"/>
       <c r="C271" s="25" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="D271" s="25" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="E271" s="25" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="F271" s="25"/>
       <c r="G271" s="25"/>
@@ -8320,13 +8399,13 @@
       <c r="A272" s="24"/>
       <c r="B272" s="25"/>
       <c r="C272" s="25" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="D272" s="25" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="E272" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F272" s="25"/>
       <c r="G272" s="25"/>
@@ -8336,13 +8415,13 @@
       <c r="A273" s="24"/>
       <c r="B273" s="25"/>
       <c r="C273" s="25" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="D273" s="25" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="E273" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F273" s="25"/>
       <c r="G273" s="25"/>
@@ -8352,13 +8431,13 @@
       <c r="A274" s="24"/>
       <c r="B274" s="25"/>
       <c r="C274" s="25" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="D274" s="25" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="E274" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F274" s="25"/>
       <c r="G274" s="25"/>
@@ -8368,13 +8447,13 @@
       <c r="A275" s="24"/>
       <c r="B275" s="25"/>
       <c r="C275" s="25" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="D275" s="25" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="E275" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F275" s="25"/>
       <c r="G275" s="25"/>
@@ -8384,13 +8463,13 @@
       <c r="A276" s="24"/>
       <c r="B276" s="25"/>
       <c r="C276" s="25" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="D276" s="25" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="E276" s="25" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="F276" s="25"/>
       <c r="G276" s="25"/>
@@ -8400,13 +8479,13 @@
       <c r="A277" s="24"/>
       <c r="B277" s="25"/>
       <c r="C277" s="25" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="D277" s="25" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="E277" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F277" s="25"/>
       <c r="G277" s="25"/>
@@ -8416,13 +8495,13 @@
       <c r="A278" s="24"/>
       <c r="B278" s="25"/>
       <c r="C278" s="25" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="D278" s="25" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="E278" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F278" s="25"/>
       <c r="G278" s="25"/>
@@ -8432,13 +8511,13 @@
       <c r="A279" s="24"/>
       <c r="B279" s="25"/>
       <c r="C279" s="25" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="D279" s="25" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="E279" s="25" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="F279" s="25"/>
       <c r="G279" s="25"/>
@@ -8448,13 +8527,13 @@
       <c r="A280" s="24"/>
       <c r="B280" s="25"/>
       <c r="C280" s="25" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="D280" s="25" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="E280" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F280" s="25"/>
       <c r="G280" s="25"/>
@@ -8464,13 +8543,13 @@
       <c r="A281" s="24"/>
       <c r="B281" s="25"/>
       <c r="C281" s="25" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="D281" s="25" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="E281" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F281" s="25"/>
       <c r="G281" s="25"/>
@@ -8480,13 +8559,13 @@
       <c r="A282" s="24"/>
       <c r="B282" s="25"/>
       <c r="C282" s="25" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="D282" s="25" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="E282" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F282" s="25"/>
       <c r="G282" s="25"/>
@@ -8496,13 +8575,13 @@
       <c r="A283" s="24"/>
       <c r="B283" s="25"/>
       <c r="C283" s="25" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="D283" s="25" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="E283" s="25" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="F283" s="25"/>
       <c r="G283" s="25"/>
@@ -8512,13 +8591,13 @@
       <c r="A284" s="24"/>
       <c r="B284" s="25"/>
       <c r="C284" s="25" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="D284" s="25" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="E284" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F284" s="25"/>
       <c r="G284" s="25"/>
@@ -8528,13 +8607,13 @@
       <c r="A285" s="24"/>
       <c r="B285" s="25"/>
       <c r="C285" s="25" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D285" s="25" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="E285" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F285" s="25"/>
       <c r="G285" s="25"/>
@@ -8544,13 +8623,13 @@
       <c r="A286" s="24"/>
       <c r="B286" s="25"/>
       <c r="C286" s="25" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="D286" s="25" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="E286" s="25" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="F286" s="25"/>
       <c r="G286" s="25"/>
@@ -8560,13 +8639,13 @@
       <c r="A287" s="24"/>
       <c r="B287" s="25"/>
       <c r="C287" s="25" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="D287" s="25" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="E287" s="25" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="F287" s="25"/>
       <c r="G287" s="25"/>
@@ -8576,13 +8655,13 @@
       <c r="A288" s="24"/>
       <c r="B288" s="25"/>
       <c r="C288" s="25" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="D288" s="25" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E288" s="25" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="F288" s="25"/>
       <c r="G288" s="25"/>
@@ -8592,13 +8671,13 @@
       <c r="A289" s="24"/>
       <c r="B289" s="25"/>
       <c r="C289" s="25" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="D289" s="25" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="E289" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F289" s="25"/>
       <c r="G289" s="25"/>
@@ -8608,13 +8687,13 @@
       <c r="A290" s="24"/>
       <c r="B290" s="25"/>
       <c r="C290" s="25" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="D290" s="25" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="E290" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F290" s="25"/>
       <c r="G290" s="25"/>
@@ -8624,13 +8703,13 @@
       <c r="A291" s="24"/>
       <c r="B291" s="25"/>
       <c r="C291" s="25" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="D291" s="25" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="E291" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F291" s="25"/>
       <c r="G291" s="25"/>
@@ -8640,13 +8719,13 @@
       <c r="A292" s="24"/>
       <c r="B292" s="25"/>
       <c r="C292" s="25" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="D292" s="25" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="E292" s="25" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="F292" s="25"/>
       <c r="G292" s="25"/>
@@ -8656,13 +8735,13 @@
       <c r="A293" s="24"/>
       <c r="B293" s="25"/>
       <c r="C293" s="25" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="D293" s="25" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="E293" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F293" s="25"/>
       <c r="G293" s="25"/>
@@ -8672,13 +8751,13 @@
       <c r="A294" s="24"/>
       <c r="B294" s="25"/>
       <c r="C294" s="25" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="D294" s="25" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="E294" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F294" s="25"/>
       <c r="G294" s="25"/>
@@ -8688,13 +8767,13 @@
       <c r="A295" s="24"/>
       <c r="B295" s="25"/>
       <c r="C295" s="25" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="D295" s="25" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="E295" s="25" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="F295" s="25"/>
       <c r="G295" s="25"/>
@@ -8704,13 +8783,13 @@
       <c r="A296" s="24"/>
       <c r="B296" s="25"/>
       <c r="C296" s="25" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="D296" s="25" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="E296" s="25" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="F296" s="25"/>
       <c r="G296" s="25"/>
@@ -8720,13 +8799,13 @@
       <c r="A297" s="24"/>
       <c r="B297" s="25"/>
       <c r="C297" s="25" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="D297" s="25" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="E297" s="25" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="F297" s="25"/>
       <c r="G297" s="25"/>
@@ -8736,13 +8815,13 @@
       <c r="A298" s="24"/>
       <c r="B298" s="25"/>
       <c r="C298" s="25" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="D298" s="25" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="E298" s="25" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="F298" s="25"/>
       <c r="G298" s="25"/>
@@ -8752,13 +8831,13 @@
       <c r="A299" s="24"/>
       <c r="B299" s="25"/>
       <c r="C299" s="25" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="D299" s="25" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="E299" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F299" s="25"/>
       <c r="G299" s="25"/>
@@ -8768,13 +8847,13 @@
       <c r="A300" s="24"/>
       <c r="B300" s="25"/>
       <c r="C300" s="25" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="D300" s="25" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="E300" s="25" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="F300" s="25"/>
       <c r="G300" s="25"/>
@@ -8784,13 +8863,13 @@
       <c r="A301" s="24"/>
       <c r="B301" s="25"/>
       <c r="C301" s="25" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="D301" s="25" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="E301" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F301" s="25"/>
       <c r="G301" s="25"/>
@@ -8800,13 +8879,13 @@
       <c r="A302" s="24"/>
       <c r="B302" s="25"/>
       <c r="C302" s="25" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="D302" s="25" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="E302" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F302" s="25"/>
       <c r="G302" s="25"/>
@@ -8816,13 +8895,13 @@
       <c r="A303" s="24"/>
       <c r="B303" s="25"/>
       <c r="C303" s="25" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="D303" s="25" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="E303" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F303" s="25"/>
       <c r="G303" s="25"/>
@@ -8832,13 +8911,13 @@
       <c r="A304" s="24"/>
       <c r="B304" s="25"/>
       <c r="C304" s="25" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="D304" s="25" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="E304" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F304" s="25"/>
       <c r="G304" s="25"/>
@@ -8848,13 +8927,13 @@
       <c r="A305" s="24"/>
       <c r="B305" s="25"/>
       <c r="C305" s="25" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="D305" s="25" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="E305" s="25" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="F305" s="25"/>
       <c r="G305" s="25"/>
@@ -8864,13 +8943,13 @@
       <c r="A306" s="24"/>
       <c r="B306" s="25"/>
       <c r="C306" s="25" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="D306" s="25" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="E306" s="25" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="F306" s="25"/>
       <c r="G306" s="25"/>
@@ -8880,13 +8959,13 @@
       <c r="A307" s="24"/>
       <c r="B307" s="25"/>
       <c r="C307" s="25" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="D307" s="25" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="E307" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F307" s="25"/>
       <c r="G307" s="25"/>
@@ -8896,13 +8975,13 @@
       <c r="A308" s="24"/>
       <c r="B308" s="25"/>
       <c r="C308" s="25" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="D308" s="25" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="E308" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F308" s="25"/>
       <c r="G308" s="25"/>
@@ -8912,13 +8991,13 @@
       <c r="A309" s="24"/>
       <c r="B309" s="25"/>
       <c r="C309" s="25" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="D309" s="25" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="E309" s="25" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="F309" s="25"/>
       <c r="G309" s="25"/>
@@ -8928,13 +9007,13 @@
       <c r="A310" s="24"/>
       <c r="B310" s="25"/>
       <c r="C310" s="25" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="D310" s="25" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="E310" s="25" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="F310" s="25"/>
       <c r="G310" s="25"/>
@@ -8944,13 +9023,13 @@
       <c r="A311" s="24"/>
       <c r="B311" s="25"/>
       <c r="C311" s="25" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="D311" s="25" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="E311" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F311" s="25"/>
       <c r="G311" s="25"/>
@@ -8960,13 +9039,13 @@
       <c r="A312" s="24"/>
       <c r="B312" s="25"/>
       <c r="C312" s="25" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="D312" s="25" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="E312" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F312" s="25"/>
       <c r="G312" s="25"/>
@@ -8976,13 +9055,13 @@
       <c r="A313" s="24"/>
       <c r="B313" s="25"/>
       <c r="C313" s="25" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="D313" s="25" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="E313" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F313" s="25"/>
       <c r="G313" s="25"/>
@@ -8992,13 +9071,13 @@
       <c r="A314" s="24"/>
       <c r="B314" s="25"/>
       <c r="C314" s="25" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="D314" s="25" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="E314" s="25" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="F314" s="25"/>
       <c r="G314" s="25"/>
@@ -9008,13 +9087,13 @@
       <c r="A315" s="24"/>
       <c r="B315" s="25"/>
       <c r="C315" s="25" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="D315" s="25" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="E315" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F315" s="25"/>
       <c r="G315" s="25"/>
@@ -9024,13 +9103,13 @@
       <c r="A316" s="24"/>
       <c r="B316" s="25"/>
       <c r="C316" s="25" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="D316" s="25" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="E316" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F316" s="25"/>
       <c r="G316" s="25"/>
@@ -9040,13 +9119,13 @@
       <c r="A317" s="24"/>
       <c r="B317" s="25"/>
       <c r="C317" s="25" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="D317" s="25" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="E317" s="25" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="F317" s="25"/>
       <c r="G317" s="25"/>
@@ -9056,13 +9135,13 @@
       <c r="A318" s="24"/>
       <c r="B318" s="25"/>
       <c r="C318" s="25" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="D318" s="25" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="E318" s="25" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="F318" s="25"/>
       <c r="G318" s="25"/>
@@ -9072,13 +9151,13 @@
       <c r="A319" s="24"/>
       <c r="B319" s="25"/>
       <c r="C319" s="25" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="D319" s="25" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="E319" s="25" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="F319" s="25"/>
       <c r="G319" s="25"/>
@@ -9088,13 +9167,13 @@
       <c r="A320" s="24"/>
       <c r="B320" s="25"/>
       <c r="C320" s="25" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="D320" s="25" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="E320" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F320" s="25"/>
       <c r="G320" s="25"/>
@@ -9104,13 +9183,13 @@
       <c r="A321" s="24"/>
       <c r="B321" s="25"/>
       <c r="C321" s="25" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="D321" s="25" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="E321" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F321" s="25"/>
       <c r="G321" s="25"/>
@@ -9120,13 +9199,13 @@
       <c r="A322" s="24"/>
       <c r="B322" s="25"/>
       <c r="C322" s="25" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="D322" s="25" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="E322" s="25" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F322" s="25"/>
       <c r="G322" s="25"/>
@@ -9136,13 +9215,13 @@
       <c r="A323" s="24"/>
       <c r="B323" s="25"/>
       <c r="C323" s="25" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="D323" s="25" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="E323" s="25" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="F323" s="25"/>
       <c r="G323" s="25"/>
@@ -9156,17 +9235,17 @@
     </row>
     <row r="325" spans="1:8">
       <c r="A325" s="26" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="B325" s="27"/>
       <c r="C325" s="27" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="D325" s="27" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="E325" s="27" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="F325" s="27"/>
       <c r="G325" s="27"/>
@@ -9176,13 +9255,13 @@
       <c r="A326" s="26"/>
       <c r="B326" s="27"/>
       <c r="C326" s="27" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="D326" s="27" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="E326" s="27" t="s">
-        <v>453</v>
+        <v>147</v>
       </c>
       <c r="F326" s="27"/>
       <c r="G326" s="27"/>
@@ -9192,13 +9271,13 @@
       <c r="A327" s="26"/>
       <c r="B327" s="27"/>
       <c r="C327" s="27" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="D327" s="27" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="E327" s="27" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="F327" s="27"/>
       <c r="G327" s="27"/>
@@ -9210,16 +9289,16 @@
     </row>
     <row r="329" spans="1:8">
       <c r="A329" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="C329" s="8" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="E329" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="G329">
         <v>23</v>
@@ -9230,13 +9309,13 @@
     </row>
     <row r="330" spans="1:8">
       <c r="C330" s="8" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="D330" s="28" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="E330" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="G330">
         <v>8</v>
@@ -9274,23 +9353,23 @@
     <mergeCell ref="B188:B205"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D66" r:id="rId1" display="https://gitcode.com/Ascend/msmodeling"/>
-    <hyperlink ref="D65" r:id="rId2" display="https://gitcode.com/Ascend/msmodelslim"/>
-    <hyperlink ref="D67" r:id="rId3" display="https://gitcode.com/Ascend/mssanitizer"/>
+    <hyperlink ref="D66" r:id="rId1" display="https://gitcode.com/Ascend/msmodeling" tooltip="https://gitcode.com/Ascend/msmodeling"/>
+    <hyperlink ref="D65" r:id="rId2" display="https://gitcode.com/Ascend/msmodelslim" tooltip="https://gitcode.com/Ascend/msmodelslim"/>
+    <hyperlink ref="D67" r:id="rId3" display="https://gitcode.com/Ascend/mssanitizer" tooltip="https://gitcode.com/Ascend/mssanitizer"/>
     <hyperlink ref="D69" r:id="rId4" display="https://gitcode.com/Ascend/mspti"/>
     <hyperlink ref="D56" r:id="rId5" display="https://gitcode.com/Ascend/mstt"/>
     <hyperlink ref="D57" r:id="rId6" display="https://gitcode.com/Ascend/msit"/>
     <hyperlink ref="D58" r:id="rId7" display="https://gitcode.com/Ascend/msot"/>
-    <hyperlink ref="D76" r:id="rId8" display="https://gitcode.com/Ascend/mskl"/>
+    <hyperlink ref="D76" r:id="rId8" display="https://gitcode.com/Ascend/mskl" tooltip="https://gitcode.com/Ascend/mskl"/>
     <hyperlink ref="D77" r:id="rId9" display="https://gitcode.com/Ascend/msoptuner" tooltip="https://gitcode.com/Ascend/msoptuner"/>
     <hyperlink ref="D78" r:id="rId10" display="https://gitcode.com/Ascend/msopgen" tooltip="https://gitcode.com/Ascend/msopgen"/>
-    <hyperlink ref="D79" r:id="rId11" display="https://gitcode.com/Ascend/mskpp"/>
+    <hyperlink ref="D79" r:id="rId11" display="https://gitcode.com/Ascend/mskpp" tooltip="https://gitcode.com/Ascend/mskpp"/>
     <hyperlink ref="C325" r:id="rId12" display="openlibing-web" tooltip="https://gitcode.com/openlibing/openlibing-web"/>
     <hyperlink ref="C326" r:id="rId13" display="openlibing-pytest-executor" tooltip="https://gitcode.com/openlibing/openlibing-pytest-executor"/>
     <hyperlink ref="C327" r:id="rId14" display="openlibing-platform-release" tooltip="https://gitcode.com/openlibing/openlibing-platform-release"/>
-    <hyperlink ref="D70" r:id="rId15" display="https://gitcode.com/Ascend/msagent"/>
+    <hyperlink ref="D70" r:id="rId15" display="https://gitcode.com/Ascend/msagent" tooltip="https://gitcode.com/Ascend/msagent"/>
     <hyperlink ref="D80" r:id="rId16" display="https://gitcode.com/Ascend/mockcpp"/>
-    <hyperlink ref="D41" r:id="rId17" display="https://gitcode.com/Ascend/mind-cluster"/>
+    <hyperlink ref="D41" r:id="rId17" display="https://gitcode.com/Ascend/mind-cluster" tooltip="https://gitcode.com/Ascend/mind-cluster"/>
     <hyperlink ref="D42" r:id="rId18" display="https://gitcode.com/Ascend/MEF"/>
     <hyperlink ref="D43" r:id="rId19" display="https://gitcode.com/Ascend/OMSDK"/>
     <hyperlink ref="D44" r:id="rId20" display="https://gitcode.com/Ascend/memcache"/>
@@ -9362,6 +9441,25 @@
     <hyperlink ref="D204" r:id="rId86" display="https://gitcode.com/mindspore-lab/mindface"/>
     <hyperlink ref="D205" r:id="rId87" display="https://gitcode.com/mindspore-lab/mindaudio"/>
     <hyperlink ref="D83" r:id="rId88" display="https://gitcode.com/Ascend/torchair" tooltip="https://gitcode.com/Ascend/torchair"/>
+    <hyperlink ref="D111" r:id="rId89" display="https://gitcode.com/openUBMC/component_drivers"/>
+    <hyperlink ref="D116" r:id="rId90" display="https://gitcode.com/openUBMC/vpd"/>
+    <hyperlink ref="D117" r:id="rId91" display="https://gitcode.com/openUBMC/manifest"/>
+    <hyperlink ref="D137" r:id="rId92" display="https://gitcode.com/openUBMC/libipmi"/>
+    <hyperlink ref="D130" r:id="rId93" display="https://gitcode.com/openUBMC/bcal"/>
+    <hyperlink ref="D128" r:id="rId94" display="https://gitcode.com/openUBMC/libmcpp"/>
+    <hyperlink ref="D113" r:id="rId95" display="https://gitcode.com/openUBMC/profile_schema"/>
+    <hyperlink ref="D112" r:id="rId96" display="https://gitcode.com/openUBMC/general_hardware"/>
+    <hyperlink ref="D59" r:id="rId97" display="https://gitcode.com/Ascend/msdebug"/>
+    <hyperlink ref="D60" r:id="rId98" display="https://gitcode.com/Ascend/msmonitor"/>
+    <hyperlink ref="D61" r:id="rId99" display="https://gitcode.com/Ascend/msprobe"/>
+    <hyperlink ref="D62" r:id="rId100" display="https://gitcode.com/Ascend/msinsight"/>
+    <hyperlink ref="D63" r:id="rId101" display="https://gitcode.com/Ascend/msprof"/>
+    <hyperlink ref="D64" r:id="rId102" display="https://gitcode.com/Ascend/msserviceprofiler"/>
+    <hyperlink ref="D71" r:id="rId103" display="https://gitcode.com/Ascend/msopprof"/>
+    <hyperlink ref="D72" r:id="rId104" display="https://gitcode.com/Ascend/msmemscope"/>
+    <hyperlink ref="D73" r:id="rId105" display="https://gitcode.com/Ascend/msprof-analyze" tooltip="https://gitcode.com/Ascend/msprof-analyze"/>
+    <hyperlink ref="D74" r:id="rId106" display="https://gitcode.com/Ascend/mstx" tooltip="https://gitcode.com/Ascend/mstx"/>
+    <hyperlink ref="D75" r:id="rId107" display="https://gitcode.com/Ascend/mscommreport"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -9387,19 +9485,19 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -9407,16 +9505,16 @@
         <v>124</v>
       </c>
       <c r="B2" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="C2" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="D2" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="F2" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -9424,16 +9522,16 @@
         <v>124</v>
       </c>
       <c r="B3" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="C3" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="D3" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="F3" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -9441,16 +9539,16 @@
         <v>124</v>
       </c>
       <c r="B4" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="C4" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="D4" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="F4" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -9458,16 +9556,16 @@
         <v>124</v>
       </c>
       <c r="B5" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="C5" t="s">
+        <v>844</v>
+      </c>
+      <c r="D5" t="s">
         <v>840</v>
       </c>
-      <c r="D5" t="s">
-        <v>836</v>
-      </c>
       <c r="F5" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -9475,16 +9573,16 @@
         <v>124</v>
       </c>
       <c r="B6" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="C6" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="D6" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="F6" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -9492,16 +9590,16 @@
         <v>124</v>
       </c>
       <c r="B7" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="C7" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="D7" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="F7" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -9509,16 +9607,16 @@
         <v>124</v>
       </c>
       <c r="B8" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="C8" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="D8" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="F8" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -9526,16 +9624,16 @@
         <v>124</v>
       </c>
       <c r="B9" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="C9" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="D9" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="F9" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -9543,16 +9641,16 @@
         <v>124</v>
       </c>
       <c r="B10" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="C10" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="D10" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="F10" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -9560,16 +9658,16 @@
         <v>124</v>
       </c>
       <c r="B11" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="C11" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="D11" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="F11" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -9577,16 +9675,16 @@
         <v>94</v>
       </c>
       <c r="B12" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="C12" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="D12" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="F12" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
     </row>
   </sheetData>
@@ -9615,232 +9713,232 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="B2" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C2" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="D2" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="F2" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="B3" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C3" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="D3" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="F3" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="B4" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C4" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="D4" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="F4" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="B5" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C5" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="D5" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="F5" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="B6" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C6" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="D6" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="F6" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="B7" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C7" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="D7" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="F7" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="B8" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C8" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="D8" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="F8" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="B9" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C9" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D9" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="F9" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="B10" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C10" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="D10" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="E10" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="F10" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="B11" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C11" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="D11" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="B12" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C12" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="D12" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="F12" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="B13" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C13" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="D13" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="F13" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="B14" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C14" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="D14" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="F14" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="B15" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C15" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="D15" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="F15" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="B16" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C16" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="D16" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="F16" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
     </row>
     <row r="21" spans="6:6">
@@ -9875,19 +9973,19 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
     </row>
     <row r="21" spans="6:6">
@@ -9919,19 +10017,19 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
     </row>
     <row r="21" spans="6:6">
@@ -9963,19 +10061,19 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
     </row>
     <row r="21" spans="6:6">
